--- a/Deliverable/BOM/Digikey_BOM_Grant.xlsx
+++ b/Deliverable/BOM/Digikey_BOM_Grant.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GrantKros-CoopMonitor\Deliverable\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA789883-F71F-4C44-A1ED-00514DAA430E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{072E0D1C-2C15-41AE-A304-46E92361F783}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-10635" yWindow="4695" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Jude_Project" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="369">
   <si>
     <t>Description</t>
   </si>
@@ -541,9 +541,6 @@
     <t>LED</t>
   </si>
   <si>
-    <t>470 ±5% 1/16W ±100ppm/°C 0402 Chip Resistor - Surface Mount RoHS</t>
-  </si>
-  <si>
     <t>R1</t>
   </si>
   <si>
@@ -977,9 +974,6 @@
   </si>
   <si>
     <t>SB2, SB3, SB14, SB15, SB16, SB17, SB18, SB19, SB20, SB_ZD1</t>
-  </si>
-  <si>
-    <t>Jing Extension of the Electronic Co.</t>
   </si>
   <si>
     <t>Amphenol FCI</t>
@@ -1116,6 +1110,53 @@
   <si>
     <t xml:space="preserve">MOSFET P-CH 20V 1.6A SUPERSOT3
 </t>
+  </si>
+  <si>
+    <t>25SEV10M4X5.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alternate part ki Specs Same han footprint change ha </t>
+  </si>
+  <si>
+    <t>BMRA00040420100MA1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alternate part ki Specs Change han footprint change ha </t>
+  </si>
+  <si>
+    <t>Out of Stock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2538-B24G00DBT
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCJ250-05-A-K1-A
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MCR-B-S-RA-SMT-CS5A-NF-T/R
+</t>
+  </si>
+  <si>
+    <t>Jing Extension of the Electronic</t>
+  </si>
+  <si>
+    <t>CH25</t>
+  </si>
+  <si>
+    <t>MS12ASG30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RES 470 OHM 5% 1/16W 0402
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B2B-XH-A(LF)(SN)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Do NOT Mount </t>
   </si>
 </sst>
 </file>
@@ -1126,7 +1167,7 @@
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1226,6 +1267,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
@@ -1235,7 +1285,7 @@
     <font>
       <b/>
       <sz val="10"/>
-      <color theme="0"/>
+      <color theme="5"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1261,7 +1311,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="36">
+  <borders count="40">
     <border>
       <left/>
       <right/>
@@ -1710,12 +1760,62 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="134">
+  <cellXfs count="144">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1823,9 +1923,6 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1847,15 +1944,6 @@
     <xf numFmtId="165" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1910,9 +1998,6 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1922,35 +2007,23 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1958,16 +2031,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1975,35 +2042,18 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2028,6 +2078,21 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2061,30 +2126,99 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="1" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2373,12 +2507,12 @@
     <col min="1" max="1" width="6.140625" style="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.42578125" customWidth="1"/>
     <col min="3" max="3" width="39.42578125" style="14" customWidth="1"/>
-    <col min="4" max="4" width="33.85546875" style="5" customWidth="1"/>
+    <col min="4" max="4" width="32.28515625" style="5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.140625" style="5" customWidth="1"/>
-    <col min="8" max="8" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.140625" style="50" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.140625" style="46" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="19.42578125" style="5" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="11.140625" bestFit="1" customWidth="1"/>
@@ -2389,96 +2523,96 @@
     <col min="17" max="17" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="19" max="20" width="13.7109375" customWidth="1"/>
-    <col min="21" max="21" width="27.85546875" customWidth="1"/>
+    <col min="21" max="21" width="44" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="114" t="s">
-        <v>353</v>
-      </c>
-      <c r="B1" s="115"/>
-      <c r="C1" s="115"/>
-      <c r="D1" s="115"/>
-      <c r="E1" s="115"/>
-      <c r="F1" s="115"/>
-      <c r="G1" s="115"/>
-      <c r="H1" s="115"/>
-      <c r="I1" s="115"/>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="116"/>
+      <c r="A1" s="99" t="s">
+        <v>351</v>
+      </c>
+      <c r="B1" s="100"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="100"/>
+      <c r="E1" s="100"/>
+      <c r="F1" s="100"/>
+      <c r="G1" s="100"/>
+      <c r="H1" s="100"/>
+      <c r="I1" s="100"/>
+      <c r="J1" s="100"/>
+      <c r="K1" s="100"/>
+      <c r="L1" s="100"/>
+      <c r="M1" s="100"/>
+      <c r="N1" s="100"/>
+      <c r="O1" s="100"/>
+      <c r="P1" s="100"/>
+      <c r="Q1" s="100"/>
+      <c r="R1" s="100"/>
+      <c r="S1" s="100"/>
+      <c r="T1" s="100"/>
+      <c r="U1" s="101"/>
     </row>
     <row r="2" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="51" t="s">
+      <c r="B2" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="51" t="s">
+      <c r="C2" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="51" t="s">
+      <c r="D2" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="51" t="s">
+      <c r="E2" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="51" t="s">
+      <c r="F2" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="51" t="s">
+      <c r="G2" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="51" t="s">
+      <c r="H2" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="51" t="s">
+      <c r="I2" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="51" t="s">
+      <c r="J2" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="51" t="s">
+      <c r="K2" s="47" t="s">
+        <v>318</v>
+      </c>
+      <c r="L2" s="47" t="s">
+        <v>319</v>
+      </c>
+      <c r="M2" s="47" t="s">
         <v>320</v>
       </c>
-      <c r="L2" s="51" t="s">
+      <c r="N2" s="59" t="s">
+        <v>14</v>
+      </c>
+      <c r="O2" s="47" t="s">
         <v>321</v>
       </c>
-      <c r="M2" s="51" t="s">
+      <c r="P2" s="47" t="s">
         <v>322</v>
       </c>
-      <c r="N2" s="63" t="s">
-        <v>14</v>
-      </c>
-      <c r="O2" s="51" t="s">
+      <c r="Q2" s="47" t="s">
         <v>323</v>
       </c>
-      <c r="P2" s="51" t="s">
+      <c r="R2" s="47" t="s">
         <v>324</v>
       </c>
-      <c r="Q2" s="51" t="s">
+      <c r="S2" s="47" t="s">
         <v>325</v>
       </c>
-      <c r="R2" s="51" t="s">
+      <c r="T2" s="47" t="s">
         <v>326</v>
       </c>
-      <c r="S2" s="51" t="s">
-        <v>327</v>
-      </c>
-      <c r="T2" s="51" t="s">
-        <v>328</v>
-      </c>
-      <c r="U2" s="51" t="s">
+      <c r="U2" s="47" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2486,13 +2620,13 @@
       <c r="A3" s="17">
         <v>1</v>
       </c>
-      <c r="B3" s="119" t="s">
+      <c r="B3" s="104" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="71" t="s">
+      <c r="C3" s="66" t="s">
         <v>47</v>
       </c>
-      <c r="D3" s="72" t="s">
+      <c r="D3" s="7" t="s">
         <v>48</v>
       </c>
       <c r="E3" s="7" t="s">
@@ -2501,7 +2635,7 @@
       <c r="F3" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="G3" s="73" t="s">
+      <c r="G3" s="67" t="s">
         <v>98</v>
       </c>
       <c r="H3" s="31" t="s">
@@ -2510,7 +2644,7 @@
       <c r="I3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="J3" s="73">
+      <c r="J3" s="67">
         <v>1</v>
       </c>
       <c r="K3" s="8">
@@ -2525,57 +2659,59 @@
         <f>J3*100</f>
         <v>100</v>
       </c>
-      <c r="N3" s="108" t="s">
+      <c r="N3" s="88" t="s">
         <v>20</v>
       </c>
-      <c r="O3" s="56">
+      <c r="O3" s="52">
         <v>0.43</v>
       </c>
-      <c r="P3" s="33">
+      <c r="P3" s="19">
         <f>O3*K3</f>
         <v>2.15</v>
       </c>
-      <c r="Q3" s="56">
+      <c r="Q3" s="52">
         <v>0.1956</v>
       </c>
       <c r="R3" s="19">
         <f>Q3*L3</f>
         <v>9.7799999999999994</v>
       </c>
-      <c r="S3" s="58">
+      <c r="S3" s="54">
         <v>0.16619999999999999</v>
       </c>
-      <c r="T3" s="62">
+      <c r="T3" s="58">
         <f>S3*M3</f>
         <v>16.619999999999997</v>
       </c>
-      <c r="U3" s="74"/>
+      <c r="U3" s="68"/>
     </row>
     <row r="4" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10">
         <v>2</v>
       </c>
-      <c r="B4" s="120"/>
-      <c r="C4" s="75" t="s">
+      <c r="B4" s="105"/>
+      <c r="C4" s="69" t="s">
         <v>50</v>
       </c>
-      <c r="D4" s="76" t="s">
+      <c r="D4" s="12" t="s">
         <v>51</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="G4" s="45" t="s">
+      <c r="G4" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="H4" s="11"/>
+      <c r="H4" s="11" t="s">
+        <v>355</v>
+      </c>
       <c r="I4" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="J4" s="45">
+      <c r="J4" s="44">
         <v>1</v>
       </c>
       <c r="K4" s="13">
@@ -2590,33 +2726,43 @@
         <f t="shared" ref="M4:M67" si="2">J4*100</f>
         <v>100</v>
       </c>
-      <c r="N4" s="106"/>
-      <c r="O4" s="52"/>
-      <c r="P4" s="19">
+      <c r="N4" s="86" t="s">
+        <v>20</v>
+      </c>
+      <c r="O4" s="48">
+        <v>0.47</v>
+      </c>
+      <c r="P4" s="21">
         <f t="shared" ref="P4:P67" si="3">O4*K4</f>
-        <v>0</v>
-      </c>
-      <c r="Q4" s="52"/>
+        <v>2.3499999999999996</v>
+      </c>
+      <c r="Q4" s="48">
+        <v>0.22620000000000001</v>
+      </c>
       <c r="R4" s="21">
         <f t="shared" ref="R4:R67" si="4">Q4*L4</f>
-        <v>0</v>
-      </c>
-      <c r="S4" s="59"/>
+        <v>11.31</v>
+      </c>
+      <c r="S4" s="55">
+        <v>0.19389999999999999</v>
+      </c>
       <c r="T4" s="21">
         <f t="shared" ref="T4:T67" si="5">S4*M4</f>
-        <v>0</v>
-      </c>
-      <c r="U4" s="77"/>
+        <v>19.39</v>
+      </c>
+      <c r="U4" s="111" t="s">
+        <v>356</v>
+      </c>
     </row>
     <row r="5" spans="1:23" s="22" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10">
         <v>3</v>
       </c>
-      <c r="B5" s="120"/>
-      <c r="C5" s="75" t="s">
+      <c r="B5" s="105"/>
+      <c r="C5" s="69" t="s">
         <v>53</v>
       </c>
-      <c r="D5" s="78" t="s">
+      <c r="D5" s="11" t="s">
         <v>54</v>
       </c>
       <c r="E5" s="12" t="s">
@@ -2625,7 +2771,7 @@
       <c r="F5" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="G5" s="45" t="s">
+      <c r="G5" s="44" t="s">
         <v>100</v>
       </c>
       <c r="H5" s="12" t="s">
@@ -2634,7 +2780,7 @@
       <c r="I5" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="J5" s="45">
+      <c r="J5" s="44">
         <v>13</v>
       </c>
       <c r="K5" s="13">
@@ -2649,41 +2795,41 @@
         <f t="shared" si="2"/>
         <v>1300</v>
       </c>
-      <c r="N5" s="106" t="s">
+      <c r="N5" s="110" t="s">
         <v>20</v>
       </c>
-      <c r="O5" s="52">
+      <c r="O5" s="48">
         <v>1.5800000000000002E-2</v>
       </c>
       <c r="P5" s="21">
         <f t="shared" si="3"/>
         <v>1.0270000000000001</v>
       </c>
-      <c r="Q5" s="52">
+      <c r="Q5" s="48">
         <v>9.2399999999999999E-3</v>
       </c>
       <c r="R5" s="21">
         <f t="shared" si="4"/>
         <v>6.0060000000000002</v>
       </c>
-      <c r="S5" s="59">
+      <c r="S5" s="55">
         <v>7.26E-3</v>
       </c>
       <c r="T5" s="21">
         <f t="shared" si="5"/>
         <v>9.4380000000000006</v>
       </c>
-      <c r="U5" s="77"/>
+      <c r="U5" s="70"/>
     </row>
     <row r="6" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="10">
         <v>4</v>
       </c>
-      <c r="B6" s="120"/>
-      <c r="C6" s="75" t="s">
+      <c r="B6" s="105"/>
+      <c r="C6" s="69" t="s">
         <v>57</v>
       </c>
-      <c r="D6" s="76" t="s">
+      <c r="D6" s="12" t="s">
         <v>58</v>
       </c>
       <c r="E6" s="12" t="s">
@@ -2692,7 +2838,7 @@
       <c r="F6" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="G6" s="45" t="s">
+      <c r="G6" s="44" t="s">
         <v>101</v>
       </c>
       <c r="H6" s="12" t="s">
@@ -2701,7 +2847,7 @@
       <c r="I6" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="J6" s="45">
+      <c r="J6" s="44">
         <v>2</v>
       </c>
       <c r="K6" s="13">
@@ -2716,7 +2862,7 @@
         <f t="shared" si="2"/>
         <v>200</v>
       </c>
-      <c r="N6" s="109" t="s">
+      <c r="N6" s="89" t="s">
         <v>20</v>
       </c>
       <c r="O6" s="20">
@@ -2733,7 +2879,7 @@
         <f t="shared" si="4"/>
         <v>18.149999999999999</v>
       </c>
-      <c r="S6" s="59">
+      <c r="S6" s="55">
         <v>0.18149999999999999</v>
       </c>
       <c r="T6" s="21">
@@ -2748,11 +2894,11 @@
       <c r="A7" s="10">
         <v>5</v>
       </c>
-      <c r="B7" s="120"/>
+      <c r="B7" s="105"/>
       <c r="C7" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="D7" s="76" t="s">
+      <c r="D7" s="12" t="s">
         <v>62</v>
       </c>
       <c r="E7" s="12" t="s">
@@ -2761,7 +2907,7 @@
       <c r="F7" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="G7" s="45" t="s">
+      <c r="G7" s="44" t="s">
         <v>102</v>
       </c>
       <c r="H7" s="12" t="s">
@@ -2770,7 +2916,7 @@
       <c r="I7" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="J7" s="45">
+      <c r="J7" s="44">
         <v>2</v>
       </c>
       <c r="K7" s="13">
@@ -2785,7 +2931,7 @@
         <f t="shared" si="2"/>
         <v>200</v>
       </c>
-      <c r="N7" s="109" t="s">
+      <c r="N7" s="89" t="s">
         <v>20</v>
       </c>
       <c r="O7" s="20">
@@ -2802,7 +2948,7 @@
         <f t="shared" si="4"/>
         <v>24.87</v>
       </c>
-      <c r="S7" s="59">
+      <c r="S7" s="55">
         <v>0.2487</v>
       </c>
       <c r="T7" s="21">
@@ -2817,11 +2963,11 @@
       <c r="A8" s="10">
         <v>6</v>
       </c>
-      <c r="B8" s="120"/>
-      <c r="C8" s="75" t="s">
+      <c r="B8" s="105"/>
+      <c r="C8" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="D8" s="76" t="s">
+      <c r="D8" s="12" t="s">
         <v>65</v>
       </c>
       <c r="E8" s="12" t="s">
@@ -2830,7 +2976,7 @@
       <c r="F8" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="G8" s="45" t="s">
+      <c r="G8" s="44" t="s">
         <v>22</v>
       </c>
       <c r="H8" s="12" t="s">
@@ -2839,7 +2985,7 @@
       <c r="I8" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="J8" s="45">
+      <c r="J8" s="44">
         <v>1</v>
       </c>
       <c r="K8" s="13">
@@ -2854,7 +3000,7 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N8" s="109" t="s">
+      <c r="N8" s="89" t="s">
         <v>20</v>
       </c>
       <c r="O8" s="20">
@@ -2871,7 +3017,7 @@
         <f t="shared" si="4"/>
         <v>2.1800000000000002</v>
       </c>
-      <c r="S8" s="59">
+      <c r="S8" s="55">
         <v>3.5700000000000003E-2</v>
       </c>
       <c r="T8" s="21">
@@ -2886,11 +3032,11 @@
       <c r="A9" s="10">
         <v>7</v>
       </c>
-      <c r="B9" s="120"/>
-      <c r="C9" s="75" t="s">
+      <c r="B9" s="105"/>
+      <c r="C9" s="69" t="s">
         <v>68</v>
       </c>
-      <c r="D9" s="76" t="s">
+      <c r="D9" s="12" t="s">
         <v>69</v>
       </c>
       <c r="E9" s="12" t="s">
@@ -2899,16 +3045,16 @@
       <c r="F9" s="24" t="s">
         <v>71</v>
       </c>
-      <c r="G9" s="45" t="s">
+      <c r="G9" s="44" t="s">
         <v>101</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="I9" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="J9" s="45">
+      <c r="J9" s="44">
         <v>4</v>
       </c>
       <c r="K9" s="13">
@@ -2923,7 +3069,7 @@
         <f t="shared" si="2"/>
         <v>400</v>
       </c>
-      <c r="N9" s="109" t="s">
+      <c r="N9" s="89" t="s">
         <v>20</v>
       </c>
       <c r="O9" s="20">
@@ -2940,7 +3086,7 @@
         <f t="shared" si="4"/>
         <v>2.3199999999999998</v>
       </c>
-      <c r="S9" s="59">
+      <c r="S9" s="55">
         <v>1.1599999999999999E-2</v>
       </c>
       <c r="T9" s="21">
@@ -2955,11 +3101,11 @@
       <c r="A10" s="10">
         <v>8</v>
       </c>
-      <c r="B10" s="120"/>
-      <c r="C10" s="75" t="s">
+      <c r="B10" s="105"/>
+      <c r="C10" s="69" t="s">
         <v>72</v>
       </c>
-      <c r="D10" s="76" t="s">
+      <c r="D10" s="12" t="s">
         <v>73</v>
       </c>
       <c r="E10" s="12" t="s">
@@ -2968,7 +3114,7 @@
       <c r="F10" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="G10" s="45" t="s">
+      <c r="G10" s="44" t="s">
         <v>103</v>
       </c>
       <c r="H10" s="12" t="s">
@@ -2977,7 +3123,7 @@
       <c r="I10" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="J10" s="45">
+      <c r="J10" s="44">
         <v>1</v>
       </c>
       <c r="K10" s="13">
@@ -2992,7 +3138,7 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N10" s="109" t="s">
+      <c r="N10" s="89" t="s">
         <v>20</v>
       </c>
       <c r="O10" s="20">
@@ -3009,7 +3155,7 @@
         <f t="shared" si="4"/>
         <v>2.17</v>
       </c>
-      <c r="S10" s="59">
+      <c r="S10" s="55">
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="T10" s="21">
@@ -3024,11 +3170,11 @@
       <c r="A11" s="10">
         <v>9</v>
       </c>
-      <c r="B11" s="120"/>
-      <c r="C11" s="75" t="s">
-        <v>354</v>
-      </c>
-      <c r="D11" s="76" t="s">
+      <c r="B11" s="105"/>
+      <c r="C11" s="69" t="s">
+        <v>352</v>
+      </c>
+      <c r="D11" s="12" t="s">
         <v>75</v>
       </c>
       <c r="E11" s="12" t="s">
@@ -3037,7 +3183,7 @@
       <c r="F11" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="G11" s="45" t="s">
+      <c r="G11" s="44" t="s">
         <v>104</v>
       </c>
       <c r="H11" s="12" t="s">
@@ -3046,7 +3192,7 @@
       <c r="I11" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="J11" s="45">
+      <c r="J11" s="44">
         <v>4</v>
       </c>
       <c r="K11" s="13">
@@ -3061,7 +3207,7 @@
         <f t="shared" si="2"/>
         <v>400</v>
       </c>
-      <c r="N11" s="110" t="s">
+      <c r="N11" s="90" t="s">
         <v>20</v>
       </c>
       <c r="O11" s="20">
@@ -3078,14 +3224,14 @@
         <f t="shared" si="4"/>
         <v>2.6</v>
       </c>
-      <c r="S11" s="59">
+      <c r="S11" s="55">
         <v>1.2999999999999999E-2</v>
       </c>
       <c r="T11" s="21">
         <f t="shared" si="5"/>
         <v>5.2</v>
       </c>
-      <c r="U11" s="57"/>
+      <c r="U11" s="53"/>
       <c r="V11" s="1"/>
       <c r="W11" s="1"/>
     </row>
@@ -3093,20 +3239,20 @@
       <c r="A12" s="10">
         <v>10</v>
       </c>
-      <c r="B12" s="120"/>
-      <c r="C12" s="75" t="s">
+      <c r="B12" s="105"/>
+      <c r="C12" s="69" t="s">
         <v>77</v>
       </c>
-      <c r="D12" s="76" t="s">
+      <c r="D12" s="12" t="s">
         <v>78</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F12" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="G12" s="45" t="s">
+      <c r="G12" s="44" t="s">
         <v>105</v>
       </c>
       <c r="H12" s="12" t="s">
@@ -3115,7 +3261,7 @@
       <c r="I12" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="J12" s="45">
+      <c r="J12" s="44">
         <v>1</v>
       </c>
       <c r="K12" s="13">
@@ -3130,8 +3276,8 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N12" s="106" t="s">
-        <v>331</v>
+      <c r="N12" s="86" t="s">
+        <v>329</v>
       </c>
       <c r="O12" s="20">
         <v>0.44</v>
@@ -3147,14 +3293,14 @@
         <f t="shared" si="4"/>
         <v>11.85</v>
       </c>
-      <c r="S12" s="60">
+      <c r="S12" s="56">
         <v>0.20399999999999999</v>
       </c>
       <c r="T12" s="21">
         <f t="shared" si="5"/>
         <v>20.399999999999999</v>
       </c>
-      <c r="U12" s="79"/>
+      <c r="U12" s="71"/>
       <c r="V12" s="25"/>
       <c r="W12" s="25"/>
     </row>
@@ -3162,11 +3308,11 @@
       <c r="A13" s="10">
         <v>11</v>
       </c>
-      <c r="B13" s="120"/>
-      <c r="C13" s="75" t="s">
+      <c r="B13" s="105"/>
+      <c r="C13" s="69" t="s">
         <v>80</v>
       </c>
-      <c r="D13" s="76" t="s">
+      <c r="D13" s="12" t="s">
         <v>81</v>
       </c>
       <c r="E13" s="12" t="s">
@@ -3175,7 +3321,7 @@
       <c r="F13" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="G13" s="45" t="s">
+      <c r="G13" s="44" t="s">
         <v>106</v>
       </c>
       <c r="H13" s="12" t="s">
@@ -3184,7 +3330,7 @@
       <c r="I13" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="J13" s="45">
+      <c r="J13" s="44">
         <v>1</v>
       </c>
       <c r="K13" s="13">
@@ -3199,31 +3345,31 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N13" s="106" t="s">
-        <v>332</v>
-      </c>
-      <c r="O13" s="46">
+      <c r="N13" s="86" t="s">
+        <v>330</v>
+      </c>
+      <c r="O13" s="45">
         <v>0.6411</v>
       </c>
       <c r="P13" s="21">
         <f t="shared" si="3"/>
         <v>3.2054999999999998</v>
       </c>
-      <c r="Q13" s="46">
+      <c r="Q13" s="45">
         <v>0.6411</v>
       </c>
       <c r="R13" s="21">
         <f t="shared" si="4"/>
         <v>32.055</v>
       </c>
-      <c r="S13" s="59">
+      <c r="S13" s="55">
         <v>0.6411</v>
       </c>
       <c r="T13" s="21">
         <f t="shared" si="5"/>
         <v>64.11</v>
       </c>
-      <c r="U13" s="80"/>
+      <c r="U13" s="72"/>
       <c r="V13" s="1"/>
       <c r="W13" s="1"/>
     </row>
@@ -3231,11 +3377,11 @@
       <c r="A14" s="10">
         <v>12</v>
       </c>
-      <c r="B14" s="120"/>
-      <c r="C14" s="75" t="s">
+      <c r="B14" s="105"/>
+      <c r="C14" s="69" t="s">
         <v>83</v>
       </c>
-      <c r="D14" s="76" t="s">
+      <c r="D14" s="12" t="s">
         <v>84</v>
       </c>
       <c r="E14" s="12" t="s">
@@ -3244,7 +3390,7 @@
       <c r="F14" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="G14" s="45" t="s">
+      <c r="G14" s="44" t="s">
         <v>101</v>
       </c>
       <c r="H14" s="12" t="s">
@@ -3253,7 +3399,7 @@
       <c r="I14" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="J14" s="45">
+      <c r="J14" s="44">
         <v>2</v>
       </c>
       <c r="K14" s="13">
@@ -3268,7 +3414,7 @@
         <f t="shared" si="2"/>
         <v>200</v>
       </c>
-      <c r="N14" s="106" t="s">
+      <c r="N14" s="86" t="s">
         <v>20</v>
       </c>
       <c r="O14" s="20">
@@ -3285,14 +3431,14 @@
         <f t="shared" si="4"/>
         <v>3.56</v>
       </c>
-      <c r="S14" s="59">
+      <c r="S14" s="55">
         <v>3.56E-2</v>
       </c>
       <c r="T14" s="21">
         <f t="shared" si="5"/>
         <v>7.12</v>
       </c>
-      <c r="U14" s="80"/>
+      <c r="U14" s="72"/>
       <c r="V14" s="1"/>
       <c r="W14" s="1"/>
     </row>
@@ -3300,11 +3446,11 @@
       <c r="A15" s="10">
         <v>13</v>
       </c>
-      <c r="B15" s="120"/>
-      <c r="C15" s="75" t="s">
+      <c r="B15" s="105"/>
+      <c r="C15" s="69" t="s">
         <v>86</v>
       </c>
-      <c r="D15" s="76" t="s">
+      <c r="D15" s="12" t="s">
         <v>87</v>
       </c>
       <c r="E15" s="12" t="s">
@@ -3313,7 +3459,7 @@
       <c r="F15" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="G15" s="45" t="s">
+      <c r="G15" s="44" t="s">
         <v>104</v>
       </c>
       <c r="H15" s="12" t="s">
@@ -3322,7 +3468,7 @@
       <c r="I15" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="J15" s="45">
+      <c r="J15" s="44">
         <v>2</v>
       </c>
       <c r="K15" s="13">
@@ -3337,7 +3483,7 @@
         <f t="shared" si="2"/>
         <v>200</v>
       </c>
-      <c r="N15" s="106" t="s">
+      <c r="N15" s="86" t="s">
         <v>20</v>
       </c>
       <c r="O15" s="20">
@@ -3354,14 +3500,14 @@
         <f t="shared" si="4"/>
         <v>14.66</v>
       </c>
-      <c r="S15" s="59">
+      <c r="S15" s="55">
         <v>0.14660000000000001</v>
       </c>
       <c r="T15" s="21">
         <f t="shared" si="5"/>
         <v>29.32</v>
       </c>
-      <c r="U15" s="80"/>
+      <c r="U15" s="72"/>
       <c r="V15" s="1"/>
       <c r="W15" s="1"/>
     </row>
@@ -3369,11 +3515,11 @@
       <c r="A16" s="10">
         <v>14</v>
       </c>
-      <c r="B16" s="120"/>
-      <c r="C16" s="75" t="s">
+      <c r="B16" s="105"/>
+      <c r="C16" s="69" t="s">
         <v>89</v>
       </c>
-      <c r="D16" s="76" t="s">
+      <c r="D16" s="12" t="s">
         <v>90</v>
       </c>
       <c r="E16" s="12" t="s">
@@ -3382,7 +3528,7 @@
       <c r="F16" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="G16" s="45" t="s">
+      <c r="G16" s="44" t="s">
         <v>107</v>
       </c>
       <c r="H16" s="12" t="s">
@@ -3391,7 +3537,7 @@
       <c r="I16" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="J16" s="45">
+      <c r="J16" s="44">
         <v>2</v>
       </c>
       <c r="K16" s="13">
@@ -3406,7 +3552,7 @@
         <f t="shared" si="2"/>
         <v>200</v>
       </c>
-      <c r="N16" s="106" t="s">
+      <c r="N16" s="86" t="s">
         <v>20</v>
       </c>
       <c r="O16" s="20">
@@ -3423,14 +3569,14 @@
         <f t="shared" si="4"/>
         <v>7.35</v>
       </c>
-      <c r="S16" s="59">
+      <c r="S16" s="55">
         <v>7.3499999999999996E-2</v>
       </c>
       <c r="T16" s="21">
         <f t="shared" si="5"/>
         <v>14.7</v>
       </c>
-      <c r="U16" s="80"/>
+      <c r="U16" s="72"/>
       <c r="V16" s="1"/>
       <c r="W16" s="1"/>
     </row>
@@ -3438,11 +3584,11 @@
       <c r="A17" s="10">
         <v>15</v>
       </c>
-      <c r="B17" s="120"/>
-      <c r="C17" s="75" t="s">
+      <c r="B17" s="105"/>
+      <c r="C17" s="69" t="s">
         <v>92</v>
       </c>
-      <c r="D17" s="76" t="s">
+      <c r="D17" s="12" t="s">
         <v>93</v>
       </c>
       <c r="E17" s="12" t="s">
@@ -3451,7 +3597,7 @@
       <c r="F17" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="G17" s="45" t="s">
+      <c r="G17" s="44" t="s">
         <v>108</v>
       </c>
       <c r="H17" s="12" t="s">
@@ -3460,7 +3606,7 @@
       <c r="I17" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="J17" s="45">
+      <c r="J17" s="44">
         <v>1</v>
       </c>
       <c r="K17" s="13">
@@ -3475,7 +3621,7 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N17" s="106" t="s">
+      <c r="N17" s="86" t="s">
         <v>20</v>
       </c>
       <c r="O17" s="20">
@@ -3492,24 +3638,24 @@
         <f t="shared" si="4"/>
         <v>13.900000000000002</v>
       </c>
-      <c r="S17" s="59">
+      <c r="S17" s="55">
         <v>0.2422</v>
       </c>
       <c r="T17" s="21">
         <f t="shared" si="5"/>
         <v>24.22</v>
       </c>
-      <c r="U17" s="80"/>
+      <c r="U17" s="72"/>
       <c r="V17" s="1"/>
       <c r="W17" s="1"/>
     </row>
     <row r="18" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="10"/>
-      <c r="B18" s="121"/>
-      <c r="C18" s="81" t="s">
+      <c r="B18" s="106"/>
+      <c r="C18" s="73" t="s">
         <v>95</v>
       </c>
-      <c r="D18" s="82" t="s">
+      <c r="D18" s="6" t="s">
         <v>96</v>
       </c>
       <c r="E18" s="6" t="s">
@@ -3518,7 +3664,7 @@
       <c r="F18" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="G18" s="83" t="s">
+      <c r="G18" s="74" t="s">
         <v>100</v>
       </c>
       <c r="H18" s="6" t="s">
@@ -3527,7 +3673,7 @@
       <c r="I18" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="J18" s="83">
+      <c r="J18" s="74">
         <v>1</v>
       </c>
       <c r="K18" s="16">
@@ -3542,7 +3688,7 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N18" s="107" t="s">
+      <c r="N18" s="87" t="s">
         <v>20</v>
       </c>
       <c r="O18" s="34">
@@ -3559,14 +3705,14 @@
         <f t="shared" si="4"/>
         <v>0.91</v>
       </c>
-      <c r="S18" s="61">
+      <c r="S18" s="57">
         <v>1.4800000000000001E-2</v>
       </c>
       <c r="T18" s="35">
         <f t="shared" si="5"/>
         <v>1.48</v>
       </c>
-      <c r="U18" s="84"/>
+      <c r="U18" s="75"/>
       <c r="V18" s="1"/>
       <c r="W18" s="1"/>
     </row>
@@ -3577,67 +3723,67 @@
       <c r="B19" s="36" t="s">
         <v>165</v>
       </c>
-      <c r="C19" s="85" t="s">
+      <c r="C19" s="76" t="s">
         <v>122</v>
       </c>
-      <c r="D19" s="86" t="s">
+      <c r="D19" s="41" t="s">
         <v>123</v>
       </c>
-      <c r="E19" s="42" t="s">
+      <c r="E19" s="41" t="s">
         <v>124</v>
       </c>
-      <c r="F19" s="42" t="s">
+      <c r="F19" s="41" t="s">
         <v>125</v>
       </c>
-      <c r="G19" s="87" t="s">
+      <c r="G19" s="77" t="s">
         <v>157</v>
       </c>
-      <c r="H19" s="42" t="s">
-        <v>333</v>
-      </c>
-      <c r="I19" s="42" t="s">
+      <c r="H19" s="41" t="s">
+        <v>331</v>
+      </c>
+      <c r="I19" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="J19" s="87">
+      <c r="J19" s="77">
         <v>3</v>
       </c>
-      <c r="K19" s="65">
+      <c r="K19" s="61">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="L19" s="65">
+      <c r="L19" s="61">
         <f t="shared" si="1"/>
         <v>150</v>
       </c>
-      <c r="M19" s="65">
+      <c r="M19" s="61">
         <f t="shared" si="2"/>
         <v>300</v>
       </c>
-      <c r="N19" s="111" t="s">
-        <v>331</v>
-      </c>
-      <c r="O19" s="66">
+      <c r="N19" s="91" t="s">
+        <v>329</v>
+      </c>
+      <c r="O19" s="62">
         <v>0.32200000000000001</v>
       </c>
-      <c r="P19" s="67">
+      <c r="P19" s="63">
         <f t="shared" si="3"/>
         <v>4.83</v>
       </c>
-      <c r="Q19" s="66">
+      <c r="Q19" s="62">
         <v>0.2</v>
       </c>
-      <c r="R19" s="67">
+      <c r="R19" s="63">
         <f t="shared" si="4"/>
         <v>30</v>
       </c>
-      <c r="S19" s="67">
+      <c r="S19" s="63">
         <v>0.2</v>
       </c>
-      <c r="T19" s="67">
+      <c r="T19" s="63">
         <f t="shared" si="5"/>
         <v>60</v>
       </c>
-      <c r="U19" s="88"/>
+      <c r="U19" s="78"/>
       <c r="V19" s="1"/>
       <c r="W19" s="1"/>
     </row>
@@ -3645,46 +3791,46 @@
       <c r="A20" s="10">
         <v>17</v>
       </c>
-      <c r="B20" s="49" t="s">
+      <c r="B20" s="94" t="s">
         <v>168</v>
       </c>
-      <c r="C20" s="125" t="s">
+      <c r="C20" s="96" t="s">
         <v>126</v>
       </c>
-      <c r="D20" s="89" t="s">
+      <c r="D20" s="37" t="s">
         <v>127</v>
       </c>
       <c r="E20" s="37" t="s">
         <v>128</v>
       </c>
-      <c r="F20" s="128" t="s">
+      <c r="F20" s="98" t="s">
         <v>129</v>
       </c>
-      <c r="G20" s="90" t="s">
+      <c r="G20" s="79" t="s">
         <v>158</v>
       </c>
       <c r="H20" s="37" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="I20" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="J20" s="90">
+      <c r="J20" s="79">
         <v>2</v>
       </c>
-      <c r="K20" s="90">
+      <c r="K20" s="79">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="L20" s="90">
+      <c r="L20" s="79">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="M20" s="90">
+      <c r="M20" s="79">
         <f t="shared" si="2"/>
         <v>200</v>
       </c>
-      <c r="N20" s="129" t="s">
+      <c r="N20" s="114" t="s">
         <v>20</v>
       </c>
       <c r="O20" s="38">
@@ -3701,14 +3847,14 @@
         <f t="shared" si="4"/>
         <v>18.25</v>
       </c>
-      <c r="S20" s="126">
+      <c r="S20" s="97">
         <v>0.1825</v>
       </c>
       <c r="T20" s="38">
         <f t="shared" si="5"/>
         <v>36.5</v>
       </c>
-      <c r="U20" s="127"/>
+      <c r="U20" s="126"/>
       <c r="V20" s="25"/>
       <c r="W20" s="25"/>
     </row>
@@ -3716,13 +3862,13 @@
       <c r="A21" s="10">
         <v>18</v>
       </c>
-      <c r="B21" s="122" t="s">
+      <c r="B21" s="107" t="s">
         <v>166</v>
       </c>
-      <c r="C21" s="71" t="s">
-        <v>356</v>
-      </c>
-      <c r="D21" s="72" t="s">
+      <c r="C21" s="66" t="s">
+        <v>354</v>
+      </c>
+      <c r="D21" s="7" t="s">
         <v>130</v>
       </c>
       <c r="E21" s="7" t="s">
@@ -3731,16 +3877,16 @@
       <c r="F21" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="G21" s="73" t="s">
+      <c r="G21" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="H21" s="12" t="s">
+      <c r="H21" s="7" t="s">
         <v>40</v>
       </c>
       <c r="I21" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="J21" s="73">
+      <c r="J21" s="67">
         <v>1</v>
       </c>
       <c r="K21" s="8">
@@ -3755,7 +3901,7 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N21" s="130" t="s">
+      <c r="N21" s="92" t="s">
         <v>20</v>
       </c>
       <c r="O21" s="32">
@@ -3772,14 +3918,16 @@
         <f t="shared" si="4"/>
         <v>20.9</v>
       </c>
-      <c r="S21" s="58">
+      <c r="S21" s="54">
         <v>0.28439999999999999</v>
       </c>
       <c r="T21" s="33">
         <f t="shared" si="5"/>
         <v>28.439999999999998</v>
       </c>
-      <c r="U21" s="91"/>
+      <c r="U21" s="128" t="s">
+        <v>359</v>
+      </c>
       <c r="V21" s="1"/>
       <c r="W21" s="1"/>
     </row>
@@ -3787,11 +3935,11 @@
       <c r="A22" s="10">
         <v>19</v>
       </c>
-      <c r="B22" s="123"/>
-      <c r="C22" s="75" t="s">
+      <c r="B22" s="108"/>
+      <c r="C22" s="69" t="s">
         <v>133</v>
       </c>
-      <c r="D22" s="76" t="s">
+      <c r="D22" s="12" t="s">
         <v>134</v>
       </c>
       <c r="E22" s="12" t="s">
@@ -3800,7 +3948,7 @@
       <c r="F22" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="G22" s="45" t="s">
+      <c r="G22" s="44" t="s">
         <v>157</v>
       </c>
       <c r="H22" s="12" t="s">
@@ -3809,7 +3957,7 @@
       <c r="I22" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="J22" s="45">
+      <c r="J22" s="44">
         <v>1</v>
       </c>
       <c r="K22" s="13">
@@ -3824,7 +3972,7 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N22" s="131" t="s">
+      <c r="N22" s="86" t="s">
         <v>20</v>
       </c>
       <c r="O22" s="20">
@@ -3841,14 +3989,16 @@
         <f t="shared" si="4"/>
         <v>17.349999999999998</v>
       </c>
-      <c r="S22" s="59">
+      <c r="S22" s="55">
         <v>0.1963</v>
       </c>
       <c r="T22" s="21">
         <f t="shared" si="5"/>
         <v>19.63</v>
       </c>
-      <c r="U22" s="80"/>
+      <c r="U22" s="113" t="s">
+        <v>359</v>
+      </c>
       <c r="V22" s="1"/>
       <c r="W22" s="1"/>
     </row>
@@ -3856,11 +4006,11 @@
       <c r="A23" s="10">
         <v>20</v>
       </c>
-      <c r="B23" s="123"/>
-      <c r="C23" s="75" t="s">
+      <c r="B23" s="108"/>
+      <c r="C23" s="69" t="s">
         <v>136</v>
       </c>
-      <c r="D23" s="76" t="s">
+      <c r="D23" s="12" t="s">
         <v>137</v>
       </c>
       <c r="E23" s="12" t="s">
@@ -3869,7 +4019,7 @@
       <c r="F23" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="G23" s="45" t="s">
+      <c r="G23" s="44" t="s">
         <v>159</v>
       </c>
       <c r="H23" s="12" t="s">
@@ -3878,7 +4028,7 @@
       <c r="I23" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="J23" s="45">
+      <c r="J23" s="44">
         <v>1</v>
       </c>
       <c r="K23" s="13">
@@ -3893,7 +4043,7 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N23" s="131" t="s">
+      <c r="N23" s="86" t="s">
         <v>20</v>
       </c>
       <c r="O23" s="20">
@@ -3910,14 +4060,16 @@
         <f t="shared" si="4"/>
         <v>29.549999999999997</v>
       </c>
-      <c r="S23" s="59">
+      <c r="S23" s="55">
         <v>0.4531</v>
       </c>
       <c r="T23" s="21">
         <f t="shared" si="5"/>
         <v>45.31</v>
       </c>
-      <c r="U23" s="80"/>
+      <c r="U23" s="113" t="s">
+        <v>359</v>
+      </c>
       <c r="V23" s="1"/>
       <c r="W23" s="1"/>
     </row>
@@ -3925,11 +4077,11 @@
       <c r="A24" s="10">
         <v>21</v>
       </c>
-      <c r="B24" s="123"/>
-      <c r="C24" s="75" t="s">
+      <c r="B24" s="108"/>
+      <c r="C24" s="69" t="s">
         <v>139</v>
       </c>
-      <c r="D24" s="76" t="s">
+      <c r="D24" s="12" t="s">
         <v>140</v>
       </c>
       <c r="E24" s="12" t="s">
@@ -3938,7 +4090,7 @@
       <c r="F24" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="G24" s="45" t="s">
+      <c r="G24" s="44" t="s">
         <v>46</v>
       </c>
       <c r="H24" s="12" t="s">
@@ -3947,7 +4099,7 @@
       <c r="I24" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="J24" s="45">
+      <c r="J24" s="44">
         <v>1</v>
       </c>
       <c r="K24" s="13">
@@ -3962,7 +4114,7 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N24" s="132" t="s">
+      <c r="N24" s="89" t="s">
         <v>20</v>
       </c>
       <c r="O24" s="20">
@@ -3979,14 +4131,16 @@
         <f t="shared" si="4"/>
         <v>22.400000000000002</v>
       </c>
-      <c r="S24" s="59">
+      <c r="S24" s="55">
         <v>0.30520000000000003</v>
       </c>
       <c r="T24" s="21">
         <f t="shared" si="5"/>
         <v>30.520000000000003</v>
       </c>
-      <c r="U24" s="68"/>
+      <c r="U24" s="113" t="s">
+        <v>359</v>
+      </c>
       <c r="V24" s="1"/>
       <c r="W24" s="1"/>
     </row>
@@ -3994,11 +4148,11 @@
       <c r="A25" s="10">
         <v>22</v>
       </c>
-      <c r="B25" s="124"/>
-      <c r="C25" s="81" t="s">
+      <c r="B25" s="109"/>
+      <c r="C25" s="73" t="s">
         <v>142</v>
       </c>
-      <c r="D25" s="82" t="s">
+      <c r="D25" s="6" t="s">
         <v>143</v>
       </c>
       <c r="E25" s="6" t="s">
@@ -4013,10 +4167,10 @@
       <c r="H25" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="I25" s="40" t="s">
+      <c r="I25" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="J25" s="83">
+      <c r="J25" s="74">
         <v>1</v>
       </c>
       <c r="K25" s="16">
@@ -4031,7 +4185,7 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N25" s="113" t="s">
+      <c r="N25" s="93" t="s">
         <v>20</v>
       </c>
       <c r="O25" s="34">
@@ -4048,14 +4202,14 @@
         <f t="shared" si="4"/>
         <v>27.55</v>
       </c>
-      <c r="S25" s="61">
+      <c r="S25" s="57">
         <v>0.41110000000000002</v>
       </c>
       <c r="T25" s="35">
         <f t="shared" si="5"/>
         <v>41.11</v>
       </c>
-      <c r="U25" s="84"/>
+      <c r="U25" s="75"/>
       <c r="V25" s="1"/>
       <c r="W25" s="1"/>
     </row>
@@ -4063,62 +4217,72 @@
       <c r="A26" s="10">
         <v>23</v>
       </c>
-      <c r="B26" s="123" t="s">
+      <c r="B26" s="108" t="s">
         <v>167</v>
       </c>
-      <c r="C26" s="92" t="s">
+      <c r="C26" s="81" t="s">
         <v>145</v>
       </c>
-      <c r="D26" s="93" t="s">
+      <c r="D26" s="15" t="s">
         <v>146</v>
       </c>
       <c r="E26" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="F26" s="15" t="s">
+      <c r="F26" s="130" t="s">
         <v>147</v>
       </c>
-      <c r="G26" s="94" t="s">
+      <c r="G26" s="82" t="s">
         <v>161</v>
       </c>
       <c r="H26" s="15" t="s">
-        <v>40</v>
+        <v>365</v>
       </c>
       <c r="I26" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="J26" s="94">
+      <c r="J26" s="82">
         <v>1</v>
       </c>
-      <c r="K26" s="41">
+      <c r="K26" s="40">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L26" s="41">
+      <c r="L26" s="40">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="M26" s="41">
+      <c r="M26" s="40">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N26" s="105"/>
-      <c r="O26" s="54"/>
-      <c r="P26" s="55">
+      <c r="N26" s="115" t="s">
+        <v>20</v>
+      </c>
+      <c r="O26" s="50">
+        <v>6.32</v>
+      </c>
+      <c r="P26" s="51">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q26" s="54"/>
-      <c r="R26" s="55">
+        <v>31.6</v>
+      </c>
+      <c r="Q26" s="50">
+        <v>5.2472000000000003</v>
+      </c>
+      <c r="R26" s="51">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S26" s="64"/>
-      <c r="T26" s="55">
+        <v>262.36</v>
+      </c>
+      <c r="S26" s="60">
+        <v>4.5328999999999997</v>
+      </c>
+      <c r="T26" s="51">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="U26" s="95"/>
+        <v>453.28999999999996</v>
+      </c>
+      <c r="U26" s="111" t="s">
+        <v>356</v>
+      </c>
       <c r="V26" s="1"/>
       <c r="W26" s="1"/>
     </row>
@@ -4126,68 +4290,68 @@
       <c r="A27" s="10">
         <v>24</v>
       </c>
-      <c r="B27" s="124"/>
-      <c r="C27" s="75" t="s">
+      <c r="B27" s="108"/>
+      <c r="C27" s="83" t="s">
         <v>148</v>
       </c>
-      <c r="D27" s="76" t="s">
+      <c r="D27" s="84" t="s">
         <v>149</v>
       </c>
-      <c r="E27" s="12" t="s">
+      <c r="E27" s="84" t="s">
         <v>41</v>
       </c>
-      <c r="F27" s="12" t="s">
+      <c r="F27" s="84" t="s">
         <v>150</v>
       </c>
-      <c r="G27" s="45" t="s">
+      <c r="G27" s="85" t="s">
         <v>162</v>
       </c>
-      <c r="H27" s="12" t="s">
+      <c r="H27" s="84" t="s">
         <v>40</v>
       </c>
-      <c r="I27" s="15" t="s">
+      <c r="I27" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="J27" s="45">
+      <c r="J27" s="85">
         <v>1</v>
       </c>
-      <c r="K27" s="13">
+      <c r="K27" s="43">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L27" s="13">
+      <c r="L27" s="43">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="M27" s="13">
+      <c r="M27" s="43">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N27" s="106" t="s">
+      <c r="N27" s="116" t="s">
         <v>20</v>
       </c>
-      <c r="O27" s="20">
+      <c r="O27" s="64">
         <v>1.01</v>
       </c>
-      <c r="P27" s="21">
+      <c r="P27" s="29">
         <f t="shared" si="3"/>
         <v>5.05</v>
       </c>
-      <c r="Q27" s="20">
+      <c r="Q27" s="64">
         <v>0.90959999999999996</v>
       </c>
-      <c r="R27" s="21">
+      <c r="R27" s="29">
         <f t="shared" si="4"/>
         <v>45.48</v>
       </c>
-      <c r="S27" s="59">
+      <c r="S27" s="65">
         <v>0.78979999999999995</v>
       </c>
-      <c r="T27" s="21">
+      <c r="T27" s="29">
         <f t="shared" si="5"/>
         <v>78.97999999999999</v>
       </c>
-      <c r="U27" s="96"/>
+      <c r="U27" s="127"/>
       <c r="V27" s="1"/>
       <c r="W27" s="1"/>
     </row>
@@ -4195,60 +4359,72 @@
       <c r="A28" s="10">
         <v>25</v>
       </c>
-      <c r="B28" s="53" t="s">
-        <v>254</v>
-      </c>
-      <c r="C28" s="23" t="s">
+      <c r="B28" s="49" t="s">
+        <v>253</v>
+      </c>
+      <c r="C28" s="138" t="s">
         <v>151</v>
       </c>
-      <c r="D28" s="76" t="s">
+      <c r="D28" s="41" t="s">
         <v>152</v>
       </c>
-      <c r="E28" s="12" t="s">
+      <c r="E28" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="F28" s="12" t="s">
+      <c r="F28" s="139" t="s">
         <v>153</v>
       </c>
-      <c r="G28" s="45" t="s">
+      <c r="G28" s="77" t="s">
         <v>163</v>
       </c>
-      <c r="H28" s="96"/>
-      <c r="I28" s="15" t="s">
+      <c r="H28" s="77" t="s">
+        <v>357</v>
+      </c>
+      <c r="I28" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="J28" s="45">
+      <c r="J28" s="77">
         <v>1</v>
       </c>
-      <c r="K28" s="13">
+      <c r="K28" s="61">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L28" s="13">
+      <c r="L28" s="61">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="M28" s="13">
+      <c r="M28" s="61">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N28" s="26"/>
-      <c r="O28" s="20"/>
-      <c r="P28" s="21">
+      <c r="N28" s="140" t="s">
+        <v>20</v>
+      </c>
+      <c r="O28" s="62">
+        <v>0.68</v>
+      </c>
+      <c r="P28" s="63">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q28" s="20"/>
-      <c r="R28" s="21">
+        <v>3.4000000000000004</v>
+      </c>
+      <c r="Q28" s="62">
+        <v>0.47</v>
+      </c>
+      <c r="R28" s="63">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S28" s="59"/>
-      <c r="T28" s="21">
+        <v>23.5</v>
+      </c>
+      <c r="S28" s="141">
+        <v>0.42720000000000002</v>
+      </c>
+      <c r="T28" s="63">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="U28" s="96"/>
+        <v>42.72</v>
+      </c>
+      <c r="U28" s="142" t="s">
+        <v>358</v>
+      </c>
       <c r="V28" s="1"/>
       <c r="W28" s="1"/>
     </row>
@@ -4256,102 +4432,102 @@
       <c r="A29" s="10">
         <v>26</v>
       </c>
-      <c r="B29" s="48" t="s">
+      <c r="B29" s="95" t="s">
         <v>39</v>
       </c>
-      <c r="C29" s="97" t="s">
+      <c r="C29" s="96" t="s">
         <v>154</v>
       </c>
-      <c r="D29" s="98" t="s">
+      <c r="D29" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="E29" s="99" t="s">
+      <c r="E29" s="37" t="s">
         <v>41</v>
       </c>
-      <c r="F29" s="99" t="s">
+      <c r="F29" s="37" t="s">
         <v>156</v>
       </c>
-      <c r="G29" s="100" t="s">
+      <c r="G29" s="79" t="s">
         <v>164</v>
       </c>
-      <c r="H29" s="12" t="s">
+      <c r="H29" s="15" t="s">
         <v>40</v>
       </c>
       <c r="I29" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="J29" s="100">
+      <c r="J29" s="79">
         <v>2</v>
       </c>
-      <c r="K29" s="44">
+      <c r="K29" s="134">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="L29" s="44">
+      <c r="L29" s="134">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="M29" s="44">
+      <c r="M29" s="134">
         <f t="shared" si="2"/>
         <v>200</v>
       </c>
-      <c r="N29" s="133" t="s">
+      <c r="N29" s="114" t="s">
         <v>20</v>
       </c>
-      <c r="O29" s="69">
+      <c r="O29" s="38">
         <v>0.65400000000000003</v>
       </c>
-      <c r="P29" s="29">
+      <c r="P29" s="135">
         <f t="shared" si="3"/>
         <v>6.54</v>
       </c>
-      <c r="Q29" s="69">
+      <c r="Q29" s="38">
         <v>0.52359999999999995</v>
       </c>
-      <c r="R29" s="29">
+      <c r="R29" s="135">
         <f t="shared" si="4"/>
         <v>52.359999999999992</v>
       </c>
-      <c r="S29" s="70">
+      <c r="S29" s="136">
         <v>0.52359999999999995</v>
       </c>
-      <c r="T29" s="29">
+      <c r="T29" s="135">
         <f t="shared" si="5"/>
         <v>104.71999999999998</v>
       </c>
-      <c r="U29" s="101"/>
+      <c r="U29" s="137"/>
       <c r="V29" s="1"/>
       <c r="W29" s="1"/>
     </row>
-    <row r="30" spans="1:23" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>27</v>
       </c>
-      <c r="B30" s="122" t="s">
+      <c r="B30" s="107" t="s">
         <v>18</v>
       </c>
-      <c r="C30" s="30" t="s">
+      <c r="C30" s="132" t="s">
+        <v>366</v>
+      </c>
+      <c r="D30" s="7" t="s">
         <v>169</v>
-      </c>
-      <c r="D30" s="72" t="s">
-        <v>170</v>
       </c>
       <c r="E30" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="F30" s="43" t="s">
-        <v>171</v>
-      </c>
-      <c r="G30" s="73" t="s">
+      <c r="F30" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="G30" s="67" t="s">
+        <v>229</v>
+      </c>
+      <c r="H30" s="67" t="s">
+        <v>341</v>
+      </c>
+      <c r="I30" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="H30" s="73" t="s">
-        <v>343</v>
-      </c>
-      <c r="I30" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="J30" s="73">
+      <c r="J30" s="67">
         <v>1</v>
       </c>
       <c r="K30" s="8">
@@ -4366,7 +4542,7 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N30" s="112" t="s">
+      <c r="N30" s="131" t="s">
         <v>20</v>
       </c>
       <c r="O30" s="32">
@@ -4383,14 +4559,14 @@
         <f t="shared" si="4"/>
         <v>0.6</v>
       </c>
-      <c r="S30" s="58">
+      <c r="S30" s="54">
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="T30" s="33">
         <f t="shared" si="5"/>
         <v>0.47000000000000003</v>
       </c>
-      <c r="U30" s="91"/>
+      <c r="U30" s="80"/>
       <c r="V30" s="1"/>
       <c r="W30" s="1"/>
     </row>
@@ -4398,29 +4574,29 @@
       <c r="A31" s="10">
         <v>28</v>
       </c>
-      <c r="B31" s="123"/>
-      <c r="C31" s="75" t="s">
+      <c r="B31" s="108"/>
+      <c r="C31" s="69" t="s">
+        <v>171</v>
+      </c>
+      <c r="D31" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="D31" s="76" t="s">
+      <c r="E31" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="E31" s="12" t="s">
+      <c r="F31" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="F31" s="12" t="s">
-        <v>175</v>
-      </c>
-      <c r="G31" s="45" t="s">
-        <v>232</v>
+      <c r="G31" s="44" t="s">
+        <v>231</v>
       </c>
       <c r="H31" s="12" t="s">
         <v>40</v>
       </c>
       <c r="I31" s="12" t="s">
-        <v>233</v>
-      </c>
-      <c r="J31" s="45">
+        <v>232</v>
+      </c>
+      <c r="J31" s="44">
         <v>1</v>
       </c>
       <c r="K31" s="13">
@@ -4435,7 +4611,7 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N31" s="106" t="s">
+      <c r="N31" s="86" t="s">
         <v>20</v>
       </c>
       <c r="O31" s="20">
@@ -4452,14 +4628,14 @@
         <f t="shared" si="4"/>
         <v>1.35</v>
       </c>
-      <c r="S31" s="59">
+      <c r="S31" s="55">
         <v>1.09E-2</v>
       </c>
       <c r="T31" s="21">
         <f t="shared" si="5"/>
         <v>1.0900000000000001</v>
       </c>
-      <c r="U31" s="80"/>
+      <c r="U31" s="72"/>
       <c r="V31" s="1"/>
       <c r="W31" s="1"/>
     </row>
@@ -4467,29 +4643,29 @@
       <c r="A32" s="10">
         <v>29</v>
       </c>
-      <c r="B32" s="123"/>
-      <c r="C32" s="75" t="s">
+      <c r="B32" s="108"/>
+      <c r="C32" s="69" t="s">
+        <v>175</v>
+      </c>
+      <c r="D32" s="12" t="s">
         <v>176</v>
-      </c>
-      <c r="D32" s="76" t="s">
-        <v>177</v>
       </c>
       <c r="E32" s="12" t="s">
         <v>15</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="G32" s="45" t="s">
+        <v>177</v>
+      </c>
+      <c r="G32" s="44" t="s">
         <v>100</v>
       </c>
       <c r="H32" s="12" t="s">
         <v>40</v>
       </c>
       <c r="I32" s="12" t="s">
-        <v>234</v>
-      </c>
-      <c r="J32" s="45">
+        <v>233</v>
+      </c>
+      <c r="J32" s="44">
         <v>7</v>
       </c>
       <c r="K32" s="13">
@@ -4504,7 +4680,7 @@
         <f t="shared" si="2"/>
         <v>700</v>
       </c>
-      <c r="N32" s="106" t="s">
+      <c r="N32" s="86" t="s">
         <v>20</v>
       </c>
       <c r="O32" s="20">
@@ -4521,14 +4697,14 @@
         <f t="shared" si="4"/>
         <v>1.8900000000000001</v>
       </c>
-      <c r="S32" s="59">
+      <c r="S32" s="55">
         <v>5.4000000000000003E-3</v>
       </c>
       <c r="T32" s="21">
         <f t="shared" si="5"/>
         <v>3.7800000000000002</v>
       </c>
-      <c r="U32" s="80"/>
+      <c r="U32" s="72"/>
       <c r="V32" s="1"/>
       <c r="W32" s="1"/>
     </row>
@@ -4536,29 +4712,29 @@
       <c r="A33" s="10">
         <v>30</v>
       </c>
-      <c r="B33" s="123"/>
-      <c r="C33" s="75" t="s">
-        <v>179</v>
-      </c>
-      <c r="D33" s="76" t="s">
+      <c r="B33" s="108"/>
+      <c r="C33" s="69" t="s">
+        <v>178</v>
+      </c>
+      <c r="D33" s="12" t="s">
         <v>24</v>
       </c>
       <c r="E33" s="12" t="s">
         <v>15</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>180</v>
-      </c>
-      <c r="G33" s="45" t="s">
+        <v>179</v>
+      </c>
+      <c r="G33" s="44" t="s">
         <v>100</v>
       </c>
       <c r="H33" s="12" t="s">
         <v>40</v>
       </c>
       <c r="I33" s="12" t="s">
-        <v>235</v>
-      </c>
-      <c r="J33" s="45">
+        <v>234</v>
+      </c>
+      <c r="J33" s="44">
         <v>1</v>
       </c>
       <c r="K33" s="13">
@@ -4573,7 +4749,7 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N33" s="106" t="s">
+      <c r="N33" s="86" t="s">
         <v>20</v>
       </c>
       <c r="O33" s="20">
@@ -4590,14 +4766,14 @@
         <f t="shared" si="4"/>
         <v>0.8</v>
       </c>
-      <c r="S33" s="59">
+      <c r="S33" s="55">
         <v>6.6E-3</v>
       </c>
       <c r="T33" s="21">
         <f t="shared" si="5"/>
         <v>0.66</v>
       </c>
-      <c r="U33" s="80"/>
+      <c r="U33" s="72"/>
       <c r="V33" s="1"/>
       <c r="W33" s="1"/>
     </row>
@@ -4605,29 +4781,29 @@
       <c r="A34" s="10">
         <v>31</v>
       </c>
-      <c r="B34" s="123"/>
-      <c r="C34" s="75" t="s">
+      <c r="B34" s="108"/>
+      <c r="C34" s="69" t="s">
+        <v>180</v>
+      </c>
+      <c r="D34" s="12" t="s">
         <v>181</v>
-      </c>
-      <c r="D34" s="76" t="s">
-        <v>182</v>
       </c>
       <c r="E34" s="12" t="s">
         <v>15</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="G34" s="45" t="s">
+        <v>182</v>
+      </c>
+      <c r="G34" s="44" t="s">
         <v>100</v>
       </c>
       <c r="H34" s="12" t="s">
         <v>40</v>
       </c>
       <c r="I34" s="12" t="s">
-        <v>236</v>
-      </c>
-      <c r="J34" s="45">
+        <v>235</v>
+      </c>
+      <c r="J34" s="44">
         <v>1</v>
       </c>
       <c r="K34" s="13">
@@ -4642,7 +4818,7 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N34" s="106" t="s">
+      <c r="N34" s="86" t="s">
         <v>20</v>
       </c>
       <c r="O34" s="20">
@@ -4659,14 +4835,14 @@
         <f t="shared" si="4"/>
         <v>1.0999999999999999</v>
       </c>
-      <c r="S34" s="59">
+      <c r="S34" s="55">
         <v>8.9999999999999993E-3</v>
       </c>
       <c r="T34" s="21">
         <f t="shared" si="5"/>
         <v>0.89999999999999991</v>
       </c>
-      <c r="U34" s="80"/>
+      <c r="U34" s="72"/>
       <c r="V34" s="1"/>
       <c r="W34" s="1"/>
     </row>
@@ -4674,29 +4850,29 @@
       <c r="A35" s="10">
         <v>32</v>
       </c>
-      <c r="B35" s="123"/>
-      <c r="C35" s="75" t="s">
+      <c r="B35" s="108"/>
+      <c r="C35" s="69" t="s">
+        <v>183</v>
+      </c>
+      <c r="D35" s="12" t="s">
         <v>184</v>
-      </c>
-      <c r="D35" s="76" t="s">
-        <v>185</v>
       </c>
       <c r="E35" s="12" t="s">
         <v>15</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>186</v>
-      </c>
-      <c r="G35" s="45" t="s">
+        <v>185</v>
+      </c>
+      <c r="G35" s="44" t="s">
         <v>100</v>
       </c>
       <c r="H35" s="12" t="s">
         <v>40</v>
       </c>
       <c r="I35" s="12" t="s">
-        <v>237</v>
-      </c>
-      <c r="J35" s="45">
+        <v>236</v>
+      </c>
+      <c r="J35" s="44">
         <v>1</v>
       </c>
       <c r="K35" s="13">
@@ -4711,7 +4887,7 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N35" s="106" t="s">
+      <c r="N35" s="86" t="s">
         <v>20</v>
       </c>
       <c r="O35" s="20">
@@ -4728,14 +4904,14 @@
         <f t="shared" si="4"/>
         <v>1.0999999999999999</v>
       </c>
-      <c r="S35" s="59">
+      <c r="S35" s="55">
         <v>8.9999999999999993E-3</v>
       </c>
       <c r="T35" s="21">
         <f t="shared" si="5"/>
         <v>0.89999999999999991</v>
       </c>
-      <c r="U35" s="80"/>
+      <c r="U35" s="72"/>
       <c r="V35" s="1"/>
       <c r="W35" s="1"/>
     </row>
@@ -4743,29 +4919,29 @@
       <c r="A36" s="10">
         <v>33</v>
       </c>
-      <c r="B36" s="123"/>
-      <c r="C36" s="75" t="s">
+      <c r="B36" s="108"/>
+      <c r="C36" s="69" t="s">
+        <v>186</v>
+      </c>
+      <c r="D36" s="12" t="s">
         <v>187</v>
-      </c>
-      <c r="D36" s="76" t="s">
-        <v>188</v>
       </c>
       <c r="E36" s="12" t="s">
         <v>15</v>
       </c>
       <c r="F36" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="G36" s="45" t="s">
-        <v>238</v>
+        <v>188</v>
+      </c>
+      <c r="G36" s="44" t="s">
+        <v>237</v>
       </c>
       <c r="H36" s="26" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="I36" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="J36" s="45">
+      <c r="J36" s="44">
         <v>5</v>
       </c>
       <c r="K36" s="13">
@@ -4780,7 +4956,7 @@
         <f t="shared" si="2"/>
         <v>500</v>
       </c>
-      <c r="N36" s="106" t="s">
+      <c r="N36" s="86" t="s">
         <v>20</v>
       </c>
       <c r="O36" s="20">
@@ -4797,14 +4973,14 @@
         <f t="shared" si="4"/>
         <v>21.75</v>
       </c>
-      <c r="S36" s="59">
+      <c r="S36" s="55">
         <v>8.6999999999999994E-2</v>
       </c>
       <c r="T36" s="21">
         <f t="shared" si="5"/>
         <v>43.5</v>
       </c>
-      <c r="U36" s="80"/>
+      <c r="U36" s="72"/>
       <c r="V36" s="1"/>
       <c r="W36" s="1"/>
     </row>
@@ -4812,29 +4988,29 @@
       <c r="A37" s="10">
         <v>34</v>
       </c>
-      <c r="B37" s="123"/>
-      <c r="C37" s="75" t="s">
+      <c r="B37" s="108"/>
+      <c r="C37" s="69" t="s">
+        <v>189</v>
+      </c>
+      <c r="D37" s="12" t="s">
         <v>190</v>
-      </c>
-      <c r="D37" s="76" t="s">
-        <v>191</v>
       </c>
       <c r="E37" s="12" t="s">
         <v>15</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="G37" s="45" t="s">
+        <v>191</v>
+      </c>
+      <c r="G37" s="44" t="s">
         <v>100</v>
       </c>
       <c r="H37" s="12" t="s">
         <v>40</v>
       </c>
       <c r="I37" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="J37" s="45">
+        <v>238</v>
+      </c>
+      <c r="J37" s="44">
         <v>1</v>
       </c>
       <c r="K37" s="13">
@@ -4849,8 +5025,8 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N37" s="106" t="s">
-        <v>331</v>
+      <c r="N37" s="86" t="s">
+        <v>329</v>
       </c>
       <c r="O37" s="20">
         <v>0.10100000000000001</v>
@@ -4866,14 +5042,14 @@
         <f t="shared" si="4"/>
         <v>0.8</v>
       </c>
-      <c r="S37" s="59">
+      <c r="S37" s="55">
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="T37" s="21">
         <f t="shared" si="5"/>
         <v>0.70000000000000007</v>
       </c>
-      <c r="U37" s="80"/>
+      <c r="U37" s="72"/>
       <c r="V37" s="1"/>
       <c r="W37" s="1"/>
     </row>
@@ -4881,29 +5057,29 @@
       <c r="A38" s="10">
         <v>35</v>
       </c>
-      <c r="B38" s="123"/>
-      <c r="C38" s="75" t="s">
+      <c r="B38" s="108"/>
+      <c r="C38" s="69" t="s">
+        <v>192</v>
+      </c>
+      <c r="D38" s="12" t="s">
         <v>193</v>
-      </c>
-      <c r="D38" s="76" t="s">
-        <v>194</v>
       </c>
       <c r="E38" s="12" t="s">
         <v>15</v>
       </c>
       <c r="F38" s="24" t="s">
-        <v>195</v>
-      </c>
-      <c r="G38" s="45" t="s">
-        <v>238</v>
-      </c>
-      <c r="H38" s="45" t="s">
-        <v>335</v>
+        <v>194</v>
+      </c>
+      <c r="G38" s="44" t="s">
+        <v>237</v>
+      </c>
+      <c r="H38" s="44" t="s">
+        <v>333</v>
       </c>
       <c r="I38" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="J38" s="45">
+        <v>239</v>
+      </c>
+      <c r="J38" s="44">
         <v>1</v>
       </c>
       <c r="K38" s="13">
@@ -4918,7 +5094,7 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N38" s="106" t="s">
+      <c r="N38" s="86" t="s">
         <v>20</v>
       </c>
       <c r="O38" s="20">
@@ -4935,14 +5111,14 @@
         <f t="shared" si="4"/>
         <v>0.75</v>
       </c>
-      <c r="S38" s="59">
+      <c r="S38" s="55">
         <v>6.1000000000000004E-3</v>
       </c>
       <c r="T38" s="21">
         <f t="shared" si="5"/>
         <v>0.61</v>
       </c>
-      <c r="U38" s="80"/>
+      <c r="U38" s="72"/>
       <c r="V38" s="1"/>
       <c r="W38" s="1"/>
     </row>
@@ -4950,29 +5126,29 @@
       <c r="A39" s="10">
         <v>36</v>
       </c>
-      <c r="B39" s="123"/>
-      <c r="C39" s="75" t="s">
+      <c r="B39" s="108"/>
+      <c r="C39" s="69" t="s">
+        <v>195</v>
+      </c>
+      <c r="D39" s="12" t="s">
         <v>196</v>
-      </c>
-      <c r="D39" s="76" t="s">
-        <v>197</v>
       </c>
       <c r="E39" s="12" t="s">
         <v>15</v>
       </c>
       <c r="F39" s="24" t="s">
-        <v>198</v>
-      </c>
-      <c r="G39" s="45" t="s">
+        <v>197</v>
+      </c>
+      <c r="G39" s="44" t="s">
         <v>100</v>
       </c>
-      <c r="H39" s="45" t="s">
-        <v>336</v>
+      <c r="H39" s="44" t="s">
+        <v>334</v>
       </c>
       <c r="I39" s="12" t="s">
-        <v>241</v>
-      </c>
-      <c r="J39" s="45">
+        <v>240</v>
+      </c>
+      <c r="J39" s="44">
         <v>4</v>
       </c>
       <c r="K39" s="13">
@@ -4987,7 +5163,7 @@
         <f t="shared" si="2"/>
         <v>400</v>
       </c>
-      <c r="N39" s="106" t="s">
+      <c r="N39" s="86" t="s">
         <v>20</v>
       </c>
       <c r="O39" s="20">
@@ -5004,14 +5180,14 @@
         <f t="shared" si="4"/>
         <v>0.94000000000000006</v>
       </c>
-      <c r="S39" s="59">
+      <c r="S39" s="55">
         <v>3.5999999999999999E-3</v>
       </c>
       <c r="T39" s="21">
         <f t="shared" si="5"/>
         <v>1.44</v>
       </c>
-      <c r="U39" s="80"/>
+      <c r="U39" s="72"/>
       <c r="V39" s="1"/>
       <c r="W39" s="1"/>
     </row>
@@ -5019,29 +5195,29 @@
       <c r="A40" s="10">
         <v>37</v>
       </c>
-      <c r="B40" s="123"/>
-      <c r="C40" s="75" t="s">
-        <v>345</v>
-      </c>
-      <c r="D40" s="76" t="s">
-        <v>199</v>
+      <c r="B40" s="108"/>
+      <c r="C40" s="69" t="s">
+        <v>343</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>198</v>
       </c>
       <c r="E40" s="12" t="s">
         <v>15</v>
       </c>
       <c r="F40" s="24" t="s">
-        <v>200</v>
-      </c>
-      <c r="G40" s="45" t="s">
-        <v>242</v>
-      </c>
-      <c r="H40" s="45" t="s">
-        <v>344</v>
+        <v>199</v>
+      </c>
+      <c r="G40" s="44" t="s">
+        <v>241</v>
+      </c>
+      <c r="H40" s="44" t="s">
+        <v>342</v>
       </c>
       <c r="I40" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="J40" s="45">
+      <c r="J40" s="44">
         <v>3</v>
       </c>
       <c r="K40" s="13">
@@ -5056,7 +5232,7 @@
         <f t="shared" si="2"/>
         <v>300</v>
       </c>
-      <c r="N40" s="106" t="s">
+      <c r="N40" s="86" t="s">
         <v>20</v>
       </c>
       <c r="O40" s="20">
@@ -5073,14 +5249,14 @@
         <f t="shared" si="4"/>
         <v>1.665</v>
       </c>
-      <c r="S40" s="59">
+      <c r="S40" s="55">
         <v>1.11E-2</v>
       </c>
       <c r="T40" s="21">
         <f t="shared" si="5"/>
         <v>3.33</v>
       </c>
-      <c r="U40" s="80"/>
+      <c r="U40" s="72"/>
       <c r="V40" s="1"/>
       <c r="W40" s="1"/>
     </row>
@@ -5088,29 +5264,29 @@
       <c r="A41" s="10">
         <v>38</v>
       </c>
-      <c r="B41" s="123"/>
-      <c r="C41" s="75" t="s">
-        <v>347</v>
-      </c>
-      <c r="D41" s="76" t="s">
+      <c r="B41" s="108"/>
+      <c r="C41" s="69" t="s">
+        <v>345</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="E41" s="12" t="s">
         <v>201</v>
       </c>
-      <c r="E41" s="12" t="s">
+      <c r="F41" s="24" t="s">
         <v>202</v>
       </c>
-      <c r="F41" s="24" t="s">
-        <v>203</v>
-      </c>
-      <c r="G41" s="45" t="s">
+      <c r="G41" s="44" t="s">
+        <v>242</v>
+      </c>
+      <c r="H41" s="44" t="s">
+        <v>344</v>
+      </c>
+      <c r="I41" s="12" t="s">
         <v>243</v>
       </c>
-      <c r="H41" s="45" t="s">
-        <v>346</v>
-      </c>
-      <c r="I41" s="12" t="s">
-        <v>244</v>
-      </c>
-      <c r="J41" s="45">
+      <c r="J41" s="44">
         <v>1</v>
       </c>
       <c r="K41" s="13">
@@ -5125,7 +5301,7 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N41" s="106" t="s">
+      <c r="N41" s="86" t="s">
         <v>20</v>
       </c>
       <c r="O41" s="20">
@@ -5142,14 +5318,14 @@
         <f t="shared" si="4"/>
         <v>0.85000000000000009</v>
       </c>
-      <c r="S41" s="59">
+      <c r="S41" s="55">
         <v>6.7999999999999996E-3</v>
       </c>
       <c r="T41" s="21">
         <f t="shared" si="5"/>
         <v>0.67999999999999994</v>
       </c>
-      <c r="U41" s="80"/>
+      <c r="U41" s="72"/>
       <c r="V41" s="1"/>
       <c r="W41" s="1"/>
     </row>
@@ -5157,29 +5333,29 @@
       <c r="A42" s="10">
         <v>39</v>
       </c>
-      <c r="B42" s="123"/>
-      <c r="C42" s="75" t="s">
+      <c r="B42" s="108"/>
+      <c r="C42" s="69" t="s">
+        <v>203</v>
+      </c>
+      <c r="D42" s="12" t="s">
         <v>204</v>
-      </c>
-      <c r="D42" s="76" t="s">
-        <v>205</v>
       </c>
       <c r="E42" s="12" t="s">
         <v>15</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>206</v>
-      </c>
-      <c r="G42" s="45" t="s">
+        <v>205</v>
+      </c>
+      <c r="G42" s="44" t="s">
         <v>100</v>
       </c>
       <c r="H42" s="12" t="s">
         <v>40</v>
       </c>
       <c r="I42" s="12" t="s">
-        <v>245</v>
-      </c>
-      <c r="J42" s="45">
+        <v>244</v>
+      </c>
+      <c r="J42" s="44">
         <v>3</v>
       </c>
       <c r="K42" s="13">
@@ -5194,7 +5370,7 @@
         <f t="shared" si="2"/>
         <v>300</v>
       </c>
-      <c r="N42" s="106" t="s">
+      <c r="N42" s="86" t="s">
         <v>20</v>
       </c>
       <c r="O42" s="20">
@@ -5211,14 +5387,14 @@
         <f t="shared" si="4"/>
         <v>0.99</v>
       </c>
-      <c r="S42" s="59">
+      <c r="S42" s="55">
         <v>6.6E-3</v>
       </c>
       <c r="T42" s="21">
         <f t="shared" si="5"/>
         <v>1.98</v>
       </c>
-      <c r="U42" s="80"/>
+      <c r="U42" s="72"/>
       <c r="V42" s="1"/>
       <c r="W42" s="1"/>
     </row>
@@ -5226,29 +5402,29 @@
       <c r="A43" s="10">
         <v>40</v>
       </c>
-      <c r="B43" s="123"/>
-      <c r="C43" s="75" t="s">
+      <c r="B43" s="108"/>
+      <c r="C43" s="69" t="s">
+        <v>206</v>
+      </c>
+      <c r="D43" s="12" t="s">
         <v>207</v>
-      </c>
-      <c r="D43" s="76" t="s">
-        <v>208</v>
       </c>
       <c r="E43" s="12" t="s">
         <v>15</v>
       </c>
       <c r="F43" s="24" t="s">
-        <v>209</v>
-      </c>
-      <c r="G43" s="45" t="s">
+        <v>208</v>
+      </c>
+      <c r="G43" s="44" t="s">
         <v>98</v>
       </c>
-      <c r="H43" s="45" t="s">
-        <v>337</v>
+      <c r="H43" s="44" t="s">
+        <v>335</v>
       </c>
       <c r="I43" s="12" t="s">
-        <v>246</v>
-      </c>
-      <c r="J43" s="45">
+        <v>245</v>
+      </c>
+      <c r="J43" s="44">
         <v>2</v>
       </c>
       <c r="K43" s="13">
@@ -5263,7 +5439,7 @@
         <f t="shared" si="2"/>
         <v>200</v>
       </c>
-      <c r="N43" s="106" t="s">
+      <c r="N43" s="86" t="s">
         <v>20</v>
       </c>
       <c r="O43" s="20">
@@ -5280,14 +5456,14 @@
         <f t="shared" si="4"/>
         <v>0.54</v>
       </c>
-      <c r="S43" s="59">
+      <c r="S43" s="55">
         <v>5.4000000000000003E-3</v>
       </c>
       <c r="T43" s="21">
         <f t="shared" si="5"/>
         <v>1.08</v>
       </c>
-      <c r="U43" s="80"/>
+      <c r="U43" s="72"/>
       <c r="V43" s="1"/>
       <c r="W43" s="1"/>
     </row>
@@ -5295,29 +5471,29 @@
       <c r="A44" s="10">
         <v>41</v>
       </c>
-      <c r="B44" s="123"/>
-      <c r="C44" s="75" t="s">
-        <v>348</v>
-      </c>
-      <c r="D44" s="76" t="s">
+      <c r="B44" s="108"/>
+      <c r="C44" s="69" t="s">
+        <v>346</v>
+      </c>
+      <c r="D44" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="E44" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="E44" s="12" t="s">
+      <c r="F44" s="24" t="s">
         <v>211</v>
       </c>
-      <c r="F44" s="24" t="s">
-        <v>212</v>
-      </c>
-      <c r="G44" s="45" t="s">
+      <c r="G44" s="44" t="s">
+        <v>246</v>
+      </c>
+      <c r="H44" s="44" t="s">
+        <v>347</v>
+      </c>
+      <c r="I44" s="12" t="s">
         <v>247</v>
       </c>
-      <c r="H44" s="45" t="s">
-        <v>349</v>
-      </c>
-      <c r="I44" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="J44" s="45">
+      <c r="J44" s="44">
         <v>1</v>
       </c>
       <c r="K44" s="13">
@@ -5332,7 +5508,7 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N44" s="106" t="s">
+      <c r="N44" s="86" t="s">
         <v>20</v>
       </c>
       <c r="O44" s="20">
@@ -5349,14 +5525,14 @@
         <f t="shared" si="4"/>
         <v>6.67</v>
       </c>
-      <c r="S44" s="59">
+      <c r="S44" s="55">
         <v>9.8900000000000002E-2</v>
       </c>
       <c r="T44" s="21">
         <f t="shared" si="5"/>
         <v>9.89</v>
       </c>
-      <c r="U44" s="80"/>
+      <c r="U44" s="72"/>
       <c r="V44" s="1"/>
       <c r="W44" s="1"/>
     </row>
@@ -5364,29 +5540,29 @@
       <c r="A45" s="10">
         <v>42</v>
       </c>
-      <c r="B45" s="123"/>
-      <c r="C45" s="75" t="s">
+      <c r="B45" s="108"/>
+      <c r="C45" s="69" t="s">
+        <v>212</v>
+      </c>
+      <c r="D45" s="12" t="s">
         <v>213</v>
-      </c>
-      <c r="D45" s="76" t="s">
-        <v>214</v>
       </c>
       <c r="E45" s="12" t="s">
         <v>15</v>
       </c>
       <c r="F45" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="G45" s="45" t="s">
+        <v>214</v>
+      </c>
+      <c r="G45" s="44" t="s">
         <v>100</v>
       </c>
-      <c r="H45" s="45" t="s">
-        <v>350</v>
+      <c r="H45" s="44" t="s">
+        <v>348</v>
       </c>
       <c r="I45" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="J45" s="45">
+      <c r="J45" s="44">
         <v>2</v>
       </c>
       <c r="K45" s="13">
@@ -5401,7 +5577,7 @@
         <f t="shared" si="2"/>
         <v>200</v>
       </c>
-      <c r="N45" s="106" t="s">
+      <c r="N45" s="86" t="s">
         <v>20</v>
       </c>
       <c r="O45" s="20">
@@ -5418,14 +5594,14 @@
         <f t="shared" si="4"/>
         <v>0.47000000000000003</v>
       </c>
-      <c r="S45" s="59">
+      <c r="S45" s="55">
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="T45" s="21">
         <f t="shared" si="5"/>
         <v>0.94000000000000006</v>
       </c>
-      <c r="U45" s="80"/>
+      <c r="U45" s="72"/>
       <c r="V45" s="1"/>
       <c r="W45" s="1"/>
     </row>
@@ -5433,29 +5609,29 @@
       <c r="A46" s="10">
         <v>43</v>
       </c>
-      <c r="B46" s="123"/>
-      <c r="C46" s="75" t="s">
+      <c r="B46" s="108"/>
+      <c r="C46" s="69" t="s">
+        <v>215</v>
+      </c>
+      <c r="D46" s="12" t="s">
         <v>216</v>
-      </c>
-      <c r="D46" s="76" t="s">
-        <v>217</v>
       </c>
       <c r="E46" s="12" t="s">
         <v>15</v>
       </c>
       <c r="F46" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="G46" s="45" t="s">
+        <v>217</v>
+      </c>
+      <c r="G46" s="44" t="s">
         <v>100</v>
       </c>
       <c r="H46" s="12" t="s">
         <v>40</v>
       </c>
       <c r="I46" s="12" t="s">
-        <v>249</v>
-      </c>
-      <c r="J46" s="45">
+        <v>248</v>
+      </c>
+      <c r="J46" s="44">
         <v>1</v>
       </c>
       <c r="K46" s="13">
@@ -5470,7 +5646,7 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N46" s="106" t="s">
+      <c r="N46" s="86" t="s">
         <v>20</v>
       </c>
       <c r="O46" s="20">
@@ -5487,14 +5663,14 @@
         <f t="shared" si="4"/>
         <v>1.0999999999999999</v>
       </c>
-      <c r="S46" s="59">
+      <c r="S46" s="55">
         <v>8.9999999999999993E-3</v>
       </c>
       <c r="T46" s="21">
         <f t="shared" si="5"/>
         <v>0.89999999999999991</v>
       </c>
-      <c r="U46" s="80"/>
+      <c r="U46" s="72"/>
       <c r="V46" s="1"/>
       <c r="W46" s="1"/>
     </row>
@@ -5502,29 +5678,29 @@
       <c r="A47" s="10">
         <v>44</v>
       </c>
-      <c r="B47" s="123"/>
-      <c r="C47" s="75" t="s">
+      <c r="B47" s="108"/>
+      <c r="C47" s="69" t="s">
+        <v>218</v>
+      </c>
+      <c r="D47" s="12" t="s">
         <v>219</v>
-      </c>
-      <c r="D47" s="76" t="s">
-        <v>220</v>
       </c>
       <c r="E47" s="12" t="s">
         <v>15</v>
       </c>
       <c r="F47" s="12" t="s">
-        <v>221</v>
-      </c>
-      <c r="G47" s="45" t="s">
+        <v>220</v>
+      </c>
+      <c r="G47" s="44" t="s">
         <v>100</v>
       </c>
       <c r="H47" s="12" t="s">
         <v>40</v>
       </c>
       <c r="I47" s="12" t="s">
-        <v>250</v>
-      </c>
-      <c r="J47" s="45">
+        <v>249</v>
+      </c>
+      <c r="J47" s="44">
         <v>1</v>
       </c>
       <c r="K47" s="13">
@@ -5539,7 +5715,7 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N47" s="106" t="s">
+      <c r="N47" s="86" t="s">
         <v>20</v>
       </c>
       <c r="O47" s="20">
@@ -5556,14 +5732,14 @@
         <f t="shared" si="4"/>
         <v>0.8</v>
       </c>
-      <c r="S47" s="59">
+      <c r="S47" s="55">
         <v>6.6E-3</v>
       </c>
       <c r="T47" s="21">
         <f t="shared" si="5"/>
         <v>0.66</v>
       </c>
-      <c r="U47" s="80"/>
+      <c r="U47" s="72"/>
       <c r="V47" s="1"/>
       <c r="W47" s="1"/>
     </row>
@@ -5571,29 +5747,29 @@
       <c r="A48" s="10">
         <v>45</v>
       </c>
-      <c r="B48" s="123"/>
-      <c r="C48" s="75" t="s">
+      <c r="B48" s="108"/>
+      <c r="C48" s="69" t="s">
+        <v>221</v>
+      </c>
+      <c r="D48" s="12" t="s">
         <v>222</v>
-      </c>
-      <c r="D48" s="76" t="s">
-        <v>223</v>
       </c>
       <c r="E48" s="12" t="s">
         <v>15</v>
       </c>
       <c r="F48" s="12" t="s">
-        <v>224</v>
-      </c>
-      <c r="G48" s="45" t="s">
+        <v>223</v>
+      </c>
+      <c r="G48" s="44" t="s">
         <v>100</v>
       </c>
       <c r="H48" s="12" t="s">
         <v>40</v>
       </c>
       <c r="I48" s="12" t="s">
-        <v>251</v>
-      </c>
-      <c r="J48" s="45">
+        <v>250</v>
+      </c>
+      <c r="J48" s="44">
         <v>1</v>
       </c>
       <c r="K48" s="13">
@@ -5608,7 +5784,7 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N48" s="106" t="s">
+      <c r="N48" s="86" t="s">
         <v>20</v>
       </c>
       <c r="O48" s="20">
@@ -5625,14 +5801,14 @@
         <f t="shared" si="4"/>
         <v>0.8</v>
       </c>
-      <c r="S48" s="59">
+      <c r="S48" s="55">
         <v>6.6E-3</v>
       </c>
       <c r="T48" s="21">
         <f t="shared" si="5"/>
         <v>0.66</v>
       </c>
-      <c r="U48" s="80"/>
+      <c r="U48" s="72"/>
       <c r="V48" s="1"/>
       <c r="W48" s="1"/>
     </row>
@@ -5640,29 +5816,29 @@
       <c r="A49" s="10">
         <v>46</v>
       </c>
-      <c r="B49" s="123"/>
-      <c r="C49" s="75" t="s">
+      <c r="B49" s="108"/>
+      <c r="C49" s="69" t="s">
+        <v>224</v>
+      </c>
+      <c r="D49" s="12" t="s">
         <v>225</v>
-      </c>
-      <c r="D49" s="76" t="s">
-        <v>226</v>
       </c>
       <c r="E49" s="12" t="s">
         <v>15</v>
       </c>
       <c r="F49" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="G49" s="45" t="s">
+        <v>226</v>
+      </c>
+      <c r="G49" s="44" t="s">
         <v>100</v>
       </c>
       <c r="H49" s="12" t="s">
         <v>40</v>
       </c>
       <c r="I49" s="12" t="s">
-        <v>252</v>
-      </c>
-      <c r="J49" s="45">
+        <v>251</v>
+      </c>
+      <c r="J49" s="44">
         <v>1</v>
       </c>
       <c r="K49" s="13">
@@ -5677,7 +5853,7 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N49" s="106" t="s">
+      <c r="N49" s="86" t="s">
         <v>20</v>
       </c>
       <c r="O49" s="20">
@@ -5694,14 +5870,14 @@
         <f t="shared" si="4"/>
         <v>1.0999999999999999</v>
       </c>
-      <c r="S49" s="59">
+      <c r="S49" s="55">
         <v>8.9999999999999993E-3</v>
       </c>
       <c r="T49" s="21">
         <f t="shared" si="5"/>
         <v>0.89999999999999991</v>
       </c>
-      <c r="U49" s="80"/>
+      <c r="U49" s="72"/>
       <c r="V49" s="1"/>
       <c r="W49" s="1"/>
     </row>
@@ -5709,29 +5885,29 @@
       <c r="A50" s="10">
         <v>47</v>
       </c>
-      <c r="B50" s="124"/>
-      <c r="C50" s="81" t="s">
-        <v>352</v>
-      </c>
-      <c r="D50" s="82" t="s">
-        <v>228</v>
+      <c r="B50" s="109"/>
+      <c r="C50" s="73" t="s">
+        <v>350</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>227</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F50" s="28" t="s">
+        <v>228</v>
+      </c>
+      <c r="G50" s="74" t="s">
         <v>229</v>
       </c>
-      <c r="G50" s="83" t="s">
-        <v>230</v>
-      </c>
-      <c r="H50" s="83" t="s">
-        <v>351</v>
+      <c r="H50" s="74" t="s">
+        <v>349</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="J50" s="83">
+        <v>252</v>
+      </c>
+      <c r="J50" s="74">
         <v>1</v>
       </c>
       <c r="K50" s="16">
@@ -5746,7 +5922,7 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N50" s="107" t="s">
+      <c r="N50" s="87" t="s">
         <v>20</v>
       </c>
       <c r="O50" s="34">
@@ -5763,14 +5939,14 @@
         <f t="shared" si="4"/>
         <v>1.55</v>
       </c>
-      <c r="S50" s="61">
+      <c r="S50" s="57">
         <v>1.2500000000000001E-2</v>
       </c>
       <c r="T50" s="35">
         <f t="shared" si="5"/>
         <v>1.25</v>
       </c>
-      <c r="U50" s="84"/>
+      <c r="U50" s="75"/>
       <c r="V50" s="1"/>
       <c r="W50" s="1"/>
     </row>
@@ -5778,23 +5954,23 @@
       <c r="A51" s="10">
         <v>48</v>
       </c>
-      <c r="B51" s="122" t="s">
+      <c r="B51" s="107" t="s">
         <v>38</v>
       </c>
-      <c r="C51" s="71" t="s">
+      <c r="C51" s="66" t="s">
+        <v>254</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="F51" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="D51" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="E51" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="F51" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="G51" s="73" t="s">
-        <v>281</v>
+      <c r="G51" s="67" t="s">
+        <v>280</v>
       </c>
       <c r="H51" s="7" t="s">
         <v>40</v>
@@ -5802,7 +5978,7 @@
       <c r="I51" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="J51" s="73">
+      <c r="J51" s="67">
         <v>1</v>
       </c>
       <c r="K51" s="8">
@@ -5817,7 +5993,7 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N51" s="130" t="s">
+      <c r="N51" s="92" t="s">
         <v>20</v>
       </c>
       <c r="O51" s="32">
@@ -5834,14 +6010,16 @@
         <f t="shared" si="4"/>
         <v>60</v>
       </c>
-      <c r="S51" s="58">
+      <c r="S51" s="54">
         <v>1</v>
       </c>
       <c r="T51" s="33">
         <f t="shared" si="5"/>
         <v>100</v>
       </c>
-      <c r="U51" s="91"/>
+      <c r="U51" s="128" t="s">
+        <v>359</v>
+      </c>
       <c r="V51" s="1"/>
       <c r="W51" s="1"/>
     </row>
@@ -5849,21 +6027,21 @@
       <c r="A52" s="10">
         <v>49</v>
       </c>
-      <c r="B52" s="123"/>
-      <c r="C52" s="75" t="s">
+      <c r="B52" s="108"/>
+      <c r="C52" s="69" t="s">
+        <v>256</v>
+      </c>
+      <c r="D52" s="12" t="s">
         <v>257</v>
       </c>
-      <c r="D52" s="76" t="s">
+      <c r="E52" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="F52" s="12" t="s">
         <v>258</v>
       </c>
-      <c r="E52" s="12" t="s">
-        <v>341</v>
-      </c>
-      <c r="F52" s="12" t="s">
-        <v>259</v>
-      </c>
-      <c r="G52" s="45" t="s">
-        <v>282</v>
+      <c r="G52" s="44" t="s">
+        <v>281</v>
       </c>
       <c r="H52" s="12" t="s">
         <v>40</v>
@@ -5871,7 +6049,7 @@
       <c r="I52" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J52" s="45">
+      <c r="J52" s="44">
         <v>1</v>
       </c>
       <c r="K52" s="13">
@@ -5886,23 +6064,33 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N52" s="131"/>
-      <c r="O52" s="20"/>
+      <c r="N52" s="86" t="s">
+        <v>329</v>
+      </c>
+      <c r="O52" s="20">
+        <v>0.65400000000000003</v>
+      </c>
       <c r="P52" s="21">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q52" s="20"/>
+        <v>3.27</v>
+      </c>
+      <c r="Q52" s="20">
+        <v>0.57599999999999996</v>
+      </c>
       <c r="R52" s="21">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S52" s="59"/>
+        <v>28.799999999999997</v>
+      </c>
+      <c r="S52" s="55">
+        <v>0.442</v>
+      </c>
       <c r="T52" s="21">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="U52" s="80"/>
+        <v>44.2</v>
+      </c>
+      <c r="U52" s="113" t="s">
+        <v>359</v>
+      </c>
       <c r="V52" s="1"/>
       <c r="W52" s="1"/>
     </row>
@@ -5910,27 +6098,29 @@
       <c r="A53" s="10">
         <v>50</v>
       </c>
-      <c r="B53" s="123"/>
-      <c r="C53" s="75" t="s">
+      <c r="B53" s="108"/>
+      <c r="C53" s="69" t="s">
+        <v>259</v>
+      </c>
+      <c r="D53" s="12" t="s">
         <v>260</v>
-      </c>
-      <c r="D53" s="76" t="s">
-        <v>261</v>
       </c>
       <c r="E53" s="12" t="s">
         <v>131</v>
       </c>
       <c r="F53" s="12" t="s">
-        <v>262</v>
-      </c>
-      <c r="G53" s="45" t="s">
+        <v>261</v>
+      </c>
+      <c r="G53" s="44" t="s">
         <v>159</v>
       </c>
-      <c r="H53" s="96"/>
+      <c r="H53" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="I53" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J53" s="45">
+      <c r="J53" s="44">
         <v>1</v>
       </c>
       <c r="K53" s="13">
@@ -5945,7 +6135,7 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N53" s="131" t="s">
+      <c r="N53" s="86" t="s">
         <v>20</v>
       </c>
       <c r="O53" s="20">
@@ -5962,14 +6152,16 @@
         <f t="shared" si="4"/>
         <v>21.42</v>
       </c>
-      <c r="S53" s="59">
+      <c r="S53" s="55">
         <v>0.34279999999999999</v>
       </c>
       <c r="T53" s="21">
         <f t="shared" si="5"/>
         <v>34.28</v>
       </c>
-      <c r="U53" s="80"/>
+      <c r="U53" s="113" t="s">
+        <v>359</v>
+      </c>
       <c r="V53" s="1"/>
       <c r="W53" s="1"/>
     </row>
@@ -5977,21 +6169,21 @@
       <c r="A54" s="10">
         <v>51</v>
       </c>
-      <c r="B54" s="123"/>
-      <c r="C54" s="75" t="s">
+      <c r="B54" s="108"/>
+      <c r="C54" s="69" t="s">
+        <v>262</v>
+      </c>
+      <c r="D54" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E54" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="F54" s="12" t="s">
         <v>263</v>
       </c>
-      <c r="D54" s="76" t="s">
-        <v>28</v>
-      </c>
-      <c r="E54" s="12" t="s">
-        <v>338</v>
-      </c>
-      <c r="F54" s="12" t="s">
-        <v>264</v>
-      </c>
-      <c r="G54" s="45" t="s">
-        <v>283</v>
+      <c r="G54" s="44" t="s">
+        <v>282</v>
       </c>
       <c r="H54" s="12" t="s">
         <v>40</v>
@@ -5999,7 +6191,7 @@
       <c r="I54" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J54" s="45">
+      <c r="J54" s="44">
         <v>1</v>
       </c>
       <c r="K54" s="13">
@@ -6014,7 +6206,7 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N54" s="106" t="s">
+      <c r="N54" s="86" t="s">
         <v>20</v>
       </c>
       <c r="O54" s="20">
@@ -6031,14 +6223,14 @@
         <f t="shared" si="4"/>
         <v>14.12</v>
       </c>
-      <c r="S54" s="59">
+      <c r="S54" s="55">
         <v>0.21029999999999999</v>
       </c>
       <c r="T54" s="21">
         <f t="shared" si="5"/>
         <v>21.029999999999998</v>
       </c>
-      <c r="U54" s="80"/>
+      <c r="U54" s="72"/>
       <c r="V54" s="1"/>
       <c r="W54" s="1"/>
     </row>
@@ -6046,27 +6238,29 @@
       <c r="A55" s="10">
         <v>52</v>
       </c>
-      <c r="B55" s="123"/>
-      <c r="C55" s="75" t="s">
+      <c r="B55" s="108"/>
+      <c r="C55" s="69" t="s">
+        <v>264</v>
+      </c>
+      <c r="D55" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="E55" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="F55" s="12" t="s">
         <v>265</v>
       </c>
-      <c r="D55" s="76" t="s">
-        <v>29</v>
-      </c>
-      <c r="E55" s="12" t="s">
-        <v>342</v>
-      </c>
-      <c r="F55" s="12" t="s">
-        <v>266</v>
-      </c>
-      <c r="G55" s="45" t="s">
-        <v>284</v>
-      </c>
-      <c r="H55" s="96"/>
+      <c r="G55" s="44" t="s">
+        <v>283</v>
+      </c>
+      <c r="H55" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="I55" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J55" s="45">
+      <c r="J55" s="44">
         <v>1</v>
       </c>
       <c r="K55" s="13">
@@ -6081,23 +6275,33 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N55" s="26"/>
-      <c r="O55" s="20"/>
+      <c r="N55" s="86" t="s">
+        <v>20</v>
+      </c>
+      <c r="O55" s="20">
+        <v>4.2300000000000004</v>
+      </c>
       <c r="P55" s="21">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q55" s="20"/>
+        <v>21.150000000000002</v>
+      </c>
+      <c r="Q55" s="20">
+        <v>3.8412000000000002</v>
+      </c>
       <c r="R55" s="21">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S55" s="59"/>
+        <v>192.06</v>
+      </c>
+      <c r="S55" s="55">
+        <v>3.8250000000000002</v>
+      </c>
       <c r="T55" s="21">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="U55" s="80"/>
+        <v>382.5</v>
+      </c>
+      <c r="U55" s="113" t="s">
+        <v>359</v>
+      </c>
       <c r="V55" s="1"/>
       <c r="W55" s="1"/>
     </row>
@@ -6105,20 +6309,20 @@
       <c r="A56" s="10">
         <v>53</v>
       </c>
-      <c r="B56" s="123"/>
-      <c r="C56" s="75" t="s">
-        <v>267</v>
-      </c>
-      <c r="D56" s="76" t="s">
+      <c r="B56" s="108"/>
+      <c r="C56" s="69" t="s">
+        <v>266</v>
+      </c>
+      <c r="D56" s="12" t="s">
         <v>30</v>
       </c>
       <c r="E56" s="12" t="s">
         <v>45</v>
       </c>
       <c r="F56" s="12" t="s">
-        <v>268</v>
-      </c>
-      <c r="G56" s="45" t="s">
+        <v>267</v>
+      </c>
+      <c r="G56" s="44" t="s">
         <v>44</v>
       </c>
       <c r="H56" s="12" t="s">
@@ -6127,7 +6331,7 @@
       <c r="I56" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J56" s="45">
+      <c r="J56" s="44">
         <v>1</v>
       </c>
       <c r="K56" s="13">
@@ -6142,8 +6346,8 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N56" s="106" t="s">
-        <v>332</v>
+      <c r="N56" s="86" t="s">
+        <v>330</v>
       </c>
       <c r="O56" s="20">
         <v>1.3006</v>
@@ -6159,14 +6363,14 @@
         <f t="shared" si="4"/>
         <v>54.244999999999997</v>
       </c>
-      <c r="S56" s="59">
+      <c r="S56" s="55">
         <v>0.82869999999999999</v>
       </c>
       <c r="T56" s="21">
         <f t="shared" si="5"/>
         <v>82.87</v>
       </c>
-      <c r="U56" s="80"/>
+      <c r="U56" s="72"/>
       <c r="V56" s="1"/>
       <c r="W56" s="1"/>
     </row>
@@ -6174,27 +6378,29 @@
       <c r="A57" s="10">
         <v>54</v>
       </c>
-      <c r="B57" s="123"/>
-      <c r="C57" s="75" t="s">
+      <c r="B57" s="108"/>
+      <c r="C57" s="69" t="s">
+        <v>268</v>
+      </c>
+      <c r="D57" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="E57" s="12" t="s">
         <v>269</v>
       </c>
-      <c r="D57" s="76" t="s">
-        <v>31</v>
-      </c>
-      <c r="E57" s="12" t="s">
+      <c r="F57" s="12" t="s">
         <v>270</v>
       </c>
-      <c r="F57" s="12" t="s">
-        <v>271</v>
-      </c>
-      <c r="G57" s="45" t="s">
+      <c r="G57" s="44" t="s">
         <v>44</v>
       </c>
-      <c r="H57" s="96"/>
+      <c r="H57" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="I57" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J57" s="45">
+      <c r="J57" s="44">
         <v>1</v>
       </c>
       <c r="K57" s="13">
@@ -6209,23 +6415,33 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N57" s="26"/>
-      <c r="O57" s="20"/>
+      <c r="N57" s="86" t="s">
+        <v>20</v>
+      </c>
+      <c r="O57" s="20">
+        <v>2.4</v>
+      </c>
       <c r="P57" s="21">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q57" s="20"/>
+        <v>12</v>
+      </c>
+      <c r="Q57" s="20">
+        <v>2.0352000000000001</v>
+      </c>
       <c r="R57" s="21">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S57" s="59"/>
+        <v>101.76</v>
+      </c>
+      <c r="S57" s="55">
+        <v>1.734</v>
+      </c>
       <c r="T57" s="21">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="U57" s="80"/>
+        <v>173.4</v>
+      </c>
+      <c r="U57" s="113" t="s">
+        <v>359</v>
+      </c>
       <c r="V57" s="1"/>
       <c r="W57" s="1"/>
     </row>
@@ -6233,27 +6449,29 @@
       <c r="A58" s="10">
         <v>55</v>
       </c>
-      <c r="B58" s="123"/>
-      <c r="C58" s="75" t="s">
+      <c r="B58" s="108"/>
+      <c r="C58" s="69" t="s">
+        <v>271</v>
+      </c>
+      <c r="D58" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E58" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="F58" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="D58" s="76" t="s">
-        <v>32</v>
-      </c>
-      <c r="E58" s="12" t="s">
-        <v>338</v>
-      </c>
-      <c r="F58" s="12" t="s">
-        <v>273</v>
-      </c>
-      <c r="G58" s="45" t="s">
-        <v>284</v>
-      </c>
-      <c r="H58" s="96"/>
+      <c r="G58" s="44" t="s">
+        <v>283</v>
+      </c>
+      <c r="H58" s="12" t="s">
+        <v>40</v>
+      </c>
       <c r="I58" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J58" s="45">
+      <c r="J58" s="44">
         <v>1</v>
       </c>
       <c r="K58" s="13">
@@ -6268,23 +6486,33 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N58" s="26"/>
-      <c r="O58" s="20"/>
+      <c r="N58" s="86" t="s">
+        <v>20</v>
+      </c>
+      <c r="O58" s="20">
+        <v>0.86</v>
+      </c>
       <c r="P58" s="21">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q58" s="20"/>
+        <v>4.3</v>
+      </c>
+      <c r="Q58" s="20">
+        <v>0.86</v>
+      </c>
       <c r="R58" s="21">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S58" s="59"/>
+        <v>43</v>
+      </c>
+      <c r="S58" s="55">
+        <v>0.86</v>
+      </c>
       <c r="T58" s="21">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="U58" s="80"/>
+        <v>86</v>
+      </c>
+      <c r="U58" s="113" t="s">
+        <v>359</v>
+      </c>
       <c r="V58" s="1"/>
       <c r="W58" s="1"/>
     </row>
@@ -6292,20 +6520,20 @@
       <c r="A59" s="10">
         <v>56</v>
       </c>
-      <c r="B59" s="123"/>
-      <c r="C59" s="75" t="s">
+      <c r="B59" s="108"/>
+      <c r="C59" s="69" t="s">
+        <v>273</v>
+      </c>
+      <c r="D59" s="12" t="s">
         <v>274</v>
       </c>
-      <c r="D59" s="76" t="s">
+      <c r="E59" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="F59" s="12" t="s">
         <v>275</v>
       </c>
-      <c r="E59" s="12" t="s">
-        <v>338</v>
-      </c>
-      <c r="F59" s="12" t="s">
-        <v>276</v>
-      </c>
-      <c r="G59" s="45" t="s">
+      <c r="G59" s="44" t="s">
         <v>44</v>
       </c>
       <c r="H59" s="12" t="s">
@@ -6314,7 +6542,7 @@
       <c r="I59" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J59" s="45">
+      <c r="J59" s="44">
         <v>1</v>
       </c>
       <c r="K59" s="13">
@@ -6329,7 +6557,7 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N59" s="106" t="s">
+      <c r="N59" s="86" t="s">
         <v>20</v>
       </c>
       <c r="O59" s="20">
@@ -6346,14 +6574,14 @@
         <f t="shared" si="4"/>
         <v>170.4</v>
       </c>
-      <c r="S59" s="59">
+      <c r="S59" s="55">
         <v>2.9537</v>
       </c>
       <c r="T59" s="21">
         <f t="shared" si="5"/>
         <v>295.37</v>
       </c>
-      <c r="U59" s="80"/>
+      <c r="U59" s="72"/>
       <c r="V59" s="1"/>
       <c r="W59" s="1"/>
     </row>
@@ -6361,29 +6589,29 @@
       <c r="A60" s="10">
         <v>57</v>
       </c>
-      <c r="B60" s="124"/>
-      <c r="C60" s="81" t="s">
+      <c r="B60" s="109"/>
+      <c r="C60" s="73" t="s">
+        <v>276</v>
+      </c>
+      <c r="D60" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="D60" s="82" t="s">
+      <c r="E60" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="E60" s="6" t="s">
+      <c r="F60" s="28" t="s">
         <v>279</v>
       </c>
-      <c r="F60" s="28" t="s">
-        <v>280</v>
-      </c>
-      <c r="G60" s="83" t="s">
-        <v>285</v>
-      </c>
-      <c r="H60" s="83" t="s">
-        <v>339</v>
+      <c r="G60" s="74" t="s">
+        <v>284</v>
+      </c>
+      <c r="H60" s="74" t="s">
+        <v>337</v>
       </c>
       <c r="I60" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="J60" s="83">
+      <c r="J60" s="74">
         <v>1</v>
       </c>
       <c r="K60" s="16">
@@ -6398,7 +6626,7 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N60" s="107" t="s">
+      <c r="N60" s="87" t="s">
         <v>20</v>
       </c>
       <c r="O60" s="34">
@@ -6415,14 +6643,14 @@
         <f t="shared" si="4"/>
         <v>48.980000000000004</v>
       </c>
-      <c r="S60" s="61">
+      <c r="S60" s="57">
         <v>0.80449999999999999</v>
       </c>
       <c r="T60" s="35">
         <f t="shared" si="5"/>
         <v>80.45</v>
       </c>
-      <c r="U60" s="84"/>
+      <c r="U60" s="75"/>
       <c r="V60" s="1"/>
       <c r="W60" s="1"/>
     </row>
@@ -6430,27 +6658,31 @@
       <c r="A61" s="10">
         <v>58</v>
       </c>
-      <c r="B61" s="122" t="s">
+      <c r="B61" s="107" t="s">
         <v>19</v>
       </c>
       <c r="C61" s="30" t="s">
-        <v>286</v>
-      </c>
-      <c r="D61" s="72" t="s">
+        <v>285</v>
+      </c>
+      <c r="D61" s="7" t="s">
         <v>34</v>
       </c>
       <c r="E61" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="F61" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="G61" s="73"/>
-      <c r="H61" s="102"/>
+      <c r="F61" s="42" t="s">
+        <v>286</v>
+      </c>
+      <c r="G61" s="67" t="s">
+        <v>41</v>
+      </c>
+      <c r="H61" s="117" t="s">
+        <v>360</v>
+      </c>
       <c r="I61" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="J61" s="73">
+      <c r="J61" s="67">
         <v>1</v>
       </c>
       <c r="K61" s="8">
@@ -6465,49 +6697,61 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N61" s="39"/>
-      <c r="O61" s="32"/>
+      <c r="N61" s="131" t="s">
+        <v>20</v>
+      </c>
+      <c r="O61" s="32">
+        <v>0.73</v>
+      </c>
       <c r="P61" s="33">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q61" s="32"/>
+        <v>3.65</v>
+      </c>
+      <c r="Q61" s="32">
+        <v>0.73</v>
+      </c>
       <c r="R61" s="33">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S61" s="58"/>
+        <v>36.5</v>
+      </c>
+      <c r="S61" s="54">
+        <v>0.73</v>
+      </c>
       <c r="T61" s="33">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="U61" s="91"/>
+        <v>73</v>
+      </c>
+      <c r="U61" s="129" t="s">
+        <v>356</v>
+      </c>
     </row>
     <row r="62" spans="1:23" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="10">
         <v>59</v>
       </c>
-      <c r="B62" s="123"/>
+      <c r="B62" s="108"/>
       <c r="C62" s="23" t="s">
-        <v>288</v>
-      </c>
-      <c r="D62" s="76" t="s">
+        <v>287</v>
+      </c>
+      <c r="D62" s="12" t="s">
         <v>35</v>
       </c>
       <c r="E62" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="F62" s="12" t="s">
-        <v>289</v>
-      </c>
-      <c r="G62" s="45" t="s">
+      <c r="F62" s="24" t="s">
+        <v>288</v>
+      </c>
+      <c r="G62" s="44" t="s">
         <v>161</v>
       </c>
-      <c r="H62" s="96"/>
+      <c r="H62" s="12" t="s">
+        <v>361</v>
+      </c>
       <c r="I62" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J62" s="45">
+      <c r="J62" s="44">
         <v>1</v>
       </c>
       <c r="K62" s="13">
@@ -6522,49 +6766,59 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N62" s="26"/>
-      <c r="O62" s="20"/>
+      <c r="N62" s="110" t="s">
+        <v>20</v>
+      </c>
+      <c r="O62" s="20">
+        <v>1.01</v>
+      </c>
       <c r="P62" s="21">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q62" s="20"/>
+        <v>5.05</v>
+      </c>
+      <c r="Q62" s="20">
+        <v>0.79800000000000004</v>
+      </c>
       <c r="R62" s="21">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S62" s="59"/>
+        <v>39.900000000000006</v>
+      </c>
+      <c r="S62" s="55">
+        <v>0.76339999999999997</v>
+      </c>
       <c r="T62" s="21">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="U62" s="80"/>
+        <v>76.34</v>
+      </c>
+      <c r="U62" s="111"/>
     </row>
-    <row r="63" spans="1:23" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="10">
+    <row r="63" spans="1:23" s="18" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="17">
         <v>60</v>
       </c>
-      <c r="B63" s="123"/>
+      <c r="B63" s="108"/>
       <c r="C63" s="23" t="s">
+        <v>289</v>
+      </c>
+      <c r="D63" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E63" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="F63" s="112" t="s">
         <v>290</v>
       </c>
-      <c r="D63" s="76" t="s">
-        <v>36</v>
-      </c>
-      <c r="E63" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="F63" s="12" t="s">
-        <v>291</v>
-      </c>
       <c r="G63" s="13" t="s">
-        <v>315</v>
-      </c>
-      <c r="H63" s="96"/>
-      <c r="I63" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="H63" s="44" t="s">
+        <v>362</v>
+      </c>
+      <c r="I63" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="J63" s="45">
+      <c r="J63" s="13">
         <v>1</v>
       </c>
       <c r="K63" s="13">
@@ -6579,43 +6833,53 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N63" s="26"/>
-      <c r="O63" s="20"/>
+      <c r="N63" s="143" t="s">
+        <v>20</v>
+      </c>
+      <c r="O63" s="21">
+        <v>0.35</v>
+      </c>
       <c r="P63" s="21">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q63" s="20"/>
+        <v>1.75</v>
+      </c>
+      <c r="Q63" s="21">
+        <v>0.24099999999999999</v>
+      </c>
       <c r="R63" s="21">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S63" s="59"/>
+        <v>12.049999999999999</v>
+      </c>
+      <c r="S63" s="55">
+        <v>0.23150000000000001</v>
+      </c>
       <c r="T63" s="21">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="U63" s="80"/>
+        <v>23.150000000000002</v>
+      </c>
+      <c r="U63" s="111" t="s">
+        <v>356</v>
+      </c>
     </row>
     <row r="64" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="10">
         <v>61</v>
       </c>
-      <c r="B64" s="123"/>
-      <c r="C64" s="75" t="s">
-        <v>292</v>
-      </c>
-      <c r="D64" s="76" t="s">
+      <c r="B64" s="108"/>
+      <c r="C64" s="69" t="s">
+        <v>291</v>
+      </c>
+      <c r="D64" s="12" t="s">
         <v>37</v>
       </c>
       <c r="E64" s="12" t="s">
         <v>41</v>
       </c>
       <c r="F64" s="12" t="s">
-        <v>293</v>
-      </c>
-      <c r="G64" s="45" t="s">
-        <v>316</v>
+        <v>292</v>
+      </c>
+      <c r="G64" s="44" t="s">
+        <v>314</v>
       </c>
       <c r="H64" s="12" t="s">
         <v>40</v>
@@ -6623,7 +6887,7 @@
       <c r="I64" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J64" s="45">
+      <c r="J64" s="44">
         <v>1</v>
       </c>
       <c r="K64" s="13">
@@ -6638,7 +6902,7 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N64" s="106" t="s">
+      <c r="N64" s="86" t="s">
         <v>20</v>
       </c>
       <c r="O64" s="20">
@@ -6655,97 +6919,106 @@
         <f t="shared" si="4"/>
         <v>40.75</v>
       </c>
-      <c r="S64" s="59">
+      <c r="S64" s="55">
         <v>0.73180000000000001</v>
       </c>
       <c r="T64" s="21">
         <f t="shared" si="5"/>
         <v>73.180000000000007</v>
       </c>
-      <c r="U64" s="80"/>
+      <c r="U64" s="72"/>
     </row>
     <row r="65" spans="1:21" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="10">
         <v>62</v>
       </c>
-      <c r="B65" s="123"/>
-      <c r="C65" s="75" t="s">
+      <c r="B65" s="108"/>
+      <c r="C65" s="118" t="s">
+        <v>293</v>
+      </c>
+      <c r="D65" s="24" t="s">
         <v>294</v>
       </c>
-      <c r="D65" s="76" t="s">
+      <c r="E65" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="F65" s="24" t="s">
         <v>295</v>
       </c>
-      <c r="E65" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="F65" s="12" t="s">
-        <v>296</v>
-      </c>
-      <c r="G65" s="45" t="s">
-        <v>317</v>
-      </c>
-      <c r="H65" s="96"/>
-      <c r="I65" s="12" t="s">
+      <c r="G65" s="119" t="s">
+        <v>315</v>
+      </c>
+      <c r="H65" s="124"/>
+      <c r="I65" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="J65" s="45">
+      <c r="J65" s="119">
         <v>1</v>
       </c>
-      <c r="K65" s="13">
+      <c r="K65" s="125">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L65" s="13">
+      <c r="L65" s="125">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="M65" s="13">
+      <c r="M65" s="125">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N65" s="26"/>
-      <c r="O65" s="20"/>
-      <c r="P65" s="21">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q65" s="20"/>
-      <c r="R65" s="21">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S65" s="59"/>
-      <c r="T65" s="21">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="U65" s="80"/>
+      <c r="N65" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="O65" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="P65" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q65" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="R65" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="S65" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="T65" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="U65" s="111" t="s">
+        <v>368</v>
+      </c>
     </row>
     <row r="66" spans="1:21" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="10">
         <v>63</v>
       </c>
-      <c r="B66" s="123"/>
-      <c r="C66" s="75" t="s">
+      <c r="B66" s="108"/>
+      <c r="C66" s="69" t="s">
+        <v>296</v>
+      </c>
+      <c r="D66" s="12" t="s">
         <v>297</v>
-      </c>
-      <c r="D66" s="76" t="s">
-        <v>298</v>
       </c>
       <c r="E66" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="F66" s="12" t="s">
-        <v>299</v>
-      </c>
-      <c r="G66" s="45" t="s">
-        <v>318</v>
-      </c>
-      <c r="H66" s="96"/>
+      <c r="F66" s="24" t="s">
+        <v>298</v>
+      </c>
+      <c r="G66" s="44" t="s">
+        <v>316</v>
+      </c>
+      <c r="H66" s="44" t="s">
+        <v>364</v>
+      </c>
       <c r="I66" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J66" s="45">
+      <c r="J66" s="44">
         <v>1</v>
       </c>
       <c r="K66" s="13">
@@ -6760,49 +7033,61 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N66" s="26"/>
-      <c r="O66" s="20"/>
+      <c r="N66" s="86" t="s">
+        <v>20</v>
+      </c>
+      <c r="O66" s="20">
+        <v>0.45</v>
+      </c>
       <c r="P66" s="21">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q66" s="20"/>
+        <v>2.25</v>
+      </c>
+      <c r="Q66" s="20">
+        <v>0.45</v>
+      </c>
       <c r="R66" s="21">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S66" s="59"/>
+        <v>22.5</v>
+      </c>
+      <c r="S66" s="55">
+        <v>0.4</v>
+      </c>
       <c r="T66" s="21">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="U66" s="80"/>
+        <v>40</v>
+      </c>
+      <c r="U66" s="111" t="s">
+        <v>356</v>
+      </c>
     </row>
     <row r="67" spans="1:21" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="10">
         <v>64</v>
       </c>
-      <c r="B67" s="123"/>
-      <c r="C67" s="75" t="s">
+      <c r="B67" s="108"/>
+      <c r="C67" s="69" t="s">
+        <v>299</v>
+      </c>
+      <c r="D67" s="12" t="s">
         <v>300</v>
-      </c>
-      <c r="D67" s="76" t="s">
-        <v>301</v>
       </c>
       <c r="E67" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="F67" s="12" t="s">
-        <v>302</v>
-      </c>
-      <c r="G67" s="45" t="s">
-        <v>319</v>
-      </c>
-      <c r="H67" s="96"/>
+      <c r="F67" s="24" t="s">
+        <v>301</v>
+      </c>
+      <c r="G67" s="44" t="s">
+        <v>317</v>
+      </c>
+      <c r="H67" s="44">
+        <v>1715260000</v>
+      </c>
       <c r="I67" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J67" s="45">
+      <c r="J67" s="44">
         <v>1</v>
       </c>
       <c r="K67" s="13">
@@ -6817,49 +7102,61 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N67" s="26"/>
-      <c r="O67" s="20"/>
+      <c r="N67" s="86" t="s">
+        <v>20</v>
+      </c>
+      <c r="O67" s="20">
+        <v>2.13</v>
+      </c>
       <c r="P67" s="21">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q67" s="20"/>
+        <v>10.649999999999999</v>
+      </c>
+      <c r="Q67" s="20">
+        <v>1.3431999999999999</v>
+      </c>
       <c r="R67" s="21">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S67" s="59"/>
+        <v>67.16</v>
+      </c>
+      <c r="S67" s="55">
+        <v>1.3104</v>
+      </c>
       <c r="T67" s="21">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="U67" s="80"/>
+        <v>131.04</v>
+      </c>
+      <c r="U67" s="111" t="s">
+        <v>356</v>
+      </c>
     </row>
     <row r="68" spans="1:21" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="10">
         <v>65</v>
       </c>
-      <c r="B68" s="123"/>
-      <c r="C68" s="75" t="s">
-        <v>300</v>
-      </c>
-      <c r="D68" s="76" t="s">
-        <v>303</v>
+      <c r="B68" s="108"/>
+      <c r="C68" s="69" t="s">
+        <v>299</v>
+      </c>
+      <c r="D68" s="12" t="s">
+        <v>302</v>
       </c>
       <c r="E68" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="F68" s="12" t="s">
-        <v>304</v>
-      </c>
-      <c r="G68" s="45" t="s">
-        <v>319</v>
-      </c>
-      <c r="H68" s="96"/>
+      <c r="F68" s="24" t="s">
+        <v>303</v>
+      </c>
+      <c r="G68" s="44" t="s">
+        <v>317</v>
+      </c>
+      <c r="H68" s="44">
+        <v>1711725</v>
+      </c>
       <c r="I68" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J68" s="45">
+      <c r="J68" s="44">
         <v>2</v>
       </c>
       <c r="K68" s="13">
@@ -6874,163 +7171,193 @@
         <f t="shared" ref="M68:M72" si="8">J68*100</f>
         <v>200</v>
       </c>
-      <c r="N68" s="26"/>
-      <c r="O68" s="20"/>
+      <c r="N68" s="86" t="s">
+        <v>20</v>
+      </c>
+      <c r="O68" s="20">
+        <v>2.1120000000000001</v>
+      </c>
       <c r="P68" s="21">
         <f t="shared" ref="P68:P72" si="9">O68*K68</f>
-        <v>0</v>
-      </c>
-      <c r="Q68" s="20"/>
+        <v>21.12</v>
+      </c>
+      <c r="Q68" s="20">
+        <v>1.92</v>
+      </c>
       <c r="R68" s="21">
         <f t="shared" ref="R68:R72" si="10">Q68*L68</f>
-        <v>0</v>
-      </c>
-      <c r="S68" s="59"/>
+        <v>192</v>
+      </c>
+      <c r="S68" s="55">
+        <v>1.92</v>
+      </c>
       <c r="T68" s="21">
         <f t="shared" ref="T68:T72" si="11">S68*M68</f>
-        <v>0</v>
-      </c>
-      <c r="U68" s="80"/>
+        <v>384</v>
+      </c>
+      <c r="U68" s="111" t="s">
+        <v>356</v>
+      </c>
     </row>
     <row r="69" spans="1:21" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="10">
         <v>66</v>
       </c>
-      <c r="B69" s="123"/>
-      <c r="C69" s="75" t="s">
+      <c r="B69" s="108"/>
+      <c r="C69" s="118" t="s">
+        <v>304</v>
+      </c>
+      <c r="D69" s="24" t="s">
         <v>305</v>
       </c>
-      <c r="D69" s="76" t="s">
+      <c r="E69" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="F69" s="24" t="s">
         <v>306</v>
       </c>
-      <c r="E69" s="12" t="s">
+      <c r="G69" s="119" t="s">
         <v>41</v>
       </c>
-      <c r="F69" s="12" t="s">
-        <v>307</v>
-      </c>
-      <c r="G69" s="45" t="s">
-        <v>41</v>
-      </c>
-      <c r="H69" s="96"/>
-      <c r="I69" s="12" t="s">
+      <c r="H69" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="I69" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="J69" s="45">
+      <c r="J69" s="119">
         <v>1</v>
       </c>
-      <c r="K69" s="13">
+      <c r="K69" s="125">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="L69" s="13">
+      <c r="L69" s="125">
         <f t="shared" si="7"/>
         <v>50</v>
       </c>
-      <c r="M69" s="13">
+      <c r="M69" s="125">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="N69" s="26"/>
-      <c r="O69" s="20"/>
-      <c r="P69" s="21">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="Q69" s="20"/>
-      <c r="R69" s="21">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="S69" s="59"/>
-      <c r="T69" s="21">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="U69" s="80"/>
+      <c r="N69" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="O69" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="P69" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q69" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="R69" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="S69" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="T69" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="U69" s="111" t="s">
+        <v>368</v>
+      </c>
     </row>
     <row r="70" spans="1:21" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="10">
         <v>67</v>
       </c>
-      <c r="B70" s="123"/>
-      <c r="C70" s="75" t="s">
+      <c r="B70" s="108"/>
+      <c r="C70" s="118" t="s">
+        <v>307</v>
+      </c>
+      <c r="D70" s="24" t="s">
         <v>308</v>
       </c>
-      <c r="D70" s="76" t="s">
+      <c r="E70" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="F70" s="24" t="s">
         <v>309</v>
       </c>
-      <c r="E70" s="12" t="s">
+      <c r="G70" s="119" t="s">
         <v>41</v>
       </c>
-      <c r="F70" s="12" t="s">
-        <v>310</v>
-      </c>
-      <c r="G70" s="45" t="s">
-        <v>41</v>
-      </c>
-      <c r="H70" s="96"/>
-      <c r="I70" s="12" t="s">
+      <c r="H70" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="I70" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="J70" s="45">
+      <c r="J70" s="119">
         <v>6</v>
       </c>
-      <c r="K70" s="13">
+      <c r="K70" s="125">
         <f t="shared" si="6"/>
         <v>30</v>
       </c>
-      <c r="L70" s="13">
+      <c r="L70" s="125">
         <f t="shared" si="7"/>
         <v>300</v>
       </c>
-      <c r="M70" s="13">
+      <c r="M70" s="125">
         <f t="shared" si="8"/>
         <v>600</v>
       </c>
-      <c r="N70" s="26"/>
-      <c r="O70" s="20"/>
-      <c r="P70" s="21">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="Q70" s="20"/>
-      <c r="R70" s="21">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="S70" s="59"/>
-      <c r="T70" s="21">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="U70" s="80"/>
+      <c r="N70" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="O70" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="P70" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q70" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="R70" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="S70" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="T70" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="U70" s="111" t="s">
+        <v>368</v>
+      </c>
     </row>
     <row r="71" spans="1:21" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="10">
         <v>68</v>
       </c>
-      <c r="B71" s="123"/>
-      <c r="C71" s="75" t="s">
+      <c r="B71" s="108"/>
+      <c r="C71" s="69" t="s">
+        <v>310</v>
+      </c>
+      <c r="D71" s="12" t="s">
         <v>311</v>
-      </c>
-      <c r="D71" s="76" t="s">
-        <v>312</v>
       </c>
       <c r="E71" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="F71" s="12" t="s">
-        <v>313</v>
-      </c>
-      <c r="G71" s="45" t="s">
+      <c r="F71" s="24" t="s">
+        <v>312</v>
+      </c>
+      <c r="G71" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="H71" s="96"/>
+      <c r="H71" s="44" t="s">
+        <v>367</v>
+      </c>
       <c r="I71" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J71" s="45">
+      <c r="J71" s="44">
         <v>1</v>
       </c>
       <c r="K71" s="13">
@@ -7045,127 +7372,144 @@
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="N71" s="26"/>
-      <c r="O71" s="20"/>
+      <c r="N71" s="86" t="s">
+        <v>20</v>
+      </c>
+      <c r="O71" s="20">
+        <v>0.15</v>
+      </c>
       <c r="P71" s="21">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="Q71" s="20"/>
+        <v>0.75</v>
+      </c>
+      <c r="Q71" s="20">
+        <v>0.11799999999999999</v>
+      </c>
       <c r="R71" s="21">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="S71" s="59"/>
+        <v>5.8999999999999995</v>
+      </c>
+      <c r="S71" s="55">
+        <v>8.6800000000000002E-2</v>
+      </c>
       <c r="T71" s="21">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="U71" s="80"/>
+        <v>8.68</v>
+      </c>
+      <c r="U71" s="72"/>
     </row>
     <row r="72" spans="1:21" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="10">
         <v>69</v>
       </c>
-      <c r="B72" s="124"/>
-      <c r="C72" s="81" t="s">
+      <c r="B72" s="109"/>
+      <c r="C72" s="120" t="s">
         <v>16</v>
       </c>
-      <c r="D72" s="103" t="s">
-        <v>314</v>
-      </c>
-      <c r="E72" s="6" t="s">
+      <c r="D72" s="121" t="s">
+        <v>313</v>
+      </c>
+      <c r="E72" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="F72" s="6" t="s">
+      <c r="F72" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="G72" s="83" t="s">
+      <c r="G72" s="122" t="s">
         <v>41</v>
       </c>
-      <c r="H72" s="104"/>
-      <c r="I72" s="6" t="s">
+      <c r="H72" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="I72" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="J72" s="83">
+      <c r="J72" s="122">
         <v>10</v>
       </c>
-      <c r="K72" s="16">
+      <c r="K72" s="123">
         <f t="shared" si="6"/>
         <v>50</v>
       </c>
-      <c r="L72" s="16">
+      <c r="L72" s="123">
         <f t="shared" si="7"/>
         <v>500</v>
       </c>
-      <c r="M72" s="16">
+      <c r="M72" s="123">
         <f t="shared" si="8"/>
         <v>1000</v>
       </c>
-      <c r="N72" s="47"/>
-      <c r="O72" s="34"/>
-      <c r="P72" s="35">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="Q72" s="34"/>
-      <c r="R72" s="35">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="S72" s="61"/>
-      <c r="T72" s="35">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="U72" s="84"/>
+      <c r="N72" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="O72" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="P72" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q72" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="R72" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="S72" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="T72" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="U72" s="133" t="s">
+        <v>368</v>
+      </c>
     </row>
     <row r="73" spans="1:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="I73" s="117" t="s">
+      <c r="I73" s="102" t="s">
         <v>12</v>
       </c>
-      <c r="J73" s="117"/>
-      <c r="K73" s="117"/>
-      <c r="L73" s="117"/>
-      <c r="M73" s="117"/>
-      <c r="N73" s="117"/>
+      <c r="J73" s="102"/>
+      <c r="K73" s="102"/>
+      <c r="L73" s="102"/>
+      <c r="M73" s="102"/>
+      <c r="N73" s="102"/>
       <c r="P73" s="9">
-        <f>SUM(P3:P72)</f>
-        <v>122.3955</v>
+        <f>SUM(P1:P72)</f>
+        <v>245.6855000000001</v>
       </c>
       <c r="Q73" s="2"/>
       <c r="R73" s="9">
-        <f>SUM(R3:R24)</f>
-        <v>290.81099999999998</v>
+        <f>SUM(R1:R72)</f>
+        <v>1912.5309999999999</v>
       </c>
       <c r="S73" s="9"/>
       <c r="T73" s="9">
-        <f>SUM(T3:T72)</f>
-        <v>1499.1579999999999</v>
+        <f>SUM(T1:T72)</f>
+        <v>3436.8680000000004</v>
       </c>
     </row>
     <row r="74" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="I74" s="118" t="s">
+      <c r="I74" s="103" t="s">
         <v>13</v>
       </c>
-      <c r="J74" s="118"/>
-      <c r="K74" s="118"/>
-      <c r="L74" s="118"/>
-      <c r="M74" s="118"/>
-      <c r="N74" s="118"/>
+      <c r="J74" s="103"/>
+      <c r="K74" s="103"/>
+      <c r="L74" s="103"/>
+      <c r="M74" s="103"/>
+      <c r="N74" s="103"/>
       <c r="P74" s="4">
         <f>P73/5</f>
-        <v>24.479099999999999</v>
+        <v>49.137100000000018</v>
       </c>
       <c r="Q74" s="3"/>
       <c r="R74" s="4">
         <f>R73/50</f>
-        <v>5.8162199999999995</v>
+        <v>38.250619999999998</v>
       </c>
       <c r="S74" s="4"/>
       <c r="T74" s="4">
         <f>T73/100</f>
-        <v>14.991579999999999</v>
+        <v>34.368680000000005</v>
       </c>
     </row>
   </sheetData>
@@ -7181,7 +7525,7 @@
     <mergeCell ref="B61:B72"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
-  <conditionalFormatting sqref="P3:P72">
+  <conditionalFormatting sqref="P3:P64 P71 P66:P68">
     <cfRule type="dataBar" priority="47">
       <dataBar>
         <cfvo type="min"/>
@@ -7233,7 +7577,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R3:T72">
+  <conditionalFormatting sqref="R3:T64 R71:T71 R66:T68">
     <cfRule type="dataBar" priority="110">
       <dataBar>
         <cfvo type="min"/>
@@ -7379,7 +7723,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J52 J30">
+  <conditionalFormatting sqref="J30 J52">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -7403,7 +7747,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J51 J29">
+  <conditionalFormatting sqref="J29 J51">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
@@ -7415,7 +7759,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J55 J33">
+  <conditionalFormatting sqref="J33 J55">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
@@ -7499,7 +7843,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J68 J46">
+  <conditionalFormatting sqref="J46 J68">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -7511,7 +7855,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J68 J46">
+  <conditionalFormatting sqref="J46 J68">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -7576,9 +7920,23 @@
     <hyperlink ref="N29" r:id="rId50" xr:uid="{2AFD90F5-7189-4A7E-B7A6-AB55F8E1927F}"/>
     <hyperlink ref="N51" r:id="rId51" xr:uid="{CC580313-421C-452B-9168-C71CF9B145C8}"/>
     <hyperlink ref="N53" r:id="rId52" xr:uid="{2DE0EA7E-F5A2-4717-B312-6E9347B0E9F6}"/>
+    <hyperlink ref="N4" r:id="rId53" xr:uid="{44209F46-1B93-4F12-A4CC-E4A094978F3C}"/>
+    <hyperlink ref="N26" r:id="rId54" xr:uid="{44EA4EA8-AA27-4C9D-9863-2B16E294FC91}"/>
+    <hyperlink ref="N28" r:id="rId55" xr:uid="{2ED51590-8659-4DAC-84DC-7D7213D8CF43}"/>
+    <hyperlink ref="N52" r:id="rId56" xr:uid="{469E2288-EBAB-40EF-9F9B-CF42849950E1}"/>
+    <hyperlink ref="N55" r:id="rId57" xr:uid="{2413E98B-0791-406B-AB80-BBE245C68DDA}"/>
+    <hyperlink ref="N57" r:id="rId58" xr:uid="{4BD46842-B719-44ED-B21D-E7983C525D0E}"/>
+    <hyperlink ref="N58" r:id="rId59" xr:uid="{350C6503-BE03-4E2C-9C55-FF6C5D20AE69}"/>
+    <hyperlink ref="N61" r:id="rId60" xr:uid="{412B014F-51F9-4E5B-AC57-2B95C1EDA7A9}"/>
+    <hyperlink ref="N62" r:id="rId61" xr:uid="{D48DD52B-391E-4AB6-AAA3-DADAE7922EAC}"/>
+    <hyperlink ref="N63" r:id="rId62" xr:uid="{12DC5CF1-9576-4CA2-887F-F628E86240CE}"/>
+    <hyperlink ref="N66" r:id="rId63" xr:uid="{51C46423-15C7-4B06-94C1-84BF03991E13}"/>
+    <hyperlink ref="N67" r:id="rId64" xr:uid="{B30C34BB-74FB-4742-A49A-6DC81507E306}"/>
+    <hyperlink ref="N68" r:id="rId65" xr:uid="{E1587D9F-4670-45BE-B47C-D68A753F9EBF}"/>
+    <hyperlink ref="N71" r:id="rId66" xr:uid="{17B3BE3D-FC16-4FF8-8A71-4F20689EDB33}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId53"/>
+  <pageSetup orientation="portrait" r:id="rId67"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -7593,7 +7951,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>P3:P72</xm:sqref>
+          <xm:sqref>P3:P64 P71 P66:P68</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{00F4DBD2-6698-4ADA-B9BF-608AE474FCE0}">
@@ -7619,7 +7977,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>R3:T72</xm:sqref>
+          <xm:sqref>R3:T64 R71:T71 R66:T68</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/Deliverable/BOM/Digikey_BOM_Grant.xlsx
+++ b/Deliverable/BOM/Digikey_BOM_Grant.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GrantKros-CoopMonitor\Deliverable\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{072E0D1C-2C15-41AE-A304-46E92361F783}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{240EE8D2-F8BB-4187-9C99-7D70872CAB8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="368">
   <si>
     <t>Description</t>
   </si>
@@ -193,18 +193,9 @@
     <t>RVT1E100M0405</t>
   </si>
   <si>
-    <t>CAP CER 0.1UF 16V X7R 0402</t>
-  </si>
-  <si>
-    <t>C6, C10, C11, C12, C13, C14, C15, C18, C21, C24, C29, C30, CF2</t>
-  </si>
-  <si>
     <t>Cap 0402</t>
   </si>
   <si>
-    <t>CC0402KRX7R7BB104</t>
-  </si>
-  <si>
     <t>CAP CER 22UF 25V X5R 0805</t>
   </si>
   <si>
@@ -257,12 +248,6 @@
   </si>
   <si>
     <t>CGA3E2X7R2A223K080AA</t>
-  </si>
-  <si>
-    <t>C22, C25, C27, C35</t>
-  </si>
-  <si>
-    <t>CL10B104KB8NNNC</t>
   </si>
   <si>
     <t>CAP TANT 4.7UF 10% 35V 1411</t>
@@ -1100,10 +1085,6 @@
     <t>Bill of Material (BOM) for Grant</t>
   </si>
   <si>
-    <t xml:space="preserve">CAP CER 0.1UF 50V X7R 0603
-</t>
-  </si>
-  <si>
     <t xml:space="preserve">VLMS1500-GS08
 </t>
   </si>
@@ -1157,6 +1138,24 @@
   </si>
   <si>
     <t xml:space="preserve">Do NOT Mount </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAP CER 0.1UF 50V X7R 0402
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1005X7R1H104K050BB
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+TDK Corporation</t>
+  </si>
+  <si>
+    <t>Ye part change kia ha voltage rating ki waja se design me 16V ka part use ho raha ha or 'C22, C25, C27, C35 ye designator merge kiye han humne iska footprint 0603 ha ye design me b change krne han hume</t>
+  </si>
+  <si>
+    <t>C6, C10, C11, C12, C13, C14, C15, C18, C21, C24, C29, C30, CF2,C22, C25, C27, C35</t>
   </si>
 </sst>
 </file>
@@ -1167,7 +1166,7 @@
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1222,15 +1221,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <strike/>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <strike/>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
@@ -1815,7 +1805,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="144">
+  <cellXfs count="142">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1914,7 +1904,7 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1950,10 +1940,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1962,10 +1952,7 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2010,14 +1997,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2054,34 +2038,31 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2093,58 +2074,25 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2174,22 +2122,22 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2208,16 +2156,52 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2501,13 +2485,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W74"/>
+  <dimension ref="A1:W73"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.42578125" customWidth="1"/>
     <col min="3" max="3" width="39.42578125" style="14" customWidth="1"/>
-    <col min="4" max="4" width="32.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.7109375" style="5" customWidth="1"/>
     <col min="5" max="5" width="18.5703125" style="5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="25.85546875" style="5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="24.7109375" style="5" bestFit="1" customWidth="1"/>
@@ -2527,29 +2511,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="99" t="s">
-        <v>351</v>
-      </c>
-      <c r="B1" s="100"/>
-      <c r="C1" s="100"/>
-      <c r="D1" s="100"/>
-      <c r="E1" s="100"/>
-      <c r="F1" s="100"/>
-      <c r="G1" s="100"/>
-      <c r="H1" s="100"/>
-      <c r="I1" s="100"/>
-      <c r="J1" s="100"/>
-      <c r="K1" s="100"/>
-      <c r="L1" s="100"/>
-      <c r="M1" s="100"/>
-      <c r="N1" s="100"/>
-      <c r="O1" s="100"/>
-      <c r="P1" s="100"/>
-      <c r="Q1" s="100"/>
-      <c r="R1" s="100"/>
-      <c r="S1" s="100"/>
-      <c r="T1" s="100"/>
-      <c r="U1" s="101"/>
+      <c r="A1" s="130" t="s">
+        <v>346</v>
+      </c>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="131"/>
+      <c r="I1" s="131"/>
+      <c r="J1" s="131"/>
+      <c r="K1" s="131"/>
+      <c r="L1" s="131"/>
+      <c r="M1" s="131"/>
+      <c r="N1" s="131"/>
+      <c r="O1" s="131"/>
+      <c r="P1" s="131"/>
+      <c r="Q1" s="131"/>
+      <c r="R1" s="131"/>
+      <c r="S1" s="131"/>
+      <c r="T1" s="131"/>
+      <c r="U1" s="132"/>
     </row>
     <row r="2" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
@@ -2583,34 +2567,34 @@
         <v>9</v>
       </c>
       <c r="K2" s="47" t="s">
+        <v>313</v>
+      </c>
+      <c r="L2" s="47" t="s">
+        <v>314</v>
+      </c>
+      <c r="M2" s="47" t="s">
+        <v>315</v>
+      </c>
+      <c r="N2" s="58" t="s">
+        <v>14</v>
+      </c>
+      <c r="O2" s="47" t="s">
+        <v>316</v>
+      </c>
+      <c r="P2" s="47" t="s">
+        <v>317</v>
+      </c>
+      <c r="Q2" s="47" t="s">
         <v>318</v>
       </c>
-      <c r="L2" s="47" t="s">
+      <c r="R2" s="47" t="s">
         <v>319</v>
       </c>
-      <c r="M2" s="47" t="s">
+      <c r="S2" s="47" t="s">
         <v>320</v>
       </c>
-      <c r="N2" s="59" t="s">
-        <v>14</v>
-      </c>
-      <c r="O2" s="47" t="s">
+      <c r="T2" s="47" t="s">
         <v>321</v>
-      </c>
-      <c r="P2" s="47" t="s">
-        <v>322</v>
-      </c>
-      <c r="Q2" s="47" t="s">
-        <v>323</v>
-      </c>
-      <c r="R2" s="47" t="s">
-        <v>324</v>
-      </c>
-      <c r="S2" s="47" t="s">
-        <v>325</v>
-      </c>
-      <c r="T2" s="47" t="s">
-        <v>326</v>
       </c>
       <c r="U2" s="47" t="s">
         <v>10</v>
@@ -2620,10 +2604,10 @@
       <c r="A3" s="17">
         <v>1</v>
       </c>
-      <c r="B3" s="104" t="s">
+      <c r="B3" s="135" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="66" t="s">
+      <c r="C3" s="65" t="s">
         <v>47</v>
       </c>
       <c r="D3" s="7" t="s">
@@ -2635,16 +2619,16 @@
       <c r="F3" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="G3" s="67" t="s">
-        <v>98</v>
+      <c r="G3" s="66" t="s">
+        <v>93</v>
       </c>
       <c r="H3" s="31" t="s">
         <v>40</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="J3" s="67">
+        <v>104</v>
+      </c>
+      <c r="J3" s="66">
         <v>1</v>
       </c>
       <c r="K3" s="8">
@@ -2659,7 +2643,7 @@
         <f>J3*100</f>
         <v>100</v>
       </c>
-      <c r="N3" s="88" t="s">
+      <c r="N3" s="86" t="s">
         <v>20</v>
       </c>
       <c r="O3" s="52">
@@ -2676,21 +2660,21 @@
         <f>Q3*L3</f>
         <v>9.7799999999999994</v>
       </c>
-      <c r="S3" s="54">
+      <c r="S3" s="53">
         <v>0.16619999999999999</v>
       </c>
-      <c r="T3" s="58">
+      <c r="T3" s="57">
         <f>S3*M3</f>
         <v>16.619999999999997</v>
       </c>
-      <c r="U3" s="68"/>
+      <c r="U3" s="67"/>
     </row>
     <row r="4" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="10">
+      <c r="A4" s="17">
         <v>2</v>
       </c>
-      <c r="B4" s="105"/>
-      <c r="C4" s="69" t="s">
+      <c r="B4" s="136"/>
+      <c r="C4" s="68" t="s">
         <v>50</v>
       </c>
       <c r="D4" s="12" t="s">
@@ -2703,76 +2687,76 @@
         <v>52</v>
       </c>
       <c r="G4" s="44" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="J4" s="44">
         <v>1</v>
       </c>
       <c r="K4" s="13">
-        <f t="shared" ref="K4:K67" si="0">J4*5</f>
+        <f t="shared" ref="K4:K66" si="0">J4*5</f>
         <v>5</v>
       </c>
       <c r="L4" s="13">
-        <f t="shared" ref="L4:L67" si="1">J4*50</f>
+        <f t="shared" ref="L4:L66" si="1">J4*50</f>
         <v>50</v>
       </c>
       <c r="M4" s="13">
-        <f t="shared" ref="M4:M67" si="2">J4*100</f>
+        <f t="shared" ref="M4:M66" si="2">J4*100</f>
         <v>100</v>
       </c>
-      <c r="N4" s="86" t="s">
+      <c r="N4" s="84" t="s">
         <v>20</v>
       </c>
       <c r="O4" s="48">
         <v>0.47</v>
       </c>
       <c r="P4" s="21">
-        <f t="shared" ref="P4:P67" si="3">O4*K4</f>
+        <f t="shared" ref="P4:P66" si="3">O4*K4</f>
         <v>2.3499999999999996</v>
       </c>
       <c r="Q4" s="48">
         <v>0.22620000000000001</v>
       </c>
       <c r="R4" s="21">
-        <f t="shared" ref="R4:R67" si="4">Q4*L4</f>
+        <f t="shared" ref="R4:R66" si="4">Q4*L4</f>
         <v>11.31</v>
       </c>
-      <c r="S4" s="55">
+      <c r="S4" s="54">
         <v>0.19389999999999999</v>
       </c>
       <c r="T4" s="21">
-        <f t="shared" ref="T4:T67" si="5">S4*M4</f>
+        <f t="shared" ref="T4:T66" si="5">S4*M4</f>
         <v>19.39</v>
       </c>
-      <c r="U4" s="111" t="s">
-        <v>356</v>
+      <c r="U4" s="97" t="s">
+        <v>350</v>
       </c>
     </row>
-    <row r="5" spans="1:23" s="22" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="10">
+    <row r="5" spans="1:23" s="22" customFormat="1" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="17">
         <v>3</v>
       </c>
-      <c r="B5" s="105"/>
-      <c r="C5" s="69" t="s">
+      <c r="B5" s="136"/>
+      <c r="C5" s="68" t="s">
+        <v>363</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>367</v>
+      </c>
+      <c r="E5" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="D5" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>55</v>
-      </c>
       <c r="F5" s="12" t="s">
-        <v>56</v>
+        <v>364</v>
       </c>
       <c r="G5" s="44" t="s">
-        <v>100</v>
+        <v>365</v>
       </c>
       <c r="H5" s="12" t="s">
         <v>40</v>
@@ -2781,21 +2765,21 @@
         <v>43</v>
       </c>
       <c r="J5" s="44">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K5" s="13">
         <f t="shared" si="0"/>
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="L5" s="13">
         <f t="shared" si="1"/>
-        <v>650</v>
+        <v>850</v>
       </c>
       <c r="M5" s="13">
         <f t="shared" si="2"/>
-        <v>1300</v>
-      </c>
-      <c r="N5" s="110" t="s">
+        <v>1700</v>
+      </c>
+      <c r="N5" s="96" t="s">
         <v>20</v>
       </c>
       <c r="O5" s="48">
@@ -2803,49 +2787,51 @@
       </c>
       <c r="P5" s="21">
         <f t="shared" si="3"/>
-        <v>1.0270000000000001</v>
+        <v>1.3430000000000002</v>
       </c>
       <c r="Q5" s="48">
         <v>9.2399999999999999E-3</v>
       </c>
       <c r="R5" s="21">
         <f t="shared" si="4"/>
-        <v>6.0060000000000002</v>
-      </c>
-      <c r="S5" s="55">
+        <v>7.8540000000000001</v>
+      </c>
+      <c r="S5" s="54">
         <v>7.26E-3</v>
       </c>
       <c r="T5" s="21">
         <f t="shared" si="5"/>
-        <v>9.4380000000000006</v>
-      </c>
-      <c r="U5" s="70"/>
+        <v>12.342000000000001</v>
+      </c>
+      <c r="U5" s="141" t="s">
+        <v>366</v>
+      </c>
     </row>
     <row r="6" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="10">
+      <c r="A6" s="17">
         <v>4</v>
       </c>
-      <c r="B6" s="105"/>
-      <c r="C6" s="69" t="s">
+      <c r="B6" s="136"/>
+      <c r="C6" s="68" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="F6" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="D6" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>60</v>
-      </c>
       <c r="G6" s="44" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H6" s="12" t="s">
         <v>40</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="J6" s="44">
         <v>2</v>
@@ -2862,7 +2848,7 @@
         <f t="shared" si="2"/>
         <v>200</v>
       </c>
-      <c r="N6" s="89" t="s">
+      <c r="N6" s="87" t="s">
         <v>20</v>
       </c>
       <c r="O6" s="20">
@@ -2879,7 +2865,7 @@
         <f t="shared" si="4"/>
         <v>18.149999999999999</v>
       </c>
-      <c r="S6" s="55">
+      <c r="S6" s="54">
         <v>0.18149999999999999</v>
       </c>
       <c r="T6" s="21">
@@ -2891,30 +2877,30 @@
       <c r="W6" s="1"/>
     </row>
     <row r="7" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="10">
+      <c r="A7" s="17">
         <v>5</v>
       </c>
-      <c r="B7" s="105"/>
+      <c r="B7" s="136"/>
       <c r="C7" s="23" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E7" s="12" t="s">
         <v>41</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G7" s="44" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="H7" s="12" t="s">
         <v>40</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="J7" s="44">
         <v>2</v>
@@ -2931,7 +2917,7 @@
         <f t="shared" si="2"/>
         <v>200</v>
       </c>
-      <c r="N7" s="89" t="s">
+      <c r="N7" s="87" t="s">
         <v>20</v>
       </c>
       <c r="O7" s="20">
@@ -2948,7 +2934,7 @@
         <f t="shared" si="4"/>
         <v>24.87</v>
       </c>
-      <c r="S7" s="55">
+      <c r="S7" s="54">
         <v>0.2487</v>
       </c>
       <c r="T7" s="21">
@@ -2960,21 +2946,21 @@
       <c r="W7" s="1"/>
     </row>
     <row r="8" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="10">
+      <c r="A8" s="17">
         <v>6</v>
       </c>
-      <c r="B8" s="105"/>
-      <c r="C8" s="69" t="s">
+      <c r="B8" s="136"/>
+      <c r="C8" s="68" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="F8" s="12" t="s">
         <v>64</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>67</v>
       </c>
       <c r="G8" s="44" t="s">
         <v>22</v>
@@ -2983,7 +2969,7 @@
         <v>40</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="J8" s="44">
         <v>1</v>
@@ -3000,7 +2986,7 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N8" s="89" t="s">
+      <c r="N8" s="87" t="s">
         <v>20</v>
       </c>
       <c r="O8" s="20">
@@ -3017,7 +3003,7 @@
         <f t="shared" si="4"/>
         <v>2.1800000000000002</v>
       </c>
-      <c r="S8" s="55">
+      <c r="S8" s="54">
         <v>3.5700000000000003E-2</v>
       </c>
       <c r="T8" s="21">
@@ -3029,30 +3015,30 @@
       <c r="W8" s="1"/>
     </row>
     <row r="9" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="10">
+      <c r="A9" s="17">
         <v>7</v>
       </c>
-      <c r="B9" s="105"/>
-      <c r="C9" s="69" t="s">
+      <c r="B9" s="136"/>
+      <c r="C9" s="68" t="s">
+        <v>65</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="F9" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="D9" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="F9" s="24" t="s">
-        <v>71</v>
-      </c>
       <c r="G9" s="44" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="J9" s="44">
         <v>4</v>
@@ -3069,7 +3055,7 @@
         <f t="shared" si="2"/>
         <v>400</v>
       </c>
-      <c r="N9" s="89" t="s">
+      <c r="N9" s="87" t="s">
         <v>20</v>
       </c>
       <c r="O9" s="20">
@@ -3086,7 +3072,7 @@
         <f t="shared" si="4"/>
         <v>2.3199999999999998</v>
       </c>
-      <c r="S9" s="55">
+      <c r="S9" s="54">
         <v>1.1599999999999999E-2</v>
       </c>
       <c r="T9" s="21">
@@ -3098,30 +3084,30 @@
       <c r="W9" s="1"/>
     </row>
     <row r="10" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="10">
+      <c r="A10" s="17">
         <v>8</v>
       </c>
-      <c r="B10" s="105"/>
-      <c r="C10" s="69" t="s">
-        <v>72</v>
+      <c r="B10" s="136"/>
+      <c r="C10" s="68" t="s">
+        <v>69</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G10" s="44" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="H10" s="12" t="s">
         <v>40</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="J10" s="44">
         <v>1</v>
@@ -3138,7 +3124,7 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N10" s="89" t="s">
+      <c r="N10" s="87" t="s">
         <v>20</v>
       </c>
       <c r="O10" s="20">
@@ -3155,7 +3141,7 @@
         <f t="shared" si="4"/>
         <v>2.17</v>
       </c>
-      <c r="S10" s="55">
+      <c r="S10" s="54">
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="T10" s="21">
@@ -3166,100 +3152,100 @@
       <c r="V10" s="1"/>
       <c r="W10" s="1"/>
     </row>
-    <row r="11" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="10">
+    <row r="11" spans="1:23" s="22" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="17">
         <v>9</v>
       </c>
-      <c r="B11" s="105"/>
-      <c r="C11" s="69" t="s">
-        <v>352</v>
+      <c r="B11" s="136"/>
+      <c r="C11" s="68" t="s">
+        <v>72</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>66</v>
+        <v>323</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G11" s="44" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="H11" s="12" t="s">
         <v>40</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>43</v>
+        <v>111</v>
       </c>
       <c r="J11" s="44">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K11" s="13">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="L11" s="13">
         <f t="shared" si="1"/>
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="M11" s="13">
         <f t="shared" si="2"/>
-        <v>400</v>
-      </c>
-      <c r="N11" s="90" t="s">
-        <v>20</v>
+        <v>100</v>
+      </c>
+      <c r="N11" s="84" t="s">
+        <v>324</v>
       </c>
       <c r="O11" s="20">
-        <v>2.9000000000000001E-2</v>
+        <v>0.44</v>
       </c>
       <c r="P11" s="21">
         <f t="shared" si="3"/>
-        <v>0.58000000000000007</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="Q11" s="20">
-        <v>1.2999999999999999E-2</v>
+        <v>0.23699999999999999</v>
       </c>
       <c r="R11" s="21">
         <f t="shared" si="4"/>
-        <v>2.6</v>
+        <v>11.85</v>
       </c>
       <c r="S11" s="55">
-        <v>1.2999999999999999E-2</v>
+        <v>0.20399999999999999</v>
       </c>
       <c r="T11" s="21">
         <f t="shared" si="5"/>
-        <v>5.2</v>
-      </c>
-      <c r="U11" s="53"/>
-      <c r="V11" s="1"/>
-      <c r="W11" s="1"/>
+        <v>20.399999999999999</v>
+      </c>
+      <c r="U11" s="69"/>
+      <c r="V11" s="25"/>
+      <c r="W11" s="25"/>
     </row>
-    <row r="12" spans="1:23" s="22" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="10">
+    <row r="12" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="17">
         <v>10</v>
       </c>
-      <c r="B12" s="105"/>
-      <c r="C12" s="69" t="s">
+      <c r="B12" s="136"/>
+      <c r="C12" s="68" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="D12" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>328</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>79</v>
-      </c>
       <c r="G12" s="44" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="H12" s="12" t="s">
         <v>40</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="J12" s="44">
         <v>1</v>
@@ -3276,128 +3262,128 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N12" s="86" t="s">
-        <v>329</v>
-      </c>
-      <c r="O12" s="20">
-        <v>0.44</v>
+      <c r="N12" s="84" t="s">
+        <v>325</v>
+      </c>
+      <c r="O12" s="45">
+        <v>0.6411</v>
       </c>
       <c r="P12" s="21">
         <f t="shared" si="3"/>
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="Q12" s="20">
-        <v>0.23699999999999999</v>
+        <v>3.2054999999999998</v>
+      </c>
+      <c r="Q12" s="45">
+        <v>0.6411</v>
       </c>
       <c r="R12" s="21">
         <f t="shared" si="4"/>
-        <v>11.85</v>
-      </c>
-      <c r="S12" s="56">
-        <v>0.20399999999999999</v>
+        <v>32.055</v>
+      </c>
+      <c r="S12" s="54">
+        <v>0.6411</v>
       </c>
       <c r="T12" s="21">
         <f t="shared" si="5"/>
-        <v>20.399999999999999</v>
-      </c>
-      <c r="U12" s="71"/>
-      <c r="V12" s="25"/>
-      <c r="W12" s="25"/>
+        <v>64.11</v>
+      </c>
+      <c r="U12" s="70"/>
+      <c r="V12" s="1"/>
+      <c r="W12" s="1"/>
     </row>
     <row r="13" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="10">
+      <c r="A13" s="17">
         <v>11</v>
       </c>
-      <c r="B13" s="105"/>
-      <c r="C13" s="69" t="s">
+      <c r="B13" s="136"/>
+      <c r="C13" s="68" t="s">
+        <v>78</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="D13" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>82</v>
-      </c>
       <c r="G13" s="44" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="H13" s="12" t="s">
         <v>40</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>117</v>
+        <v>42</v>
       </c>
       <c r="J13" s="44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K13" s="13">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L13" s="13">
         <f t="shared" si="1"/>
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M13" s="13">
         <f t="shared" si="2"/>
-        <v>100</v>
-      </c>
-      <c r="N13" s="86" t="s">
-        <v>330</v>
-      </c>
-      <c r="O13" s="45">
-        <v>0.6411</v>
+        <v>200</v>
+      </c>
+      <c r="N13" s="84" t="s">
+        <v>20</v>
+      </c>
+      <c r="O13" s="20">
+        <v>0.08</v>
       </c>
       <c r="P13" s="21">
         <f t="shared" si="3"/>
-        <v>3.2054999999999998</v>
-      </c>
-      <c r="Q13" s="45">
-        <v>0.6411</v>
+        <v>0.8</v>
+      </c>
+      <c r="Q13" s="20">
+        <v>3.56E-2</v>
       </c>
       <c r="R13" s="21">
         <f t="shared" si="4"/>
-        <v>32.055</v>
-      </c>
-      <c r="S13" s="55">
-        <v>0.6411</v>
+        <v>3.56</v>
+      </c>
+      <c r="S13" s="54">
+        <v>3.56E-2</v>
       </c>
       <c r="T13" s="21">
         <f t="shared" si="5"/>
-        <v>64.11</v>
-      </c>
-      <c r="U13" s="72"/>
+        <v>7.12</v>
+      </c>
+      <c r="U13" s="70"/>
       <c r="V13" s="1"/>
       <c r="W13" s="1"/>
     </row>
     <row r="14" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="10">
+      <c r="A14" s="17">
         <v>12</v>
       </c>
-      <c r="B14" s="105"/>
-      <c r="C14" s="69" t="s">
+      <c r="B14" s="136"/>
+      <c r="C14" s="68" t="s">
+        <v>81</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="F14" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="D14" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>85</v>
-      </c>
       <c r="G14" s="44" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H14" s="12" t="s">
         <v>40</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>42</v>
+        <v>113</v>
       </c>
       <c r="J14" s="44">
         <v>2</v>
@@ -3414,59 +3400,59 @@
         <f t="shared" si="2"/>
         <v>200</v>
       </c>
-      <c r="N14" s="86" t="s">
+      <c r="N14" s="84" t="s">
         <v>20</v>
       </c>
       <c r="O14" s="20">
-        <v>0.08</v>
+        <v>0.25900000000000001</v>
       </c>
       <c r="P14" s="21">
         <f t="shared" si="3"/>
-        <v>0.8</v>
+        <v>2.59</v>
       </c>
       <c r="Q14" s="20">
-        <v>3.56E-2</v>
+        <v>0.14660000000000001</v>
       </c>
       <c r="R14" s="21">
         <f t="shared" si="4"/>
-        <v>3.56</v>
-      </c>
-      <c r="S14" s="55">
-        <v>3.56E-2</v>
+        <v>14.66</v>
+      </c>
+      <c r="S14" s="54">
+        <v>0.14660000000000001</v>
       </c>
       <c r="T14" s="21">
         <f t="shared" si="5"/>
-        <v>7.12</v>
-      </c>
-      <c r="U14" s="72"/>
+        <v>29.32</v>
+      </c>
+      <c r="U14" s="70"/>
       <c r="V14" s="1"/>
       <c r="W14" s="1"/>
     </row>
     <row r="15" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="10">
+      <c r="A15" s="17">
         <v>13</v>
       </c>
-      <c r="B15" s="105"/>
-      <c r="C15" s="69" t="s">
+      <c r="B15" s="136"/>
+      <c r="C15" s="68" t="s">
+        <v>84</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="F15" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="D15" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="E15" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="F15" s="12" t="s">
-        <v>88</v>
-      </c>
       <c r="G15" s="44" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H15" s="12" t="s">
         <v>40</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="J15" s="44">
         <v>2</v>
@@ -3483,473 +3469,477 @@
         <f t="shared" si="2"/>
         <v>200</v>
       </c>
-      <c r="N15" s="86" t="s">
+      <c r="N15" s="84" t="s">
         <v>20</v>
       </c>
       <c r="O15" s="20">
-        <v>0.25900000000000001</v>
+        <v>0.156</v>
       </c>
       <c r="P15" s="21">
         <f t="shared" si="3"/>
-        <v>2.59</v>
+        <v>1.56</v>
       </c>
       <c r="Q15" s="20">
-        <v>0.14660000000000001</v>
+        <v>7.3499999999999996E-2</v>
       </c>
       <c r="R15" s="21">
         <f t="shared" si="4"/>
-        <v>14.66</v>
-      </c>
-      <c r="S15" s="55">
-        <v>0.14660000000000001</v>
+        <v>7.35</v>
+      </c>
+      <c r="S15" s="54">
+        <v>7.3499999999999996E-2</v>
       </c>
       <c r="T15" s="21">
         <f t="shared" si="5"/>
-        <v>29.32</v>
-      </c>
-      <c r="U15" s="72"/>
+        <v>14.7</v>
+      </c>
+      <c r="U15" s="70"/>
       <c r="V15" s="1"/>
       <c r="W15" s="1"/>
     </row>
     <row r="16" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="10">
+      <c r="A16" s="17">
         <v>14</v>
       </c>
-      <c r="B16" s="105"/>
-      <c r="C16" s="69" t="s">
+      <c r="B16" s="136"/>
+      <c r="C16" s="68" t="s">
+        <v>87</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="F16" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="D16" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>91</v>
-      </c>
       <c r="G16" s="44" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="H16" s="12" t="s">
         <v>40</v>
       </c>
       <c r="I16" s="12" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="J16" s="44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K16" s="13">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L16" s="13">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M16" s="13">
         <f t="shared" si="2"/>
-        <v>200</v>
-      </c>
-      <c r="N16" s="86" t="s">
+        <v>100</v>
+      </c>
+      <c r="N16" s="84" t="s">
         <v>20</v>
       </c>
       <c r="O16" s="20">
-        <v>0.156</v>
+        <v>0.52</v>
       </c>
       <c r="P16" s="21">
         <f t="shared" si="3"/>
-        <v>1.56</v>
+        <v>2.6</v>
       </c>
       <c r="Q16" s="20">
-        <v>7.3499999999999996E-2</v>
+        <v>0.27800000000000002</v>
       </c>
       <c r="R16" s="21">
         <f t="shared" si="4"/>
-        <v>7.35</v>
-      </c>
-      <c r="S16" s="55">
-        <v>7.3499999999999996E-2</v>
+        <v>13.900000000000002</v>
+      </c>
+      <c r="S16" s="54">
+        <v>0.2422</v>
       </c>
       <c r="T16" s="21">
         <f t="shared" si="5"/>
-        <v>14.7</v>
-      </c>
-      <c r="U16" s="72"/>
+        <v>24.22</v>
+      </c>
+      <c r="U16" s="70"/>
       <c r="V16" s="1"/>
       <c r="W16" s="1"/>
     </row>
     <row r="17" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="10">
+      <c r="A17" s="17">
         <v>15</v>
       </c>
-      <c r="B17" s="105"/>
-      <c r="C17" s="69" t="s">
+      <c r="B17" s="137"/>
+      <c r="C17" s="71" t="s">
+        <v>90</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="F17" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D17" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="G17" s="44" t="s">
-        <v>108</v>
-      </c>
-      <c r="H17" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="I17" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="J17" s="44">
+      <c r="G17" s="72" t="s">
+        <v>95</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="J17" s="72">
         <v>1</v>
       </c>
-      <c r="K17" s="13">
+      <c r="K17" s="16">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L17" s="13">
+      <c r="L17" s="16">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="M17" s="13">
+      <c r="M17" s="16">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N17" s="86" t="s">
+      <c r="N17" s="85" t="s">
         <v>20</v>
       </c>
-      <c r="O17" s="20">
-        <v>0.52</v>
-      </c>
-      <c r="P17" s="21">
+      <c r="O17" s="34">
+        <v>0.1</v>
+      </c>
+      <c r="P17" s="35">
         <f t="shared" si="3"/>
-        <v>2.6</v>
-      </c>
-      <c r="Q17" s="20">
-        <v>0.27800000000000002</v>
-      </c>
-      <c r="R17" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="Q17" s="34">
+        <v>1.8200000000000001E-2</v>
+      </c>
+      <c r="R17" s="35">
         <f t="shared" si="4"/>
-        <v>13.900000000000002</v>
-      </c>
-      <c r="S17" s="55">
-        <v>0.2422</v>
-      </c>
-      <c r="T17" s="21">
+        <v>0.91</v>
+      </c>
+      <c r="S17" s="56">
+        <v>1.4800000000000001E-2</v>
+      </c>
+      <c r="T17" s="35">
         <f t="shared" si="5"/>
-        <v>24.22</v>
-      </c>
-      <c r="U17" s="72"/>
+        <v>1.48</v>
+      </c>
+      <c r="U17" s="73"/>
       <c r="V17" s="1"/>
       <c r="W17" s="1"/>
     </row>
-    <row r="18" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="10"/>
-      <c r="B18" s="106"/>
-      <c r="C18" s="73" t="s">
-        <v>95</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="G18" s="74" t="s">
-        <v>100</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="J18" s="74">
-        <v>1</v>
-      </c>
-      <c r="K18" s="16">
+    <row r="18" spans="1:23" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="17">
+        <v>16</v>
+      </c>
+      <c r="B18" s="36" t="s">
+        <v>160</v>
+      </c>
+      <c r="C18" s="74" t="s">
+        <v>117</v>
+      </c>
+      <c r="D18" s="41" t="s">
+        <v>118</v>
+      </c>
+      <c r="E18" s="41" t="s">
+        <v>119</v>
+      </c>
+      <c r="F18" s="41" t="s">
+        <v>120</v>
+      </c>
+      <c r="G18" s="75" t="s">
+        <v>152</v>
+      </c>
+      <c r="H18" s="41" t="s">
+        <v>326</v>
+      </c>
+      <c r="I18" s="41" t="s">
+        <v>21</v>
+      </c>
+      <c r="J18" s="75">
+        <v>3</v>
+      </c>
+      <c r="K18" s="60">
         <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="L18" s="16">
+        <v>15</v>
+      </c>
+      <c r="L18" s="60">
         <f t="shared" si="1"/>
-        <v>50</v>
-      </c>
-      <c r="M18" s="16">
+        <v>150</v>
+      </c>
+      <c r="M18" s="60">
         <f t="shared" si="2"/>
-        <v>100</v>
-      </c>
-      <c r="N18" s="87" t="s">
-        <v>20</v>
-      </c>
-      <c r="O18" s="34">
-        <v>0.1</v>
-      </c>
-      <c r="P18" s="35">
+        <v>300</v>
+      </c>
+      <c r="N18" s="88" t="s">
+        <v>324</v>
+      </c>
+      <c r="O18" s="61">
+        <v>0.32200000000000001</v>
+      </c>
+      <c r="P18" s="62">
         <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="Q18" s="34">
-        <v>1.8200000000000001E-2</v>
-      </c>
-      <c r="R18" s="35">
+        <v>4.83</v>
+      </c>
+      <c r="Q18" s="61">
+        <v>0.2</v>
+      </c>
+      <c r="R18" s="62">
         <f t="shared" si="4"/>
-        <v>0.91</v>
-      </c>
-      <c r="S18" s="57">
-        <v>1.4800000000000001E-2</v>
-      </c>
-      <c r="T18" s="35">
+        <v>30</v>
+      </c>
+      <c r="S18" s="62">
+        <v>0.2</v>
+      </c>
+      <c r="T18" s="62">
         <f t="shared" si="5"/>
-        <v>1.48</v>
-      </c>
-      <c r="U18" s="75"/>
+        <v>60</v>
+      </c>
+      <c r="U18" s="76"/>
       <c r="V18" s="1"/>
       <c r="W18" s="1"/>
     </row>
-    <row r="19" spans="1:23" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="10">
-        <v>16</v>
-      </c>
-      <c r="B19" s="36" t="s">
-        <v>165</v>
-      </c>
-      <c r="C19" s="76" t="s">
+    <row r="19" spans="1:23" s="22" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="17">
+        <v>17</v>
+      </c>
+      <c r="B19" s="91" t="s">
+        <v>163</v>
+      </c>
+      <c r="C19" s="93" t="s">
+        <v>121</v>
+      </c>
+      <c r="D19" s="37" t="s">
         <v>122</v>
       </c>
-      <c r="D19" s="41" t="s">
+      <c r="E19" s="37" t="s">
         <v>123</v>
       </c>
-      <c r="E19" s="41" t="s">
+      <c r="F19" s="95" t="s">
         <v>124</v>
       </c>
-      <c r="F19" s="41" t="s">
-        <v>125</v>
-      </c>
       <c r="G19" s="77" t="s">
-        <v>157</v>
-      </c>
-      <c r="H19" s="41" t="s">
-        <v>331</v>
-      </c>
-      <c r="I19" s="41" t="s">
+        <v>153</v>
+      </c>
+      <c r="H19" s="37" t="s">
+        <v>347</v>
+      </c>
+      <c r="I19" s="37" t="s">
         <v>21</v>
       </c>
       <c r="J19" s="77">
-        <v>3</v>
-      </c>
-      <c r="K19" s="61">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="L19" s="61">
-        <f t="shared" si="1"/>
-        <v>150</v>
-      </c>
-      <c r="M19" s="61">
-        <f t="shared" si="2"/>
-        <v>300</v>
-      </c>
-      <c r="N19" s="91" t="s">
-        <v>329</v>
-      </c>
-      <c r="O19" s="62">
-        <v>0.32200000000000001</v>
-      </c>
-      <c r="P19" s="63">
-        <f t="shared" si="3"/>
-        <v>4.83</v>
-      </c>
-      <c r="Q19" s="62">
-        <v>0.2</v>
-      </c>
-      <c r="R19" s="63">
-        <f t="shared" si="4"/>
-        <v>30</v>
-      </c>
-      <c r="S19" s="63">
-        <v>0.2</v>
-      </c>
-      <c r="T19" s="63">
-        <f t="shared" si="5"/>
-        <v>60</v>
-      </c>
-      <c r="U19" s="78"/>
-      <c r="V19" s="1"/>
-      <c r="W19" s="1"/>
-    </row>
-    <row r="20" spans="1:23" s="22" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="10">
-        <v>17</v>
-      </c>
-      <c r="B20" s="94" t="s">
-        <v>168</v>
-      </c>
-      <c r="C20" s="96" t="s">
-        <v>126</v>
-      </c>
-      <c r="D20" s="37" t="s">
-        <v>127</v>
-      </c>
-      <c r="E20" s="37" t="s">
-        <v>128</v>
-      </c>
-      <c r="F20" s="98" t="s">
-        <v>129</v>
-      </c>
-      <c r="G20" s="79" t="s">
-        <v>158</v>
-      </c>
-      <c r="H20" s="37" t="s">
-        <v>353</v>
-      </c>
-      <c r="I20" s="37" t="s">
-        <v>21</v>
-      </c>
-      <c r="J20" s="79">
         <v>2</v>
       </c>
-      <c r="K20" s="79">
+      <c r="K19" s="77">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="L20" s="79">
+      <c r="L19" s="77">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="M20" s="79">
+      <c r="M19" s="77">
         <f t="shared" si="2"/>
         <v>200</v>
       </c>
-      <c r="N20" s="114" t="s">
+      <c r="N19" s="100" t="s">
         <v>20</v>
       </c>
-      <c r="O20" s="38">
+      <c r="O19" s="38">
         <v>0.32200000000000001</v>
       </c>
-      <c r="P20" s="38">
+      <c r="P19" s="38">
         <f t="shared" si="3"/>
         <v>3.22</v>
       </c>
-      <c r="Q20" s="38">
+      <c r="Q19" s="38">
         <v>0.1825</v>
       </c>
-      <c r="R20" s="38">
+      <c r="R19" s="38">
         <f t="shared" si="4"/>
         <v>18.25</v>
       </c>
-      <c r="S20" s="97">
+      <c r="S19" s="94">
         <v>0.1825</v>
       </c>
-      <c r="T20" s="38">
+      <c r="T19" s="38">
         <f t="shared" si="5"/>
         <v>36.5</v>
       </c>
-      <c r="U20" s="126"/>
-      <c r="V20" s="25"/>
-      <c r="W20" s="25"/>
+      <c r="U19" s="112"/>
+      <c r="V19" s="25"/>
+      <c r="W19" s="25"/>
     </row>
-    <row r="21" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="10">
+    <row r="20" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="17">
         <v>18</v>
       </c>
-      <c r="B21" s="107" t="s">
-        <v>166</v>
-      </c>
-      <c r="C21" s="66" t="s">
-        <v>354</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="G21" s="67" t="s">
+      <c r="B20" s="138" t="s">
+        <v>161</v>
+      </c>
+      <c r="C20" s="65" t="s">
+        <v>348</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="G20" s="66" t="s">
         <v>46</v>
       </c>
-      <c r="H21" s="7" t="s">
+      <c r="H20" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="I21" s="7" t="s">
+      <c r="I20" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="J21" s="67">
+      <c r="J20" s="66">
         <v>1</v>
       </c>
-      <c r="K21" s="8">
+      <c r="K20" s="8">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L21" s="8">
+      <c r="L20" s="8">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="M21" s="8">
+      <c r="M20" s="8">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N21" s="92" t="s">
+      <c r="N20" s="89" t="s">
         <v>20</v>
       </c>
-      <c r="O21" s="32">
+      <c r="O20" s="32">
         <v>0.52</v>
       </c>
-      <c r="P21" s="33">
+      <c r="P20" s="33">
         <f t="shared" si="3"/>
         <v>2.6</v>
       </c>
-      <c r="Q21" s="32">
+      <c r="Q20" s="32">
         <v>0.41799999999999998</v>
       </c>
-      <c r="R21" s="33">
+      <c r="R20" s="33">
         <f t="shared" si="4"/>
         <v>20.9</v>
       </c>
-      <c r="S21" s="54">
+      <c r="S20" s="53">
         <v>0.28439999999999999</v>
       </c>
-      <c r="T21" s="33">
+      <c r="T20" s="33">
         <f t="shared" si="5"/>
         <v>28.439999999999998</v>
       </c>
-      <c r="U21" s="128" t="s">
-        <v>359</v>
+      <c r="U20" s="114" t="s">
+        <v>353</v>
+      </c>
+      <c r="V20" s="1"/>
+      <c r="W20" s="1"/>
+    </row>
+    <row r="21" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="17">
+        <v>19</v>
+      </c>
+      <c r="B21" s="139"/>
+      <c r="C21" s="68" t="s">
+        <v>128</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="G21" s="44" t="s">
+        <v>152</v>
+      </c>
+      <c r="H21" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="I21" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="J21" s="44">
+        <v>1</v>
+      </c>
+      <c r="K21" s="13">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="L21" s="13">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="M21" s="13">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="N21" s="84" t="s">
+        <v>20</v>
+      </c>
+      <c r="O21" s="20">
+        <v>0.47</v>
+      </c>
+      <c r="P21" s="21">
+        <f t="shared" si="3"/>
+        <v>2.3499999999999996</v>
+      </c>
+      <c r="Q21" s="20">
+        <v>0.34699999999999998</v>
+      </c>
+      <c r="R21" s="21">
+        <f t="shared" si="4"/>
+        <v>17.349999999999998</v>
+      </c>
+      <c r="S21" s="54">
+        <v>0.1963</v>
+      </c>
+      <c r="T21" s="21">
+        <f t="shared" si="5"/>
+        <v>19.63</v>
+      </c>
+      <c r="U21" s="99" t="s">
+        <v>353</v>
       </c>
       <c r="V21" s="1"/>
       <c r="W21" s="1"/>
     </row>
     <row r="22" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="10">
-        <v>19</v>
-      </c>
-      <c r="B22" s="108"/>
-      <c r="C22" s="69" t="s">
+      <c r="A22" s="17">
+        <v>20</v>
+      </c>
+      <c r="B22" s="139"/>
+      <c r="C22" s="68" t="s">
+        <v>131</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="F22" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="D22" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="E22" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="F22" s="12" t="s">
-        <v>135</v>
-      </c>
       <c r="G22" s="44" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="H22" s="12" t="s">
         <v>40</v>
@@ -3972,55 +3962,55 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N22" s="86" t="s">
+      <c r="N22" s="84" t="s">
         <v>20</v>
       </c>
       <c r="O22" s="20">
-        <v>0.47</v>
+        <v>0.67</v>
       </c>
       <c r="P22" s="21">
         <f t="shared" si="3"/>
-        <v>2.3499999999999996</v>
+        <v>3.35</v>
       </c>
       <c r="Q22" s="20">
-        <v>0.34699999999999998</v>
+        <v>0.59099999999999997</v>
       </c>
       <c r="R22" s="21">
         <f t="shared" si="4"/>
-        <v>17.349999999999998</v>
-      </c>
-      <c r="S22" s="55">
-        <v>0.1963</v>
+        <v>29.549999999999997</v>
+      </c>
+      <c r="S22" s="54">
+        <v>0.4531</v>
       </c>
       <c r="T22" s="21">
         <f t="shared" si="5"/>
-        <v>19.63</v>
-      </c>
-      <c r="U22" s="113" t="s">
-        <v>359</v>
+        <v>45.31</v>
+      </c>
+      <c r="U22" s="99" t="s">
+        <v>353</v>
       </c>
       <c r="V22" s="1"/>
       <c r="W22" s="1"/>
     </row>
     <row r="23" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="10">
-        <v>20</v>
-      </c>
-      <c r="B23" s="108"/>
-      <c r="C23" s="69" t="s">
+      <c r="A23" s="17">
+        <v>21</v>
+      </c>
+      <c r="B23" s="139"/>
+      <c r="C23" s="68" t="s">
+        <v>134</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="F23" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="D23" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="F23" s="12" t="s">
-        <v>138</v>
-      </c>
       <c r="G23" s="44" t="s">
-        <v>159</v>
+        <v>46</v>
       </c>
       <c r="H23" s="12" t="s">
         <v>40</v>
@@ -4043,696 +4033,694 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N23" s="86" t="s">
+      <c r="N23" s="87" t="s">
         <v>20</v>
       </c>
       <c r="O23" s="20">
-        <v>0.67</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="P23" s="21">
         <f t="shared" si="3"/>
-        <v>3.35</v>
+        <v>2.75</v>
       </c>
       <c r="Q23" s="20">
-        <v>0.59099999999999997</v>
+        <v>0.44800000000000001</v>
       </c>
       <c r="R23" s="21">
         <f t="shared" si="4"/>
-        <v>29.549999999999997</v>
-      </c>
-      <c r="S23" s="55">
-        <v>0.4531</v>
+        <v>22.400000000000002</v>
+      </c>
+      <c r="S23" s="54">
+        <v>0.30520000000000003</v>
       </c>
       <c r="T23" s="21">
         <f t="shared" si="5"/>
-        <v>45.31</v>
-      </c>
-      <c r="U23" s="113" t="s">
-        <v>359</v>
+        <v>30.520000000000003</v>
+      </c>
+      <c r="U23" s="99" t="s">
+        <v>353</v>
       </c>
       <c r="V23" s="1"/>
       <c r="W23" s="1"/>
     </row>
-    <row r="24" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="10">
+    <row r="24" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="17">
+        <v>22</v>
+      </c>
+      <c r="B24" s="140"/>
+      <c r="C24" s="71" t="s">
+        <v>137</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="G24" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="I24" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="B24" s="108"/>
-      <c r="C24" s="69" t="s">
-        <v>139</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="E24" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="F24" s="12" t="s">
-        <v>141</v>
-      </c>
-      <c r="G24" s="44" t="s">
-        <v>46</v>
-      </c>
-      <c r="H24" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="I24" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="J24" s="44">
+      <c r="J24" s="72">
         <v>1</v>
       </c>
-      <c r="K24" s="13">
+      <c r="K24" s="16">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L24" s="13">
+      <c r="L24" s="16">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="M24" s="13">
+      <c r="M24" s="16">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N24" s="89" t="s">
+      <c r="N24" s="90" t="s">
         <v>20</v>
       </c>
-      <c r="O24" s="20">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="P24" s="21">
+      <c r="O24" s="34">
+        <v>0.64</v>
+      </c>
+      <c r="P24" s="35">
         <f t="shared" si="3"/>
-        <v>2.75</v>
-      </c>
-      <c r="Q24" s="20">
-        <v>0.44800000000000001</v>
-      </c>
-      <c r="R24" s="21">
+        <v>3.2</v>
+      </c>
+      <c r="Q24" s="34">
+        <v>0.55100000000000005</v>
+      </c>
+      <c r="R24" s="35">
         <f t="shared" si="4"/>
-        <v>22.400000000000002</v>
-      </c>
-      <c r="S24" s="55">
-        <v>0.30520000000000003</v>
-      </c>
-      <c r="T24" s="21">
+        <v>27.55</v>
+      </c>
+      <c r="S24" s="56">
+        <v>0.41110000000000002</v>
+      </c>
+      <c r="T24" s="35">
         <f t="shared" si="5"/>
-        <v>30.520000000000003</v>
-      </c>
-      <c r="U24" s="113" t="s">
-        <v>359</v>
-      </c>
+        <v>41.11</v>
+      </c>
+      <c r="U24" s="73"/>
       <c r="V24" s="1"/>
       <c r="W24" s="1"/>
     </row>
     <row r="25" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="10">
-        <v>22</v>
-      </c>
-      <c r="B25" s="109"/>
-      <c r="C25" s="73" t="s">
+      <c r="A25" s="17">
+        <v>23</v>
+      </c>
+      <c r="B25" s="139" t="s">
+        <v>162</v>
+      </c>
+      <c r="C25" s="79" t="s">
+        <v>140</v>
+      </c>
+      <c r="D25" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="F25" s="116" t="s">
         <v>142</v>
       </c>
-      <c r="D25" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="G25" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="I25" s="39" t="s">
+      <c r="G25" s="80" t="s">
+        <v>156</v>
+      </c>
+      <c r="H25" s="15" t="s">
+        <v>359</v>
+      </c>
+      <c r="I25" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="J25" s="74">
+      <c r="J25" s="80">
         <v>1</v>
       </c>
-      <c r="K25" s="16">
+      <c r="K25" s="40">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L25" s="16">
+      <c r="L25" s="40">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="M25" s="16">
+      <c r="M25" s="40">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N25" s="93" t="s">
+      <c r="N25" s="101" t="s">
         <v>20</v>
       </c>
-      <c r="O25" s="34">
-        <v>0.64</v>
-      </c>
-      <c r="P25" s="35">
+      <c r="O25" s="50">
+        <v>6.32</v>
+      </c>
+      <c r="P25" s="51">
         <f t="shared" si="3"/>
-        <v>3.2</v>
-      </c>
-      <c r="Q25" s="34">
-        <v>0.55100000000000005</v>
-      </c>
-      <c r="R25" s="35">
+        <v>31.6</v>
+      </c>
+      <c r="Q25" s="50">
+        <v>5.2472000000000003</v>
+      </c>
+      <c r="R25" s="51">
         <f t="shared" si="4"/>
-        <v>27.55</v>
-      </c>
-      <c r="S25" s="57">
-        <v>0.41110000000000002</v>
-      </c>
-      <c r="T25" s="35">
+        <v>262.36</v>
+      </c>
+      <c r="S25" s="59">
+        <v>4.5328999999999997</v>
+      </c>
+      <c r="T25" s="51">
         <f t="shared" si="5"/>
-        <v>41.11</v>
-      </c>
-      <c r="U25" s="75"/>
+        <v>453.28999999999996</v>
+      </c>
+      <c r="U25" s="97" t="s">
+        <v>350</v>
+      </c>
       <c r="V25" s="1"/>
       <c r="W25" s="1"/>
     </row>
     <row r="26" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="10">
-        <v>23</v>
-      </c>
-      <c r="B26" s="108" t="s">
-        <v>167</v>
-      </c>
+      <c r="A26" s="17">
+        <v>24</v>
+      </c>
+      <c r="B26" s="139"/>
       <c r="C26" s="81" t="s">
+        <v>143</v>
+      </c>
+      <c r="D26" s="82" t="s">
+        <v>144</v>
+      </c>
+      <c r="E26" s="82" t="s">
+        <v>41</v>
+      </c>
+      <c r="F26" s="82" t="s">
         <v>145</v>
       </c>
-      <c r="D26" s="15" t="s">
-        <v>146</v>
-      </c>
-      <c r="E26" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="F26" s="130" t="s">
-        <v>147</v>
-      </c>
-      <c r="G26" s="82" t="s">
-        <v>161</v>
-      </c>
-      <c r="H26" s="15" t="s">
-        <v>365</v>
-      </c>
-      <c r="I26" s="15" t="s">
+      <c r="G26" s="83" t="s">
+        <v>157</v>
+      </c>
+      <c r="H26" s="82" t="s">
+        <v>40</v>
+      </c>
+      <c r="I26" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="J26" s="82">
+      <c r="J26" s="83">
         <v>1</v>
       </c>
-      <c r="K26" s="40">
+      <c r="K26" s="43">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L26" s="40">
+      <c r="L26" s="43">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="M26" s="40">
+      <c r="M26" s="43">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N26" s="115" t="s">
+      <c r="N26" s="102" t="s">
         <v>20</v>
       </c>
-      <c r="O26" s="50">
-        <v>6.32</v>
-      </c>
-      <c r="P26" s="51">
+      <c r="O26" s="63">
+        <v>1.01</v>
+      </c>
+      <c r="P26" s="29">
         <f t="shared" si="3"/>
-        <v>31.6</v>
-      </c>
-      <c r="Q26" s="50">
-        <v>5.2472000000000003</v>
-      </c>
-      <c r="R26" s="51">
+        <v>5.05</v>
+      </c>
+      <c r="Q26" s="63">
+        <v>0.90959999999999996</v>
+      </c>
+      <c r="R26" s="29">
         <f t="shared" si="4"/>
-        <v>262.36</v>
-      </c>
-      <c r="S26" s="60">
-        <v>4.5328999999999997</v>
-      </c>
-      <c r="T26" s="51">
+        <v>45.48</v>
+      </c>
+      <c r="S26" s="64">
+        <v>0.78979999999999995</v>
+      </c>
+      <c r="T26" s="29">
         <f t="shared" si="5"/>
-        <v>453.28999999999996</v>
-      </c>
-      <c r="U26" s="111" t="s">
-        <v>356</v>
-      </c>
+        <v>78.97999999999999</v>
+      </c>
+      <c r="U26" s="113"/>
       <c r="V26" s="1"/>
       <c r="W26" s="1"/>
     </row>
-    <row r="27" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="10">
-        <v>24</v>
-      </c>
-      <c r="B27" s="108"/>
-      <c r="C27" s="83" t="s">
+    <row r="27" spans="1:23" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="17">
+        <v>25</v>
+      </c>
+      <c r="B27" s="49" t="s">
+        <v>248</v>
+      </c>
+      <c r="C27" s="124" t="s">
+        <v>146</v>
+      </c>
+      <c r="D27" s="41" t="s">
+        <v>147</v>
+      </c>
+      <c r="E27" s="41" t="s">
+        <v>41</v>
+      </c>
+      <c r="F27" s="125" t="s">
         <v>148</v>
       </c>
-      <c r="D27" s="84" t="s">
-        <v>149</v>
-      </c>
-      <c r="E27" s="84" t="s">
-        <v>41</v>
-      </c>
-      <c r="F27" s="84" t="s">
-        <v>150</v>
-      </c>
-      <c r="G27" s="85" t="s">
-        <v>162</v>
-      </c>
-      <c r="H27" s="84" t="s">
-        <v>40</v>
-      </c>
-      <c r="I27" s="37" t="s">
+      <c r="G27" s="75" t="s">
+        <v>158</v>
+      </c>
+      <c r="H27" s="75" t="s">
+        <v>351</v>
+      </c>
+      <c r="I27" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="J27" s="85">
+      <c r="J27" s="75">
         <v>1</v>
       </c>
-      <c r="K27" s="43">
+      <c r="K27" s="60">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L27" s="43">
+      <c r="L27" s="60">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="M27" s="43">
+      <c r="M27" s="60">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N27" s="116" t="s">
+      <c r="N27" s="126" t="s">
         <v>20</v>
       </c>
-      <c r="O27" s="64">
-        <v>1.01</v>
-      </c>
-      <c r="P27" s="29">
+      <c r="O27" s="61">
+        <v>0.68</v>
+      </c>
+      <c r="P27" s="62">
         <f t="shared" si="3"/>
-        <v>5.05</v>
-      </c>
-      <c r="Q27" s="64">
-        <v>0.90959999999999996</v>
-      </c>
-      <c r="R27" s="29">
+        <v>3.4000000000000004</v>
+      </c>
+      <c r="Q27" s="61">
+        <v>0.47</v>
+      </c>
+      <c r="R27" s="62">
         <f t="shared" si="4"/>
-        <v>45.48</v>
-      </c>
-      <c r="S27" s="65">
-        <v>0.78979999999999995</v>
-      </c>
-      <c r="T27" s="29">
+        <v>23.5</v>
+      </c>
+      <c r="S27" s="127">
+        <v>0.42720000000000002</v>
+      </c>
+      <c r="T27" s="62">
         <f t="shared" si="5"/>
-        <v>78.97999999999999</v>
-      </c>
-      <c r="U27" s="127"/>
+        <v>42.72</v>
+      </c>
+      <c r="U27" s="128" t="s">
+        <v>352</v>
+      </c>
       <c r="V27" s="1"/>
       <c r="W27" s="1"/>
     </row>
-    <row r="28" spans="1:23" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="10">
-        <v>25</v>
-      </c>
-      <c r="B28" s="49" t="s">
-        <v>253</v>
-      </c>
-      <c r="C28" s="138" t="s">
+    <row r="28" spans="1:23" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="17">
+        <v>26</v>
+      </c>
+      <c r="B28" s="92" t="s">
+        <v>39</v>
+      </c>
+      <c r="C28" s="93" t="s">
+        <v>149</v>
+      </c>
+      <c r="D28" s="37" t="s">
+        <v>150</v>
+      </c>
+      <c r="E28" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="F28" s="37" t="s">
         <v>151</v>
       </c>
-      <c r="D28" s="41" t="s">
-        <v>152</v>
-      </c>
-      <c r="E28" s="41" t="s">
-        <v>41</v>
-      </c>
-      <c r="F28" s="139" t="s">
-        <v>153</v>
-      </c>
       <c r="G28" s="77" t="s">
-        <v>163</v>
-      </c>
-      <c r="H28" s="77" t="s">
-        <v>357</v>
-      </c>
-      <c r="I28" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="H28" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="I28" s="37" t="s">
         <v>21</v>
       </c>
       <c r="J28" s="77">
-        <v>1</v>
-      </c>
-      <c r="K28" s="61">
+        <v>2</v>
+      </c>
+      <c r="K28" s="120">
         <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="L28" s="61">
+        <v>10</v>
+      </c>
+      <c r="L28" s="120">
         <f t="shared" si="1"/>
-        <v>50</v>
-      </c>
-      <c r="M28" s="61">
+        <v>100</v>
+      </c>
+      <c r="M28" s="120">
         <f t="shared" si="2"/>
-        <v>100</v>
-      </c>
-      <c r="N28" s="140" t="s">
+        <v>200</v>
+      </c>
+      <c r="N28" s="100" t="s">
         <v>20</v>
       </c>
-      <c r="O28" s="62">
-        <v>0.68</v>
-      </c>
-      <c r="P28" s="63">
+      <c r="O28" s="38">
+        <v>0.65400000000000003</v>
+      </c>
+      <c r="P28" s="121">
         <f t="shared" si="3"/>
-        <v>3.4000000000000004</v>
-      </c>
-      <c r="Q28" s="62">
-        <v>0.47</v>
-      </c>
-      <c r="R28" s="63">
+        <v>6.54</v>
+      </c>
+      <c r="Q28" s="38">
+        <v>0.52359999999999995</v>
+      </c>
+      <c r="R28" s="121">
         <f t="shared" si="4"/>
-        <v>23.5</v>
-      </c>
-      <c r="S28" s="141">
-        <v>0.42720000000000002</v>
-      </c>
-      <c r="T28" s="63">
+        <v>52.359999999999992</v>
+      </c>
+      <c r="S28" s="122">
+        <v>0.52359999999999995</v>
+      </c>
+      <c r="T28" s="121">
         <f t="shared" si="5"/>
-        <v>42.72</v>
-      </c>
-      <c r="U28" s="142" t="s">
-        <v>358</v>
-      </c>
+        <v>104.71999999999998</v>
+      </c>
+      <c r="U28" s="123"/>
       <c r="V28" s="1"/>
       <c r="W28" s="1"/>
     </row>
-    <row r="29" spans="1:23" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="10">
-        <v>26</v>
-      </c>
-      <c r="B29" s="95" t="s">
-        <v>39</v>
-      </c>
-      <c r="C29" s="96" t="s">
-        <v>154</v>
-      </c>
-      <c r="D29" s="37" t="s">
-        <v>155</v>
-      </c>
-      <c r="E29" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="F29" s="37" t="s">
-        <v>156</v>
-      </c>
-      <c r="G29" s="79" t="s">
+    <row r="29" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="17">
+        <v>27</v>
+      </c>
+      <c r="B29" s="138" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="118" t="s">
+        <v>360</v>
+      </c>
+      <c r="D29" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="H29" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="I29" s="37" t="s">
-        <v>21</v>
-      </c>
-      <c r="J29" s="79">
-        <v>2</v>
-      </c>
-      <c r="K29" s="134">
+      <c r="E29" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F29" s="42" t="s">
+        <v>165</v>
+      </c>
+      <c r="G29" s="66" t="s">
+        <v>224</v>
+      </c>
+      <c r="H29" s="66" t="s">
+        <v>336</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="J29" s="66">
+        <v>1</v>
+      </c>
+      <c r="K29" s="8">
         <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="L29" s="134">
+        <v>5</v>
+      </c>
+      <c r="L29" s="8">
         <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="M29" s="8">
+        <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="M29" s="134">
-        <f t="shared" si="2"/>
-        <v>200</v>
-      </c>
-      <c r="N29" s="114" t="s">
+      <c r="N29" s="117" t="s">
         <v>20</v>
       </c>
-      <c r="O29" s="38">
-        <v>0.65400000000000003</v>
-      </c>
-      <c r="P29" s="135">
+      <c r="O29" s="32">
+        <v>0.1</v>
+      </c>
+      <c r="P29" s="33">
         <f t="shared" si="3"/>
-        <v>6.54</v>
-      </c>
-      <c r="Q29" s="38">
-        <v>0.52359999999999995</v>
-      </c>
-      <c r="R29" s="135">
+        <v>0.5</v>
+      </c>
+      <c r="Q29" s="32">
+        <v>1.2E-2</v>
+      </c>
+      <c r="R29" s="33">
         <f t="shared" si="4"/>
-        <v>52.359999999999992</v>
-      </c>
-      <c r="S29" s="136">
-        <v>0.52359999999999995</v>
-      </c>
-      <c r="T29" s="135">
+        <v>0.6</v>
+      </c>
+      <c r="S29" s="53">
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="T29" s="33">
         <f t="shared" si="5"/>
-        <v>104.71999999999998</v>
-      </c>
-      <c r="U29" s="137"/>
+        <v>0.47000000000000003</v>
+      </c>
+      <c r="U29" s="78"/>
       <c r="V29" s="1"/>
       <c r="W29" s="1"/>
     </row>
-    <row r="30" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="10">
-        <v>27</v>
-      </c>
-      <c r="B30" s="107" t="s">
-        <v>18</v>
-      </c>
-      <c r="C30" s="132" t="s">
-        <v>366</v>
-      </c>
-      <c r="D30" s="7" t="s">
+    <row r="30" spans="1:23" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="17">
+        <v>28</v>
+      </c>
+      <c r="B30" s="139"/>
+      <c r="C30" s="68" t="s">
+        <v>166</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="E30" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="F30" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="E30" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F30" s="42" t="s">
-        <v>170</v>
-      </c>
-      <c r="G30" s="67" t="s">
-        <v>229</v>
-      </c>
-      <c r="H30" s="67" t="s">
-        <v>341</v>
-      </c>
-      <c r="I30" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="J30" s="67">
+      <c r="G30" s="44" t="s">
+        <v>226</v>
+      </c>
+      <c r="H30" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="I30" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="J30" s="44">
         <v>1</v>
       </c>
-      <c r="K30" s="8">
+      <c r="K30" s="13">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L30" s="8">
+      <c r="L30" s="13">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="M30" s="8">
+      <c r="M30" s="13">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N30" s="131" t="s">
+      <c r="N30" s="84" t="s">
         <v>20</v>
       </c>
-      <c r="O30" s="32">
+      <c r="O30" s="20">
         <v>0.1</v>
       </c>
-      <c r="P30" s="33">
+      <c r="P30" s="21">
         <f t="shared" si="3"/>
         <v>0.5</v>
       </c>
-      <c r="Q30" s="32">
-        <v>1.2E-2</v>
-      </c>
-      <c r="R30" s="33">
+      <c r="Q30" s="20">
+        <v>2.7E-2</v>
+      </c>
+      <c r="R30" s="21">
         <f t="shared" si="4"/>
-        <v>0.6</v>
+        <v>1.35</v>
       </c>
       <c r="S30" s="54">
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="T30" s="33">
+        <v>1.09E-2</v>
+      </c>
+      <c r="T30" s="21">
         <f t="shared" si="5"/>
-        <v>0.47000000000000003</v>
-      </c>
-      <c r="U30" s="80"/>
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="U30" s="70"/>
       <c r="V30" s="1"/>
       <c r="W30" s="1"/>
     </row>
     <row r="31" spans="1:23" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="10">
-        <v>28</v>
-      </c>
-      <c r="B31" s="108"/>
-      <c r="C31" s="69" t="s">
+      <c r="A31" s="17">
+        <v>29</v>
+      </c>
+      <c r="B31" s="139"/>
+      <c r="C31" s="68" t="s">
+        <v>170</v>
+      </c>
+      <c r="D31" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="D31" s="12" t="s">
+      <c r="E31" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="F31" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="E31" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="F31" s="12" t="s">
-        <v>174</v>
-      </c>
       <c r="G31" s="44" t="s">
-        <v>231</v>
+        <v>95</v>
       </c>
       <c r="H31" s="12" t="s">
         <v>40</v>
       </c>
       <c r="I31" s="12" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="J31" s="44">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K31" s="13">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="L31" s="13">
         <f t="shared" si="1"/>
-        <v>50</v>
+        <v>350</v>
       </c>
       <c r="M31" s="13">
         <f t="shared" si="2"/>
-        <v>100</v>
-      </c>
-      <c r="N31" s="86" t="s">
+        <v>700</v>
+      </c>
+      <c r="N31" s="84" t="s">
         <v>20</v>
       </c>
       <c r="O31" s="20">
-        <v>0.1</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="P31" s="21">
         <f t="shared" si="3"/>
-        <v>0.5</v>
+        <v>0.45499999999999996</v>
       </c>
       <c r="Q31" s="20">
-        <v>2.7E-2</v>
+        <v>5.4000000000000003E-3</v>
       </c>
       <c r="R31" s="21">
         <f t="shared" si="4"/>
-        <v>1.35</v>
-      </c>
-      <c r="S31" s="55">
-        <v>1.09E-2</v>
+        <v>1.8900000000000001</v>
+      </c>
+      <c r="S31" s="54">
+        <v>5.4000000000000003E-3</v>
       </c>
       <c r="T31" s="21">
         <f t="shared" si="5"/>
-        <v>1.0900000000000001</v>
-      </c>
-      <c r="U31" s="72"/>
+        <v>3.7800000000000002</v>
+      </c>
+      <c r="U31" s="70"/>
       <c r="V31" s="1"/>
       <c r="W31" s="1"/>
     </row>
-    <row r="32" spans="1:23" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="10">
-        <v>29</v>
-      </c>
-      <c r="B32" s="108"/>
-      <c r="C32" s="69" t="s">
-        <v>175</v>
+    <row r="32" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="17">
+        <v>30</v>
+      </c>
+      <c r="B32" s="139"/>
+      <c r="C32" s="68" t="s">
+        <v>173</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>176</v>
+        <v>24</v>
       </c>
       <c r="E32" s="12" t="s">
         <v>15</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G32" s="44" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H32" s="12" t="s">
         <v>40</v>
       </c>
       <c r="I32" s="12" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="J32" s="44">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K32" s="13">
         <f t="shared" si="0"/>
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="L32" s="13">
         <f t="shared" si="1"/>
-        <v>350</v>
+        <v>50</v>
       </c>
       <c r="M32" s="13">
         <f t="shared" si="2"/>
-        <v>700</v>
-      </c>
-      <c r="N32" s="86" t="s">
+        <v>100</v>
+      </c>
+      <c r="N32" s="84" t="s">
         <v>20</v>
       </c>
       <c r="O32" s="20">
-        <v>1.2999999999999999E-2</v>
+        <v>0.1</v>
       </c>
       <c r="P32" s="21">
         <f t="shared" si="3"/>
-        <v>0.45499999999999996</v>
+        <v>0.5</v>
       </c>
       <c r="Q32" s="20">
-        <v>5.4000000000000003E-3</v>
+        <v>1.6E-2</v>
       </c>
       <c r="R32" s="21">
         <f t="shared" si="4"/>
-        <v>1.8900000000000001</v>
-      </c>
-      <c r="S32" s="55">
-        <v>5.4000000000000003E-3</v>
+        <v>0.8</v>
+      </c>
+      <c r="S32" s="54">
+        <v>6.6E-3</v>
       </c>
       <c r="T32" s="21">
         <f t="shared" si="5"/>
-        <v>3.7800000000000002</v>
-      </c>
-      <c r="U32" s="72"/>
+        <v>0.66</v>
+      </c>
+      <c r="U32" s="70"/>
       <c r="V32" s="1"/>
       <c r="W32" s="1"/>
     </row>
     <row r="33" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="10">
-        <v>30</v>
-      </c>
-      <c r="B33" s="108"/>
-      <c r="C33" s="69" t="s">
-        <v>178</v>
+      <c r="A33" s="17">
+        <v>31</v>
+      </c>
+      <c r="B33" s="139"/>
+      <c r="C33" s="68" t="s">
+        <v>175</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>24</v>
+        <v>176</v>
       </c>
       <c r="E33" s="12" t="s">
         <v>15</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="G33" s="44" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H33" s="12" t="s">
         <v>40</v>
       </c>
       <c r="I33" s="12" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="J33" s="44">
         <v>1</v>
@@ -4749,7 +4737,7 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N33" s="86" t="s">
+      <c r="N33" s="84" t="s">
         <v>20</v>
       </c>
       <c r="O33" s="20">
@@ -4760,48 +4748,48 @@
         <v>0.5</v>
       </c>
       <c r="Q33" s="20">
-        <v>1.6E-2</v>
+        <v>2.1999999999999999E-2</v>
       </c>
       <c r="R33" s="21">
         <f t="shared" si="4"/>
-        <v>0.8</v>
-      </c>
-      <c r="S33" s="55">
-        <v>6.6E-3</v>
+        <v>1.0999999999999999</v>
+      </c>
+      <c r="S33" s="54">
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="T33" s="21">
         <f t="shared" si="5"/>
-        <v>0.66</v>
-      </c>
-      <c r="U33" s="72"/>
+        <v>0.89999999999999991</v>
+      </c>
+      <c r="U33" s="70"/>
       <c r="V33" s="1"/>
       <c r="W33" s="1"/>
     </row>
     <row r="34" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="10">
-        <v>31</v>
-      </c>
-      <c r="B34" s="108"/>
-      <c r="C34" s="69" t="s">
-        <v>180</v>
+      <c r="A34" s="17">
+        <v>32</v>
+      </c>
+      <c r="B34" s="139"/>
+      <c r="C34" s="68" t="s">
+        <v>178</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E34" s="12" t="s">
         <v>15</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G34" s="44" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H34" s="12" t="s">
         <v>40</v>
       </c>
       <c r="I34" s="12" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="J34" s="44">
         <v>1</v>
@@ -4818,7 +4806,7 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N34" s="86" t="s">
+      <c r="N34" s="84" t="s">
         <v>20</v>
       </c>
       <c r="O34" s="20">
@@ -4835,180 +4823,180 @@
         <f t="shared" si="4"/>
         <v>1.0999999999999999</v>
       </c>
-      <c r="S34" s="55">
+      <c r="S34" s="54">
         <v>8.9999999999999993E-3</v>
       </c>
       <c r="T34" s="21">
         <f t="shared" si="5"/>
         <v>0.89999999999999991</v>
       </c>
-      <c r="U34" s="72"/>
+      <c r="U34" s="70"/>
       <c r="V34" s="1"/>
       <c r="W34" s="1"/>
     </row>
     <row r="35" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="10">
-        <v>32</v>
-      </c>
-      <c r="B35" s="108"/>
-      <c r="C35" s="69" t="s">
-        <v>183</v>
+      <c r="A35" s="17">
+        <v>33</v>
+      </c>
+      <c r="B35" s="139"/>
+      <c r="C35" s="68" t="s">
+        <v>181</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E35" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="F35" s="12" t="s">
-        <v>185</v>
+      <c r="F35" s="24" t="s">
+        <v>183</v>
       </c>
       <c r="G35" s="44" t="s">
-        <v>100</v>
-      </c>
-      <c r="H35" s="12" t="s">
-        <v>40</v>
+        <v>232</v>
+      </c>
+      <c r="H35" s="26" t="s">
+        <v>327</v>
       </c>
       <c r="I35" s="12" t="s">
-        <v>236</v>
+        <v>17</v>
       </c>
       <c r="J35" s="44">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K35" s="13">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="L35" s="13">
         <f t="shared" si="1"/>
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="M35" s="13">
         <f t="shared" si="2"/>
-        <v>100</v>
-      </c>
-      <c r="N35" s="86" t="s">
+        <v>500</v>
+      </c>
+      <c r="N35" s="84" t="s">
         <v>20</v>
       </c>
       <c r="O35" s="20">
-        <v>0.1</v>
+        <v>0.223</v>
       </c>
       <c r="P35" s="21">
         <f t="shared" si="3"/>
-        <v>0.5</v>
+        <v>5.5750000000000002</v>
       </c>
       <c r="Q35" s="20">
-        <v>2.1999999999999999E-2</v>
+        <v>8.6999999999999994E-2</v>
       </c>
       <c r="R35" s="21">
         <f t="shared" si="4"/>
-        <v>1.0999999999999999</v>
-      </c>
-      <c r="S35" s="55">
-        <v>8.9999999999999993E-3</v>
+        <v>21.75</v>
+      </c>
+      <c r="S35" s="54">
+        <v>8.6999999999999994E-2</v>
       </c>
       <c r="T35" s="21">
         <f t="shared" si="5"/>
-        <v>0.89999999999999991</v>
-      </c>
-      <c r="U35" s="72"/>
+        <v>43.5</v>
+      </c>
+      <c r="U35" s="70"/>
       <c r="V35" s="1"/>
       <c r="W35" s="1"/>
     </row>
     <row r="36" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="10">
-        <v>33</v>
-      </c>
-      <c r="B36" s="108"/>
-      <c r="C36" s="69" t="s">
-        <v>186</v>
+      <c r="A36" s="17">
+        <v>34</v>
+      </c>
+      <c r="B36" s="139"/>
+      <c r="C36" s="68" t="s">
+        <v>184</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E36" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="F36" s="24" t="s">
-        <v>188</v>
+      <c r="F36" s="12" t="s">
+        <v>186</v>
       </c>
       <c r="G36" s="44" t="s">
-        <v>237</v>
-      </c>
-      <c r="H36" s="26" t="s">
-        <v>332</v>
+        <v>95</v>
+      </c>
+      <c r="H36" s="12" t="s">
+        <v>40</v>
       </c>
       <c r="I36" s="12" t="s">
-        <v>17</v>
+        <v>233</v>
       </c>
       <c r="J36" s="44">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K36" s="13">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="L36" s="13">
         <f t="shared" si="1"/>
-        <v>250</v>
+        <v>50</v>
       </c>
       <c r="M36" s="13">
         <f t="shared" si="2"/>
-        <v>500</v>
-      </c>
-      <c r="N36" s="86" t="s">
-        <v>20</v>
+        <v>100</v>
+      </c>
+      <c r="N36" s="84" t="s">
+        <v>324</v>
       </c>
       <c r="O36" s="20">
-        <v>0.223</v>
+        <v>0.10100000000000001</v>
       </c>
       <c r="P36" s="21">
         <f t="shared" si="3"/>
-        <v>5.5750000000000002</v>
+        <v>0.505</v>
       </c>
       <c r="Q36" s="20">
-        <v>8.6999999999999994E-2</v>
+        <v>1.6E-2</v>
       </c>
       <c r="R36" s="21">
         <f t="shared" si="4"/>
-        <v>21.75</v>
-      </c>
-      <c r="S36" s="55">
-        <v>8.6999999999999994E-2</v>
+        <v>0.8</v>
+      </c>
+      <c r="S36" s="54">
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="T36" s="21">
         <f t="shared" si="5"/>
-        <v>43.5</v>
-      </c>
-      <c r="U36" s="72"/>
+        <v>0.70000000000000007</v>
+      </c>
+      <c r="U36" s="70"/>
       <c r="V36" s="1"/>
       <c r="W36" s="1"/>
     </row>
     <row r="37" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="10">
-        <v>34</v>
-      </c>
-      <c r="B37" s="108"/>
-      <c r="C37" s="69" t="s">
-        <v>189</v>
+      <c r="A37" s="17">
+        <v>35</v>
+      </c>
+      <c r="B37" s="139"/>
+      <c r="C37" s="68" t="s">
+        <v>187</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E37" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="F37" s="12" t="s">
-        <v>191</v>
+      <c r="F37" s="24" t="s">
+        <v>189</v>
       </c>
       <c r="G37" s="44" t="s">
-        <v>100</v>
-      </c>
-      <c r="H37" s="12" t="s">
-        <v>40</v>
+        <v>232</v>
+      </c>
+      <c r="H37" s="44" t="s">
+        <v>328</v>
       </c>
       <c r="I37" s="12" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="J37" s="44">
         <v>1</v>
@@ -5025,611 +5013,611 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N37" s="86" t="s">
-        <v>329</v>
+      <c r="N37" s="84" t="s">
+        <v>20</v>
       </c>
       <c r="O37" s="20">
-        <v>0.10100000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="P37" s="21">
         <f t="shared" si="3"/>
-        <v>0.505</v>
+        <v>0.5</v>
       </c>
       <c r="Q37" s="20">
-        <v>1.6E-2</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="R37" s="21">
         <f t="shared" si="4"/>
-        <v>0.8</v>
-      </c>
-      <c r="S37" s="55">
-        <v>7.0000000000000001E-3</v>
+        <v>0.75</v>
+      </c>
+      <c r="S37" s="54">
+        <v>6.1000000000000004E-3</v>
       </c>
       <c r="T37" s="21">
         <f t="shared" si="5"/>
-        <v>0.70000000000000007</v>
-      </c>
-      <c r="U37" s="72"/>
+        <v>0.61</v>
+      </c>
+      <c r="U37" s="70"/>
       <c r="V37" s="1"/>
       <c r="W37" s="1"/>
     </row>
     <row r="38" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="10">
-        <v>35</v>
-      </c>
-      <c r="B38" s="108"/>
-      <c r="C38" s="69" t="s">
-        <v>192</v>
+      <c r="A38" s="17">
+        <v>36</v>
+      </c>
+      <c r="B38" s="139"/>
+      <c r="C38" s="68" t="s">
+        <v>190</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E38" s="12" t="s">
         <v>15</v>
       </c>
       <c r="F38" s="24" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G38" s="44" t="s">
-        <v>237</v>
+        <v>95</v>
       </c>
       <c r="H38" s="44" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="I38" s="12" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="J38" s="44">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K38" s="13">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="L38" s="13">
         <f t="shared" si="1"/>
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="M38" s="13">
         <f t="shared" si="2"/>
-        <v>100</v>
-      </c>
-      <c r="N38" s="86" t="s">
+        <v>400</v>
+      </c>
+      <c r="N38" s="84" t="s">
         <v>20</v>
       </c>
       <c r="O38" s="20">
-        <v>0.1</v>
+        <v>1.2E-2</v>
       </c>
       <c r="P38" s="21">
         <f t="shared" si="3"/>
-        <v>0.5</v>
+        <v>0.24</v>
       </c>
       <c r="Q38" s="20">
-        <v>1.4999999999999999E-2</v>
+        <v>4.7000000000000002E-3</v>
       </c>
       <c r="R38" s="21">
         <f t="shared" si="4"/>
-        <v>0.75</v>
-      </c>
-      <c r="S38" s="55">
-        <v>6.1000000000000004E-3</v>
+        <v>0.94000000000000006</v>
+      </c>
+      <c r="S38" s="54">
+        <v>3.5999999999999999E-3</v>
       </c>
       <c r="T38" s="21">
         <f t="shared" si="5"/>
-        <v>0.61</v>
-      </c>
-      <c r="U38" s="72"/>
+        <v>1.44</v>
+      </c>
+      <c r="U38" s="70"/>
       <c r="V38" s="1"/>
       <c r="W38" s="1"/>
     </row>
     <row r="39" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="10">
-        <v>36</v>
-      </c>
-      <c r="B39" s="108"/>
-      <c r="C39" s="69" t="s">
-        <v>195</v>
+      <c r="A39" s="17">
+        <v>37</v>
+      </c>
+      <c r="B39" s="139"/>
+      <c r="C39" s="68" t="s">
+        <v>338</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E39" s="12" t="s">
         <v>15</v>
       </c>
       <c r="F39" s="24" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="G39" s="44" t="s">
-        <v>100</v>
+        <v>236</v>
       </c>
       <c r="H39" s="44" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="I39" s="12" t="s">
-        <v>240</v>
+        <v>26</v>
       </c>
       <c r="J39" s="44">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K39" s="13">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="L39" s="13">
         <f t="shared" si="1"/>
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="M39" s="13">
         <f t="shared" si="2"/>
-        <v>400</v>
-      </c>
-      <c r="N39" s="86" t="s">
+        <v>300</v>
+      </c>
+      <c r="N39" s="84" t="s">
         <v>20</v>
       </c>
       <c r="O39" s="20">
-        <v>1.2E-2</v>
+        <v>2.7E-2</v>
       </c>
       <c r="P39" s="21">
         <f t="shared" si="3"/>
-        <v>0.24</v>
+        <v>0.40499999999999997</v>
       </c>
       <c r="Q39" s="20">
-        <v>4.7000000000000002E-3</v>
+        <v>1.11E-2</v>
       </c>
       <c r="R39" s="21">
         <f t="shared" si="4"/>
-        <v>0.94000000000000006</v>
-      </c>
-      <c r="S39" s="55">
-        <v>3.5999999999999999E-3</v>
+        <v>1.665</v>
+      </c>
+      <c r="S39" s="54">
+        <v>1.11E-2</v>
       </c>
       <c r="T39" s="21">
         <f t="shared" si="5"/>
-        <v>1.44</v>
-      </c>
-      <c r="U39" s="72"/>
+        <v>3.33</v>
+      </c>
+      <c r="U39" s="70"/>
       <c r="V39" s="1"/>
       <c r="W39" s="1"/>
     </row>
     <row r="40" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="10">
-        <v>37</v>
-      </c>
-      <c r="B40" s="108"/>
-      <c r="C40" s="69" t="s">
-        <v>343</v>
+      <c r="A40" s="17">
+        <v>38</v>
+      </c>
+      <c r="B40" s="139"/>
+      <c r="C40" s="68" t="s">
+        <v>340</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>15</v>
+        <v>196</v>
       </c>
       <c r="F40" s="24" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="G40" s="44" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="H40" s="44" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="I40" s="12" t="s">
-        <v>26</v>
+        <v>238</v>
       </c>
       <c r="J40" s="44">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K40" s="13">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="L40" s="13">
         <f t="shared" si="1"/>
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="M40" s="13">
         <f t="shared" si="2"/>
-        <v>300</v>
-      </c>
-      <c r="N40" s="86" t="s">
+        <v>100</v>
+      </c>
+      <c r="N40" s="84" t="s">
         <v>20</v>
       </c>
       <c r="O40" s="20">
-        <v>2.7E-2</v>
+        <v>0.1</v>
       </c>
       <c r="P40" s="21">
         <f t="shared" si="3"/>
-        <v>0.40499999999999997</v>
+        <v>0.5</v>
       </c>
       <c r="Q40" s="20">
-        <v>1.11E-2</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="R40" s="21">
         <f t="shared" si="4"/>
-        <v>1.665</v>
-      </c>
-      <c r="S40" s="55">
-        <v>1.11E-2</v>
+        <v>0.85000000000000009</v>
+      </c>
+      <c r="S40" s="54">
+        <v>6.7999999999999996E-3</v>
       </c>
       <c r="T40" s="21">
         <f t="shared" si="5"/>
-        <v>3.33</v>
-      </c>
-      <c r="U40" s="72"/>
+        <v>0.67999999999999994</v>
+      </c>
+      <c r="U40" s="70"/>
       <c r="V40" s="1"/>
       <c r="W40" s="1"/>
     </row>
     <row r="41" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="10">
-        <v>38</v>
-      </c>
-      <c r="B41" s="108"/>
-      <c r="C41" s="69" t="s">
-        <v>345</v>
+      <c r="A41" s="17">
+        <v>39</v>
+      </c>
+      <c r="B41" s="139"/>
+      <c r="C41" s="68" t="s">
+        <v>198</v>
       </c>
       <c r="D41" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="E41" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="F41" s="12" t="s">
         <v>200</v>
       </c>
-      <c r="E41" s="12" t="s">
-        <v>201</v>
-      </c>
-      <c r="F41" s="24" t="s">
-        <v>202</v>
-      </c>
       <c r="G41" s="44" t="s">
-        <v>242</v>
-      </c>
-      <c r="H41" s="44" t="s">
-        <v>344</v>
+        <v>95</v>
+      </c>
+      <c r="H41" s="12" t="s">
+        <v>40</v>
       </c>
       <c r="I41" s="12" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="J41" s="44">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K41" s="13">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="L41" s="13">
         <f t="shared" si="1"/>
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="M41" s="13">
         <f t="shared" si="2"/>
-        <v>100</v>
-      </c>
-      <c r="N41" s="86" t="s">
+        <v>300</v>
+      </c>
+      <c r="N41" s="84" t="s">
         <v>20</v>
       </c>
       <c r="O41" s="20">
-        <v>0.1</v>
+        <v>1.6E-2</v>
       </c>
       <c r="P41" s="21">
         <f t="shared" si="3"/>
-        <v>0.5</v>
+        <v>0.24</v>
       </c>
       <c r="Q41" s="20">
-        <v>1.7000000000000001E-2</v>
+        <v>6.6E-3</v>
       </c>
       <c r="R41" s="21">
         <f t="shared" si="4"/>
-        <v>0.85000000000000009</v>
-      </c>
-      <c r="S41" s="55">
-        <v>6.7999999999999996E-3</v>
+        <v>0.99</v>
+      </c>
+      <c r="S41" s="54">
+        <v>6.6E-3</v>
       </c>
       <c r="T41" s="21">
         <f t="shared" si="5"/>
-        <v>0.67999999999999994</v>
-      </c>
-      <c r="U41" s="72"/>
+        <v>1.98</v>
+      </c>
+      <c r="U41" s="70"/>
       <c r="V41" s="1"/>
       <c r="W41" s="1"/>
     </row>
     <row r="42" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="10">
-        <v>39</v>
-      </c>
-      <c r="B42" s="108"/>
-      <c r="C42" s="69" t="s">
-        <v>203</v>
+      <c r="A42" s="17">
+        <v>40</v>
+      </c>
+      <c r="B42" s="139"/>
+      <c r="C42" s="68" t="s">
+        <v>201</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E42" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="F42" s="12" t="s">
-        <v>205</v>
+      <c r="F42" s="24" t="s">
+        <v>203</v>
       </c>
       <c r="G42" s="44" t="s">
-        <v>100</v>
-      </c>
-      <c r="H42" s="12" t="s">
-        <v>40</v>
+        <v>93</v>
+      </c>
+      <c r="H42" s="44" t="s">
+        <v>330</v>
       </c>
       <c r="I42" s="12" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="J42" s="44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K42" s="13">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="L42" s="13">
         <f t="shared" si="1"/>
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="M42" s="13">
         <f t="shared" si="2"/>
-        <v>300</v>
-      </c>
-      <c r="N42" s="86" t="s">
+        <v>200</v>
+      </c>
+      <c r="N42" s="84" t="s">
         <v>20</v>
       </c>
       <c r="O42" s="20">
-        <v>1.6E-2</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="P42" s="21">
         <f t="shared" si="3"/>
-        <v>0.24</v>
+        <v>0.13</v>
       </c>
       <c r="Q42" s="20">
-        <v>6.6E-3</v>
+        <v>5.4000000000000003E-3</v>
       </c>
       <c r="R42" s="21">
         <f t="shared" si="4"/>
-        <v>0.99</v>
-      </c>
-      <c r="S42" s="55">
-        <v>6.6E-3</v>
+        <v>0.54</v>
+      </c>
+      <c r="S42" s="54">
+        <v>5.4000000000000003E-3</v>
       </c>
       <c r="T42" s="21">
         <f t="shared" si="5"/>
-        <v>1.98</v>
-      </c>
-      <c r="U42" s="72"/>
+        <v>1.08</v>
+      </c>
+      <c r="U42" s="70"/>
       <c r="V42" s="1"/>
       <c r="W42" s="1"/>
     </row>
     <row r="43" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="10">
-        <v>40</v>
-      </c>
-      <c r="B43" s="108"/>
-      <c r="C43" s="69" t="s">
+      <c r="A43" s="17">
+        <v>41</v>
+      </c>
+      <c r="B43" s="139"/>
+      <c r="C43" s="68" t="s">
+        <v>341</v>
+      </c>
+      <c r="D43" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="E43" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="F43" s="24" t="s">
         <v>206</v>
       </c>
-      <c r="D43" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="E43" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="F43" s="24" t="s">
-        <v>208</v>
-      </c>
       <c r="G43" s="44" t="s">
-        <v>98</v>
+        <v>241</v>
       </c>
       <c r="H43" s="44" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="I43" s="12" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="J43" s="44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K43" s="13">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L43" s="13">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M43" s="13">
         <f t="shared" si="2"/>
-        <v>200</v>
-      </c>
-      <c r="N43" s="86" t="s">
+        <v>100</v>
+      </c>
+      <c r="N43" s="84" t="s">
         <v>20</v>
       </c>
       <c r="O43" s="20">
-        <v>1.2999999999999999E-2</v>
+        <v>0.3</v>
       </c>
       <c r="P43" s="21">
         <f t="shared" si="3"/>
-        <v>0.13</v>
+        <v>1.5</v>
       </c>
       <c r="Q43" s="20">
-        <v>5.4000000000000003E-3</v>
+        <v>0.13339999999999999</v>
       </c>
       <c r="R43" s="21">
         <f t="shared" si="4"/>
-        <v>0.54</v>
-      </c>
-      <c r="S43" s="55">
-        <v>5.4000000000000003E-3</v>
+        <v>6.67</v>
+      </c>
+      <c r="S43" s="54">
+        <v>9.8900000000000002E-2</v>
       </c>
       <c r="T43" s="21">
         <f t="shared" si="5"/>
-        <v>1.08</v>
-      </c>
-      <c r="U43" s="72"/>
+        <v>9.89</v>
+      </c>
+      <c r="U43" s="70"/>
       <c r="V43" s="1"/>
       <c r="W43" s="1"/>
     </row>
     <row r="44" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="10">
-        <v>41</v>
-      </c>
-      <c r="B44" s="108"/>
-      <c r="C44" s="69" t="s">
-        <v>346</v>
+      <c r="A44" s="17">
+        <v>42</v>
+      </c>
+      <c r="B44" s="139"/>
+      <c r="C44" s="68" t="s">
+        <v>207</v>
       </c>
       <c r="D44" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="E44" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="F44" s="24" t="s">
         <v>209</v>
       </c>
-      <c r="E44" s="12" t="s">
-        <v>210</v>
-      </c>
-      <c r="F44" s="24" t="s">
-        <v>211</v>
-      </c>
       <c r="G44" s="44" t="s">
-        <v>246</v>
+        <v>95</v>
       </c>
       <c r="H44" s="44" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="I44" s="12" t="s">
-        <v>247</v>
+        <v>25</v>
       </c>
       <c r="J44" s="44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K44" s="13">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L44" s="13">
         <f t="shared" si="1"/>
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M44" s="13">
         <f t="shared" si="2"/>
-        <v>100</v>
-      </c>
-      <c r="N44" s="86" t="s">
+        <v>200</v>
+      </c>
+      <c r="N44" s="84" t="s">
         <v>20</v>
       </c>
       <c r="O44" s="20">
-        <v>0.3</v>
+        <v>1.2E-2</v>
       </c>
       <c r="P44" s="21">
         <f t="shared" si="3"/>
-        <v>1.5</v>
+        <v>0.12</v>
       </c>
       <c r="Q44" s="20">
-        <v>0.13339999999999999</v>
+        <v>4.7000000000000002E-3</v>
       </c>
       <c r="R44" s="21">
         <f t="shared" si="4"/>
-        <v>6.67</v>
-      </c>
-      <c r="S44" s="55">
-        <v>9.8900000000000002E-2</v>
+        <v>0.47000000000000003</v>
+      </c>
+      <c r="S44" s="54">
+        <v>4.7000000000000002E-3</v>
       </c>
       <c r="T44" s="21">
         <f t="shared" si="5"/>
-        <v>9.89</v>
-      </c>
-      <c r="U44" s="72"/>
+        <v>0.94000000000000006</v>
+      </c>
+      <c r="U44" s="70"/>
       <c r="V44" s="1"/>
       <c r="W44" s="1"/>
     </row>
     <row r="45" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="10">
-        <v>42</v>
-      </c>
-      <c r="B45" s="108"/>
-      <c r="C45" s="69" t="s">
-        <v>212</v>
+      <c r="A45" s="17">
+        <v>43</v>
+      </c>
+      <c r="B45" s="139"/>
+      <c r="C45" s="68" t="s">
+        <v>210</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E45" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="F45" s="24" t="s">
-        <v>214</v>
+      <c r="F45" s="12" t="s">
+        <v>212</v>
       </c>
       <c r="G45" s="44" t="s">
-        <v>100</v>
-      </c>
-      <c r="H45" s="44" t="s">
-        <v>348</v>
+        <v>95</v>
+      </c>
+      <c r="H45" s="12" t="s">
+        <v>40</v>
       </c>
       <c r="I45" s="12" t="s">
-        <v>25</v>
+        <v>243</v>
       </c>
       <c r="J45" s="44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K45" s="13">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L45" s="13">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M45" s="13">
         <f t="shared" si="2"/>
-        <v>200</v>
-      </c>
-      <c r="N45" s="86" t="s">
+        <v>100</v>
+      </c>
+      <c r="N45" s="84" t="s">
         <v>20</v>
       </c>
       <c r="O45" s="20">
-        <v>1.2E-2</v>
+        <v>0.1</v>
       </c>
       <c r="P45" s="21">
         <f t="shared" si="3"/>
-        <v>0.12</v>
+        <v>0.5</v>
       </c>
       <c r="Q45" s="20">
-        <v>4.7000000000000002E-3</v>
+        <v>2.1999999999999999E-2</v>
       </c>
       <c r="R45" s="21">
         <f t="shared" si="4"/>
-        <v>0.47000000000000003</v>
-      </c>
-      <c r="S45" s="55">
-        <v>4.7000000000000002E-3</v>
+        <v>1.0999999999999999</v>
+      </c>
+      <c r="S45" s="54">
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="T45" s="21">
         <f t="shared" si="5"/>
-        <v>0.94000000000000006</v>
-      </c>
-      <c r="U45" s="72"/>
+        <v>0.89999999999999991</v>
+      </c>
+      <c r="U45" s="70"/>
       <c r="V45" s="1"/>
       <c r="W45" s="1"/>
     </row>
     <row r="46" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="10">
-        <v>43</v>
-      </c>
-      <c r="B46" s="108"/>
-      <c r="C46" s="69" t="s">
-        <v>215</v>
+      <c r="A46" s="17">
+        <v>44</v>
+      </c>
+      <c r="B46" s="139"/>
+      <c r="C46" s="68" t="s">
+        <v>213</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E46" s="12" t="s">
         <v>15</v>
       </c>
       <c r="F46" s="12" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="G46" s="44" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H46" s="12" t="s">
         <v>40</v>
       </c>
       <c r="I46" s="12" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="J46" s="44">
         <v>1</v>
@@ -5646,7 +5634,7 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N46" s="86" t="s">
+      <c r="N46" s="84" t="s">
         <v>20</v>
       </c>
       <c r="O46" s="20">
@@ -5657,48 +5645,48 @@
         <v>0.5</v>
       </c>
       <c r="Q46" s="20">
-        <v>2.1999999999999999E-2</v>
+        <v>1.6E-2</v>
       </c>
       <c r="R46" s="21">
         <f t="shared" si="4"/>
-        <v>1.0999999999999999</v>
-      </c>
-      <c r="S46" s="55">
-        <v>8.9999999999999993E-3</v>
+        <v>0.8</v>
+      </c>
+      <c r="S46" s="54">
+        <v>6.6E-3</v>
       </c>
       <c r="T46" s="21">
         <f t="shared" si="5"/>
-        <v>0.89999999999999991</v>
-      </c>
-      <c r="U46" s="72"/>
+        <v>0.66</v>
+      </c>
+      <c r="U46" s="70"/>
       <c r="V46" s="1"/>
       <c r="W46" s="1"/>
     </row>
     <row r="47" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="10">
-        <v>44</v>
-      </c>
-      <c r="B47" s="108"/>
-      <c r="C47" s="69" t="s">
-        <v>218</v>
+      <c r="A47" s="17">
+        <v>45</v>
+      </c>
+      <c r="B47" s="139"/>
+      <c r="C47" s="68" t="s">
+        <v>216</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E47" s="12" t="s">
         <v>15</v>
       </c>
       <c r="F47" s="12" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G47" s="44" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H47" s="12" t="s">
         <v>40</v>
       </c>
       <c r="I47" s="12" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="J47" s="44">
         <v>1</v>
@@ -5715,7 +5703,7 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N47" s="86" t="s">
+      <c r="N47" s="84" t="s">
         <v>20</v>
       </c>
       <c r="O47" s="20">
@@ -5732,42 +5720,42 @@
         <f t="shared" si="4"/>
         <v>0.8</v>
       </c>
-      <c r="S47" s="55">
+      <c r="S47" s="54">
         <v>6.6E-3</v>
       </c>
       <c r="T47" s="21">
         <f t="shared" si="5"/>
         <v>0.66</v>
       </c>
-      <c r="U47" s="72"/>
+      <c r="U47" s="70"/>
       <c r="V47" s="1"/>
       <c r="W47" s="1"/>
     </row>
     <row r="48" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="10">
-        <v>45</v>
-      </c>
-      <c r="B48" s="108"/>
-      <c r="C48" s="69" t="s">
-        <v>221</v>
+      <c r="A48" s="17">
+        <v>46</v>
+      </c>
+      <c r="B48" s="139"/>
+      <c r="C48" s="68" t="s">
+        <v>219</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E48" s="12" t="s">
         <v>15</v>
       </c>
       <c r="F48" s="12" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="G48" s="44" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H48" s="12" t="s">
         <v>40</v>
       </c>
       <c r="I48" s="12" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="J48" s="44">
         <v>1</v>
@@ -5784,7 +5772,7 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N48" s="86" t="s">
+      <c r="N48" s="84" t="s">
         <v>20</v>
       </c>
       <c r="O48" s="20">
@@ -5795,253 +5783,255 @@
         <v>0.5</v>
       </c>
       <c r="Q48" s="20">
-        <v>1.6E-2</v>
+        <v>2.1999999999999999E-2</v>
       </c>
       <c r="R48" s="21">
         <f t="shared" si="4"/>
-        <v>0.8</v>
-      </c>
-      <c r="S48" s="55">
-        <v>6.6E-3</v>
+        <v>1.0999999999999999</v>
+      </c>
+      <c r="S48" s="54">
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="T48" s="21">
         <f t="shared" si="5"/>
-        <v>0.66</v>
-      </c>
-      <c r="U48" s="72"/>
+        <v>0.89999999999999991</v>
+      </c>
+      <c r="U48" s="70"/>
       <c r="V48" s="1"/>
       <c r="W48" s="1"/>
     </row>
     <row r="49" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="10">
-        <v>46</v>
-      </c>
-      <c r="B49" s="108"/>
-      <c r="C49" s="69" t="s">
+      <c r="A49" s="17">
+        <v>47</v>
+      </c>
+      <c r="B49" s="140"/>
+      <c r="C49" s="71" t="s">
+        <v>345</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F49" s="28" t="s">
+        <v>223</v>
+      </c>
+      <c r="G49" s="72" t="s">
         <v>224</v>
       </c>
-      <c r="D49" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="E49" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="F49" s="12" t="s">
-        <v>226</v>
-      </c>
-      <c r="G49" s="44" t="s">
-        <v>100</v>
-      </c>
-      <c r="H49" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="I49" s="12" t="s">
-        <v>251</v>
-      </c>
-      <c r="J49" s="44">
+      <c r="H49" s="72" t="s">
+        <v>344</v>
+      </c>
+      <c r="I49" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="J49" s="72">
         <v>1</v>
       </c>
-      <c r="K49" s="13">
+      <c r="K49" s="16">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L49" s="13">
+      <c r="L49" s="16">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="M49" s="13">
+      <c r="M49" s="16">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N49" s="86" t="s">
+      <c r="N49" s="85" t="s">
         <v>20</v>
       </c>
-      <c r="O49" s="20">
+      <c r="O49" s="34">
         <v>0.1</v>
       </c>
-      <c r="P49" s="21">
+      <c r="P49" s="35">
         <f t="shared" si="3"/>
         <v>0.5</v>
       </c>
-      <c r="Q49" s="20">
-        <v>2.1999999999999999E-2</v>
-      </c>
-      <c r="R49" s="21">
+      <c r="Q49" s="34">
+        <v>3.1E-2</v>
+      </c>
+      <c r="R49" s="35">
         <f t="shared" si="4"/>
-        <v>1.0999999999999999</v>
-      </c>
-      <c r="S49" s="55">
-        <v>8.9999999999999993E-3</v>
-      </c>
-      <c r="T49" s="21">
+        <v>1.55</v>
+      </c>
+      <c r="S49" s="56">
+        <v>1.2500000000000001E-2</v>
+      </c>
+      <c r="T49" s="35">
         <f t="shared" si="5"/>
-        <v>0.89999999999999991</v>
-      </c>
-      <c r="U49" s="72"/>
+        <v>1.25</v>
+      </c>
+      <c r="U49" s="73"/>
       <c r="V49" s="1"/>
       <c r="W49" s="1"/>
     </row>
     <row r="50" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="10">
-        <v>47</v>
-      </c>
-      <c r="B50" s="109"/>
-      <c r="C50" s="73" t="s">
-        <v>350</v>
-      </c>
-      <c r="D50" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="E50" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F50" s="28" t="s">
-        <v>228</v>
-      </c>
-      <c r="G50" s="74" t="s">
-        <v>229</v>
-      </c>
-      <c r="H50" s="74" t="s">
-        <v>349</v>
-      </c>
-      <c r="I50" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="J50" s="74">
+      <c r="A50" s="17">
+        <v>48</v>
+      </c>
+      <c r="B50" s="138" t="s">
+        <v>38</v>
+      </c>
+      <c r="C50" s="65" t="s">
+        <v>249</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="G50" s="66" t="s">
+        <v>275</v>
+      </c>
+      <c r="H50" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="I50" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J50" s="66">
         <v>1</v>
       </c>
-      <c r="K50" s="16">
+      <c r="K50" s="8">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L50" s="16">
+      <c r="L50" s="8">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="M50" s="16">
+      <c r="M50" s="8">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N50" s="87" t="s">
+      <c r="N50" s="89" t="s">
         <v>20</v>
       </c>
-      <c r="O50" s="34">
-        <v>0.1</v>
-      </c>
-      <c r="P50" s="35">
+      <c r="O50" s="32">
+        <v>1.2</v>
+      </c>
+      <c r="P50" s="33">
         <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="Q50" s="34">
-        <v>3.1E-2</v>
-      </c>
-      <c r="R50" s="35">
+        <v>6</v>
+      </c>
+      <c r="Q50" s="32">
+        <v>1.2</v>
+      </c>
+      <c r="R50" s="33">
         <f t="shared" si="4"/>
-        <v>1.55</v>
-      </c>
-      <c r="S50" s="57">
-        <v>1.2500000000000001E-2</v>
-      </c>
-      <c r="T50" s="35">
+        <v>60</v>
+      </c>
+      <c r="S50" s="53">
+        <v>1</v>
+      </c>
+      <c r="T50" s="33">
         <f t="shared" si="5"/>
-        <v>1.25</v>
-      </c>
-      <c r="U50" s="75"/>
+        <v>100</v>
+      </c>
+      <c r="U50" s="114" t="s">
+        <v>353</v>
+      </c>
       <c r="V50" s="1"/>
       <c r="W50" s="1"/>
     </row>
     <row r="51" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="10">
-        <v>48</v>
-      </c>
-      <c r="B51" s="107" t="s">
-        <v>38</v>
-      </c>
-      <c r="C51" s="66" t="s">
-        <v>254</v>
-      </c>
-      <c r="D51" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E51" s="7" t="s">
-        <v>338</v>
-      </c>
-      <c r="F51" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="G51" s="67" t="s">
-        <v>280</v>
-      </c>
-      <c r="H51" s="7" t="s">
+      <c r="A51" s="17">
+        <v>49</v>
+      </c>
+      <c r="B51" s="139"/>
+      <c r="C51" s="68" t="s">
+        <v>251</v>
+      </c>
+      <c r="D51" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="E51" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="F51" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="G51" s="44" t="s">
+        <v>276</v>
+      </c>
+      <c r="H51" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="I51" s="7" t="s">
+      <c r="I51" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J51" s="67">
+      <c r="J51" s="44">
         <v>1</v>
       </c>
-      <c r="K51" s="8">
+      <c r="K51" s="13">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L51" s="8">
+      <c r="L51" s="13">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="M51" s="8">
+      <c r="M51" s="13">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N51" s="92" t="s">
-        <v>20</v>
-      </c>
-      <c r="O51" s="32">
-        <v>1.2</v>
-      </c>
-      <c r="P51" s="33">
+      <c r="N51" s="84" t="s">
+        <v>324</v>
+      </c>
+      <c r="O51" s="20">
+        <v>0.65400000000000003</v>
+      </c>
+      <c r="P51" s="21">
         <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-      <c r="Q51" s="32">
-        <v>1.2</v>
-      </c>
-      <c r="R51" s="33">
+        <v>3.27</v>
+      </c>
+      <c r="Q51" s="20">
+        <v>0.57599999999999996</v>
+      </c>
+      <c r="R51" s="21">
         <f t="shared" si="4"/>
-        <v>60</v>
+        <v>28.799999999999997</v>
       </c>
       <c r="S51" s="54">
-        <v>1</v>
-      </c>
-      <c r="T51" s="33">
+        <v>0.442</v>
+      </c>
+      <c r="T51" s="21">
         <f t="shared" si="5"/>
-        <v>100</v>
-      </c>
-      <c r="U51" s="128" t="s">
-        <v>359</v>
+        <v>44.2</v>
+      </c>
+      <c r="U51" s="99" t="s">
+        <v>353</v>
       </c>
       <c r="V51" s="1"/>
       <c r="W51" s="1"/>
     </row>
     <row r="52" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="10">
-        <v>49</v>
-      </c>
-      <c r="B52" s="108"/>
-      <c r="C52" s="69" t="s">
+      <c r="A52" s="17">
+        <v>50</v>
+      </c>
+      <c r="B52" s="139"/>
+      <c r="C52" s="68" t="s">
+        <v>254</v>
+      </c>
+      <c r="D52" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="E52" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="F52" s="12" t="s">
         <v>256</v>
       </c>
-      <c r="D52" s="12" t="s">
-        <v>257</v>
-      </c>
-      <c r="E52" s="12" t="s">
-        <v>339</v>
-      </c>
-      <c r="F52" s="12" t="s">
-        <v>258</v>
-      </c>
       <c r="G52" s="44" t="s">
-        <v>281</v>
+        <v>154</v>
       </c>
       <c r="H52" s="12" t="s">
         <v>40</v>
@@ -6064,55 +6054,55 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N52" s="86" t="s">
-        <v>329</v>
+      <c r="N52" s="84" t="s">
+        <v>20</v>
       </c>
       <c r="O52" s="20">
-        <v>0.65400000000000003</v>
+        <v>0.54</v>
       </c>
       <c r="P52" s="21">
         <f t="shared" si="3"/>
-        <v>3.27</v>
+        <v>2.7</v>
       </c>
       <c r="Q52" s="20">
-        <v>0.57599999999999996</v>
+        <v>0.4284</v>
       </c>
       <c r="R52" s="21">
         <f t="shared" si="4"/>
-        <v>28.799999999999997</v>
-      </c>
-      <c r="S52" s="55">
-        <v>0.442</v>
+        <v>21.42</v>
+      </c>
+      <c r="S52" s="54">
+        <v>0.34279999999999999</v>
       </c>
       <c r="T52" s="21">
         <f t="shared" si="5"/>
-        <v>44.2</v>
-      </c>
-      <c r="U52" s="113" t="s">
-        <v>359</v>
+        <v>34.28</v>
+      </c>
+      <c r="U52" s="99" t="s">
+        <v>353</v>
       </c>
       <c r="V52" s="1"/>
       <c r="W52" s="1"/>
     </row>
     <row r="53" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="10">
-        <v>50</v>
-      </c>
-      <c r="B53" s="108"/>
-      <c r="C53" s="69" t="s">
-        <v>259</v>
+      <c r="A53" s="17">
+        <v>51</v>
+      </c>
+      <c r="B53" s="139"/>
+      <c r="C53" s="68" t="s">
+        <v>257</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>260</v>
+        <v>28</v>
       </c>
       <c r="E53" s="12" t="s">
-        <v>131</v>
+        <v>331</v>
       </c>
       <c r="F53" s="12" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="G53" s="44" t="s">
-        <v>159</v>
+        <v>277</v>
       </c>
       <c r="H53" s="12" t="s">
         <v>40</v>
@@ -6135,55 +6125,53 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N53" s="86" t="s">
+      <c r="N53" s="84" t="s">
         <v>20</v>
       </c>
       <c r="O53" s="20">
-        <v>0.54</v>
+        <v>0.38</v>
       </c>
       <c r="P53" s="21">
         <f t="shared" si="3"/>
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="Q53" s="20">
-        <v>0.4284</v>
+        <v>0.28239999999999998</v>
       </c>
       <c r="R53" s="21">
         <f t="shared" si="4"/>
-        <v>21.42</v>
-      </c>
-      <c r="S53" s="55">
-        <v>0.34279999999999999</v>
+        <v>14.12</v>
+      </c>
+      <c r="S53" s="54">
+        <v>0.21029999999999999</v>
       </c>
       <c r="T53" s="21">
         <f t="shared" si="5"/>
-        <v>34.28</v>
-      </c>
-      <c r="U53" s="113" t="s">
-        <v>359</v>
-      </c>
+        <v>21.029999999999998</v>
+      </c>
+      <c r="U53" s="70"/>
       <c r="V53" s="1"/>
       <c r="W53" s="1"/>
     </row>
     <row r="54" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="10">
-        <v>51</v>
-      </c>
-      <c r="B54" s="108"/>
-      <c r="C54" s="69" t="s">
-        <v>262</v>
+      <c r="A54" s="17">
+        <v>52</v>
+      </c>
+      <c r="B54" s="139"/>
+      <c r="C54" s="68" t="s">
+        <v>259</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E54" s="12" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F54" s="12" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="G54" s="44" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="H54" s="12" t="s">
         <v>40</v>
@@ -6206,53 +6194,55 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N54" s="86" t="s">
+      <c r="N54" s="84" t="s">
         <v>20</v>
       </c>
       <c r="O54" s="20">
-        <v>0.38</v>
+        <v>4.2300000000000004</v>
       </c>
       <c r="P54" s="21">
         <f t="shared" si="3"/>
-        <v>1.9</v>
+        <v>21.150000000000002</v>
       </c>
       <c r="Q54" s="20">
-        <v>0.28239999999999998</v>
+        <v>3.8412000000000002</v>
       </c>
       <c r="R54" s="21">
         <f t="shared" si="4"/>
-        <v>14.12</v>
-      </c>
-      <c r="S54" s="55">
-        <v>0.21029999999999999</v>
+        <v>192.06</v>
+      </c>
+      <c r="S54" s="54">
+        <v>3.8250000000000002</v>
       </c>
       <c r="T54" s="21">
         <f t="shared" si="5"/>
-        <v>21.029999999999998</v>
-      </c>
-      <c r="U54" s="72"/>
+        <v>382.5</v>
+      </c>
+      <c r="U54" s="99" t="s">
+        <v>353</v>
+      </c>
       <c r="V54" s="1"/>
       <c r="W54" s="1"/>
     </row>
     <row r="55" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="10">
-        <v>52</v>
-      </c>
-      <c r="B55" s="108"/>
-      <c r="C55" s="69" t="s">
-        <v>264</v>
+      <c r="A55" s="17">
+        <v>53</v>
+      </c>
+      <c r="B55" s="139"/>
+      <c r="C55" s="68" t="s">
+        <v>261</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E55" s="12" t="s">
-        <v>340</v>
+        <v>45</v>
       </c>
       <c r="F55" s="12" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="G55" s="44" t="s">
-        <v>283</v>
+        <v>44</v>
       </c>
       <c r="H55" s="12" t="s">
         <v>40</v>
@@ -6275,52 +6265,50 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N55" s="86" t="s">
-        <v>20</v>
+      <c r="N55" s="84" t="s">
+        <v>325</v>
       </c>
       <c r="O55" s="20">
-        <v>4.2300000000000004</v>
+        <v>1.3006</v>
       </c>
       <c r="P55" s="21">
         <f t="shared" si="3"/>
-        <v>21.150000000000002</v>
+        <v>6.5030000000000001</v>
       </c>
       <c r="Q55" s="20">
-        <v>3.8412000000000002</v>
+        <v>1.0849</v>
       </c>
       <c r="R55" s="21">
         <f t="shared" si="4"/>
-        <v>192.06</v>
-      </c>
-      <c r="S55" s="55">
-        <v>3.8250000000000002</v>
+        <v>54.244999999999997</v>
+      </c>
+      <c r="S55" s="54">
+        <v>0.82869999999999999</v>
       </c>
       <c r="T55" s="21">
         <f t="shared" si="5"/>
-        <v>382.5</v>
-      </c>
-      <c r="U55" s="113" t="s">
-        <v>359</v>
-      </c>
+        <v>82.87</v>
+      </c>
+      <c r="U55" s="70"/>
       <c r="V55" s="1"/>
       <c r="W55" s="1"/>
     </row>
     <row r="56" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="10">
-        <v>53</v>
-      </c>
-      <c r="B56" s="108"/>
-      <c r="C56" s="69" t="s">
-        <v>266</v>
+      <c r="A56" s="17">
+        <v>54</v>
+      </c>
+      <c r="B56" s="139"/>
+      <c r="C56" s="68" t="s">
+        <v>263</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E56" s="12" t="s">
-        <v>45</v>
+        <v>264</v>
       </c>
       <c r="F56" s="12" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G56" s="44" t="s">
         <v>44</v>
@@ -6346,53 +6334,55 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N56" s="86" t="s">
-        <v>330</v>
+      <c r="N56" s="84" t="s">
+        <v>20</v>
       </c>
       <c r="O56" s="20">
-        <v>1.3006</v>
+        <v>2.4</v>
       </c>
       <c r="P56" s="21">
         <f t="shared" si="3"/>
-        <v>6.5030000000000001</v>
+        <v>12</v>
       </c>
       <c r="Q56" s="20">
-        <v>1.0849</v>
+        <v>2.0352000000000001</v>
       </c>
       <c r="R56" s="21">
         <f t="shared" si="4"/>
-        <v>54.244999999999997</v>
-      </c>
-      <c r="S56" s="55">
-        <v>0.82869999999999999</v>
+        <v>101.76</v>
+      </c>
+      <c r="S56" s="54">
+        <v>1.734</v>
       </c>
       <c r="T56" s="21">
         <f t="shared" si="5"/>
-        <v>82.87</v>
-      </c>
-      <c r="U56" s="72"/>
+        <v>173.4</v>
+      </c>
+      <c r="U56" s="99" t="s">
+        <v>353</v>
+      </c>
       <c r="V56" s="1"/>
       <c r="W56" s="1"/>
     </row>
-    <row r="57" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="10">
-        <v>54</v>
-      </c>
-      <c r="B57" s="108"/>
-      <c r="C57" s="69" t="s">
-        <v>268</v>
+    <row r="57" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="17">
+        <v>55</v>
+      </c>
+      <c r="B57" s="139"/>
+      <c r="C57" s="68" t="s">
+        <v>266</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E57" s="12" t="s">
-        <v>269</v>
+        <v>331</v>
       </c>
       <c r="F57" s="12" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G57" s="44" t="s">
-        <v>44</v>
+        <v>278</v>
       </c>
       <c r="H57" s="12" t="s">
         <v>40</v>
@@ -6415,55 +6405,55 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N57" s="86" t="s">
+      <c r="N57" s="84" t="s">
         <v>20</v>
       </c>
       <c r="O57" s="20">
-        <v>2.4</v>
+        <v>0.86</v>
       </c>
       <c r="P57" s="21">
         <f t="shared" si="3"/>
-        <v>12</v>
+        <v>4.3</v>
       </c>
       <c r="Q57" s="20">
-        <v>2.0352000000000001</v>
+        <v>0.86</v>
       </c>
       <c r="R57" s="21">
         <f t="shared" si="4"/>
-        <v>101.76</v>
-      </c>
-      <c r="S57" s="55">
-        <v>1.734</v>
+        <v>43</v>
+      </c>
+      <c r="S57" s="54">
+        <v>0.86</v>
       </c>
       <c r="T57" s="21">
         <f t="shared" si="5"/>
-        <v>173.4</v>
-      </c>
-      <c r="U57" s="113" t="s">
-        <v>359</v>
+        <v>86</v>
+      </c>
+      <c r="U57" s="99" t="s">
+        <v>353</v>
       </c>
       <c r="V57" s="1"/>
       <c r="W57" s="1"/>
     </row>
-    <row r="58" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="10">
-        <v>55</v>
-      </c>
-      <c r="B58" s="108"/>
-      <c r="C58" s="69" t="s">
-        <v>271</v>
+    <row r="58" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="17">
+        <v>56</v>
+      </c>
+      <c r="B58" s="139"/>
+      <c r="C58" s="68" t="s">
+        <v>268</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>32</v>
+        <v>269</v>
       </c>
       <c r="E58" s="12" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="F58" s="12" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="G58" s="44" t="s">
-        <v>283</v>
+        <v>44</v>
       </c>
       <c r="H58" s="12" t="s">
         <v>40</v>
@@ -6486,272 +6476,268 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N58" s="86" t="s">
+      <c r="N58" s="84" t="s">
         <v>20</v>
       </c>
       <c r="O58" s="20">
-        <v>0.86</v>
+        <v>4.01</v>
       </c>
       <c r="P58" s="21">
         <f t="shared" si="3"/>
-        <v>4.3</v>
+        <v>20.049999999999997</v>
       </c>
       <c r="Q58" s="20">
-        <v>0.86</v>
+        <v>3.4079999999999999</v>
       </c>
       <c r="R58" s="21">
         <f t="shared" si="4"/>
-        <v>43</v>
-      </c>
-      <c r="S58" s="55">
-        <v>0.86</v>
+        <v>170.4</v>
+      </c>
+      <c r="S58" s="54">
+        <v>2.9537</v>
       </c>
       <c r="T58" s="21">
         <f t="shared" si="5"/>
-        <v>86</v>
-      </c>
-      <c r="U58" s="113" t="s">
-        <v>359</v>
-      </c>
+        <v>295.37</v>
+      </c>
+      <c r="U58" s="70"/>
       <c r="V58" s="1"/>
       <c r="W58" s="1"/>
     </row>
     <row r="59" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="10">
-        <v>56</v>
-      </c>
-      <c r="B59" s="108"/>
-      <c r="C59" s="69" t="s">
+      <c r="A59" s="17">
+        <v>57</v>
+      </c>
+      <c r="B59" s="140"/>
+      <c r="C59" s="71" t="s">
+        <v>271</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="E59" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="D59" s="12" t="s">
+      <c r="F59" s="28" t="s">
         <v>274</v>
       </c>
-      <c r="E59" s="12" t="s">
-        <v>336</v>
-      </c>
-      <c r="F59" s="12" t="s">
-        <v>275</v>
-      </c>
-      <c r="G59" s="44" t="s">
-        <v>44</v>
-      </c>
-      <c r="H59" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="I59" s="12" t="s">
+      <c r="G59" s="72" t="s">
+        <v>279</v>
+      </c>
+      <c r="H59" s="72" t="s">
+        <v>332</v>
+      </c>
+      <c r="I59" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="J59" s="44">
+      <c r="J59" s="72">
         <v>1</v>
       </c>
-      <c r="K59" s="13">
+      <c r="K59" s="16">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L59" s="13">
+      <c r="L59" s="16">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="M59" s="13">
+      <c r="M59" s="16">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N59" s="86" t="s">
+      <c r="N59" s="85" t="s">
         <v>20</v>
       </c>
-      <c r="O59" s="20">
-        <v>4.01</v>
-      </c>
-      <c r="P59" s="21">
+      <c r="O59" s="34">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="P59" s="35">
         <f t="shared" si="3"/>
-        <v>20.049999999999997</v>
-      </c>
-      <c r="Q59" s="20">
-        <v>3.4079999999999999</v>
-      </c>
-      <c r="R59" s="21">
+        <v>5.75</v>
+      </c>
+      <c r="Q59" s="34">
+        <v>0.97960000000000003</v>
+      </c>
+      <c r="R59" s="35">
         <f t="shared" si="4"/>
-        <v>170.4</v>
-      </c>
-      <c r="S59" s="55">
-        <v>2.9537</v>
-      </c>
-      <c r="T59" s="21">
+        <v>48.980000000000004</v>
+      </c>
+      <c r="S59" s="56">
+        <v>0.80449999999999999</v>
+      </c>
+      <c r="T59" s="35">
         <f t="shared" si="5"/>
-        <v>295.37</v>
-      </c>
-      <c r="U59" s="72"/>
+        <v>80.45</v>
+      </c>
+      <c r="U59" s="73"/>
       <c r="V59" s="1"/>
       <c r="W59" s="1"/>
     </row>
-    <row r="60" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="10">
-        <v>57</v>
-      </c>
-      <c r="B60" s="109"/>
-      <c r="C60" s="73" t="s">
-        <v>276</v>
-      </c>
-      <c r="D60" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="E60" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="F60" s="28" t="s">
-        <v>279</v>
-      </c>
-      <c r="G60" s="74" t="s">
-        <v>284</v>
-      </c>
-      <c r="H60" s="74" t="s">
-        <v>337</v>
-      </c>
-      <c r="I60" s="6" t="s">
+    <row r="60" spans="1:23" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="17">
+        <v>58</v>
+      </c>
+      <c r="B60" s="138" t="s">
+        <v>19</v>
+      </c>
+      <c r="C60" s="30" t="s">
+        <v>280</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E60" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F60" s="42" t="s">
+        <v>281</v>
+      </c>
+      <c r="G60" s="66" t="s">
+        <v>41</v>
+      </c>
+      <c r="H60" s="103" t="s">
+        <v>354</v>
+      </c>
+      <c r="I60" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="J60" s="74">
+      <c r="J60" s="66">
         <v>1</v>
       </c>
-      <c r="K60" s="16">
+      <c r="K60" s="8">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L60" s="16">
+      <c r="L60" s="8">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="M60" s="16">
+      <c r="M60" s="8">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N60" s="87" t="s">
+      <c r="N60" s="117" t="s">
         <v>20</v>
       </c>
-      <c r="O60" s="34">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="P60" s="35">
+      <c r="O60" s="32">
+        <v>0.73</v>
+      </c>
+      <c r="P60" s="33">
         <f t="shared" si="3"/>
-        <v>5.75</v>
-      </c>
-      <c r="Q60" s="34">
-        <v>0.97960000000000003</v>
-      </c>
-      <c r="R60" s="35">
+        <v>3.65</v>
+      </c>
+      <c r="Q60" s="32">
+        <v>0.73</v>
+      </c>
+      <c r="R60" s="33">
         <f t="shared" si="4"/>
-        <v>48.980000000000004</v>
-      </c>
-      <c r="S60" s="57">
-        <v>0.80449999999999999</v>
-      </c>
-      <c r="T60" s="35">
+        <v>36.5</v>
+      </c>
+      <c r="S60" s="53">
+        <v>0.73</v>
+      </c>
+      <c r="T60" s="33">
         <f t="shared" si="5"/>
-        <v>80.45</v>
-      </c>
-      <c r="U60" s="75"/>
-      <c r="V60" s="1"/>
-      <c r="W60" s="1"/>
+        <v>73</v>
+      </c>
+      <c r="U60" s="115" t="s">
+        <v>350</v>
+      </c>
     </row>
-    <row r="61" spans="1:23" ht="39" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="10">
-        <v>58</v>
-      </c>
-      <c r="B61" s="107" t="s">
-        <v>19</v>
-      </c>
-      <c r="C61" s="30" t="s">
-        <v>285</v>
-      </c>
-      <c r="D61" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="E61" s="7" t="s">
+    <row r="61" spans="1:23" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="17">
+        <v>59</v>
+      </c>
+      <c r="B61" s="139"/>
+      <c r="C61" s="23" t="s">
+        <v>282</v>
+      </c>
+      <c r="D61" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E61" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="F61" s="42" t="s">
-        <v>286</v>
-      </c>
-      <c r="G61" s="67" t="s">
-        <v>41</v>
-      </c>
-      <c r="H61" s="117" t="s">
-        <v>360</v>
-      </c>
-      <c r="I61" s="7" t="s">
+      <c r="F61" s="24" t="s">
+        <v>283</v>
+      </c>
+      <c r="G61" s="44" t="s">
+        <v>156</v>
+      </c>
+      <c r="H61" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="I61" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J61" s="67">
+      <c r="J61" s="44">
         <v>1</v>
       </c>
-      <c r="K61" s="8">
+      <c r="K61" s="13">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L61" s="8">
+      <c r="L61" s="13">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="M61" s="8">
+      <c r="M61" s="13">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N61" s="131" t="s">
+      <c r="N61" s="96" t="s">
         <v>20</v>
       </c>
-      <c r="O61" s="32">
-        <v>0.73</v>
-      </c>
-      <c r="P61" s="33">
+      <c r="O61" s="20">
+        <v>1.01</v>
+      </c>
+      <c r="P61" s="21">
         <f t="shared" si="3"/>
-        <v>3.65</v>
-      </c>
-      <c r="Q61" s="32">
-        <v>0.73</v>
-      </c>
-      <c r="R61" s="33">
+        <v>5.05</v>
+      </c>
+      <c r="Q61" s="20">
+        <v>0.79800000000000004</v>
+      </c>
+      <c r="R61" s="21">
         <f t="shared" si="4"/>
-        <v>36.5</v>
+        <v>39.900000000000006</v>
       </c>
       <c r="S61" s="54">
-        <v>0.73</v>
-      </c>
-      <c r="T61" s="33">
+        <v>0.76339999999999997</v>
+      </c>
+      <c r="T61" s="21">
         <f t="shared" si="5"/>
-        <v>73</v>
-      </c>
-      <c r="U61" s="129" t="s">
+        <v>76.34</v>
+      </c>
+      <c r="U61" s="97"/>
+    </row>
+    <row r="62" spans="1:23" s="18" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="17">
+        <v>60</v>
+      </c>
+      <c r="B62" s="139"/>
+      <c r="C62" s="23" t="s">
+        <v>284</v>
+      </c>
+      <c r="D62" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E62" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="F62" s="98" t="s">
+        <v>285</v>
+      </c>
+      <c r="G62" s="13" t="s">
+        <v>357</v>
+      </c>
+      <c r="H62" s="44" t="s">
         <v>356</v>
       </c>
-    </row>
-    <row r="62" spans="1:23" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="10">
-        <v>59</v>
-      </c>
-      <c r="B62" s="108"/>
-      <c r="C62" s="23" t="s">
-        <v>287</v>
-      </c>
-      <c r="D62" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E62" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="F62" s="24" t="s">
-        <v>288</v>
-      </c>
-      <c r="G62" s="44" t="s">
-        <v>161</v>
-      </c>
-      <c r="H62" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="I62" s="12" t="s">
+      <c r="I62" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="J62" s="44">
+      <c r="J62" s="13">
         <v>1</v>
       </c>
       <c r="K62" s="13">
@@ -6766,59 +6752,61 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N62" s="110" t="s">
+      <c r="N62" s="129" t="s">
         <v>20</v>
       </c>
-      <c r="O62" s="20">
-        <v>1.01</v>
+      <c r="O62" s="21">
+        <v>0.35</v>
       </c>
       <c r="P62" s="21">
         <f t="shared" si="3"/>
-        <v>5.05</v>
-      </c>
-      <c r="Q62" s="20">
-        <v>0.79800000000000004</v>
+        <v>1.75</v>
+      </c>
+      <c r="Q62" s="21">
+        <v>0.24099999999999999</v>
       </c>
       <c r="R62" s="21">
         <f t="shared" si="4"/>
-        <v>39.900000000000006</v>
-      </c>
-      <c r="S62" s="55">
-        <v>0.76339999999999997</v>
+        <v>12.049999999999999</v>
+      </c>
+      <c r="S62" s="54">
+        <v>0.23150000000000001</v>
       </c>
       <c r="T62" s="21">
         <f t="shared" si="5"/>
-        <v>76.34</v>
-      </c>
-      <c r="U62" s="111"/>
+        <v>23.150000000000002</v>
+      </c>
+      <c r="U62" s="97" t="s">
+        <v>350</v>
+      </c>
     </row>
-    <row r="63" spans="1:23" s="18" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="17">
-        <v>60</v>
-      </c>
-      <c r="B63" s="108"/>
-      <c r="C63" s="23" t="s">
-        <v>289</v>
-      </c>
-      <c r="D63" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="E63" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="B63" s="139"/>
+      <c r="C63" s="68" t="s">
+        <v>286</v>
+      </c>
+      <c r="D63" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E63" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="F63" s="112" t="s">
-        <v>290</v>
-      </c>
-      <c r="G63" s="13" t="s">
-        <v>363</v>
-      </c>
-      <c r="H63" s="44" t="s">
-        <v>362</v>
-      </c>
-      <c r="I63" s="11" t="s">
+      <c r="F63" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="G63" s="44" t="s">
+        <v>309</v>
+      </c>
+      <c r="H63" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="I63" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J63" s="13">
+      <c r="J63" s="44">
         <v>1</v>
       </c>
       <c r="K63" s="13">
@@ -6833,187 +6821,187 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N63" s="143" t="s">
+      <c r="N63" s="84" t="s">
         <v>20</v>
       </c>
-      <c r="O63" s="21">
-        <v>0.35</v>
+      <c r="O63" s="20">
+        <v>0.96</v>
       </c>
       <c r="P63" s="21">
         <f t="shared" si="3"/>
-        <v>1.75</v>
-      </c>
-      <c r="Q63" s="21">
-        <v>0.24099999999999999</v>
+        <v>4.8</v>
+      </c>
+      <c r="Q63" s="20">
+        <v>0.81499999999999995</v>
       </c>
       <c r="R63" s="21">
         <f t="shared" si="4"/>
-        <v>12.049999999999999</v>
-      </c>
-      <c r="S63" s="55">
-        <v>0.23150000000000001</v>
+        <v>40.75</v>
+      </c>
+      <c r="S63" s="54">
+        <v>0.73180000000000001</v>
       </c>
       <c r="T63" s="21">
         <f t="shared" si="5"/>
-        <v>23.150000000000002</v>
-      </c>
-      <c r="U63" s="111" t="s">
-        <v>356</v>
-      </c>
+        <v>73.180000000000007</v>
+      </c>
+      <c r="U63" s="70"/>
     </row>
     <row r="64" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="10">
-        <v>61</v>
-      </c>
-      <c r="B64" s="108"/>
-      <c r="C64" s="69" t="s">
-        <v>291</v>
-      </c>
-      <c r="D64" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="E64" s="12" t="s">
+      <c r="A64" s="17">
+        <v>62</v>
+      </c>
+      <c r="B64" s="139"/>
+      <c r="C64" s="104" t="s">
+        <v>288</v>
+      </c>
+      <c r="D64" s="24" t="s">
+        <v>289</v>
+      </c>
+      <c r="E64" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="F64" s="12" t="s">
-        <v>292</v>
-      </c>
-      <c r="G64" s="44" t="s">
-        <v>314</v>
-      </c>
-      <c r="H64" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="I64" s="12" t="s">
+      <c r="F64" s="24" t="s">
+        <v>290</v>
+      </c>
+      <c r="G64" s="105" t="s">
+        <v>310</v>
+      </c>
+      <c r="H64" s="110"/>
+      <c r="I64" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="J64" s="44">
+      <c r="J64" s="105">
         <v>1</v>
       </c>
-      <c r="K64" s="13">
+      <c r="K64" s="111">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L64" s="13">
+      <c r="L64" s="111">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="M64" s="13">
+      <c r="M64" s="111">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N64" s="86" t="s">
-        <v>20</v>
-      </c>
-      <c r="O64" s="20">
-        <v>0.96</v>
-      </c>
-      <c r="P64" s="21">
-        <f t="shared" si="3"/>
-        <v>4.8</v>
-      </c>
-      <c r="Q64" s="20">
-        <v>0.81499999999999995</v>
-      </c>
-      <c r="R64" s="21">
-        <f t="shared" si="4"/>
-        <v>40.75</v>
-      </c>
-      <c r="S64" s="55">
-        <v>0.73180000000000001</v>
-      </c>
-      <c r="T64" s="21">
-        <f t="shared" si="5"/>
-        <v>73.180000000000007</v>
-      </c>
-      <c r="U64" s="72"/>
+      <c r="N64" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="O64" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="P64" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q64" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="R64" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="S64" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="T64" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="U64" s="97" t="s">
+        <v>362</v>
+      </c>
     </row>
     <row r="65" spans="1:21" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="10">
-        <v>62</v>
-      </c>
-      <c r="B65" s="108"/>
-      <c r="C65" s="118" t="s">
+      <c r="A65" s="17">
+        <v>63</v>
+      </c>
+      <c r="B65" s="139"/>
+      <c r="C65" s="68" t="s">
+        <v>291</v>
+      </c>
+      <c r="D65" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="E65" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F65" s="24" t="s">
         <v>293</v>
       </c>
-      <c r="D65" s="24" t="s">
-        <v>294</v>
-      </c>
-      <c r="E65" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="F65" s="24" t="s">
-        <v>295</v>
-      </c>
-      <c r="G65" s="119" t="s">
-        <v>315</v>
-      </c>
-      <c r="H65" s="124"/>
-      <c r="I65" s="24" t="s">
+      <c r="G65" s="44" t="s">
+        <v>311</v>
+      </c>
+      <c r="H65" s="44" t="s">
+        <v>358</v>
+      </c>
+      <c r="I65" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J65" s="119">
+      <c r="J65" s="44">
         <v>1</v>
       </c>
-      <c r="K65" s="125">
+      <c r="K65" s="13">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L65" s="125">
+      <c r="L65" s="13">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="M65" s="125">
+      <c r="M65" s="13">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N65" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="O65" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="P65" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q65" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="R65" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="S65" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="T65" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="U65" s="111" t="s">
-        <v>368</v>
+      <c r="N65" s="84" t="s">
+        <v>20</v>
+      </c>
+      <c r="O65" s="20">
+        <v>0.45</v>
+      </c>
+      <c r="P65" s="21">
+        <f t="shared" si="3"/>
+        <v>2.25</v>
+      </c>
+      <c r="Q65" s="20">
+        <v>0.45</v>
+      </c>
+      <c r="R65" s="21">
+        <f t="shared" si="4"/>
+        <v>22.5</v>
+      </c>
+      <c r="S65" s="54">
+        <v>0.4</v>
+      </c>
+      <c r="T65" s="21">
+        <f t="shared" si="5"/>
+        <v>40</v>
+      </c>
+      <c r="U65" s="97" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="66" spans="1:21" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="10">
-        <v>63</v>
-      </c>
-      <c r="B66" s="108"/>
-      <c r="C66" s="69" t="s">
-        <v>296</v>
+      <c r="A66" s="17">
+        <v>64</v>
+      </c>
+      <c r="B66" s="139"/>
+      <c r="C66" s="68" t="s">
+        <v>294</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E66" s="12" t="s">
         <v>41</v>
       </c>
       <c r="F66" s="24" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G66" s="44" t="s">
-        <v>316</v>
-      </c>
-      <c r="H66" s="44" t="s">
-        <v>364</v>
+        <v>312</v>
+      </c>
+      <c r="H66" s="44">
+        <v>1715260000</v>
       </c>
       <c r="I66" s="12" t="s">
         <v>21</v>
@@ -7033,190 +7021,187 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N66" s="86" t="s">
+      <c r="N66" s="84" t="s">
         <v>20</v>
       </c>
       <c r="O66" s="20">
-        <v>0.45</v>
+        <v>2.13</v>
       </c>
       <c r="P66" s="21">
         <f t="shared" si="3"/>
-        <v>2.25</v>
+        <v>10.649999999999999</v>
       </c>
       <c r="Q66" s="20">
-        <v>0.45</v>
+        <v>1.3431999999999999</v>
       </c>
       <c r="R66" s="21">
         <f t="shared" si="4"/>
-        <v>22.5</v>
-      </c>
-      <c r="S66" s="55">
-        <v>0.4</v>
+        <v>67.16</v>
+      </c>
+      <c r="S66" s="54">
+        <v>1.3104</v>
       </c>
       <c r="T66" s="21">
         <f t="shared" si="5"/>
-        <v>40</v>
-      </c>
-      <c r="U66" s="111" t="s">
-        <v>356</v>
+        <v>131.04</v>
+      </c>
+      <c r="U66" s="97" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="67" spans="1:21" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="10">
-        <v>64</v>
-      </c>
-      <c r="B67" s="108"/>
-      <c r="C67" s="69" t="s">
-        <v>299</v>
+      <c r="A67" s="17">
+        <v>65</v>
+      </c>
+      <c r="B67" s="139"/>
+      <c r="C67" s="68" t="s">
+        <v>294</v>
       </c>
       <c r="D67" s="12" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="E67" s="12" t="s">
         <v>41</v>
       </c>
       <c r="F67" s="24" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="G67" s="44" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="H67" s="44">
-        <v>1715260000</v>
+        <v>1711725</v>
       </c>
       <c r="I67" s="12" t="s">
         <v>21</v>
       </c>
       <c r="J67" s="44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K67" s="13">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <f t="shared" ref="K67:K71" si="6">J67*5</f>
+        <v>10</v>
       </c>
       <c r="L67" s="13">
-        <f t="shared" si="1"/>
-        <v>50</v>
+        <f t="shared" ref="L67:L71" si="7">J67*50</f>
+        <v>100</v>
       </c>
       <c r="M67" s="13">
-        <f t="shared" si="2"/>
-        <v>100</v>
-      </c>
-      <c r="N67" s="86" t="s">
+        <f t="shared" ref="M67:M71" si="8">J67*100</f>
+        <v>200</v>
+      </c>
+      <c r="N67" s="84" t="s">
         <v>20</v>
       </c>
       <c r="O67" s="20">
-        <v>2.13</v>
+        <v>2.1120000000000001</v>
       </c>
       <c r="P67" s="21">
-        <f t="shared" si="3"/>
-        <v>10.649999999999999</v>
+        <f t="shared" ref="P67:P70" si="9">O67*K67</f>
+        <v>21.12</v>
       </c>
       <c r="Q67" s="20">
-        <v>1.3431999999999999</v>
+        <v>1.92</v>
       </c>
       <c r="R67" s="21">
-        <f t="shared" si="4"/>
-        <v>67.16</v>
-      </c>
-      <c r="S67" s="55">
-        <v>1.3104</v>
+        <f t="shared" ref="R67:R70" si="10">Q67*L67</f>
+        <v>192</v>
+      </c>
+      <c r="S67" s="54">
+        <v>1.92</v>
       </c>
       <c r="T67" s="21">
-        <f t="shared" si="5"/>
-        <v>131.04</v>
-      </c>
-      <c r="U67" s="111" t="s">
-        <v>356</v>
+        <f t="shared" ref="T67:T70" si="11">S67*M67</f>
+        <v>384</v>
+      </c>
+      <c r="U67" s="97" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="68" spans="1:21" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="10">
-        <v>65</v>
-      </c>
-      <c r="B68" s="108"/>
-      <c r="C68" s="69" t="s">
+      <c r="A68" s="17">
+        <v>66</v>
+      </c>
+      <c r="B68" s="139"/>
+      <c r="C68" s="104" t="s">
         <v>299</v>
       </c>
-      <c r="D68" s="12" t="s">
-        <v>302</v>
-      </c>
-      <c r="E68" s="12" t="s">
+      <c r="D68" s="24" t="s">
+        <v>300</v>
+      </c>
+      <c r="E68" s="24" t="s">
         <v>41</v>
       </c>
       <c r="F68" s="24" t="s">
-        <v>303</v>
-      </c>
-      <c r="G68" s="44" t="s">
-        <v>317</v>
-      </c>
-      <c r="H68" s="44">
-        <v>1711725</v>
-      </c>
-      <c r="I68" s="12" t="s">
+        <v>301</v>
+      </c>
+      <c r="G68" s="105" t="s">
+        <v>41</v>
+      </c>
+      <c r="H68" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="I68" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="J68" s="44">
-        <v>2</v>
-      </c>
-      <c r="K68" s="13">
-        <f t="shared" ref="K68:K72" si="6">J68*5</f>
-        <v>10</v>
-      </c>
-      <c r="L68" s="13">
-        <f t="shared" ref="L68:L72" si="7">J68*50</f>
+      <c r="J68" s="105">
+        <v>1</v>
+      </c>
+      <c r="K68" s="111">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="L68" s="111">
+        <f t="shared" si="7"/>
+        <v>50</v>
+      </c>
+      <c r="M68" s="111">
+        <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="M68" s="13">
-        <f t="shared" ref="M68:M72" si="8">J68*100</f>
-        <v>200</v>
-      </c>
-      <c r="N68" s="86" t="s">
-        <v>20</v>
-      </c>
-      <c r="O68" s="20">
-        <v>2.1120000000000001</v>
-      </c>
-      <c r="P68" s="21">
-        <f t="shared" ref="P68:P72" si="9">O68*K68</f>
-        <v>21.12</v>
-      </c>
-      <c r="Q68" s="20">
-        <v>1.92</v>
-      </c>
-      <c r="R68" s="21">
-        <f t="shared" ref="R68:R72" si="10">Q68*L68</f>
-        <v>192</v>
-      </c>
-      <c r="S68" s="55">
-        <v>1.92</v>
-      </c>
-      <c r="T68" s="21">
-        <f t="shared" ref="T68:T72" si="11">S68*M68</f>
-        <v>384</v>
-      </c>
-      <c r="U68" s="111" t="s">
-        <v>356</v>
+      <c r="N68" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="O68" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="P68" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q68" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="R68" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="S68" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="T68" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="U68" s="97" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="69" spans="1:21" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="10">
-        <v>66</v>
-      </c>
-      <c r="B69" s="108"/>
-      <c r="C69" s="118" t="s">
-        <v>304</v>
+      <c r="A69" s="17">
+        <v>67</v>
+      </c>
+      <c r="B69" s="139"/>
+      <c r="C69" s="104" t="s">
+        <v>302</v>
       </c>
       <c r="D69" s="24" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E69" s="24" t="s">
         <v>41</v>
       </c>
       <c r="F69" s="24" t="s">
-        <v>306</v>
-      </c>
-      <c r="G69" s="119" t="s">
+        <v>304</v>
+      </c>
+      <c r="G69" s="105" t="s">
         <v>41</v>
       </c>
       <c r="H69" s="24" t="s">
@@ -7225,307 +7210,241 @@
       <c r="I69" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="J69" s="119">
+      <c r="J69" s="105">
+        <v>6</v>
+      </c>
+      <c r="K69" s="111">
+        <f t="shared" si="6"/>
+        <v>30</v>
+      </c>
+      <c r="L69" s="111">
+        <f t="shared" si="7"/>
+        <v>300</v>
+      </c>
+      <c r="M69" s="111">
+        <f t="shared" si="8"/>
+        <v>600</v>
+      </c>
+      <c r="N69" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="O69" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="P69" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q69" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="R69" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="S69" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="T69" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="U69" s="97" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="70" spans="1:21" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="17">
+        <v>68</v>
+      </c>
+      <c r="B70" s="139"/>
+      <c r="C70" s="68" t="s">
+        <v>305</v>
+      </c>
+      <c r="D70" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="E70" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F70" s="24" t="s">
+        <v>307</v>
+      </c>
+      <c r="G70" s="44" t="s">
+        <v>41</v>
+      </c>
+      <c r="H70" s="44" t="s">
+        <v>361</v>
+      </c>
+      <c r="I70" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="J70" s="44">
         <v>1</v>
       </c>
-      <c r="K69" s="125">
+      <c r="K70" s="13">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="L69" s="125">
+      <c r="L70" s="13">
         <f t="shared" si="7"/>
         <v>50</v>
       </c>
-      <c r="M69" s="125">
+      <c r="M70" s="13">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="N69" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="O69" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="P69" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q69" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="R69" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="S69" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="T69" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="U69" s="111" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="70" spans="1:21" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="10">
-        <v>67</v>
-      </c>
-      <c r="B70" s="108"/>
-      <c r="C70" s="118" t="s">
-        <v>307</v>
-      </c>
-      <c r="D70" s="24" t="s">
-        <v>308</v>
-      </c>
-      <c r="E70" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="F70" s="24" t="s">
-        <v>309</v>
-      </c>
-      <c r="G70" s="119" t="s">
-        <v>41</v>
-      </c>
-      <c r="H70" s="24" t="s">
-        <v>40</v>
-      </c>
-      <c r="I70" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="J70" s="119">
-        <v>6</v>
-      </c>
-      <c r="K70" s="125">
-        <f t="shared" si="6"/>
-        <v>30</v>
-      </c>
-      <c r="L70" s="125">
-        <f t="shared" si="7"/>
-        <v>300</v>
-      </c>
-      <c r="M70" s="125">
-        <f t="shared" si="8"/>
-        <v>600</v>
-      </c>
-      <c r="N70" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="O70" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="P70" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q70" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="R70" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="S70" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="T70" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="U70" s="111" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="71" spans="1:21" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="10">
-        <v>68</v>
-      </c>
-      <c r="B71" s="108"/>
-      <c r="C71" s="69" t="s">
-        <v>310</v>
-      </c>
-      <c r="D71" s="12" t="s">
-        <v>311</v>
-      </c>
-      <c r="E71" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="F71" s="24" t="s">
-        <v>312</v>
-      </c>
-      <c r="G71" s="44" t="s">
-        <v>41</v>
-      </c>
-      <c r="H71" s="44" t="s">
-        <v>367</v>
-      </c>
-      <c r="I71" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="J71" s="44">
-        <v>1</v>
-      </c>
-      <c r="K71" s="13">
-        <f t="shared" si="6"/>
-        <v>5</v>
-      </c>
-      <c r="L71" s="13">
-        <f t="shared" si="7"/>
-        <v>50</v>
-      </c>
-      <c r="M71" s="13">
-        <f t="shared" si="8"/>
-        <v>100</v>
-      </c>
-      <c r="N71" s="86" t="s">
+      <c r="N70" s="84" t="s">
         <v>20</v>
       </c>
-      <c r="O71" s="20">
+      <c r="O70" s="20">
         <v>0.15</v>
       </c>
-      <c r="P71" s="21">
+      <c r="P70" s="21">
         <f t="shared" si="9"/>
         <v>0.75</v>
       </c>
-      <c r="Q71" s="20">
+      <c r="Q70" s="20">
         <v>0.11799999999999999</v>
       </c>
-      <c r="R71" s="21">
+      <c r="R70" s="21">
         <f t="shared" si="10"/>
         <v>5.8999999999999995</v>
       </c>
-      <c r="S71" s="55">
+      <c r="S70" s="54">
         <v>8.6800000000000002E-2</v>
       </c>
-      <c r="T71" s="21">
+      <c r="T70" s="21">
         <f t="shared" si="11"/>
         <v>8.68</v>
       </c>
-      <c r="U71" s="72"/>
+      <c r="U70" s="70"/>
     </row>
-    <row r="72" spans="1:21" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="10">
+    <row r="71" spans="1:21" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="17">
         <v>69</v>
       </c>
-      <c r="B72" s="109"/>
-      <c r="C72" s="120" t="s">
+      <c r="B71" s="140"/>
+      <c r="C71" s="106" t="s">
         <v>16</v>
       </c>
-      <c r="D72" s="121" t="s">
-        <v>313</v>
-      </c>
-      <c r="E72" s="28" t="s">
+      <c r="D71" s="107" t="s">
+        <v>308</v>
+      </c>
+      <c r="E71" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="F72" s="28" t="s">
+      <c r="F71" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="G72" s="122" t="s">
+      <c r="G71" s="108" t="s">
         <v>41</v>
       </c>
-      <c r="H72" s="28" t="s">
+      <c r="H71" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="I72" s="28" t="s">
+      <c r="I71" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="J72" s="122">
+      <c r="J71" s="108">
         <v>10</v>
       </c>
-      <c r="K72" s="123">
+      <c r="K71" s="109">
         <f t="shared" si="6"/>
         <v>50</v>
       </c>
-      <c r="L72" s="123">
+      <c r="L71" s="109">
         <f t="shared" si="7"/>
         <v>500</v>
       </c>
-      <c r="M72" s="123">
+      <c r="M71" s="109">
         <f t="shared" si="8"/>
         <v>1000</v>
       </c>
-      <c r="N72" s="28" t="s">
+      <c r="N71" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="O72" s="28" t="s">
+      <c r="O71" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="P72" s="28" t="s">
+      <c r="P71" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="Q72" s="28" t="s">
+      <c r="Q71" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="R72" s="28" t="s">
+      <c r="R71" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="S72" s="28" t="s">
+      <c r="S71" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="T72" s="28" t="s">
+      <c r="T71" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="U72" s="133" t="s">
-        <v>368</v>
+      <c r="U71" s="119" t="s">
+        <v>362</v>
       </c>
     </row>
-    <row r="73" spans="1:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="I73" s="102" t="s">
+    <row r="72" spans="1:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I72" s="133" t="s">
         <v>12</v>
       </c>
-      <c r="J73" s="102"/>
-      <c r="K73" s="102"/>
-      <c r="L73" s="102"/>
-      <c r="M73" s="102"/>
-      <c r="N73" s="102"/>
-      <c r="P73" s="9">
-        <f>SUM(P1:P72)</f>
-        <v>245.6855000000001</v>
-      </c>
-      <c r="Q73" s="2"/>
-      <c r="R73" s="9">
-        <f>SUM(R1:R72)</f>
-        <v>1912.5309999999999</v>
-      </c>
-      <c r="S73" s="9"/>
-      <c r="T73" s="9">
-        <f>SUM(T1:T72)</f>
-        <v>3436.8680000000004</v>
+      <c r="J72" s="133"/>
+      <c r="K72" s="133"/>
+      <c r="L72" s="133"/>
+      <c r="M72" s="133"/>
+      <c r="N72" s="133"/>
+      <c r="P72" s="9">
+        <f>SUM(P1:P71)</f>
+        <v>245.42150000000009</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" s="9">
+        <f>SUM(R1:R71)</f>
+        <v>1911.779</v>
+      </c>
+      <c r="S72" s="9"/>
+      <c r="T72" s="9">
+        <f>SUM(T1:T71)</f>
+        <v>3434.5720000000001</v>
       </c>
     </row>
-    <row r="74" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="I74" s="103" t="s">
+    <row r="73" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="I73" s="134" t="s">
         <v>13</v>
       </c>
-      <c r="J74" s="103"/>
-      <c r="K74" s="103"/>
-      <c r="L74" s="103"/>
-      <c r="M74" s="103"/>
-      <c r="N74" s="103"/>
-      <c r="P74" s="4">
-        <f>P73/5</f>
-        <v>49.137100000000018</v>
-      </c>
-      <c r="Q74" s="3"/>
-      <c r="R74" s="4">
-        <f>R73/50</f>
-        <v>38.250619999999998</v>
-      </c>
-      <c r="S74" s="4"/>
-      <c r="T74" s="4">
-        <f>T73/100</f>
-        <v>34.368680000000005</v>
+      <c r="J73" s="134"/>
+      <c r="K73" s="134"/>
+      <c r="L73" s="134"/>
+      <c r="M73" s="134"/>
+      <c r="N73" s="134"/>
+      <c r="P73" s="4">
+        <f>P72/5</f>
+        <v>49.08430000000002</v>
+      </c>
+      <c r="Q73" s="3"/>
+      <c r="R73" s="4">
+        <f>R72/50</f>
+        <v>38.235579999999999</v>
+      </c>
+      <c r="S73" s="4"/>
+      <c r="T73" s="4">
+        <f>T72/100</f>
+        <v>34.34572</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A1:U1"/>
+    <mergeCell ref="I72:N72"/>
     <mergeCell ref="I73:N73"/>
-    <mergeCell ref="I74:N74"/>
-    <mergeCell ref="B3:B18"/>
-    <mergeCell ref="B21:B25"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="B30:B50"/>
-    <mergeCell ref="B51:B60"/>
-    <mergeCell ref="B61:B72"/>
+    <mergeCell ref="B3:B17"/>
+    <mergeCell ref="B20:B24"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="B29:B49"/>
+    <mergeCell ref="B50:B59"/>
+    <mergeCell ref="B60:B71"/>
   </mergeCells>
-  <phoneticPr fontId="12" type="noConversion"/>
-  <conditionalFormatting sqref="P3:P64 P71 P66:P68">
+  <phoneticPr fontId="11" type="noConversion"/>
+  <conditionalFormatting sqref="P3:P63 P70 P65:P67">
     <cfRule type="dataBar" priority="47">
       <dataBar>
         <cfvo type="min"/>
@@ -7563,7 +7482,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P74:T74">
+  <conditionalFormatting sqref="P73:T73">
     <cfRule type="dataBar" priority="109">
       <dataBar>
         <cfvo type="min"/>
@@ -7577,7 +7496,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R3:T64 R71:T71 R66:T68">
+  <conditionalFormatting sqref="R70:T70 R3:T63 R65:T67">
     <cfRule type="dataBar" priority="110">
       <dataBar>
         <cfvo type="min"/>
@@ -7603,55 +7522,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J11">
-    <cfRule type="colorScale" priority="125">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J3:J11">
-    <cfRule type="colorScale" priority="128">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K3:M72">
-    <cfRule type="colorScale" priority="129">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J3:M3 J4:J6 K4:M72">
-    <cfRule type="colorScale" priority="130">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J12:J19">
+  <conditionalFormatting sqref="J11:J18">
     <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="min"/>
@@ -7663,7 +7534,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J12:J19">
+  <conditionalFormatting sqref="J11:J18">
     <cfRule type="colorScale" priority="23">
       <colorScale>
         <cfvo type="min"/>
@@ -7675,7 +7546,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J20:J23">
+  <conditionalFormatting sqref="J19:J22">
     <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="min"/>
@@ -7687,7 +7558,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J20:J23">
+  <conditionalFormatting sqref="J19:J22">
     <cfRule type="colorScale" priority="19">
       <colorScale>
         <cfvo type="min"/>
@@ -7699,7 +7570,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J24">
+  <conditionalFormatting sqref="J23">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
@@ -7711,7 +7582,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J24">
+  <conditionalFormatting sqref="J23">
     <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
@@ -7723,7 +7594,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J30 J52">
+  <conditionalFormatting sqref="J29 J51">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -7735,7 +7606,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J31:J32 J53:J54">
+  <conditionalFormatting sqref="J30:J31 J52:J53">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -7747,7 +7618,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J29 J51">
+  <conditionalFormatting sqref="J28 J50">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
@@ -7759,7 +7630,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J33 J55">
+  <conditionalFormatting sqref="J32 J54">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
@@ -7771,7 +7642,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J25:J33 J47:J55 J69:J72">
+  <conditionalFormatting sqref="J24:J32 J46:J54 J68:J71">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
@@ -7783,7 +7654,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J25:J28 J47:J50 J69:J72">
+  <conditionalFormatting sqref="J24:J27 J46:J49 J68:J71">
     <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
@@ -7795,7 +7666,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J34:J41 J56:J63">
+  <conditionalFormatting sqref="J33:J40 J55:J62">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -7807,7 +7678,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J34:J41 J56:J63">
+  <conditionalFormatting sqref="J33:J40 J55:J62">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -7819,7 +7690,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J42:J45 J64:J67">
+  <conditionalFormatting sqref="J41:J44 J63:J66">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -7831,7 +7702,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J42:J45 J64:J67">
+  <conditionalFormatting sqref="J41:J44 J63:J66">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -7843,7 +7714,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J46 J68">
+  <conditionalFormatting sqref="J45 J67">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -7855,7 +7726,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J46 J68">
+  <conditionalFormatting sqref="J45 J67">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -7867,6 +7738,42 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="J3:J10">
+    <cfRule type="colorScale" priority="137">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K3:M71">
+    <cfRule type="colorScale" priority="138">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J3:M3 J4:J6 K4:M71">
+    <cfRule type="colorScale" priority="140">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="N3" r:id="rId1" xr:uid="{23E70632-4600-4F22-83CE-FD47B3962E62}"/>
     <hyperlink ref="N5" r:id="rId2" xr:uid="{5CC6ADB0-043E-4B58-B9C4-2FE1AAD2E037}"/>
@@ -7875,68 +7782,67 @@
     <hyperlink ref="N8" r:id="rId5" xr:uid="{9C652A29-4B48-4BD4-8315-0138929EC024}"/>
     <hyperlink ref="N9" r:id="rId6" xr:uid="{2CC140B7-DC71-4FFC-96D1-93364A7F7BC0}"/>
     <hyperlink ref="N10" r:id="rId7" xr:uid="{485FB412-0395-456F-8532-06E1A4201489}"/>
-    <hyperlink ref="N11" r:id="rId8" xr:uid="{ECCAD93D-1036-43EC-9E85-C55451672DF9}"/>
-    <hyperlink ref="N12" r:id="rId9" xr:uid="{A782F953-405B-4A93-AF92-DDACBFB7CF21}"/>
-    <hyperlink ref="N13" r:id="rId10" xr:uid="{1465FBAA-9088-4F26-B330-F1168D59A0BB}"/>
-    <hyperlink ref="N14" r:id="rId11" xr:uid="{F5FA0366-D8C1-4A2F-A2B6-BDA445A49CA8}"/>
-    <hyperlink ref="N15" r:id="rId12" xr:uid="{64FD0BC1-C794-41B9-93C2-8624A75B2CEC}"/>
-    <hyperlink ref="N16" r:id="rId13" xr:uid="{EE37A9E2-7348-4062-A15A-45B9D7021328}"/>
-    <hyperlink ref="N17" r:id="rId14" xr:uid="{DE9E7CD7-DD19-4BB4-88BF-0F339415A06C}"/>
-    <hyperlink ref="N18" r:id="rId15" xr:uid="{3A4697B8-C68F-4D4B-8FFC-B8828E0C4B72}"/>
-    <hyperlink ref="N19" r:id="rId16" xr:uid="{7FBA411A-AF4D-4718-90F1-BE19F3D869B7}"/>
-    <hyperlink ref="N25" r:id="rId17" xr:uid="{E5863CE5-7E2A-4BF0-A77F-E98E095418A7}"/>
-    <hyperlink ref="N27" r:id="rId18" xr:uid="{5E3C073F-F611-443E-A174-779C9099FD94}"/>
-    <hyperlink ref="N31" r:id="rId19" xr:uid="{16F6E4E5-B45A-485A-ABAC-711BB49A11BB}"/>
-    <hyperlink ref="N32" r:id="rId20" xr:uid="{B493BA74-8621-44B7-B0F4-F3974C1A8C87}"/>
-    <hyperlink ref="N33" r:id="rId21" xr:uid="{E0A13886-59DC-45A4-8901-538C449C7214}"/>
-    <hyperlink ref="N34" r:id="rId22" xr:uid="{66EBE2A0-0FE0-4AF2-B5C3-EE42C9A4FB5C}"/>
-    <hyperlink ref="N35" r:id="rId23" xr:uid="{A1B23CC2-B8F9-49F5-8D0A-C71B70D20D86}"/>
-    <hyperlink ref="N36" r:id="rId24" xr:uid="{7360A7C5-15D9-443A-817D-72AA0B97BE09}"/>
-    <hyperlink ref="N37" r:id="rId25" xr:uid="{770F34F4-F1C4-4337-96A0-74454EF930B9}"/>
-    <hyperlink ref="N38" r:id="rId26" xr:uid="{BE39D4B0-1221-4938-BF6D-C374494317E0}"/>
-    <hyperlink ref="N39" r:id="rId27" xr:uid="{37F1B585-7022-403D-B0F1-8AC9A083AFC2}"/>
-    <hyperlink ref="N42" r:id="rId28" xr:uid="{E749F68D-C392-470C-A4EF-351FB345DEBF}"/>
-    <hyperlink ref="N43" r:id="rId29" xr:uid="{D36BC509-040F-4501-BD50-D26A0B5D1187}"/>
-    <hyperlink ref="N46" r:id="rId30" xr:uid="{97B3A6A3-AFAB-4F71-89AD-7282DB51018C}"/>
-    <hyperlink ref="N47" r:id="rId31" xr:uid="{FAE33D01-1527-4BE6-9FA7-F06AD666133D}"/>
-    <hyperlink ref="N48" r:id="rId32" xr:uid="{BBCC64DC-60F7-4D30-88F0-0168FA28E6F2}"/>
-    <hyperlink ref="N49" r:id="rId33" xr:uid="{D520933C-D8DC-46B7-A74B-AA181B26B6E1}"/>
-    <hyperlink ref="N54" r:id="rId34" xr:uid="{65AB7FAD-A185-45D9-8DB7-B6F8FC0A9E64}"/>
-    <hyperlink ref="N56" r:id="rId35" xr:uid="{4A52EC8D-6B22-4623-A56A-AED0AF91C56F}"/>
-    <hyperlink ref="N59" r:id="rId36" xr:uid="{C6D8E578-79F2-4BBD-9874-5F608C66C2D1}"/>
-    <hyperlink ref="N60" r:id="rId37" xr:uid="{05A5080D-1968-4A05-ABEF-1F13DCBDBD06}"/>
-    <hyperlink ref="N64" r:id="rId38" xr:uid="{FE001AD1-3131-4A73-A021-90F7899498D7}"/>
-    <hyperlink ref="N30" r:id="rId39" xr:uid="{E6AE8FBB-87D2-4BD9-9807-A56E5E9AEF07}"/>
-    <hyperlink ref="N40" r:id="rId40" xr:uid="{2E7B65DB-EE7D-4462-9762-B529DC0D5E61}"/>
-    <hyperlink ref="N41" r:id="rId41" xr:uid="{067C798E-BB9E-4877-A01F-5ACDC256CA5A}"/>
-    <hyperlink ref="N44" r:id="rId42" xr:uid="{CC5DE328-BEF8-4165-8559-3D94B1BFEF30}"/>
-    <hyperlink ref="N45" r:id="rId43" xr:uid="{78F87503-89E9-48F4-B5D8-2C7AF9EACE13}"/>
-    <hyperlink ref="N50" r:id="rId44" xr:uid="{0AE44462-CA64-4BB0-9C0F-FADD3C56D8A8}"/>
-    <hyperlink ref="N20" r:id="rId45" xr:uid="{B55B85CA-E2F4-45B8-AD81-98E066D6E42F}"/>
-    <hyperlink ref="N21" r:id="rId46" xr:uid="{6FE8AAF0-9900-48AC-8DC8-DB1A4A0935A3}"/>
-    <hyperlink ref="N22" r:id="rId47" xr:uid="{A054D760-5D00-4DD6-B214-B241BB83A32E}"/>
-    <hyperlink ref="N23" r:id="rId48" xr:uid="{A0A5F541-B368-478D-9EF3-3D765239C64E}"/>
-    <hyperlink ref="N24" r:id="rId49" xr:uid="{9D28FC85-AED8-4A02-A947-60501FA5A6B5}"/>
-    <hyperlink ref="N29" r:id="rId50" xr:uid="{2AFD90F5-7189-4A7E-B7A6-AB55F8E1927F}"/>
-    <hyperlink ref="N51" r:id="rId51" xr:uid="{CC580313-421C-452B-9168-C71CF9B145C8}"/>
-    <hyperlink ref="N53" r:id="rId52" xr:uid="{2DE0EA7E-F5A2-4717-B312-6E9347B0E9F6}"/>
-    <hyperlink ref="N4" r:id="rId53" xr:uid="{44209F46-1B93-4F12-A4CC-E4A094978F3C}"/>
-    <hyperlink ref="N26" r:id="rId54" xr:uid="{44EA4EA8-AA27-4C9D-9863-2B16E294FC91}"/>
-    <hyperlink ref="N28" r:id="rId55" xr:uid="{2ED51590-8659-4DAC-84DC-7D7213D8CF43}"/>
-    <hyperlink ref="N52" r:id="rId56" xr:uid="{469E2288-EBAB-40EF-9F9B-CF42849950E1}"/>
-    <hyperlink ref="N55" r:id="rId57" xr:uid="{2413E98B-0791-406B-AB80-BBE245C68DDA}"/>
-    <hyperlink ref="N57" r:id="rId58" xr:uid="{4BD46842-B719-44ED-B21D-E7983C525D0E}"/>
-    <hyperlink ref="N58" r:id="rId59" xr:uid="{350C6503-BE03-4E2C-9C55-FF6C5D20AE69}"/>
-    <hyperlink ref="N61" r:id="rId60" xr:uid="{412B014F-51F9-4E5B-AC57-2B95C1EDA7A9}"/>
-    <hyperlink ref="N62" r:id="rId61" xr:uid="{D48DD52B-391E-4AB6-AAA3-DADAE7922EAC}"/>
-    <hyperlink ref="N63" r:id="rId62" xr:uid="{12DC5CF1-9576-4CA2-887F-F628E86240CE}"/>
-    <hyperlink ref="N66" r:id="rId63" xr:uid="{51C46423-15C7-4B06-94C1-84BF03991E13}"/>
-    <hyperlink ref="N67" r:id="rId64" xr:uid="{B30C34BB-74FB-4742-A49A-6DC81507E306}"/>
-    <hyperlink ref="N68" r:id="rId65" xr:uid="{E1587D9F-4670-45BE-B47C-D68A753F9EBF}"/>
-    <hyperlink ref="N71" r:id="rId66" xr:uid="{17B3BE3D-FC16-4FF8-8A71-4F20689EDB33}"/>
+    <hyperlink ref="N11" r:id="rId8" xr:uid="{A782F953-405B-4A93-AF92-DDACBFB7CF21}"/>
+    <hyperlink ref="N12" r:id="rId9" xr:uid="{1465FBAA-9088-4F26-B330-F1168D59A0BB}"/>
+    <hyperlink ref="N13" r:id="rId10" xr:uid="{F5FA0366-D8C1-4A2F-A2B6-BDA445A49CA8}"/>
+    <hyperlink ref="N14" r:id="rId11" xr:uid="{64FD0BC1-C794-41B9-93C2-8624A75B2CEC}"/>
+    <hyperlink ref="N15" r:id="rId12" xr:uid="{EE37A9E2-7348-4062-A15A-45B9D7021328}"/>
+    <hyperlink ref="N16" r:id="rId13" xr:uid="{DE9E7CD7-DD19-4BB4-88BF-0F339415A06C}"/>
+    <hyperlink ref="N17" r:id="rId14" xr:uid="{3A4697B8-C68F-4D4B-8FFC-B8828E0C4B72}"/>
+    <hyperlink ref="N18" r:id="rId15" xr:uid="{7FBA411A-AF4D-4718-90F1-BE19F3D869B7}"/>
+    <hyperlink ref="N24" r:id="rId16" xr:uid="{E5863CE5-7E2A-4BF0-A77F-E98E095418A7}"/>
+    <hyperlink ref="N26" r:id="rId17" xr:uid="{5E3C073F-F611-443E-A174-779C9099FD94}"/>
+    <hyperlink ref="N30" r:id="rId18" xr:uid="{16F6E4E5-B45A-485A-ABAC-711BB49A11BB}"/>
+    <hyperlink ref="N31" r:id="rId19" xr:uid="{B493BA74-8621-44B7-B0F4-F3974C1A8C87}"/>
+    <hyperlink ref="N32" r:id="rId20" xr:uid="{E0A13886-59DC-45A4-8901-538C449C7214}"/>
+    <hyperlink ref="N33" r:id="rId21" xr:uid="{66EBE2A0-0FE0-4AF2-B5C3-EE42C9A4FB5C}"/>
+    <hyperlink ref="N34" r:id="rId22" xr:uid="{A1B23CC2-B8F9-49F5-8D0A-C71B70D20D86}"/>
+    <hyperlink ref="N35" r:id="rId23" xr:uid="{7360A7C5-15D9-443A-817D-72AA0B97BE09}"/>
+    <hyperlink ref="N36" r:id="rId24" xr:uid="{770F34F4-F1C4-4337-96A0-74454EF930B9}"/>
+    <hyperlink ref="N37" r:id="rId25" xr:uid="{BE39D4B0-1221-4938-BF6D-C374494317E0}"/>
+    <hyperlink ref="N38" r:id="rId26" xr:uid="{37F1B585-7022-403D-B0F1-8AC9A083AFC2}"/>
+    <hyperlink ref="N41" r:id="rId27" xr:uid="{E749F68D-C392-470C-A4EF-351FB345DEBF}"/>
+    <hyperlink ref="N42" r:id="rId28" xr:uid="{D36BC509-040F-4501-BD50-D26A0B5D1187}"/>
+    <hyperlink ref="N45" r:id="rId29" xr:uid="{97B3A6A3-AFAB-4F71-89AD-7282DB51018C}"/>
+    <hyperlink ref="N46" r:id="rId30" xr:uid="{FAE33D01-1527-4BE6-9FA7-F06AD666133D}"/>
+    <hyperlink ref="N47" r:id="rId31" xr:uid="{BBCC64DC-60F7-4D30-88F0-0168FA28E6F2}"/>
+    <hyperlink ref="N48" r:id="rId32" xr:uid="{D520933C-D8DC-46B7-A74B-AA181B26B6E1}"/>
+    <hyperlink ref="N53" r:id="rId33" xr:uid="{65AB7FAD-A185-45D9-8DB7-B6F8FC0A9E64}"/>
+    <hyperlink ref="N55" r:id="rId34" xr:uid="{4A52EC8D-6B22-4623-A56A-AED0AF91C56F}"/>
+    <hyperlink ref="N58" r:id="rId35" xr:uid="{C6D8E578-79F2-4BBD-9874-5F608C66C2D1}"/>
+    <hyperlink ref="N59" r:id="rId36" xr:uid="{05A5080D-1968-4A05-ABEF-1F13DCBDBD06}"/>
+    <hyperlink ref="N63" r:id="rId37" xr:uid="{FE001AD1-3131-4A73-A021-90F7899498D7}"/>
+    <hyperlink ref="N29" r:id="rId38" xr:uid="{E6AE8FBB-87D2-4BD9-9807-A56E5E9AEF07}"/>
+    <hyperlink ref="N39" r:id="rId39" xr:uid="{2E7B65DB-EE7D-4462-9762-B529DC0D5E61}"/>
+    <hyperlink ref="N40" r:id="rId40" xr:uid="{067C798E-BB9E-4877-A01F-5ACDC256CA5A}"/>
+    <hyperlink ref="N43" r:id="rId41" xr:uid="{CC5DE328-BEF8-4165-8559-3D94B1BFEF30}"/>
+    <hyperlink ref="N44" r:id="rId42" xr:uid="{78F87503-89E9-48F4-B5D8-2C7AF9EACE13}"/>
+    <hyperlink ref="N49" r:id="rId43" xr:uid="{0AE44462-CA64-4BB0-9C0F-FADD3C56D8A8}"/>
+    <hyperlink ref="N19" r:id="rId44" xr:uid="{B55B85CA-E2F4-45B8-AD81-98E066D6E42F}"/>
+    <hyperlink ref="N20" r:id="rId45" xr:uid="{6FE8AAF0-9900-48AC-8DC8-DB1A4A0935A3}"/>
+    <hyperlink ref="N21" r:id="rId46" xr:uid="{A054D760-5D00-4DD6-B214-B241BB83A32E}"/>
+    <hyperlink ref="N22" r:id="rId47" xr:uid="{A0A5F541-B368-478D-9EF3-3D765239C64E}"/>
+    <hyperlink ref="N23" r:id="rId48" xr:uid="{9D28FC85-AED8-4A02-A947-60501FA5A6B5}"/>
+    <hyperlink ref="N28" r:id="rId49" xr:uid="{2AFD90F5-7189-4A7E-B7A6-AB55F8E1927F}"/>
+    <hyperlink ref="N50" r:id="rId50" xr:uid="{CC580313-421C-452B-9168-C71CF9B145C8}"/>
+    <hyperlink ref="N52" r:id="rId51" xr:uid="{2DE0EA7E-F5A2-4717-B312-6E9347B0E9F6}"/>
+    <hyperlink ref="N4" r:id="rId52" xr:uid="{44209F46-1B93-4F12-A4CC-E4A094978F3C}"/>
+    <hyperlink ref="N25" r:id="rId53" xr:uid="{44EA4EA8-AA27-4C9D-9863-2B16E294FC91}"/>
+    <hyperlink ref="N27" r:id="rId54" xr:uid="{2ED51590-8659-4DAC-84DC-7D7213D8CF43}"/>
+    <hyperlink ref="N51" r:id="rId55" xr:uid="{469E2288-EBAB-40EF-9F9B-CF42849950E1}"/>
+    <hyperlink ref="N54" r:id="rId56" xr:uid="{2413E98B-0791-406B-AB80-BBE245C68DDA}"/>
+    <hyperlink ref="N56" r:id="rId57" xr:uid="{4BD46842-B719-44ED-B21D-E7983C525D0E}"/>
+    <hyperlink ref="N57" r:id="rId58" xr:uid="{350C6503-BE03-4E2C-9C55-FF6C5D20AE69}"/>
+    <hyperlink ref="N60" r:id="rId59" xr:uid="{412B014F-51F9-4E5B-AC57-2B95C1EDA7A9}"/>
+    <hyperlink ref="N61" r:id="rId60" xr:uid="{D48DD52B-391E-4AB6-AAA3-DADAE7922EAC}"/>
+    <hyperlink ref="N62" r:id="rId61" xr:uid="{12DC5CF1-9576-4CA2-887F-F628E86240CE}"/>
+    <hyperlink ref="N65" r:id="rId62" xr:uid="{51C46423-15C7-4B06-94C1-84BF03991E13}"/>
+    <hyperlink ref="N66" r:id="rId63" xr:uid="{B30C34BB-74FB-4742-A49A-6DC81507E306}"/>
+    <hyperlink ref="N67" r:id="rId64" xr:uid="{E1587D9F-4670-45BE-B47C-D68A753F9EBF}"/>
+    <hyperlink ref="N70" r:id="rId65" xr:uid="{17B3BE3D-FC16-4FF8-8A71-4F20689EDB33}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId67"/>
+  <pageSetup orientation="portrait" r:id="rId66"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -7951,7 +7857,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>P3:P64 P71 P66:P68</xm:sqref>
+          <xm:sqref>P3:P63 P70 P65:P67</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{00F4DBD2-6698-4ADA-B9BF-608AE474FCE0}">
@@ -7964,7 +7870,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>P74:T74</xm:sqref>
+          <xm:sqref>P73:T73</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{1BC7CE5C-CC8F-453E-A379-81BAD63196D1}">
@@ -7977,7 +7883,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>R3:T64 R71:T71 R66:T68</xm:sqref>
+          <xm:sqref>R70:T70 R3:T63 R65:T67</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/Deliverable/BOM/Digikey_BOM_Grant.xlsx
+++ b/Deliverable/BOM/Digikey_BOM_Grant.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24931"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GrantKros-CoopMonitor\Deliverable\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{240EE8D2-F8BB-4187-9C99-7D70872CAB8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{961FA91B-9646-4261-87F1-B5986B7E72C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2168,6 +2168,9 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2200,9 +2203,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2511,29 +2511,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="130" t="s">
+      <c r="A1" s="131" t="s">
         <v>346</v>
       </c>
-      <c r="B1" s="131"/>
-      <c r="C1" s="131"/>
-      <c r="D1" s="131"/>
-      <c r="E1" s="131"/>
-      <c r="F1" s="131"/>
-      <c r="G1" s="131"/>
-      <c r="H1" s="131"/>
-      <c r="I1" s="131"/>
-      <c r="J1" s="131"/>
-      <c r="K1" s="131"/>
-      <c r="L1" s="131"/>
-      <c r="M1" s="131"/>
-      <c r="N1" s="131"/>
-      <c r="O1" s="131"/>
-      <c r="P1" s="131"/>
-      <c r="Q1" s="131"/>
-      <c r="R1" s="131"/>
-      <c r="S1" s="131"/>
-      <c r="T1" s="131"/>
-      <c r="U1" s="132"/>
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="132"/>
+      <c r="E1" s="132"/>
+      <c r="F1" s="132"/>
+      <c r="G1" s="132"/>
+      <c r="H1" s="132"/>
+      <c r="I1" s="132"/>
+      <c r="J1" s="132"/>
+      <c r="K1" s="132"/>
+      <c r="L1" s="132"/>
+      <c r="M1" s="132"/>
+      <c r="N1" s="132"/>
+      <c r="O1" s="132"/>
+      <c r="P1" s="132"/>
+      <c r="Q1" s="132"/>
+      <c r="R1" s="132"/>
+      <c r="S1" s="132"/>
+      <c r="T1" s="132"/>
+      <c r="U1" s="133"/>
     </row>
     <row r="2" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
@@ -2604,7 +2604,7 @@
       <c r="A3" s="17">
         <v>1</v>
       </c>
-      <c r="B3" s="135" t="s">
+      <c r="B3" s="136" t="s">
         <v>11</v>
       </c>
       <c r="C3" s="65" t="s">
@@ -2673,7 +2673,7 @@
       <c r="A4" s="17">
         <v>2</v>
       </c>
-      <c r="B4" s="136"/>
+      <c r="B4" s="137"/>
       <c r="C4" s="68" t="s">
         <v>50</v>
       </c>
@@ -2742,7 +2742,7 @@
       <c r="A5" s="17">
         <v>3</v>
       </c>
-      <c r="B5" s="136"/>
+      <c r="B5" s="137"/>
       <c r="C5" s="68" t="s">
         <v>363</v>
       </c>
@@ -2803,7 +2803,7 @@
         <f t="shared" si="5"/>
         <v>12.342000000000001</v>
       </c>
-      <c r="U5" s="141" t="s">
+      <c r="U5" s="130" t="s">
         <v>366</v>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       <c r="A6" s="17">
         <v>4</v>
       </c>
-      <c r="B6" s="136"/>
+      <c r="B6" s="137"/>
       <c r="C6" s="68" t="s">
         <v>54</v>
       </c>
@@ -2880,7 +2880,7 @@
       <c r="A7" s="17">
         <v>5</v>
       </c>
-      <c r="B7" s="136"/>
+      <c r="B7" s="137"/>
       <c r="C7" s="23" t="s">
         <v>58</v>
       </c>
@@ -2949,7 +2949,7 @@
       <c r="A8" s="17">
         <v>6</v>
       </c>
-      <c r="B8" s="136"/>
+      <c r="B8" s="137"/>
       <c r="C8" s="68" t="s">
         <v>61</v>
       </c>
@@ -3018,7 +3018,7 @@
       <c r="A9" s="17">
         <v>7</v>
       </c>
-      <c r="B9" s="136"/>
+      <c r="B9" s="137"/>
       <c r="C9" s="68" t="s">
         <v>65</v>
       </c>
@@ -3087,7 +3087,7 @@
       <c r="A10" s="17">
         <v>8</v>
       </c>
-      <c r="B10" s="136"/>
+      <c r="B10" s="137"/>
       <c r="C10" s="68" t="s">
         <v>69</v>
       </c>
@@ -3156,7 +3156,7 @@
       <c r="A11" s="17">
         <v>9</v>
       </c>
-      <c r="B11" s="136"/>
+      <c r="B11" s="137"/>
       <c r="C11" s="68" t="s">
         <v>72</v>
       </c>
@@ -3225,7 +3225,7 @@
       <c r="A12" s="17">
         <v>10</v>
       </c>
-      <c r="B12" s="136"/>
+      <c r="B12" s="137"/>
       <c r="C12" s="68" t="s">
         <v>75</v>
       </c>
@@ -3294,7 +3294,7 @@
       <c r="A13" s="17">
         <v>11</v>
       </c>
-      <c r="B13" s="136"/>
+      <c r="B13" s="137"/>
       <c r="C13" s="68" t="s">
         <v>78</v>
       </c>
@@ -3363,7 +3363,7 @@
       <c r="A14" s="17">
         <v>12</v>
       </c>
-      <c r="B14" s="136"/>
+      <c r="B14" s="137"/>
       <c r="C14" s="68" t="s">
         <v>81</v>
       </c>
@@ -3432,7 +3432,7 @@
       <c r="A15" s="17">
         <v>13</v>
       </c>
-      <c r="B15" s="136"/>
+      <c r="B15" s="137"/>
       <c r="C15" s="68" t="s">
         <v>84</v>
       </c>
@@ -3501,7 +3501,7 @@
       <c r="A16" s="17">
         <v>14</v>
       </c>
-      <c r="B16" s="136"/>
+      <c r="B16" s="137"/>
       <c r="C16" s="68" t="s">
         <v>87</v>
       </c>
@@ -3570,7 +3570,7 @@
       <c r="A17" s="17">
         <v>15</v>
       </c>
-      <c r="B17" s="137"/>
+      <c r="B17" s="138"/>
       <c r="C17" s="71" t="s">
         <v>90</v>
       </c>
@@ -3781,7 +3781,7 @@
       <c r="A20" s="17">
         <v>18</v>
       </c>
-      <c r="B20" s="138" t="s">
+      <c r="B20" s="139" t="s">
         <v>161</v>
       </c>
       <c r="C20" s="65" t="s">
@@ -3854,7 +3854,7 @@
       <c r="A21" s="17">
         <v>19</v>
       </c>
-      <c r="B21" s="139"/>
+      <c r="B21" s="140"/>
       <c r="C21" s="68" t="s">
         <v>128</v>
       </c>
@@ -3925,7 +3925,7 @@
       <c r="A22" s="17">
         <v>20</v>
       </c>
-      <c r="B22" s="139"/>
+      <c r="B22" s="140"/>
       <c r="C22" s="68" t="s">
         <v>131</v>
       </c>
@@ -3996,7 +3996,7 @@
       <c r="A23" s="17">
         <v>21</v>
       </c>
-      <c r="B23" s="139"/>
+      <c r="B23" s="140"/>
       <c r="C23" s="68" t="s">
         <v>134</v>
       </c>
@@ -4067,7 +4067,7 @@
       <c r="A24" s="17">
         <v>22</v>
       </c>
-      <c r="B24" s="140"/>
+      <c r="B24" s="141"/>
       <c r="C24" s="71" t="s">
         <v>137</v>
       </c>
@@ -4136,7 +4136,7 @@
       <c r="A25" s="17">
         <v>23</v>
       </c>
-      <c r="B25" s="139" t="s">
+      <c r="B25" s="140" t="s">
         <v>162</v>
       </c>
       <c r="C25" s="79" t="s">
@@ -4209,7 +4209,7 @@
       <c r="A26" s="17">
         <v>24</v>
       </c>
-      <c r="B26" s="139"/>
+      <c r="B26" s="140"/>
       <c r="C26" s="81" t="s">
         <v>143</v>
       </c>
@@ -4422,7 +4422,7 @@
       <c r="A29" s="17">
         <v>27</v>
       </c>
-      <c r="B29" s="138" t="s">
+      <c r="B29" s="139" t="s">
         <v>18</v>
       </c>
       <c r="C29" s="118" t="s">
@@ -4493,7 +4493,7 @@
       <c r="A30" s="17">
         <v>28</v>
       </c>
-      <c r="B30" s="139"/>
+      <c r="B30" s="140"/>
       <c r="C30" s="68" t="s">
         <v>166</v>
       </c>
@@ -4562,7 +4562,7 @@
       <c r="A31" s="17">
         <v>29</v>
       </c>
-      <c r="B31" s="139"/>
+      <c r="B31" s="140"/>
       <c r="C31" s="68" t="s">
         <v>170</v>
       </c>
@@ -4631,7 +4631,7 @@
       <c r="A32" s="17">
         <v>30</v>
       </c>
-      <c r="B32" s="139"/>
+      <c r="B32" s="140"/>
       <c r="C32" s="68" t="s">
         <v>173</v>
       </c>
@@ -4700,7 +4700,7 @@
       <c r="A33" s="17">
         <v>31</v>
       </c>
-      <c r="B33" s="139"/>
+      <c r="B33" s="140"/>
       <c r="C33" s="68" t="s">
         <v>175</v>
       </c>
@@ -4769,7 +4769,7 @@
       <c r="A34" s="17">
         <v>32</v>
       </c>
-      <c r="B34" s="139"/>
+      <c r="B34" s="140"/>
       <c r="C34" s="68" t="s">
         <v>178</v>
       </c>
@@ -4838,7 +4838,7 @@
       <c r="A35" s="17">
         <v>33</v>
       </c>
-      <c r="B35" s="139"/>
+      <c r="B35" s="140"/>
       <c r="C35" s="68" t="s">
         <v>181</v>
       </c>
@@ -4907,7 +4907,7 @@
       <c r="A36" s="17">
         <v>34</v>
       </c>
-      <c r="B36" s="139"/>
+      <c r="B36" s="140"/>
       <c r="C36" s="68" t="s">
         <v>184</v>
       </c>
@@ -4976,7 +4976,7 @@
       <c r="A37" s="17">
         <v>35</v>
       </c>
-      <c r="B37" s="139"/>
+      <c r="B37" s="140"/>
       <c r="C37" s="68" t="s">
         <v>187</v>
       </c>
@@ -5045,7 +5045,7 @@
       <c r="A38" s="17">
         <v>36</v>
       </c>
-      <c r="B38" s="139"/>
+      <c r="B38" s="140"/>
       <c r="C38" s="68" t="s">
         <v>190</v>
       </c>
@@ -5114,7 +5114,7 @@
       <c r="A39" s="17">
         <v>37</v>
       </c>
-      <c r="B39" s="139"/>
+      <c r="B39" s="140"/>
       <c r="C39" s="68" t="s">
         <v>338</v>
       </c>
@@ -5183,7 +5183,7 @@
       <c r="A40" s="17">
         <v>38</v>
       </c>
-      <c r="B40" s="139"/>
+      <c r="B40" s="140"/>
       <c r="C40" s="68" t="s">
         <v>340</v>
       </c>
@@ -5252,7 +5252,7 @@
       <c r="A41" s="17">
         <v>39</v>
       </c>
-      <c r="B41" s="139"/>
+      <c r="B41" s="140"/>
       <c r="C41" s="68" t="s">
         <v>198</v>
       </c>
@@ -5321,7 +5321,7 @@
       <c r="A42" s="17">
         <v>40</v>
       </c>
-      <c r="B42" s="139"/>
+      <c r="B42" s="140"/>
       <c r="C42" s="68" t="s">
         <v>201</v>
       </c>
@@ -5390,7 +5390,7 @@
       <c r="A43" s="17">
         <v>41</v>
       </c>
-      <c r="B43" s="139"/>
+      <c r="B43" s="140"/>
       <c r="C43" s="68" t="s">
         <v>341</v>
       </c>
@@ -5459,7 +5459,7 @@
       <c r="A44" s="17">
         <v>42</v>
       </c>
-      <c r="B44" s="139"/>
+      <c r="B44" s="140"/>
       <c r="C44" s="68" t="s">
         <v>207</v>
       </c>
@@ -5528,7 +5528,7 @@
       <c r="A45" s="17">
         <v>43</v>
       </c>
-      <c r="B45" s="139"/>
+      <c r="B45" s="140"/>
       <c r="C45" s="68" t="s">
         <v>210</v>
       </c>
@@ -5597,7 +5597,7 @@
       <c r="A46" s="17">
         <v>44</v>
       </c>
-      <c r="B46" s="139"/>
+      <c r="B46" s="140"/>
       <c r="C46" s="68" t="s">
         <v>213</v>
       </c>
@@ -5666,7 +5666,7 @@
       <c r="A47" s="17">
         <v>45</v>
       </c>
-      <c r="B47" s="139"/>
+      <c r="B47" s="140"/>
       <c r="C47" s="68" t="s">
         <v>216</v>
       </c>
@@ -5735,7 +5735,7 @@
       <c r="A48" s="17">
         <v>46</v>
       </c>
-      <c r="B48" s="139"/>
+      <c r="B48" s="140"/>
       <c r="C48" s="68" t="s">
         <v>219</v>
       </c>
@@ -5804,7 +5804,7 @@
       <c r="A49" s="17">
         <v>47</v>
       </c>
-      <c r="B49" s="140"/>
+      <c r="B49" s="141"/>
       <c r="C49" s="71" t="s">
         <v>345</v>
       </c>
@@ -5873,7 +5873,7 @@
       <c r="A50" s="17">
         <v>48</v>
       </c>
-      <c r="B50" s="138" t="s">
+      <c r="B50" s="139" t="s">
         <v>38</v>
       </c>
       <c r="C50" s="65" t="s">
@@ -5946,7 +5946,7 @@
       <c r="A51" s="17">
         <v>49</v>
       </c>
-      <c r="B51" s="139"/>
+      <c r="B51" s="140"/>
       <c r="C51" s="68" t="s">
         <v>251</v>
       </c>
@@ -6017,7 +6017,7 @@
       <c r="A52" s="17">
         <v>50</v>
       </c>
-      <c r="B52" s="139"/>
+      <c r="B52" s="140"/>
       <c r="C52" s="68" t="s">
         <v>254</v>
       </c>
@@ -6088,7 +6088,7 @@
       <c r="A53" s="17">
         <v>51</v>
       </c>
-      <c r="B53" s="139"/>
+      <c r="B53" s="140"/>
       <c r="C53" s="68" t="s">
         <v>257</v>
       </c>
@@ -6157,7 +6157,7 @@
       <c r="A54" s="17">
         <v>52</v>
       </c>
-      <c r="B54" s="139"/>
+      <c r="B54" s="140"/>
       <c r="C54" s="68" t="s">
         <v>259</v>
       </c>
@@ -6228,7 +6228,7 @@
       <c r="A55" s="17">
         <v>53</v>
       </c>
-      <c r="B55" s="139"/>
+      <c r="B55" s="140"/>
       <c r="C55" s="68" t="s">
         <v>261</v>
       </c>
@@ -6297,7 +6297,7 @@
       <c r="A56" s="17">
         <v>54</v>
       </c>
-      <c r="B56" s="139"/>
+      <c r="B56" s="140"/>
       <c r="C56" s="68" t="s">
         <v>263</v>
       </c>
@@ -6368,7 +6368,7 @@
       <c r="A57" s="17">
         <v>55</v>
       </c>
-      <c r="B57" s="139"/>
+      <c r="B57" s="140"/>
       <c r="C57" s="68" t="s">
         <v>266</v>
       </c>
@@ -6439,7 +6439,7 @@
       <c r="A58" s="17">
         <v>56</v>
       </c>
-      <c r="B58" s="139"/>
+      <c r="B58" s="140"/>
       <c r="C58" s="68" t="s">
         <v>268</v>
       </c>
@@ -6508,7 +6508,7 @@
       <c r="A59" s="17">
         <v>57</v>
       </c>
-      <c r="B59" s="140"/>
+      <c r="B59" s="141"/>
       <c r="C59" s="71" t="s">
         <v>271</v>
       </c>
@@ -6577,7 +6577,7 @@
       <c r="A60" s="17">
         <v>58</v>
       </c>
-      <c r="B60" s="138" t="s">
+      <c r="B60" s="139" t="s">
         <v>19</v>
       </c>
       <c r="C60" s="30" t="s">
@@ -6648,7 +6648,7 @@
       <c r="A61" s="17">
         <v>59</v>
       </c>
-      <c r="B61" s="139"/>
+      <c r="B61" s="140"/>
       <c r="C61" s="23" t="s">
         <v>282</v>
       </c>
@@ -6715,7 +6715,7 @@
       <c r="A62" s="17">
         <v>60</v>
       </c>
-      <c r="B62" s="139"/>
+      <c r="B62" s="140"/>
       <c r="C62" s="23" t="s">
         <v>284</v>
       </c>
@@ -6784,7 +6784,7 @@
       <c r="A63" s="17">
         <v>61</v>
       </c>
-      <c r="B63" s="139"/>
+      <c r="B63" s="140"/>
       <c r="C63" s="68" t="s">
         <v>286</v>
       </c>
@@ -6851,71 +6851,74 @@
       <c r="A64" s="17">
         <v>62</v>
       </c>
-      <c r="B64" s="139"/>
-      <c r="C64" s="104" t="s">
-        <v>288</v>
-      </c>
-      <c r="D64" s="24" t="s">
-        <v>289</v>
-      </c>
-      <c r="E64" s="24" t="s">
+      <c r="B64" s="140"/>
+      <c r="C64" s="68" t="s">
+        <v>305</v>
+      </c>
+      <c r="D64" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="E64" s="12" t="s">
         <v>41</v>
       </c>
       <c r="F64" s="24" t="s">
-        <v>290</v>
-      </c>
-      <c r="G64" s="105" t="s">
-        <v>310</v>
-      </c>
-      <c r="H64" s="110"/>
-      <c r="I64" s="24" t="s">
+        <v>307</v>
+      </c>
+      <c r="G64" s="44" t="s">
+        <v>41</v>
+      </c>
+      <c r="H64" s="44" t="s">
+        <v>361</v>
+      </c>
+      <c r="I64" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J64" s="105">
+      <c r="J64" s="44">
         <v>1</v>
       </c>
-      <c r="K64" s="111">
-        <f t="shared" si="0"/>
+      <c r="K64" s="13">
+        <f>J64*5</f>
         <v>5</v>
       </c>
-      <c r="L64" s="111">
-        <f t="shared" si="1"/>
+      <c r="L64" s="13">
+        <f>J64*50</f>
         <v>50</v>
       </c>
-      <c r="M64" s="111">
-        <f t="shared" si="2"/>
+      <c r="M64" s="13">
+        <f>J64*100</f>
         <v>100</v>
       </c>
-      <c r="N64" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="O64" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="P64" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q64" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="R64" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="S64" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="T64" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="U64" s="97" t="s">
-        <v>362</v>
-      </c>
+      <c r="N64" s="84" t="s">
+        <v>20</v>
+      </c>
+      <c r="O64" s="20">
+        <v>0.15</v>
+      </c>
+      <c r="P64" s="21">
+        <f>O64*K64</f>
+        <v>0.75</v>
+      </c>
+      <c r="Q64" s="20">
+        <v>0.11799999999999999</v>
+      </c>
+      <c r="R64" s="21">
+        <f>Q64*L64</f>
+        <v>5.8999999999999995</v>
+      </c>
+      <c r="S64" s="54">
+        <v>8.6800000000000002E-2</v>
+      </c>
+      <c r="T64" s="21">
+        <f>S64*M64</f>
+        <v>8.68</v>
+      </c>
+      <c r="U64" s="70"/>
     </row>
     <row r="65" spans="1:21" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="17">
         <v>63</v>
       </c>
-      <c r="B65" s="139"/>
+      <c r="B65" s="140"/>
       <c r="C65" s="68" t="s">
         <v>291</v>
       </c>
@@ -6984,7 +6987,7 @@
       <c r="A66" s="17">
         <v>64</v>
       </c>
-      <c r="B66" s="139"/>
+      <c r="B66" s="140"/>
       <c r="C66" s="68" t="s">
         <v>294</v>
       </c>
@@ -7053,7 +7056,7 @@
       <c r="A67" s="17">
         <v>65</v>
       </c>
-      <c r="B67" s="139"/>
+      <c r="B67" s="140"/>
       <c r="C67" s="68" t="s">
         <v>294</v>
       </c>
@@ -7122,7 +7125,7 @@
       <c r="A68" s="17">
         <v>66</v>
       </c>
-      <c r="B68" s="139"/>
+      <c r="B68" s="140"/>
       <c r="C68" s="104" t="s">
         <v>299</v>
       </c>
@@ -7188,7 +7191,7 @@
       <c r="A69" s="17">
         <v>67</v>
       </c>
-      <c r="B69" s="139"/>
+      <c r="B69" s="140"/>
       <c r="C69" s="104" t="s">
         <v>302</v>
       </c>
@@ -7254,74 +7257,71 @@
       <c r="A70" s="17">
         <v>68</v>
       </c>
-      <c r="B70" s="139"/>
-      <c r="C70" s="68" t="s">
-        <v>305</v>
-      </c>
-      <c r="D70" s="12" t="s">
-        <v>306</v>
-      </c>
-      <c r="E70" s="12" t="s">
+      <c r="B70" s="140"/>
+      <c r="C70" s="104" t="s">
+        <v>288</v>
+      </c>
+      <c r="D70" s="24" t="s">
+        <v>289</v>
+      </c>
+      <c r="E70" s="24" t="s">
         <v>41</v>
       </c>
       <c r="F70" s="24" t="s">
-        <v>307</v>
-      </c>
-      <c r="G70" s="44" t="s">
-        <v>41</v>
-      </c>
-      <c r="H70" s="44" t="s">
-        <v>361</v>
-      </c>
-      <c r="I70" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="G70" s="105" t="s">
+        <v>310</v>
+      </c>
+      <c r="H70" s="110"/>
+      <c r="I70" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="J70" s="44">
+      <c r="J70" s="105">
         <v>1</v>
       </c>
-      <c r="K70" s="13">
-        <f t="shared" si="6"/>
+      <c r="K70" s="111">
+        <f>J70*5</f>
         <v>5</v>
       </c>
-      <c r="L70" s="13">
-        <f t="shared" si="7"/>
+      <c r="L70" s="111">
+        <f>J70*50</f>
         <v>50</v>
       </c>
-      <c r="M70" s="13">
-        <f t="shared" si="8"/>
+      <c r="M70" s="111">
+        <f>J70*100</f>
         <v>100</v>
       </c>
-      <c r="N70" s="84" t="s">
-        <v>20</v>
-      </c>
-      <c r="O70" s="20">
-        <v>0.15</v>
-      </c>
-      <c r="P70" s="21">
-        <f t="shared" si="9"/>
-        <v>0.75</v>
-      </c>
-      <c r="Q70" s="20">
-        <v>0.11799999999999999</v>
-      </c>
-      <c r="R70" s="21">
-        <f t="shared" si="10"/>
-        <v>5.8999999999999995</v>
-      </c>
-      <c r="S70" s="54">
-        <v>8.6800000000000002E-2</v>
-      </c>
-      <c r="T70" s="21">
-        <f t="shared" si="11"/>
-        <v>8.68</v>
-      </c>
-      <c r="U70" s="70"/>
+      <c r="N70" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="O70" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="P70" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q70" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="R70" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="S70" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="T70" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="U70" s="97" t="s">
+        <v>362</v>
+      </c>
     </row>
     <row r="71" spans="1:21" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="17">
         <v>69</v>
       </c>
-      <c r="B71" s="140"/>
+      <c r="B71" s="141"/>
       <c r="C71" s="106" t="s">
         <v>16</v>
       </c>
@@ -7384,14 +7384,14 @@
       </c>
     </row>
     <row r="72" spans="1:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="I72" s="133" t="s">
+      <c r="I72" s="134" t="s">
         <v>12</v>
       </c>
-      <c r="J72" s="133"/>
-      <c r="K72" s="133"/>
-      <c r="L72" s="133"/>
-      <c r="M72" s="133"/>
-      <c r="N72" s="133"/>
+      <c r="J72" s="134"/>
+      <c r="K72" s="134"/>
+      <c r="L72" s="134"/>
+      <c r="M72" s="134"/>
+      <c r="N72" s="134"/>
       <c r="P72" s="9">
         <f>SUM(P1:P71)</f>
         <v>245.42150000000009</v>
@@ -7408,14 +7408,14 @@
       </c>
     </row>
     <row r="73" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="I73" s="134" t="s">
+      <c r="I73" s="135" t="s">
         <v>13</v>
       </c>
-      <c r="J73" s="134"/>
-      <c r="K73" s="134"/>
-      <c r="L73" s="134"/>
-      <c r="M73" s="134"/>
-      <c r="N73" s="134"/>
+      <c r="J73" s="135"/>
+      <c r="K73" s="135"/>
+      <c r="L73" s="135"/>
+      <c r="M73" s="135"/>
+      <c r="N73" s="135"/>
       <c r="P73" s="4">
         <f>P72/5</f>
         <v>49.08430000000002</v>
@@ -7444,7 +7444,7 @@
     <mergeCell ref="B60:B71"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
-  <conditionalFormatting sqref="P3:P63 P70 P65:P67">
+  <conditionalFormatting sqref="P3:P67">
     <cfRule type="dataBar" priority="47">
       <dataBar>
         <cfvo type="min"/>
@@ -7496,7 +7496,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R70:T70 R3:T63 R65:T67">
+  <conditionalFormatting sqref="R3:T67">
     <cfRule type="dataBar" priority="110">
       <dataBar>
         <cfvo type="min"/>
@@ -7642,7 +7642,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J24:J32 J46:J54 J68:J71">
+  <conditionalFormatting sqref="J24:J32 J46:J54 J68:J69 J71 J64">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
@@ -7654,7 +7654,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J24:J27 J46:J49 J68:J71">
+  <conditionalFormatting sqref="J24:J27 J46:J49 J68:J69 J71 J64">
     <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
@@ -7690,7 +7690,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J41:J44 J63:J66">
+  <conditionalFormatting sqref="J41:J44 J70 J63 J65:J66">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -7702,7 +7702,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J41:J44 J63:J66">
+  <conditionalFormatting sqref="J41:J44 J70 J63 J65:J66">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -7714,7 +7714,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J45 J67">
+  <conditionalFormatting sqref="J67 J45">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -7726,7 +7726,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J45 J67">
+  <conditionalFormatting sqref="J67 J45">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -7839,7 +7839,7 @@
     <hyperlink ref="N65" r:id="rId62" xr:uid="{51C46423-15C7-4B06-94C1-84BF03991E13}"/>
     <hyperlink ref="N66" r:id="rId63" xr:uid="{B30C34BB-74FB-4742-A49A-6DC81507E306}"/>
     <hyperlink ref="N67" r:id="rId64" xr:uid="{E1587D9F-4670-45BE-B47C-D68A753F9EBF}"/>
-    <hyperlink ref="N70" r:id="rId65" xr:uid="{17B3BE3D-FC16-4FF8-8A71-4F20689EDB33}"/>
+    <hyperlink ref="N64" r:id="rId65" xr:uid="{17B3BE3D-FC16-4FF8-8A71-4F20689EDB33}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId66"/>
@@ -7857,7 +7857,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>P3:P63 P70 P65:P67</xm:sqref>
+          <xm:sqref>P3:P67</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{00F4DBD2-6698-4ADA-B9BF-608AE474FCE0}">
@@ -7883,7 +7883,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>R70:T70 R3:T63 R65:T67</xm:sqref>
+          <xm:sqref>R3:T67</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/Deliverable/BOM/Digikey_BOM_Grant.xlsx
+++ b/Deliverable/BOM/Digikey_BOM_Grant.xlsx
@@ -1,31 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24931"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GrantKros-CoopMonitor\Deliverable\BOM\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{984AA9A2-B537-49D7-9EA9-CC4620CDB670}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-10590" yWindow="5160" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="23325" windowHeight="9795"/>
   </bookViews>
   <sheets>
     <sheet name="Jude_Project" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
@@ -1162,52 +1146,56 @@
     <t>Solder Bridge ON</t>
   </si>
   <si>
-    <t>SB2, SB3, SB14, SB15, SB16, SB17, SB18, SB19, SB20, SB_ZD1</t>
+    <t>SB2, SB3, SB14, SB15, SB16, SB17, SB18, SB19, SB20,SB21, SB_ZD1</t>
   </si>
   <si>
     <t>Solder Bridge</t>
   </si>
   <si>
+    <t>Peripheral</t>
+  </si>
+  <si>
+    <t>LS-SG555 37MM Dc Gear Motor</t>
+  </si>
+  <si>
+    <t>LS-SG555</t>
+  </si>
+  <si>
+    <t>Ningbo Leison Motor</t>
+  </si>
+  <si>
+    <t>Custom Supplier</t>
+  </si>
+  <si>
+    <t>Delivery time: 15 days after got the payment</t>
+  </si>
+  <si>
     <t xml:space="preserve">Total Component Cost </t>
   </si>
   <si>
     <t>Single Board Cost</t>
   </si>
   <si>
-    <t>Peripheral</t>
-  </si>
-  <si>
-    <t>LS-SG555 37MM Dc Gear Motor</t>
-  </si>
-  <si>
-    <t>LS-SG555</t>
-  </si>
-  <si>
-    <t>Ningbo Leison Motor</t>
-  </si>
-  <si>
-    <t>Custom Supplier</t>
-  </si>
-  <si>
     <t>Motor Shipping Cost</t>
   </si>
   <si>
     <t>Total Cost</t>
-  </si>
-  <si>
-    <t>Delivery time: 15 days after got the payment</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.0000"/>
-    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.0000_);[Red]\(&quot;$&quot;#,##0.0000\)"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="7">
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="&quot;$&quot;#,##0.0000"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="179" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="180" formatCode="&quot;$&quot;#,##0.0000_);[Red]\(&quot;$&quot;#,##0.0000\)"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="41">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1220,7 +1208,7 @@
       <sz val="12"/>
       <color theme="0"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1228,7 +1216,7 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1236,14 +1224,14 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1251,32 +1239,32 @@
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
       <sz val="10"/>
       <color theme="10"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1284,21 +1272,21 @@
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF212529"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color theme="0"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1306,7 +1294,7 @@
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1314,14 +1302,35 @@
       <sz val="10"/>
       <color theme="5"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1329,7 +1338,7 @@
       <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1337,7 +1346,15 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF7030A0"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1345,40 +1362,147 @@
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
-      <color theme="0"/>
+      <sz val="11"/>
+      <color theme="3"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF7030A0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1397,8 +1521,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="40">
+  <borders count="48">
     <border>
       <left/>
       <right/>
@@ -1895,12 +2205,251 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="41" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="42" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="43" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="42" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="22" borderId="44" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="23" borderId="46" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="23" borderId="44" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="45" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="47" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="157">
+  <cellXfs count="140">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1915,6 +2464,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1924,12 +2479,24 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1939,9 +2506,18 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1951,33 +2527,66 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1987,31 +2596,31 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2026,100 +2635,106 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2132,19 +2747,19 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -2154,211 +2769,239 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="7" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="40% - Accent1" xfId="1" builtinId="31"/>
+    <cellStyle name="Comma" xfId="2" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="3" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
+    <cellStyle name="Currency" xfId="5" builtinId="4"/>
+    <cellStyle name="Percent" xfId="6" builtinId="5"/>
+    <cellStyle name="Hyperlink" xfId="7" builtinId="8"/>
+    <cellStyle name="60% - Accent4" xfId="8" builtinId="44"/>
+    <cellStyle name="Followed Hyperlink" xfId="9" builtinId="9"/>
+    <cellStyle name="Check Cell" xfId="10" builtinId="23"/>
+    <cellStyle name="Heading 2" xfId="11" builtinId="17"/>
+    <cellStyle name="Note" xfId="12" builtinId="10"/>
+    <cellStyle name="40% - Accent3" xfId="13" builtinId="39"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11"/>
+    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
+    <cellStyle name="Title" xfId="16" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="17" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="18" builtinId="16"/>
+    <cellStyle name="Heading 3" xfId="19" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="20" builtinId="19"/>
+    <cellStyle name="Input" xfId="21" builtinId="20"/>
+    <cellStyle name="60% - Accent3" xfId="22" builtinId="40"/>
+    <cellStyle name="Good" xfId="23" builtinId="26"/>
+    <cellStyle name="Output" xfId="24" builtinId="21"/>
+    <cellStyle name="20% - Accent1" xfId="25" builtinId="30"/>
+    <cellStyle name="Calculation" xfId="26" builtinId="22"/>
+    <cellStyle name="Linked Cell" xfId="27" builtinId="24"/>
+    <cellStyle name="Total" xfId="28" builtinId="25"/>
+    <cellStyle name="Bad" xfId="29" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="30" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="31" builtinId="29"/>
+    <cellStyle name="20% - Accent5" xfId="32" builtinId="46"/>
+    <cellStyle name="60% - Accent1" xfId="33" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="34" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="35" builtinId="34"/>
+    <cellStyle name="20% - Accent6" xfId="36" builtinId="50"/>
+    <cellStyle name="60% - Accent2" xfId="37" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="38" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="39" builtinId="38"/>
+    <cellStyle name="Accent4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="42" builtinId="43"/>
+    <cellStyle name="Accent5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - Accent5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="45" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="46" builtinId="49"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2616,5139 +3259,5139 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:W77"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="6.140625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="14.42578125" customWidth="1"/>
-    <col min="3" max="3" width="39.42578125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="35.7109375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="18.5703125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="25.85546875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="24.7109375" style="3" customWidth="1"/>
-    <col min="8" max="8" width="25.7109375" customWidth="1"/>
-    <col min="9" max="9" width="6.140625" style="5" customWidth="1"/>
-    <col min="10" max="10" width="19.42578125" style="3" customWidth="1"/>
-    <col min="11" max="11" width="10.140625" customWidth="1"/>
-    <col min="12" max="12" width="11.140625" customWidth="1"/>
-    <col min="13" max="13" width="12.140625" customWidth="1"/>
-    <col min="14" max="14" width="14" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.5703125" customWidth="1"/>
-    <col min="16" max="16" width="12.140625" customWidth="1"/>
-    <col min="17" max="17" width="12.5703125" customWidth="1"/>
-    <col min="18" max="20" width="13.7109375" customWidth="1"/>
+    <col min="1" max="1" width="6.14285714285714" style="3" customWidth="1"/>
+    <col min="2" max="2" width="14.4285714285714" customWidth="1"/>
+    <col min="3" max="3" width="39.4285714285714" style="4" customWidth="1"/>
+    <col min="4" max="4" width="35.7142857142857" style="3" customWidth="1"/>
+    <col min="5" max="5" width="18.5714285714286" style="3" customWidth="1"/>
+    <col min="6" max="6" width="25.8571428571429" style="3" customWidth="1"/>
+    <col min="7" max="7" width="24.7142857142857" style="3" customWidth="1"/>
+    <col min="8" max="8" width="25.7142857142857" customWidth="1"/>
+    <col min="9" max="9" width="6.14285714285714" style="5" customWidth="1"/>
+    <col min="10" max="10" width="19.4285714285714" style="3" customWidth="1"/>
+    <col min="11" max="11" width="10.1428571428571" customWidth="1"/>
+    <col min="12" max="12" width="11.1428571428571" customWidth="1"/>
+    <col min="13" max="13" width="12.1428571428571" customWidth="1"/>
+    <col min="14" max="14" width="14" style="3" customWidth="1"/>
+    <col min="15" max="15" width="11.5714285714286" customWidth="1"/>
+    <col min="16" max="16" width="12.1428571428571" customWidth="1"/>
+    <col min="17" max="17" width="12.5714285714286" customWidth="1"/>
+    <col min="18" max="20" width="13.7142857142857" customWidth="1"/>
     <col min="21" max="21" width="44" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="15.75">
-      <c r="A1" s="137" t="s">
+    <row r="1" ht="16.5" spans="1:21">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="138"/>
-      <c r="C1" s="138"/>
-      <c r="D1" s="138"/>
-      <c r="E1" s="138"/>
-      <c r="F1" s="138"/>
-      <c r="G1" s="138"/>
-      <c r="H1" s="138"/>
-      <c r="I1" s="138"/>
-      <c r="J1" s="138"/>
-      <c r="K1" s="138"/>
-      <c r="L1" s="138"/>
-      <c r="M1" s="138"/>
-      <c r="N1" s="138"/>
-      <c r="O1" s="138"/>
-      <c r="P1" s="138"/>
-      <c r="Q1" s="138"/>
-      <c r="R1" s="138"/>
-      <c r="S1" s="138"/>
-      <c r="T1" s="138"/>
-      <c r="U1" s="139"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
+      <c r="P1" s="7"/>
+      <c r="Q1" s="7"/>
+      <c r="R1" s="7"/>
+      <c r="S1" s="7"/>
+      <c r="T1" s="7"/>
+      <c r="U1" s="92"/>
     </row>
-    <row r="2" spans="1:23">
-      <c r="A2" s="6" t="s">
+    <row r="2" ht="15.75" spans="1:21">
+      <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="K2" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="L2" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="7" t="s">
+      <c r="M2" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="29" t="s">
+      <c r="N2" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="7" t="s">
+      <c r="O2" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="7" t="s">
+      <c r="P2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" s="7" t="s">
+      <c r="Q2" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="R2" s="7" t="s">
+      <c r="R2" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="S2" s="7" t="s">
+      <c r="S2" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="T2" s="7" t="s">
+      <c r="T2" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="U2" s="7" t="s">
+      <c r="U2" s="9" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:23" s="1" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A3" s="8">
+    <row r="3" s="1" customFormat="1" ht="15.75" customHeight="1" spans="1:21">
+      <c r="A3" s="10">
         <v>1</v>
       </c>
-      <c r="B3" s="142" t="s">
+      <c r="B3" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="105" t="s">
+      <c r="C3" s="140" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="106" t="s">
+      <c r="D3" s="141" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="106" t="s">
+      <c r="E3" s="141" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="106" t="s">
+      <c r="F3" s="141" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="107" t="s">
+      <c r="H3" s="142" t="s">
         <v>28</v>
       </c>
-      <c r="I3" s="106" t="s">
+      <c r="I3" s="141" t="s">
         <v>29</v>
       </c>
-      <c r="J3" s="9">
+      <c r="J3" s="13">
         <v>1</v>
       </c>
-      <c r="K3" s="10">
+      <c r="K3" s="14">
         <f t="shared" ref="K3:K18" si="0">J3*5</f>
         <v>5</v>
       </c>
-      <c r="L3" s="10">
+      <c r="L3" s="14">
         <f t="shared" ref="L3:L18" si="1">J3*50</f>
         <v>50</v>
       </c>
-      <c r="M3" s="10">
+      <c r="M3" s="14">
         <f t="shared" ref="M3:M18" si="2">J3*100</f>
         <v>100</v>
       </c>
-      <c r="N3" s="30" t="s">
+      <c r="N3" s="50" t="s">
         <v>30</v>
       </c>
-      <c r="O3" s="31">
+      <c r="O3" s="51">
         <v>0.43</v>
       </c>
-      <c r="P3" s="32">
+      <c r="P3" s="52">
         <f t="shared" ref="P3:P18" si="3">O3*K3</f>
         <v>2.15</v>
       </c>
-      <c r="Q3" s="31">
+      <c r="Q3" s="51">
         <v>0.1956</v>
       </c>
-      <c r="R3" s="32">
+      <c r="R3" s="52">
         <f t="shared" ref="R3:R18" si="4">Q3*L3</f>
-        <v>9.7799999999999994</v>
-      </c>
-      <c r="S3" s="71">
-        <v>0.16619999999999999</v>
-      </c>
-      <c r="T3" s="72">
+        <v>9.78</v>
+      </c>
+      <c r="S3" s="93">
+        <v>0.1662</v>
+      </c>
+      <c r="T3" s="94">
         <f t="shared" ref="T3:T18" si="5">S3*M3</f>
-        <v>16.619999999999997</v>
-      </c>
-      <c r="U3" s="73"/>
+        <v>16.62</v>
+      </c>
+      <c r="U3" s="95"/>
     </row>
-    <row r="4" spans="1:23" ht="15.75" customHeight="1">
-      <c r="A4" s="8">
+    <row r="4" ht="15.75" customHeight="1" spans="1:21">
+      <c r="A4" s="10">
         <v>2</v>
       </c>
-      <c r="B4" s="143"/>
-      <c r="C4" s="108" t="s">
+      <c r="B4" s="15"/>
+      <c r="C4" s="143" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="109" t="s">
+      <c r="D4" s="144" t="s">
         <v>32</v>
       </c>
-      <c r="E4" s="109" t="s">
+      <c r="E4" s="144" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="110" t="s">
+      <c r="F4" s="145" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="H4" s="111" t="s">
+      <c r="H4" s="146" t="s">
         <v>35</v>
       </c>
-      <c r="I4" s="109" t="s">
+      <c r="I4" s="144" t="s">
         <v>36</v>
       </c>
-      <c r="J4" s="11">
+      <c r="J4" s="17">
         <v>1</v>
       </c>
-      <c r="K4" s="13">
+      <c r="K4" s="19">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L4" s="13">
+      <c r="L4" s="19">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="M4" s="13">
+      <c r="M4" s="19">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N4" s="33" t="s">
+      <c r="N4" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="O4" s="34">
+      <c r="O4" s="54">
         <v>0.47</v>
       </c>
-      <c r="P4" s="35">
+      <c r="P4" s="55">
         <f t="shared" si="3"/>
-        <v>2.3499999999999996</v>
-      </c>
-      <c r="Q4" s="34">
-        <v>0.22620000000000001</v>
-      </c>
-      <c r="R4" s="35">
+        <v>2.35</v>
+      </c>
+      <c r="Q4" s="54">
+        <v>0.2262</v>
+      </c>
+      <c r="R4" s="55">
         <f t="shared" si="4"/>
         <v>11.31</v>
       </c>
-      <c r="S4" s="74">
-        <v>0.19389999999999999</v>
-      </c>
-      <c r="T4" s="35">
+      <c r="S4" s="96">
+        <v>0.1939</v>
+      </c>
+      <c r="T4" s="55">
         <f t="shared" si="5"/>
         <v>19.39</v>
       </c>
-      <c r="U4" s="75" t="s">
+      <c r="U4" s="97" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:23" s="2" customFormat="1" ht="51">
-      <c r="A5" s="8">
+    <row r="5" s="2" customFormat="1" ht="51.75" spans="1:21">
+      <c r="A5" s="10">
         <v>3</v>
       </c>
-      <c r="B5" s="143"/>
-      <c r="C5" s="108" t="s">
+      <c r="B5" s="15"/>
+      <c r="C5" s="143" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="111" t="s">
+      <c r="D5" s="146" t="s">
         <v>39</v>
       </c>
-      <c r="E5" s="109" t="s">
+      <c r="E5" s="144" t="s">
         <v>40</v>
       </c>
-      <c r="F5" s="109" t="s">
+      <c r="F5" s="144" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="H5" s="109" t="s">
+      <c r="H5" s="144" t="s">
         <v>28</v>
       </c>
-      <c r="I5" s="109" t="s">
+      <c r="I5" s="144" t="s">
         <v>43</v>
       </c>
-      <c r="J5" s="11">
+      <c r="J5" s="17">
         <v>17</v>
       </c>
-      <c r="K5" s="13">
+      <c r="K5" s="19">
         <f t="shared" si="0"/>
         <v>85</v>
       </c>
-      <c r="L5" s="13">
+      <c r="L5" s="19">
         <f t="shared" si="1"/>
         <v>850</v>
       </c>
-      <c r="M5" s="13">
+      <c r="M5" s="19">
         <f t="shared" si="2"/>
         <v>1700</v>
       </c>
-      <c r="N5" s="36" t="s">
+      <c r="N5" s="56" t="s">
         <v>30</v>
       </c>
-      <c r="O5" s="34">
-        <v>1.5800000000000002E-2</v>
-      </c>
-      <c r="P5" s="35">
+      <c r="O5" s="54">
+        <v>0.0158</v>
+      </c>
+      <c r="P5" s="55">
         <f t="shared" si="3"/>
-        <v>1.3430000000000002</v>
-      </c>
-      <c r="Q5" s="34">
-        <v>9.2399999999999999E-3</v>
-      </c>
-      <c r="R5" s="35">
+        <v>1.343</v>
+      </c>
+      <c r="Q5" s="54">
+        <v>0.00924</v>
+      </c>
+      <c r="R5" s="55">
         <f t="shared" si="4"/>
-        <v>7.8540000000000001</v>
-      </c>
-      <c r="S5" s="74">
-        <v>7.26E-3</v>
-      </c>
-      <c r="T5" s="35">
+        <v>7.854</v>
+      </c>
+      <c r="S5" s="96">
+        <v>0.00726</v>
+      </c>
+      <c r="T5" s="55">
         <f t="shared" si="5"/>
-        <v>12.342000000000001</v>
-      </c>
-      <c r="U5" s="76" t="s">
+        <v>12.342</v>
+      </c>
+      <c r="U5" s="98" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="15.75" customHeight="1">
-      <c r="A6" s="8">
+    <row r="6" ht="15.75" customHeight="1" spans="1:23">
+      <c r="A6" s="10">
         <v>4</v>
       </c>
-      <c r="B6" s="143"/>
-      <c r="C6" s="108" t="s">
+      <c r="B6" s="15"/>
+      <c r="C6" s="143" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="109" t="s">
+      <c r="D6" s="144" t="s">
         <v>46</v>
       </c>
-      <c r="E6" s="109" t="s">
+      <c r="E6" s="144" t="s">
         <v>47</v>
       </c>
-      <c r="F6" s="109" t="s">
+      <c r="F6" s="144" t="s">
         <v>48</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="H6" s="109" t="s">
+      <c r="H6" s="144" t="s">
         <v>28</v>
       </c>
-      <c r="I6" s="109" t="s">
+      <c r="I6" s="144" t="s">
         <v>50</v>
       </c>
-      <c r="J6" s="11">
+      <c r="J6" s="17">
         <v>2</v>
       </c>
-      <c r="K6" s="13">
+      <c r="K6" s="19">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="L6" s="13">
+      <c r="L6" s="19">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="M6" s="13">
+      <c r="M6" s="19">
         <f t="shared" si="2"/>
         <v>200</v>
       </c>
-      <c r="N6" s="112" t="s">
+      <c r="N6" s="147" t="s">
         <v>30</v>
       </c>
-      <c r="O6" s="37">
-        <v>0.30199999999999999</v>
-      </c>
-      <c r="P6" s="35">
+      <c r="O6" s="57">
+        <v>0.302</v>
+      </c>
+      <c r="P6" s="55">
         <f t="shared" si="3"/>
         <v>3.02</v>
       </c>
-      <c r="Q6" s="37">
-        <v>0.18149999999999999</v>
-      </c>
-      <c r="R6" s="35">
+      <c r="Q6" s="57">
+        <v>0.1815</v>
+      </c>
+      <c r="R6" s="55">
         <f t="shared" si="4"/>
-        <v>18.149999999999999</v>
-      </c>
-      <c r="S6" s="74">
-        <v>0.18149999999999999</v>
-      </c>
-      <c r="T6" s="35">
+        <v>18.15</v>
+      </c>
+      <c r="S6" s="96">
+        <v>0.1815</v>
+      </c>
+      <c r="T6" s="55">
         <f t="shared" si="5"/>
-        <v>36.299999999999997</v>
-      </c>
-      <c r="U6" s="77"/>
-      <c r="V6" s="78"/>
-      <c r="W6" s="78"/>
+        <v>36.3</v>
+      </c>
+      <c r="U6" s="99"/>
+      <c r="V6" s="100"/>
+      <c r="W6" s="100"/>
     </row>
-    <row r="7" spans="1:23">
-      <c r="A7" s="8">
+    <row r="7" ht="15.75" spans="1:23">
+      <c r="A7" s="10">
         <v>5</v>
       </c>
-      <c r="B7" s="143"/>
-      <c r="C7" s="113" t="s">
+      <c r="B7" s="15"/>
+      <c r="C7" s="148" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="109" t="s">
+      <c r="D7" s="144" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="109" t="s">
+      <c r="E7" s="144" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="109" t="s">
+      <c r="F7" s="144" t="s">
         <v>53</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="G7" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="H7" s="109" t="s">
+      <c r="H7" s="144" t="s">
         <v>28</v>
       </c>
-      <c r="I7" s="109" t="s">
+      <c r="I7" s="144" t="s">
         <v>55</v>
       </c>
-      <c r="J7" s="11">
+      <c r="J7" s="17">
         <v>2</v>
       </c>
-      <c r="K7" s="13">
+      <c r="K7" s="19">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="L7" s="13">
+      <c r="L7" s="19">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="M7" s="13">
+      <c r="M7" s="19">
         <f t="shared" si="2"/>
         <v>200</v>
       </c>
-      <c r="N7" s="112" t="s">
+      <c r="N7" s="147" t="s">
         <v>30</v>
       </c>
-      <c r="O7" s="37">
+      <c r="O7" s="57">
         <v>0.378</v>
       </c>
-      <c r="P7" s="35">
+      <c r="P7" s="55">
         <f t="shared" si="3"/>
-        <v>3.7800000000000002</v>
-      </c>
-      <c r="Q7" s="37">
+        <v>3.78</v>
+      </c>
+      <c r="Q7" s="57">
         <v>0.2487</v>
       </c>
-      <c r="R7" s="35">
+      <c r="R7" s="55">
         <f t="shared" si="4"/>
         <v>24.87</v>
       </c>
-      <c r="S7" s="74">
+      <c r="S7" s="96">
         <v>0.2487</v>
       </c>
-      <c r="T7" s="35">
+      <c r="T7" s="55">
         <f t="shared" si="5"/>
         <v>49.74</v>
       </c>
-      <c r="U7" s="77"/>
-      <c r="V7" s="78"/>
-      <c r="W7" s="78"/>
+      <c r="U7" s="99"/>
+      <c r="V7" s="100"/>
+      <c r="W7" s="100"/>
     </row>
-    <row r="8" spans="1:23" ht="15.75" customHeight="1">
-      <c r="A8" s="8">
+    <row r="8" ht="15.75" customHeight="1" spans="1:23">
+      <c r="A8" s="10">
         <v>6</v>
       </c>
-      <c r="B8" s="143"/>
-      <c r="C8" s="108" t="s">
+      <c r="B8" s="15"/>
+      <c r="C8" s="143" t="s">
         <v>56</v>
       </c>
-      <c r="D8" s="109" t="s">
+      <c r="D8" s="144" t="s">
         <v>57</v>
       </c>
-      <c r="E8" s="109" t="s">
+      <c r="E8" s="144" t="s">
         <v>58</v>
       </c>
-      <c r="F8" s="109" t="s">
+      <c r="F8" s="144" t="s">
         <v>59</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="G8" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="H8" s="109" t="s">
+      <c r="H8" s="144" t="s">
         <v>28</v>
       </c>
-      <c r="I8" s="109" t="s">
+      <c r="I8" s="144" t="s">
         <v>61</v>
       </c>
-      <c r="J8" s="11">
+      <c r="J8" s="17">
         <v>1</v>
       </c>
-      <c r="K8" s="13">
+      <c r="K8" s="19">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L8" s="13">
+      <c r="L8" s="19">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="M8" s="13">
+      <c r="M8" s="19">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N8" s="112" t="s">
+      <c r="N8" s="147" t="s">
         <v>30</v>
       </c>
-      <c r="O8" s="37">
+      <c r="O8" s="57">
         <v>0.11</v>
       </c>
-      <c r="P8" s="35">
+      <c r="P8" s="55">
         <f t="shared" si="3"/>
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="Q8" s="37">
-        <v>4.36E-2</v>
-      </c>
-      <c r="R8" s="35">
+        <v>0.55</v>
+      </c>
+      <c r="Q8" s="57">
+        <v>0.0436</v>
+      </c>
+      <c r="R8" s="55">
         <f t="shared" si="4"/>
-        <v>2.1800000000000002</v>
-      </c>
-      <c r="S8" s="74">
-        <v>3.5700000000000003E-2</v>
-      </c>
-      <c r="T8" s="35">
+        <v>2.18</v>
+      </c>
+      <c r="S8" s="96">
+        <v>0.0357</v>
+      </c>
+      <c r="T8" s="55">
         <f t="shared" si="5"/>
-        <v>3.5700000000000003</v>
-      </c>
-      <c r="U8" s="77"/>
-      <c r="V8" s="78"/>
-      <c r="W8" s="78"/>
+        <v>3.57</v>
+      </c>
+      <c r="U8" s="99"/>
+      <c r="V8" s="100"/>
+      <c r="W8" s="100"/>
     </row>
-    <row r="9" spans="1:23" ht="15.75" customHeight="1">
-      <c r="A9" s="8">
+    <row r="9" ht="15.75" customHeight="1" spans="1:23">
+      <c r="A9" s="10">
         <v>7</v>
       </c>
-      <c r="B9" s="143"/>
-      <c r="C9" s="108" t="s">
+      <c r="B9" s="15"/>
+      <c r="C9" s="143" t="s">
         <v>62</v>
       </c>
-      <c r="D9" s="109" t="s">
+      <c r="D9" s="144" t="s">
         <v>63</v>
       </c>
-      <c r="E9" s="109" t="s">
+      <c r="E9" s="144" t="s">
         <v>64</v>
       </c>
-      <c r="F9" s="110" t="s">
+      <c r="F9" s="145" t="s">
         <v>65</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="G9" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="H9" s="109" t="s">
+      <c r="H9" s="144" t="s">
         <v>66</v>
       </c>
-      <c r="I9" s="109" t="s">
+      <c r="I9" s="144" t="s">
         <v>67</v>
       </c>
-      <c r="J9" s="11">
+      <c r="J9" s="17">
         <v>4</v>
       </c>
-      <c r="K9" s="13">
+      <c r="K9" s="19">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="L9" s="13">
+      <c r="L9" s="19">
         <f t="shared" si="1"/>
         <v>200</v>
       </c>
-      <c r="M9" s="13">
+      <c r="M9" s="19">
         <f t="shared" si="2"/>
         <v>400</v>
       </c>
-      <c r="N9" s="112" t="s">
+      <c r="N9" s="147" t="s">
         <v>30</v>
       </c>
-      <c r="O9" s="37">
-        <v>2.5999999999999999E-2</v>
-      </c>
-      <c r="P9" s="35">
+      <c r="O9" s="57">
+        <v>0.026</v>
+      </c>
+      <c r="P9" s="55">
         <f t="shared" si="3"/>
         <v>0.52</v>
       </c>
-      <c r="Q9" s="37">
-        <v>1.1599999999999999E-2</v>
-      </c>
-      <c r="R9" s="35">
+      <c r="Q9" s="57">
+        <v>0.0116</v>
+      </c>
+      <c r="R9" s="55">
         <f t="shared" si="4"/>
-        <v>2.3199999999999998</v>
-      </c>
-      <c r="S9" s="74">
-        <v>1.1599999999999999E-2</v>
-      </c>
-      <c r="T9" s="35">
+        <v>2.32</v>
+      </c>
+      <c r="S9" s="96">
+        <v>0.0116</v>
+      </c>
+      <c r="T9" s="55">
         <f t="shared" si="5"/>
-        <v>4.6399999999999997</v>
-      </c>
-      <c r="U9" s="77"/>
-      <c r="V9" s="78"/>
-      <c r="W9" s="78"/>
+        <v>4.64</v>
+      </c>
+      <c r="U9" s="99"/>
+      <c r="V9" s="100"/>
+      <c r="W9" s="100"/>
     </row>
-    <row r="10" spans="1:23" ht="15.75" customHeight="1">
-      <c r="A10" s="8">
+    <row r="10" ht="15.75" customHeight="1" spans="1:23">
+      <c r="A10" s="10">
         <v>8</v>
       </c>
-      <c r="B10" s="143"/>
-      <c r="C10" s="108" t="s">
+      <c r="B10" s="15"/>
+      <c r="C10" s="143" t="s">
         <v>68</v>
       </c>
-      <c r="D10" s="109" t="s">
+      <c r="D10" s="144" t="s">
         <v>69</v>
       </c>
-      <c r="E10" s="109" t="s">
+      <c r="E10" s="144" t="s">
         <v>58</v>
       </c>
-      <c r="F10" s="109" t="s">
+      <c r="F10" s="144" t="s">
         <v>70</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="H10" s="109" t="s">
+      <c r="H10" s="144" t="s">
         <v>28</v>
       </c>
-      <c r="I10" s="109" t="s">
+      <c r="I10" s="144" t="s">
         <v>72</v>
       </c>
-      <c r="J10" s="11">
+      <c r="J10" s="17">
         <v>1</v>
       </c>
-      <c r="K10" s="13">
+      <c r="K10" s="19">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L10" s="13">
+      <c r="L10" s="19">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="M10" s="13">
+      <c r="M10" s="19">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N10" s="112" t="s">
+      <c r="N10" s="147" t="s">
         <v>30</v>
       </c>
-      <c r="O10" s="37">
+      <c r="O10" s="57">
         <v>0.11</v>
       </c>
-      <c r="P10" s="35">
+      <c r="P10" s="55">
         <f t="shared" si="3"/>
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="Q10" s="37">
-        <v>4.3400000000000001E-2</v>
-      </c>
-      <c r="R10" s="35">
+        <v>0.55</v>
+      </c>
+      <c r="Q10" s="57">
+        <v>0.0434</v>
+      </c>
+      <c r="R10" s="55">
         <f t="shared" si="4"/>
         <v>2.17</v>
       </c>
-      <c r="S10" s="74">
-        <v>3.5900000000000001E-2</v>
-      </c>
-      <c r="T10" s="35">
+      <c r="S10" s="96">
+        <v>0.0359</v>
+      </c>
+      <c r="T10" s="55">
         <f t="shared" si="5"/>
-        <v>3.5900000000000003</v>
-      </c>
-      <c r="U10" s="77"/>
-      <c r="V10" s="78"/>
-      <c r="W10" s="78"/>
+        <v>3.59</v>
+      </c>
+      <c r="U10" s="99"/>
+      <c r="V10" s="100"/>
+      <c r="W10" s="100"/>
     </row>
-    <row r="11" spans="1:23" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A11" s="8">
+    <row r="11" s="2" customFormat="1" ht="15.75" customHeight="1" spans="1:23">
+      <c r="A11" s="10">
         <v>9</v>
       </c>
-      <c r="B11" s="143"/>
-      <c r="C11" s="108" t="s">
+      <c r="B11" s="15"/>
+      <c r="C11" s="143" t="s">
         <v>73</v>
       </c>
-      <c r="D11" s="109" t="s">
+      <c r="D11" s="144" t="s">
         <v>74</v>
       </c>
-      <c r="E11" s="109" t="s">
+      <c r="E11" s="144" t="s">
         <v>75</v>
       </c>
-      <c r="F11" s="109" t="s">
+      <c r="F11" s="144" t="s">
         <v>76</v>
       </c>
-      <c r="G11" s="11" t="s">
+      <c r="G11" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="H11" s="109" t="s">
+      <c r="H11" s="144" t="s">
         <v>28</v>
       </c>
-      <c r="I11" s="109" t="s">
+      <c r="I11" s="144" t="s">
         <v>78</v>
       </c>
-      <c r="J11" s="11">
+      <c r="J11" s="17">
         <v>1</v>
       </c>
-      <c r="K11" s="13">
+      <c r="K11" s="19">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L11" s="13">
+      <c r="L11" s="19">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="M11" s="13">
+      <c r="M11" s="19">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N11" s="33" t="s">
+      <c r="N11" s="53" t="s">
         <v>79</v>
       </c>
-      <c r="O11" s="37">
+      <c r="O11" s="57">
         <v>0.44</v>
       </c>
-      <c r="P11" s="35">
+      <c r="P11" s="55">
         <f t="shared" si="3"/>
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="Q11" s="37">
-        <v>0.23699999999999999</v>
-      </c>
-      <c r="R11" s="35">
+        <v>2.2</v>
+      </c>
+      <c r="Q11" s="57">
+        <v>0.237</v>
+      </c>
+      <c r="R11" s="55">
         <f t="shared" si="4"/>
         <v>11.85</v>
       </c>
-      <c r="S11" s="79">
-        <v>0.20399999999999999</v>
-      </c>
-      <c r="T11" s="35">
+      <c r="S11" s="101">
+        <v>0.204</v>
+      </c>
+      <c r="T11" s="55">
         <f t="shared" si="5"/>
-        <v>20.399999999999999</v>
-      </c>
-      <c r="U11" s="80"/>
-      <c r="V11" s="81"/>
-      <c r="W11" s="81"/>
+        <v>20.4</v>
+      </c>
+      <c r="U11" s="102"/>
+      <c r="V11" s="103"/>
+      <c r="W11" s="103"/>
     </row>
-    <row r="12" spans="1:23" ht="15.75" customHeight="1">
-      <c r="A12" s="8">
+    <row r="12" ht="15.75" customHeight="1" spans="1:23">
+      <c r="A12" s="10">
         <v>10</v>
       </c>
-      <c r="B12" s="143"/>
-      <c r="C12" s="108" t="s">
+      <c r="B12" s="15"/>
+      <c r="C12" s="143" t="s">
         <v>80</v>
       </c>
-      <c r="D12" s="109" t="s">
+      <c r="D12" s="144" t="s">
         <v>81</v>
       </c>
-      <c r="E12" s="109" t="s">
+      <c r="E12" s="144" t="s">
         <v>25</v>
       </c>
-      <c r="F12" s="109" t="s">
+      <c r="F12" s="144" t="s">
         <v>82</v>
       </c>
-      <c r="G12" s="11" t="s">
+      <c r="G12" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="H12" s="109" t="s">
+      <c r="H12" s="144" t="s">
         <v>28</v>
       </c>
-      <c r="I12" s="109" t="s">
+      <c r="I12" s="144" t="s">
         <v>84</v>
       </c>
-      <c r="J12" s="11">
+      <c r="J12" s="17">
         <v>1</v>
       </c>
-      <c r="K12" s="13">
+      <c r="K12" s="19">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L12" s="13">
+      <c r="L12" s="19">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="M12" s="13">
+      <c r="M12" s="19">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N12" s="33" t="s">
+      <c r="N12" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="O12" s="38">
+      <c r="O12" s="58">
         <v>0.6411</v>
       </c>
-      <c r="P12" s="35">
+      <c r="P12" s="55">
         <f t="shared" si="3"/>
-        <v>3.2054999999999998</v>
-      </c>
-      <c r="Q12" s="38">
+        <v>3.2055</v>
+      </c>
+      <c r="Q12" s="58">
         <v>0.6411</v>
       </c>
-      <c r="R12" s="35">
+      <c r="R12" s="55">
         <f t="shared" si="4"/>
         <v>32.055</v>
       </c>
-      <c r="S12" s="74">
+      <c r="S12" s="96">
         <v>0.6411</v>
       </c>
-      <c r="T12" s="35">
+      <c r="T12" s="55">
         <f t="shared" si="5"/>
         <v>64.11</v>
       </c>
-      <c r="U12" s="82"/>
-      <c r="V12" s="78"/>
-      <c r="W12" s="78"/>
+      <c r="U12" s="104"/>
+      <c r="V12" s="100"/>
+      <c r="W12" s="100"/>
     </row>
-    <row r="13" spans="1:23" ht="15.75" customHeight="1">
-      <c r="A13" s="8">
+    <row r="13" ht="15.75" customHeight="1" spans="1:23">
+      <c r="A13" s="10">
         <v>11</v>
       </c>
-      <c r="B13" s="143"/>
-      <c r="C13" s="108" t="s">
+      <c r="B13" s="15"/>
+      <c r="C13" s="143" t="s">
         <v>86</v>
       </c>
-      <c r="D13" s="109" t="s">
+      <c r="D13" s="144" t="s">
         <v>87</v>
       </c>
-      <c r="E13" s="109" t="s">
+      <c r="E13" s="144" t="s">
         <v>40</v>
       </c>
-      <c r="F13" s="109" t="s">
+      <c r="F13" s="144" t="s">
         <v>88</v>
       </c>
-      <c r="G13" s="11" t="s">
+      <c r="G13" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="H13" s="109" t="s">
+      <c r="H13" s="144" t="s">
         <v>28</v>
       </c>
-      <c r="I13" s="109" t="s">
+      <c r="I13" s="144" t="s">
         <v>89</v>
       </c>
-      <c r="J13" s="11">
+      <c r="J13" s="17">
         <v>2</v>
       </c>
-      <c r="K13" s="13">
+      <c r="K13" s="19">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="L13" s="13">
+      <c r="L13" s="19">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="M13" s="13">
+      <c r="M13" s="19">
         <f t="shared" si="2"/>
         <v>200</v>
       </c>
-      <c r="N13" s="33" t="s">
+      <c r="N13" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="O13" s="37">
+      <c r="O13" s="57">
         <v>0.08</v>
       </c>
-      <c r="P13" s="35">
+      <c r="P13" s="55">
         <f t="shared" si="3"/>
         <v>0.8</v>
       </c>
-      <c r="Q13" s="37">
-        <v>3.56E-2</v>
-      </c>
-      <c r="R13" s="35">
+      <c r="Q13" s="57">
+        <v>0.0356</v>
+      </c>
+      <c r="R13" s="55">
         <f t="shared" si="4"/>
         <v>3.56</v>
       </c>
-      <c r="S13" s="74">
-        <v>3.56E-2</v>
-      </c>
-      <c r="T13" s="35">
+      <c r="S13" s="96">
+        <v>0.0356</v>
+      </c>
+      <c r="T13" s="55">
         <f t="shared" si="5"/>
         <v>7.12</v>
       </c>
-      <c r="U13" s="82"/>
-      <c r="V13" s="78"/>
-      <c r="W13" s="78"/>
+      <c r="U13" s="104"/>
+      <c r="V13" s="100"/>
+      <c r="W13" s="100"/>
     </row>
-    <row r="14" spans="1:23" ht="15.75" customHeight="1">
-      <c r="A14" s="8">
+    <row r="14" ht="15.75" customHeight="1" spans="1:23">
+      <c r="A14" s="10">
         <v>12</v>
       </c>
-      <c r="B14" s="143"/>
-      <c r="C14" s="108" t="s">
+      <c r="B14" s="15"/>
+      <c r="C14" s="143" t="s">
         <v>90</v>
       </c>
-      <c r="D14" s="109" t="s">
+      <c r="D14" s="144" t="s">
         <v>91</v>
       </c>
-      <c r="E14" s="109" t="s">
+      <c r="E14" s="144" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="109" t="s">
+      <c r="F14" s="144" t="s">
         <v>92</v>
       </c>
-      <c r="G14" s="11" t="s">
+      <c r="G14" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="H14" s="109" t="s">
+      <c r="H14" s="144" t="s">
         <v>28</v>
       </c>
-      <c r="I14" s="109" t="s">
+      <c r="I14" s="144" t="s">
         <v>94</v>
       </c>
-      <c r="J14" s="11">
+      <c r="J14" s="17">
         <v>2</v>
       </c>
-      <c r="K14" s="13">
+      <c r="K14" s="19">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="L14" s="13">
+      <c r="L14" s="19">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="M14" s="13">
+      <c r="M14" s="19">
         <f t="shared" si="2"/>
         <v>200</v>
       </c>
-      <c r="N14" s="33" t="s">
+      <c r="N14" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="O14" s="37">
-        <v>0.25900000000000001</v>
-      </c>
-      <c r="P14" s="35">
+      <c r="O14" s="57">
+        <v>0.259</v>
+      </c>
+      <c r="P14" s="55">
         <f t="shared" si="3"/>
         <v>2.59</v>
       </c>
-      <c r="Q14" s="37">
-        <v>0.14660000000000001</v>
-      </c>
-      <c r="R14" s="35">
+      <c r="Q14" s="57">
+        <v>0.1466</v>
+      </c>
+      <c r="R14" s="55">
         <f t="shared" si="4"/>
         <v>14.66</v>
       </c>
-      <c r="S14" s="74">
-        <v>0.14660000000000001</v>
-      </c>
-      <c r="T14" s="35">
+      <c r="S14" s="96">
+        <v>0.1466</v>
+      </c>
+      <c r="T14" s="55">
         <f t="shared" si="5"/>
         <v>29.32</v>
       </c>
-      <c r="U14" s="82"/>
-      <c r="V14" s="78"/>
-      <c r="W14" s="78"/>
+      <c r="U14" s="104"/>
+      <c r="V14" s="100"/>
+      <c r="W14" s="100"/>
     </row>
-    <row r="15" spans="1:23" ht="15.75" customHeight="1">
-      <c r="A15" s="8">
+    <row r="15" ht="15.75" customHeight="1" spans="1:23">
+      <c r="A15" s="10">
         <v>13</v>
       </c>
-      <c r="B15" s="143"/>
-      <c r="C15" s="108" t="s">
+      <c r="B15" s="15"/>
+      <c r="C15" s="143" t="s">
         <v>95</v>
       </c>
-      <c r="D15" s="109" t="s">
+      <c r="D15" s="144" t="s">
         <v>96</v>
       </c>
-      <c r="E15" s="109" t="s">
+      <c r="E15" s="144" t="s">
         <v>40</v>
       </c>
-      <c r="F15" s="109" t="s">
+      <c r="F15" s="144" t="s">
         <v>97</v>
       </c>
-      <c r="G15" s="11" t="s">
+      <c r="G15" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="H15" s="109" t="s">
+      <c r="H15" s="144" t="s">
         <v>28</v>
       </c>
-      <c r="I15" s="109" t="s">
+      <c r="I15" s="144" t="s">
         <v>99</v>
       </c>
-      <c r="J15" s="11">
+      <c r="J15" s="17">
         <v>2</v>
       </c>
-      <c r="K15" s="39">
+      <c r="K15" s="59">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="L15" s="13">
+      <c r="L15" s="19">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="M15" s="13">
+      <c r="M15" s="19">
         <f t="shared" si="2"/>
         <v>200</v>
       </c>
-      <c r="N15" s="33" t="s">
+      <c r="N15" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="O15" s="37">
+      <c r="O15" s="57">
         <v>0.156</v>
       </c>
-      <c r="P15" s="35">
+      <c r="P15" s="55">
         <f t="shared" si="3"/>
         <v>1.56</v>
       </c>
-      <c r="Q15" s="37">
-        <v>7.3499999999999996E-2</v>
-      </c>
-      <c r="R15" s="35">
+      <c r="Q15" s="57">
+        <v>0.0735</v>
+      </c>
+      <c r="R15" s="55">
         <f t="shared" si="4"/>
         <v>7.35</v>
       </c>
-      <c r="S15" s="74">
-        <v>7.3499999999999996E-2</v>
-      </c>
-      <c r="T15" s="35">
+      <c r="S15" s="96">
+        <v>0.0735</v>
+      </c>
+      <c r="T15" s="55">
         <f t="shared" si="5"/>
         <v>14.7</v>
       </c>
-      <c r="U15" s="82"/>
-      <c r="V15" s="78"/>
-      <c r="W15" s="78"/>
+      <c r="U15" s="104"/>
+      <c r="V15" s="100"/>
+      <c r="W15" s="100"/>
     </row>
-    <row r="16" spans="1:23" ht="15.75" customHeight="1">
-      <c r="A16" s="8">
+    <row r="16" ht="15.75" customHeight="1" spans="1:23">
+      <c r="A16" s="10">
         <v>14</v>
       </c>
-      <c r="B16" s="143"/>
-      <c r="C16" s="108" t="s">
+      <c r="B16" s="15"/>
+      <c r="C16" s="143" t="s">
         <v>100</v>
       </c>
-      <c r="D16" s="109" t="s">
+      <c r="D16" s="144" t="s">
         <v>101</v>
       </c>
-      <c r="E16" s="109" t="s">
+      <c r="E16" s="144" t="s">
         <v>40</v>
       </c>
-      <c r="F16" s="109" t="s">
+      <c r="F16" s="144" t="s">
         <v>102</v>
       </c>
-      <c r="G16" s="11" t="s">
+      <c r="G16" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="H16" s="109" t="s">
+      <c r="H16" s="144" t="s">
         <v>28</v>
       </c>
-      <c r="I16" s="109" t="s">
+      <c r="I16" s="144" t="s">
         <v>104</v>
       </c>
-      <c r="J16" s="40">
+      <c r="J16" s="60">
         <v>1</v>
       </c>
-      <c r="K16" s="41">
+      <c r="K16" s="61">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L16" s="42">
+      <c r="L16" s="62">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="M16" s="13">
+      <c r="M16" s="19">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N16" s="33" t="s">
+      <c r="N16" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="O16" s="43">
+      <c r="O16" s="63">
         <v>0.52</v>
       </c>
-      <c r="P16" s="44">
+      <c r="P16" s="64">
         <f t="shared" si="3"/>
         <v>2.6</v>
       </c>
-      <c r="Q16" s="43">
-        <v>0.27800000000000002</v>
-      </c>
-      <c r="R16" s="44">
+      <c r="Q16" s="63">
+        <v>0.278</v>
+      </c>
+      <c r="R16" s="64">
         <f t="shared" si="4"/>
-        <v>13.900000000000002</v>
-      </c>
-      <c r="S16" s="83">
+        <v>13.9</v>
+      </c>
+      <c r="S16" s="105">
         <v>0.2422</v>
       </c>
-      <c r="T16" s="35">
+      <c r="T16" s="55">
         <f t="shared" si="5"/>
         <v>24.22</v>
       </c>
-      <c r="U16" s="82"/>
-      <c r="V16" s="78"/>
-      <c r="W16" s="78"/>
+      <c r="U16" s="104"/>
+      <c r="V16" s="100"/>
+      <c r="W16" s="100"/>
     </row>
-    <row r="17" spans="1:23" ht="15.75" customHeight="1">
-      <c r="A17" s="8">
+    <row r="17" ht="15.75" customHeight="1" spans="1:23">
+      <c r="A17" s="10">
         <v>15</v>
       </c>
-      <c r="B17" s="143"/>
-      <c r="C17" s="114" t="s">
+      <c r="B17" s="15"/>
+      <c r="C17" s="149" t="s">
         <v>105</v>
       </c>
-      <c r="D17" s="115" t="s">
+      <c r="D17" s="150" t="s">
         <v>106</v>
       </c>
-      <c r="E17" s="115" t="s">
+      <c r="E17" s="150" t="s">
         <v>40</v>
       </c>
-      <c r="F17" s="115" t="s">
+      <c r="F17" s="150" t="s">
         <v>107</v>
       </c>
-      <c r="G17" s="14" t="s">
+      <c r="G17" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="H17" s="115" t="s">
+      <c r="H17" s="150" t="s">
         <v>109</v>
       </c>
-      <c r="I17" s="115" t="s">
+      <c r="I17" s="150" t="s">
         <v>110</v>
       </c>
-      <c r="J17" s="14">
+      <c r="J17" s="22">
         <v>1</v>
       </c>
-      <c r="K17" s="45">
+      <c r="K17" s="65">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L17" s="39">
+      <c r="L17" s="59">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="M17" s="39">
+      <c r="M17" s="59">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N17" s="46" t="s">
+      <c r="N17" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="O17" s="47">
+      <c r="O17" s="67">
         <v>0.1</v>
       </c>
-      <c r="P17" s="44">
+      <c r="P17" s="64">
         <f t="shared" si="3"/>
         <v>0.5</v>
       </c>
-      <c r="Q17" s="43">
-        <v>1.8200000000000001E-2</v>
-      </c>
-      <c r="R17" s="44">
+      <c r="Q17" s="63">
+        <v>0.0182</v>
+      </c>
+      <c r="R17" s="64">
         <f t="shared" si="4"/>
         <v>0.91</v>
       </c>
-      <c r="S17" s="83">
-        <v>1.4800000000000001E-2</v>
-      </c>
-      <c r="T17" s="44">
+      <c r="S17" s="105">
+        <v>0.0148</v>
+      </c>
+      <c r="T17" s="64">
         <f t="shared" si="5"/>
         <v>1.48</v>
       </c>
-      <c r="U17" s="84"/>
-      <c r="V17" s="78"/>
-      <c r="W17" s="78"/>
+      <c r="U17" s="106"/>
+      <c r="V17" s="100"/>
+      <c r="W17" s="100"/>
     </row>
-    <row r="18" spans="1:23" ht="15.75" customHeight="1">
-      <c r="A18" s="8"/>
-      <c r="B18" s="144" t="s">
+    <row r="18" ht="15.75" customHeight="1" spans="1:23">
+      <c r="A18" s="10"/>
+      <c r="B18" s="23" t="s">
         <v>111</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="24" t="s">
         <v>112</v>
       </c>
-      <c r="D18" s="16" t="s">
+      <c r="D18" s="25" t="s">
         <v>113</v>
       </c>
-      <c r="E18" s="116" t="s">
+      <c r="E18" s="151" t="s">
         <v>114</v>
       </c>
-      <c r="F18" s="17" t="s">
+      <c r="F18" s="26" t="s">
         <v>115</v>
       </c>
-      <c r="G18" s="17" t="s">
+      <c r="G18" s="26" t="s">
         <v>116</v>
       </c>
-      <c r="H18" s="106" t="s">
+      <c r="H18" s="141" t="s">
         <v>109</v>
       </c>
-      <c r="I18" s="116" t="s">
+      <c r="I18" s="151" t="s">
         <v>28</v>
       </c>
-      <c r="J18" s="17">
+      <c r="J18" s="26">
         <v>1</v>
       </c>
-      <c r="K18" s="17">
+      <c r="K18" s="26">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L18" s="17">
+      <c r="L18" s="26">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="M18" s="17">
+      <c r="M18" s="26">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N18" s="48" t="s">
+      <c r="N18" s="68" t="s">
         <v>117</v>
       </c>
-      <c r="O18" s="49">
+      <c r="O18" s="69">
         <v>0.5</v>
       </c>
-      <c r="P18" s="50">
+      <c r="P18" s="70">
         <f t="shared" si="3"/>
         <v>2.5</v>
       </c>
-      <c r="Q18" s="49">
+      <c r="Q18" s="69">
         <v>0.5</v>
       </c>
-      <c r="R18" s="50">
+      <c r="R18" s="70">
         <f t="shared" si="4"/>
         <v>25</v>
       </c>
-      <c r="S18" s="49">
+      <c r="S18" s="69">
         <v>0.3</v>
       </c>
-      <c r="T18" s="50">
+      <c r="T18" s="70">
         <f t="shared" si="5"/>
         <v>30</v>
       </c>
-      <c r="U18" s="85"/>
-      <c r="V18" s="78"/>
-      <c r="W18" s="78"/>
+      <c r="U18" s="107"/>
+      <c r="V18" s="100"/>
+      <c r="W18" s="100"/>
     </row>
-    <row r="19" spans="1:23">
-      <c r="A19" s="8">
+    <row r="19" ht="15.75" spans="1:23">
+      <c r="A19" s="10">
         <v>16</v>
       </c>
-      <c r="B19" s="145"/>
-      <c r="C19" s="117" t="s">
+      <c r="B19" s="27"/>
+      <c r="C19" s="152" t="s">
         <v>118</v>
       </c>
-      <c r="D19" s="118" t="s">
+      <c r="D19" s="153" t="s">
         <v>119</v>
       </c>
-      <c r="E19" s="118" t="s">
+      <c r="E19" s="153" t="s">
         <v>120</v>
       </c>
-      <c r="F19" s="118" t="s">
+      <c r="F19" s="153" t="s">
         <v>121</v>
       </c>
-      <c r="G19" s="18" t="s">
+      <c r="G19" s="29" t="s">
         <v>122</v>
       </c>
-      <c r="H19" s="118" t="s">
+      <c r="H19" s="153" t="s">
         <v>123</v>
       </c>
-      <c r="I19" s="118" t="s">
+      <c r="I19" s="153" t="s">
         <v>124</v>
       </c>
-      <c r="J19" s="18">
+      <c r="J19" s="29">
         <v>2</v>
       </c>
-      <c r="K19" s="21">
+      <c r="K19" s="34">
         <f t="shared" ref="K19:K67" si="6">J19*5</f>
         <v>10</v>
       </c>
-      <c r="L19" s="21">
+      <c r="L19" s="34">
         <f t="shared" ref="L19:L67" si="7">J19*50</f>
         <v>100</v>
       </c>
-      <c r="M19" s="21">
+      <c r="M19" s="34">
         <f t="shared" ref="M19:M67" si="8">J19*100</f>
         <v>200</v>
       </c>
-      <c r="N19" s="51" t="s">
+      <c r="N19" s="71" t="s">
         <v>79</v>
       </c>
-      <c r="O19" s="52">
-        <v>0.32200000000000001</v>
-      </c>
-      <c r="P19" s="53">
+      <c r="O19" s="72">
+        <v>0.322</v>
+      </c>
+      <c r="P19" s="73">
         <f t="shared" ref="P19:P67" si="9">O19*K19</f>
         <v>3.22</v>
       </c>
-      <c r="Q19" s="52">
+      <c r="Q19" s="72">
         <v>0.2</v>
       </c>
-      <c r="R19" s="53">
+      <c r="R19" s="73">
         <f t="shared" ref="R19:R67" si="10">Q19*L19</f>
         <v>20</v>
       </c>
-      <c r="S19" s="53">
+      <c r="S19" s="73">
         <v>0.2</v>
       </c>
-      <c r="T19" s="53">
+      <c r="T19" s="73">
         <f t="shared" ref="T19:T67" si="11">S19*M19</f>
         <v>40</v>
       </c>
-      <c r="U19" s="86"/>
-      <c r="V19" s="78"/>
-      <c r="W19" s="78"/>
+      <c r="U19" s="108"/>
+      <c r="V19" s="100"/>
+      <c r="W19" s="100"/>
     </row>
-    <row r="20" spans="1:23" s="2" customFormat="1" ht="15.75">
-      <c r="A20" s="8">
+    <row r="20" s="2" customFormat="1" ht="16.5" spans="1:23">
+      <c r="A20" s="10">
         <v>17</v>
       </c>
-      <c r="B20" s="19" t="s">
+      <c r="B20" s="30" t="s">
         <v>125</v>
       </c>
-      <c r="C20" s="119" t="s">
+      <c r="C20" s="154" t="s">
         <v>126</v>
       </c>
-      <c r="D20" s="120" t="s">
+      <c r="D20" s="155" t="s">
         <v>127</v>
       </c>
-      <c r="E20" s="120" t="s">
+      <c r="E20" s="155" t="s">
         <v>128</v>
       </c>
-      <c r="F20" s="121" t="s">
+      <c r="F20" s="156" t="s">
         <v>129</v>
       </c>
-      <c r="G20" s="20" t="s">
+      <c r="G20" s="32" t="s">
         <v>130</v>
       </c>
-      <c r="H20" s="120" t="s">
+      <c r="H20" s="155" t="s">
         <v>131</v>
       </c>
-      <c r="I20" s="120" t="s">
+      <c r="I20" s="155" t="s">
         <v>124</v>
       </c>
-      <c r="J20" s="20">
+      <c r="J20" s="32">
         <v>2</v>
       </c>
-      <c r="K20" s="20">
+      <c r="K20" s="32">
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="L20" s="20">
+      <c r="L20" s="32">
         <f t="shared" si="7"/>
         <v>100</v>
       </c>
-      <c r="M20" s="20">
+      <c r="M20" s="32">
         <f t="shared" si="8"/>
         <v>200</v>
       </c>
-      <c r="N20" s="54" t="s">
+      <c r="N20" s="74" t="s">
         <v>30</v>
       </c>
-      <c r="O20" s="55">
-        <v>0.32200000000000001</v>
-      </c>
-      <c r="P20" s="55">
+      <c r="O20" s="75">
+        <v>0.322</v>
+      </c>
+      <c r="P20" s="75">
         <f t="shared" si="9"/>
         <v>3.22</v>
       </c>
-      <c r="Q20" s="55">
+      <c r="Q20" s="75">
         <v>0.1825</v>
       </c>
-      <c r="R20" s="55">
+      <c r="R20" s="75">
         <f t="shared" si="10"/>
         <v>18.25</v>
       </c>
-      <c r="S20" s="87">
+      <c r="S20" s="109">
         <v>0.1825</v>
       </c>
-      <c r="T20" s="55">
+      <c r="T20" s="75">
         <f t="shared" si="11"/>
         <v>36.5</v>
       </c>
-      <c r="U20" s="88"/>
-      <c r="V20" s="81"/>
-      <c r="W20" s="81"/>
+      <c r="U20" s="110"/>
+      <c r="V20" s="103"/>
+      <c r="W20" s="103"/>
     </row>
-    <row r="21" spans="1:23">
-      <c r="A21" s="8">
+    <row r="21" ht="15.75" spans="1:23">
+      <c r="A21" s="10">
         <v>18</v>
       </c>
-      <c r="B21" s="144" t="s">
+      <c r="B21" s="23" t="s">
         <v>132</v>
       </c>
-      <c r="C21" s="105" t="s">
+      <c r="C21" s="140" t="s">
         <v>133</v>
       </c>
-      <c r="D21" s="106" t="s">
+      <c r="D21" s="141" t="s">
         <v>134</v>
       </c>
-      <c r="E21" s="106" t="s">
+      <c r="E21" s="141" t="s">
         <v>135</v>
       </c>
-      <c r="F21" s="106" t="s">
+      <c r="F21" s="141" t="s">
         <v>136</v>
       </c>
-      <c r="G21" s="9" t="s">
+      <c r="G21" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="H21" s="106" t="s">
+      <c r="H21" s="141" t="s">
         <v>28</v>
       </c>
-      <c r="I21" s="106" t="s">
+      <c r="I21" s="141" t="s">
         <v>124</v>
       </c>
-      <c r="J21" s="9">
+      <c r="J21" s="13">
         <v>1</v>
       </c>
-      <c r="K21" s="10">
+      <c r="K21" s="14">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="L21" s="10">
+      <c r="L21" s="14">
         <f t="shared" si="7"/>
         <v>50</v>
       </c>
-      <c r="M21" s="10">
+      <c r="M21" s="14">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="N21" s="56" t="s">
+      <c r="N21" s="76" t="s">
         <v>30</v>
       </c>
-      <c r="O21" s="57">
+      <c r="O21" s="77">
         <v>0.52</v>
       </c>
-      <c r="P21" s="50">
+      <c r="P21" s="70">
         <f t="shared" si="9"/>
         <v>2.6</v>
       </c>
-      <c r="Q21" s="57">
-        <v>0.41799999999999998</v>
-      </c>
-      <c r="R21" s="50">
+      <c r="Q21" s="77">
+        <v>0.418</v>
+      </c>
+      <c r="R21" s="70">
         <f t="shared" si="10"/>
         <v>20.9</v>
       </c>
-      <c r="S21" s="71">
-        <v>0.28439999999999999</v>
-      </c>
-      <c r="T21" s="50">
+      <c r="S21" s="93">
+        <v>0.2844</v>
+      </c>
+      <c r="T21" s="70">
         <f t="shared" si="11"/>
-        <v>28.439999999999998</v>
-      </c>
-      <c r="U21" s="89" t="s">
+        <v>28.44</v>
+      </c>
+      <c r="U21" s="111" t="s">
         <v>138</v>
       </c>
-      <c r="V21" s="78"/>
-      <c r="W21" s="78"/>
+      <c r="V21" s="100"/>
+      <c r="W21" s="100"/>
     </row>
-    <row r="22" spans="1:23" ht="15.75" customHeight="1">
-      <c r="A22" s="8">
+    <row r="22" ht="15.75" customHeight="1" spans="1:23">
+      <c r="A22" s="10">
         <v>19</v>
       </c>
-      <c r="B22" s="146"/>
-      <c r="C22" s="108" t="s">
+      <c r="B22" s="30"/>
+      <c r="C22" s="143" t="s">
         <v>139</v>
       </c>
-      <c r="D22" s="109" t="s">
+      <c r="D22" s="144" t="s">
         <v>140</v>
       </c>
-      <c r="E22" s="109" t="s">
+      <c r="E22" s="144" t="s">
         <v>135</v>
       </c>
-      <c r="F22" s="109" t="s">
+      <c r="F22" s="144" t="s">
         <v>141</v>
       </c>
-      <c r="G22" s="11" t="s">
+      <c r="G22" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="H22" s="109" t="s">
+      <c r="H22" s="144" t="s">
         <v>28</v>
       </c>
-      <c r="I22" s="122" t="s">
+      <c r="I22" s="157" t="s">
         <v>124</v>
       </c>
-      <c r="J22" s="11">
+      <c r="J22" s="17">
         <v>1</v>
       </c>
-      <c r="K22" s="13">
+      <c r="K22" s="19">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="L22" s="13">
+      <c r="L22" s="19">
         <f t="shared" si="7"/>
         <v>50</v>
       </c>
-      <c r="M22" s="13">
+      <c r="M22" s="19">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="N22" s="33" t="s">
+      <c r="N22" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="O22" s="37">
+      <c r="O22" s="57">
         <v>0.47</v>
       </c>
-      <c r="P22" s="35">
+      <c r="P22" s="55">
         <f t="shared" si="9"/>
-        <v>2.3499999999999996</v>
-      </c>
-      <c r="Q22" s="37">
-        <v>0.34699999999999998</v>
-      </c>
-      <c r="R22" s="35">
+        <v>2.35</v>
+      </c>
+      <c r="Q22" s="57">
+        <v>0.347</v>
+      </c>
+      <c r="R22" s="55">
         <f t="shared" si="10"/>
-        <v>17.349999999999998</v>
-      </c>
-      <c r="S22" s="74">
+        <v>17.35</v>
+      </c>
+      <c r="S22" s="96">
         <v>0.1963</v>
       </c>
-      <c r="T22" s="35">
+      <c r="T22" s="55">
         <f t="shared" si="11"/>
         <v>19.63</v>
       </c>
-      <c r="U22" s="90" t="s">
+      <c r="U22" s="112" t="s">
         <v>138</v>
       </c>
-      <c r="V22" s="78"/>
-      <c r="W22" s="78"/>
+      <c r="V22" s="100"/>
+      <c r="W22" s="100"/>
     </row>
-    <row r="23" spans="1:23" ht="15.75" customHeight="1">
-      <c r="A23" s="8">
+    <row r="23" ht="15.75" customHeight="1" spans="1:23">
+      <c r="A23" s="10">
         <v>20</v>
       </c>
-      <c r="B23" s="146"/>
-      <c r="C23" s="108" t="s">
+      <c r="B23" s="30"/>
+      <c r="C23" s="143" t="s">
         <v>142</v>
       </c>
-      <c r="D23" s="109" t="s">
+      <c r="D23" s="144" t="s">
         <v>143</v>
       </c>
-      <c r="E23" s="109" t="s">
+      <c r="E23" s="144" t="s">
         <v>135</v>
       </c>
-      <c r="F23" s="109" t="s">
+      <c r="F23" s="144" t="s">
         <v>144</v>
       </c>
-      <c r="G23" s="11" t="s">
+      <c r="G23" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="H23" s="109" t="s">
+      <c r="H23" s="144" t="s">
         <v>28</v>
       </c>
-      <c r="I23" s="122" t="s">
+      <c r="I23" s="157" t="s">
         <v>124</v>
       </c>
-      <c r="J23" s="11">
+      <c r="J23" s="17">
         <v>1</v>
       </c>
-      <c r="K23" s="13">
+      <c r="K23" s="19">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="L23" s="13">
+      <c r="L23" s="19">
         <f t="shared" si="7"/>
         <v>50</v>
       </c>
-      <c r="M23" s="13">
+      <c r="M23" s="19">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="N23" s="33" t="s">
+      <c r="N23" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="O23" s="37">
+      <c r="O23" s="57">
         <v>0.67</v>
       </c>
-      <c r="P23" s="35">
+      <c r="P23" s="55">
         <f t="shared" si="9"/>
         <v>3.35</v>
       </c>
-      <c r="Q23" s="37">
-        <v>0.59099999999999997</v>
-      </c>
-      <c r="R23" s="35">
+      <c r="Q23" s="57">
+        <v>0.591</v>
+      </c>
+      <c r="R23" s="55">
         <f t="shared" si="10"/>
-        <v>29.549999999999997</v>
-      </c>
-      <c r="S23" s="74">
+        <v>29.55</v>
+      </c>
+      <c r="S23" s="96">
         <v>0.4531</v>
       </c>
-      <c r="T23" s="35">
+      <c r="T23" s="55">
         <f t="shared" si="11"/>
         <v>45.31</v>
       </c>
-      <c r="U23" s="90" t="s">
+      <c r="U23" s="112" t="s">
         <v>138</v>
       </c>
-      <c r="V23" s="78"/>
-      <c r="W23" s="78"/>
+      <c r="V23" s="100"/>
+      <c r="W23" s="100"/>
     </row>
-    <row r="24" spans="1:23" ht="15.75" customHeight="1">
-      <c r="A24" s="8">
+    <row r="24" ht="15.75" customHeight="1" spans="1:23">
+      <c r="A24" s="10">
         <v>21</v>
       </c>
-      <c r="B24" s="146"/>
-      <c r="C24" s="108" t="s">
+      <c r="B24" s="30"/>
+      <c r="C24" s="143" t="s">
         <v>146</v>
       </c>
-      <c r="D24" s="109" t="s">
+      <c r="D24" s="144" t="s">
         <v>147</v>
       </c>
-      <c r="E24" s="109" t="s">
+      <c r="E24" s="144" t="s">
         <v>135</v>
       </c>
-      <c r="F24" s="109" t="s">
+      <c r="F24" s="144" t="s">
         <v>148</v>
       </c>
-      <c r="G24" s="11" t="s">
+      <c r="G24" s="17" t="s">
         <v>137</v>
       </c>
-      <c r="H24" s="109" t="s">
+      <c r="H24" s="144" t="s">
         <v>28</v>
       </c>
-      <c r="I24" s="122" t="s">
+      <c r="I24" s="157" t="s">
         <v>124</v>
       </c>
-      <c r="J24" s="11">
+      <c r="J24" s="17">
         <v>1</v>
       </c>
-      <c r="K24" s="13">
+      <c r="K24" s="19">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="L24" s="13">
+      <c r="L24" s="19">
         <f t="shared" si="7"/>
         <v>50</v>
       </c>
-      <c r="M24" s="13">
+      <c r="M24" s="19">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="N24" s="112" t="s">
+      <c r="N24" s="147" t="s">
         <v>30</v>
       </c>
-      <c r="O24" s="37">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="P24" s="35">
+      <c r="O24" s="57">
+        <v>0.55</v>
+      </c>
+      <c r="P24" s="55">
         <f t="shared" si="9"/>
         <v>2.75</v>
       </c>
-      <c r="Q24" s="37">
-        <v>0.44800000000000001</v>
-      </c>
-      <c r="R24" s="35">
+      <c r="Q24" s="57">
+        <v>0.448</v>
+      </c>
+      <c r="R24" s="55">
         <f t="shared" si="10"/>
-        <v>22.400000000000002</v>
-      </c>
-      <c r="S24" s="74">
-        <v>0.30520000000000003</v>
-      </c>
-      <c r="T24" s="35">
+        <v>22.4</v>
+      </c>
+      <c r="S24" s="96">
+        <v>0.3052</v>
+      </c>
+      <c r="T24" s="55">
         <f t="shared" si="11"/>
-        <v>30.520000000000003</v>
-      </c>
-      <c r="U24" s="90" t="s">
+        <v>30.52</v>
+      </c>
+      <c r="U24" s="112" t="s">
         <v>138</v>
       </c>
-      <c r="V24" s="78"/>
-      <c r="W24" s="78"/>
+      <c r="V24" s="100"/>
+      <c r="W24" s="100"/>
     </row>
-    <row r="25" spans="1:23" ht="25.5">
-      <c r="A25" s="8">
+    <row r="25" ht="15.75" spans="1:23">
+      <c r="A25" s="10">
         <v>22</v>
       </c>
-      <c r="B25" s="145"/>
-      <c r="C25" s="117" t="s">
+      <c r="B25" s="27"/>
+      <c r="C25" s="152" t="s">
         <v>149</v>
       </c>
-      <c r="D25" s="118" t="s">
+      <c r="D25" s="153" t="s">
         <v>150</v>
       </c>
-      <c r="E25" s="118" t="s">
+      <c r="E25" s="153" t="s">
         <v>135</v>
       </c>
-      <c r="F25" s="118" t="s">
+      <c r="F25" s="153" t="s">
         <v>151</v>
       </c>
-      <c r="G25" s="21" t="s">
+      <c r="G25" s="34" t="s">
         <v>152</v>
       </c>
-      <c r="H25" s="118" t="s">
+      <c r="H25" s="153" t="s">
         <v>28</v>
       </c>
-      <c r="I25" s="123" t="s">
+      <c r="I25" s="158" t="s">
         <v>124</v>
       </c>
-      <c r="J25" s="18">
+      <c r="J25" s="29">
         <v>1</v>
       </c>
-      <c r="K25" s="21">
+      <c r="K25" s="34">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="L25" s="21">
+      <c r="L25" s="34">
         <f t="shared" si="7"/>
         <v>50</v>
       </c>
-      <c r="M25" s="21">
+      <c r="M25" s="34">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="N25" s="58" t="s">
+      <c r="N25" s="79" t="s">
         <v>30</v>
       </c>
-      <c r="O25" s="52">
+      <c r="O25" s="72">
         <v>0.64</v>
       </c>
-      <c r="P25" s="53">
+      <c r="P25" s="73">
         <f t="shared" si="9"/>
         <v>3.2</v>
       </c>
-      <c r="Q25" s="52">
-        <v>0.55100000000000005</v>
-      </c>
-      <c r="R25" s="53">
+      <c r="Q25" s="72">
+        <v>0.551</v>
+      </c>
+      <c r="R25" s="73">
         <f t="shared" si="10"/>
         <v>27.55</v>
       </c>
-      <c r="S25" s="91">
-        <v>0.41110000000000002</v>
-      </c>
-      <c r="T25" s="53">
+      <c r="S25" s="113">
+        <v>0.4111</v>
+      </c>
+      <c r="T25" s="73">
         <f t="shared" si="11"/>
         <v>41.11</v>
       </c>
-      <c r="U25" s="86"/>
-      <c r="V25" s="78"/>
-      <c r="W25" s="78"/>
+      <c r="U25" s="108"/>
+      <c r="V25" s="100"/>
+      <c r="W25" s="100"/>
     </row>
-    <row r="26" spans="1:23">
-      <c r="A26" s="8">
+    <row r="26" ht="15.75" spans="1:23">
+      <c r="A26" s="10">
         <v>23</v>
       </c>
-      <c r="B26" s="146" t="s">
+      <c r="B26" s="30" t="s">
         <v>153</v>
       </c>
-      <c r="C26" s="124" t="s">
+      <c r="C26" s="159" t="s">
         <v>154</v>
       </c>
-      <c r="D26" s="122" t="s">
+      <c r="D26" s="157" t="s">
         <v>155</v>
       </c>
-      <c r="E26" s="122" t="s">
+      <c r="E26" s="157" t="s">
         <v>25</v>
       </c>
-      <c r="F26" s="125" t="s">
+      <c r="F26" s="160" t="s">
         <v>156</v>
       </c>
-      <c r="G26" s="22" t="s">
+      <c r="G26" s="36" t="s">
         <v>157</v>
       </c>
-      <c r="H26" s="122" t="s">
+      <c r="H26" s="157" t="s">
         <v>158</v>
       </c>
-      <c r="I26" s="122" t="s">
+      <c r="I26" s="157" t="s">
         <v>124</v>
       </c>
-      <c r="J26" s="22">
+      <c r="J26" s="36">
         <v>1</v>
       </c>
-      <c r="K26" s="59">
+      <c r="K26" s="80">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="L26" s="59">
+      <c r="L26" s="80">
         <f t="shared" si="7"/>
         <v>50</v>
       </c>
-      <c r="M26" s="59">
+      <c r="M26" s="80">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="N26" s="60" t="s">
+      <c r="N26" s="81" t="s">
         <v>30</v>
       </c>
-      <c r="O26" s="61">
+      <c r="O26" s="82">
         <v>6.32</v>
       </c>
-      <c r="P26" s="62">
+      <c r="P26" s="83">
         <f t="shared" si="9"/>
         <v>31.6</v>
       </c>
-      <c r="Q26" s="61">
-        <v>5.2472000000000003</v>
-      </c>
-      <c r="R26" s="62">
+      <c r="Q26" s="82">
+        <v>5.2472</v>
+      </c>
+      <c r="R26" s="83">
         <f t="shared" si="10"/>
         <v>262.36</v>
       </c>
-      <c r="S26" s="92">
-        <v>4.5328999999999997</v>
-      </c>
-      <c r="T26" s="62">
+      <c r="S26" s="114">
+        <v>4.5329</v>
+      </c>
+      <c r="T26" s="83">
         <f t="shared" si="11"/>
-        <v>453.28999999999996</v>
-      </c>
-      <c r="U26" s="75" t="s">
+        <v>453.29</v>
+      </c>
+      <c r="U26" s="97" t="s">
         <v>37</v>
       </c>
-      <c r="V26" s="78"/>
-      <c r="W26" s="78"/>
+      <c r="V26" s="100"/>
+      <c r="W26" s="100"/>
     </row>
-    <row r="27" spans="1:23">
-      <c r="A27" s="8">
+    <row r="27" ht="15.75" spans="1:23">
+      <c r="A27" s="10">
         <v>24</v>
       </c>
-      <c r="B27" s="146"/>
-      <c r="C27" s="114" t="s">
+      <c r="B27" s="30"/>
+      <c r="C27" s="149" t="s">
         <v>159</v>
       </c>
-      <c r="D27" s="115" t="s">
+      <c r="D27" s="150" t="s">
         <v>160</v>
       </c>
-      <c r="E27" s="115" t="s">
+      <c r="E27" s="150" t="s">
         <v>25</v>
       </c>
-      <c r="F27" s="115" t="s">
+      <c r="F27" s="150" t="s">
         <v>161</v>
       </c>
-      <c r="G27" s="14" t="s">
+      <c r="G27" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="H27" s="115" t="s">
+      <c r="H27" s="150" t="s">
         <v>28</v>
       </c>
-      <c r="I27" s="120" t="s">
+      <c r="I27" s="155" t="s">
         <v>124</v>
       </c>
-      <c r="J27" s="14">
+      <c r="J27" s="22">
         <v>1</v>
       </c>
-      <c r="K27" s="39">
+      <c r="K27" s="59">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="L27" s="39">
+      <c r="L27" s="59">
         <f t="shared" si="7"/>
         <v>50</v>
       </c>
-      <c r="M27" s="39">
+      <c r="M27" s="59">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="N27" s="63" t="s">
+      <c r="N27" s="84" t="s">
         <v>30</v>
       </c>
-      <c r="O27" s="43">
+      <c r="O27" s="63">
         <v>1.01</v>
       </c>
-      <c r="P27" s="44">
+      <c r="P27" s="64">
         <f t="shared" si="9"/>
         <v>5.05</v>
       </c>
-      <c r="Q27" s="43">
-        <v>0.90959999999999996</v>
-      </c>
-      <c r="R27" s="44">
+      <c r="Q27" s="63">
+        <v>0.9096</v>
+      </c>
+      <c r="R27" s="64">
         <f t="shared" si="10"/>
         <v>45.48</v>
       </c>
-      <c r="S27" s="83">
-        <v>0.78979999999999995</v>
-      </c>
-      <c r="T27" s="44">
+      <c r="S27" s="105">
+        <v>0.7898</v>
+      </c>
+      <c r="T27" s="64">
         <f t="shared" si="11"/>
-        <v>78.97999999999999</v>
-      </c>
-      <c r="U27" s="84"/>
-      <c r="V27" s="78"/>
-      <c r="W27" s="78"/>
+        <v>78.98</v>
+      </c>
+      <c r="U27" s="106"/>
+      <c r="V27" s="100"/>
+      <c r="W27" s="100"/>
     </row>
-    <row r="28" spans="1:23" ht="25.5">
-      <c r="A28" s="8">
+    <row r="28" ht="26.25" spans="1:23">
+      <c r="A28" s="10">
         <v>25</v>
       </c>
-      <c r="B28" s="23" t="s">
+      <c r="B28" s="38" t="s">
         <v>163</v>
       </c>
-      <c r="C28" s="126" t="s">
+      <c r="C28" s="161" t="s">
         <v>164</v>
       </c>
-      <c r="D28" s="127" t="s">
+      <c r="D28" s="162" t="s">
         <v>165</v>
       </c>
-      <c r="E28" s="127" t="s">
+      <c r="E28" s="162" t="s">
         <v>25</v>
       </c>
-      <c r="F28" s="128" t="s">
+      <c r="F28" s="163" t="s">
         <v>166</v>
       </c>
-      <c r="G28" s="24" t="s">
+      <c r="G28" s="40" t="s">
         <v>167</v>
       </c>
-      <c r="H28" s="24" t="s">
+      <c r="H28" s="40" t="s">
         <v>168</v>
       </c>
-      <c r="I28" s="127" t="s">
+      <c r="I28" s="162" t="s">
         <v>124</v>
       </c>
-      <c r="J28" s="24">
+      <c r="J28" s="40">
         <v>1</v>
       </c>
-      <c r="K28" s="64">
+      <c r="K28" s="85">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="L28" s="64">
+      <c r="L28" s="85">
         <f t="shared" si="7"/>
         <v>50</v>
       </c>
-      <c r="M28" s="64">
+      <c r="M28" s="85">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="N28" s="65" t="s">
+      <c r="N28" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="O28" s="66">
+      <c r="O28" s="87">
         <v>0.68</v>
       </c>
-      <c r="P28" s="67">
+      <c r="P28" s="88">
         <f t="shared" si="9"/>
-        <v>3.4000000000000004</v>
-      </c>
-      <c r="Q28" s="66">
+        <v>3.4</v>
+      </c>
+      <c r="Q28" s="87">
         <v>0.47</v>
       </c>
-      <c r="R28" s="67">
+      <c r="R28" s="88">
         <f t="shared" si="10"/>
         <v>23.5</v>
       </c>
-      <c r="S28" s="93">
-        <v>0.42720000000000002</v>
-      </c>
-      <c r="T28" s="67">
+      <c r="S28" s="115">
+        <v>0.4272</v>
+      </c>
+      <c r="T28" s="88">
         <f t="shared" si="11"/>
         <v>42.72</v>
       </c>
-      <c r="U28" s="94" t="s">
+      <c r="U28" s="116" t="s">
         <v>169</v>
       </c>
-      <c r="V28" s="78"/>
-      <c r="W28" s="78"/>
+      <c r="V28" s="100"/>
+      <c r="W28" s="100"/>
     </row>
-    <row r="29" spans="1:23" ht="15" customHeight="1">
-      <c r="A29" s="8">
+    <row r="29" customHeight="1" spans="1:23">
+      <c r="A29" s="10">
         <v>26</v>
       </c>
-      <c r="B29" s="19" t="s">
+      <c r="B29" s="30" t="s">
         <v>170</v>
       </c>
-      <c r="C29" s="119" t="s">
+      <c r="C29" s="154" t="s">
         <v>171</v>
       </c>
-      <c r="D29" s="120" t="s">
+      <c r="D29" s="155" t="s">
         <v>172</v>
       </c>
-      <c r="E29" s="120" t="s">
+      <c r="E29" s="155" t="s">
         <v>25</v>
       </c>
-      <c r="F29" s="120" t="s">
+      <c r="F29" s="155" t="s">
         <v>173</v>
       </c>
-      <c r="G29" s="20" t="s">
+      <c r="G29" s="32" t="s">
         <v>174</v>
       </c>
-      <c r="H29" s="122" t="s">
+      <c r="H29" s="157" t="s">
         <v>28</v>
       </c>
-      <c r="I29" s="120" t="s">
+      <c r="I29" s="155" t="s">
         <v>124</v>
       </c>
-      <c r="J29" s="20">
+      <c r="J29" s="32">
         <v>2</v>
       </c>
-      <c r="K29" s="45">
+      <c r="K29" s="65">
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="L29" s="45">
+      <c r="L29" s="65">
         <f t="shared" si="7"/>
         <v>100</v>
       </c>
-      <c r="M29" s="45">
+      <c r="M29" s="65">
         <f t="shared" si="8"/>
         <v>200</v>
       </c>
-      <c r="N29" s="54" t="s">
+      <c r="N29" s="74" t="s">
         <v>30</v>
       </c>
-      <c r="O29" s="55">
-        <v>0.65400000000000003</v>
-      </c>
-      <c r="P29" s="68">
+      <c r="O29" s="75">
+        <v>0.654</v>
+      </c>
+      <c r="P29" s="89">
         <f t="shared" si="9"/>
         <v>6.54</v>
       </c>
-      <c r="Q29" s="55">
-        <v>0.52359999999999995</v>
-      </c>
-      <c r="R29" s="68">
+      <c r="Q29" s="75">
+        <v>0.5236</v>
+      </c>
+      <c r="R29" s="89">
         <f t="shared" si="10"/>
-        <v>52.359999999999992</v>
-      </c>
-      <c r="S29" s="95">
-        <v>0.52359999999999995</v>
-      </c>
-      <c r="T29" s="68">
+        <v>52.36</v>
+      </c>
+      <c r="S29" s="117">
+        <v>0.5236</v>
+      </c>
+      <c r="T29" s="89">
         <f t="shared" si="11"/>
-        <v>104.71999999999998</v>
-      </c>
-      <c r="U29" s="96"/>
-      <c r="V29" s="78"/>
-      <c r="W29" s="78"/>
+        <v>104.72</v>
+      </c>
+      <c r="U29" s="118"/>
+      <c r="V29" s="100"/>
+      <c r="W29" s="100"/>
     </row>
-    <row r="30" spans="1:23">
-      <c r="A30" s="8">
+    <row r="30" ht="15.75" spans="1:23">
+      <c r="A30" s="10">
         <v>27</v>
       </c>
-      <c r="B30" s="144" t="s">
+      <c r="B30" s="23" t="s">
         <v>175</v>
       </c>
-      <c r="C30" s="129" t="s">
+      <c r="C30" s="164" t="s">
         <v>176</v>
       </c>
-      <c r="D30" s="106" t="s">
+      <c r="D30" s="141" t="s">
         <v>177</v>
       </c>
-      <c r="E30" s="106" t="s">
+      <c r="E30" s="141" t="s">
         <v>178</v>
       </c>
-      <c r="F30" s="130" t="s">
+      <c r="F30" s="165" t="s">
         <v>179</v>
       </c>
-      <c r="G30" s="9" t="s">
+      <c r="G30" s="13" t="s">
         <v>180</v>
       </c>
-      <c r="H30" s="9" t="s">
+      <c r="H30" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="I30" s="106" t="s">
+      <c r="I30" s="141" t="s">
         <v>182</v>
       </c>
-      <c r="J30" s="9">
+      <c r="J30" s="13">
         <v>1</v>
       </c>
-      <c r="K30" s="10">
+      <c r="K30" s="14">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="L30" s="10">
+      <c r="L30" s="14">
         <f t="shared" si="7"/>
         <v>50</v>
       </c>
-      <c r="M30" s="10">
+      <c r="M30" s="14">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="N30" s="69" t="s">
+      <c r="N30" s="90" t="s">
         <v>30</v>
       </c>
-      <c r="O30" s="57">
+      <c r="O30" s="77">
         <v>0.1</v>
       </c>
-      <c r="P30" s="50">
+      <c r="P30" s="70">
         <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
-      <c r="Q30" s="57">
-        <v>1.2E-2</v>
-      </c>
-      <c r="R30" s="50">
+      <c r="Q30" s="77">
+        <v>0.012</v>
+      </c>
+      <c r="R30" s="70">
         <f t="shared" si="10"/>
         <v>0.6</v>
       </c>
-      <c r="S30" s="71">
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="T30" s="50">
+      <c r="S30" s="93">
+        <v>0.0047</v>
+      </c>
+      <c r="T30" s="70">
         <f t="shared" si="11"/>
-        <v>0.47000000000000003</v>
-      </c>
-      <c r="U30" s="85"/>
-      <c r="V30" s="78"/>
-      <c r="W30" s="78"/>
+        <v>0.47</v>
+      </c>
+      <c r="U30" s="107"/>
+      <c r="V30" s="100"/>
+      <c r="W30" s="100"/>
     </row>
-    <row r="31" spans="1:23" ht="15" customHeight="1">
-      <c r="A31" s="8">
+    <row r="31" customHeight="1" spans="1:23">
+      <c r="A31" s="10">
         <v>28</v>
       </c>
-      <c r="B31" s="146"/>
-      <c r="C31" s="108" t="s">
+      <c r="B31" s="30"/>
+      <c r="C31" s="143" t="s">
         <v>183</v>
       </c>
-      <c r="D31" s="109" t="s">
+      <c r="D31" s="144" t="s">
         <v>184</v>
       </c>
-      <c r="E31" s="109" t="s">
+      <c r="E31" s="144" t="s">
         <v>185</v>
       </c>
-      <c r="F31" s="109" t="s">
+      <c r="F31" s="144" t="s">
         <v>186</v>
       </c>
-      <c r="G31" s="11" t="s">
+      <c r="G31" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="H31" s="109" t="s">
+      <c r="H31" s="144" t="s">
         <v>28</v>
       </c>
-      <c r="I31" s="109" t="s">
+      <c r="I31" s="144" t="s">
         <v>188</v>
       </c>
-      <c r="J31" s="11">
+      <c r="J31" s="17">
         <v>1</v>
       </c>
-      <c r="K31" s="13">
+      <c r="K31" s="19">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="L31" s="13">
+      <c r="L31" s="19">
         <f t="shared" si="7"/>
         <v>50</v>
       </c>
-      <c r="M31" s="13">
+      <c r="M31" s="19">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="N31" s="33" t="s">
+      <c r="N31" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="O31" s="37">
+      <c r="O31" s="57">
         <v>0.1</v>
       </c>
-      <c r="P31" s="35">
+      <c r="P31" s="55">
         <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
-      <c r="Q31" s="37">
-        <v>2.7E-2</v>
-      </c>
-      <c r="R31" s="35">
+      <c r="Q31" s="57">
+        <v>0.027</v>
+      </c>
+      <c r="R31" s="55">
         <f t="shared" si="10"/>
         <v>1.35</v>
       </c>
-      <c r="S31" s="74">
-        <v>1.09E-2</v>
-      </c>
-      <c r="T31" s="35">
+      <c r="S31" s="96">
+        <v>0.0109</v>
+      </c>
+      <c r="T31" s="55">
         <f t="shared" si="11"/>
-        <v>1.0900000000000001</v>
-      </c>
-      <c r="U31" s="82"/>
-      <c r="V31" s="78"/>
-      <c r="W31" s="78"/>
+        <v>1.09</v>
+      </c>
+      <c r="U31" s="104"/>
+      <c r="V31" s="100"/>
+      <c r="W31" s="100"/>
     </row>
-    <row r="32" spans="1:23" ht="15" customHeight="1">
-      <c r="A32" s="8">
+    <row r="32" customHeight="1" spans="1:23">
+      <c r="A32" s="10">
         <v>29</v>
       </c>
-      <c r="B32" s="146"/>
-      <c r="C32" s="108" t="s">
+      <c r="B32" s="30"/>
+      <c r="C32" s="143" t="s">
         <v>189</v>
       </c>
-      <c r="D32" s="109" t="s">
+      <c r="D32" s="144" t="s">
         <v>190</v>
       </c>
-      <c r="E32" s="109" t="s">
+      <c r="E32" s="144" t="s">
         <v>178</v>
       </c>
-      <c r="F32" s="109" t="s">
+      <c r="F32" s="144" t="s">
         <v>191</v>
       </c>
-      <c r="G32" s="11" t="s">
+      <c r="G32" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="H32" s="109" t="s">
+      <c r="H32" s="144" t="s">
         <v>28</v>
       </c>
-      <c r="I32" s="109" t="s">
+      <c r="I32" s="144" t="s">
         <v>192</v>
       </c>
-      <c r="J32" s="11">
+      <c r="J32" s="17">
         <v>7</v>
       </c>
-      <c r="K32" s="13">
+      <c r="K32" s="19">
         <f t="shared" si="6"/>
         <v>35</v>
       </c>
-      <c r="L32" s="13">
+      <c r="L32" s="19">
         <f t="shared" si="7"/>
         <v>350</v>
       </c>
-      <c r="M32" s="13">
+      <c r="M32" s="19">
         <f t="shared" si="8"/>
         <v>700</v>
       </c>
-      <c r="N32" s="33" t="s">
+      <c r="N32" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="O32" s="37">
-        <v>1.2999999999999999E-2</v>
-      </c>
-      <c r="P32" s="35">
+      <c r="O32" s="57">
+        <v>0.013</v>
+      </c>
+      <c r="P32" s="55">
         <f t="shared" si="9"/>
-        <v>0.45499999999999996</v>
-      </c>
-      <c r="Q32" s="37">
-        <v>5.4000000000000003E-3</v>
-      </c>
-      <c r="R32" s="35">
+        <v>0.455</v>
+      </c>
+      <c r="Q32" s="57">
+        <v>0.0054</v>
+      </c>
+      <c r="R32" s="55">
         <f t="shared" si="10"/>
-        <v>1.8900000000000001</v>
-      </c>
-      <c r="S32" s="74">
-        <v>5.4000000000000003E-3</v>
-      </c>
-      <c r="T32" s="35">
+        <v>1.89</v>
+      </c>
+      <c r="S32" s="96">
+        <v>0.0054</v>
+      </c>
+      <c r="T32" s="55">
         <f t="shared" si="11"/>
-        <v>3.7800000000000002</v>
-      </c>
-      <c r="U32" s="82"/>
-      <c r="V32" s="78"/>
-      <c r="W32" s="78"/>
+        <v>3.78</v>
+      </c>
+      <c r="U32" s="104"/>
+      <c r="V32" s="100"/>
+      <c r="W32" s="100"/>
     </row>
-    <row r="33" spans="1:23">
-      <c r="A33" s="8">
+    <row r="33" ht="15.75" spans="1:23">
+      <c r="A33" s="10">
         <v>30</v>
       </c>
-      <c r="B33" s="146"/>
-      <c r="C33" s="108" t="s">
+      <c r="B33" s="30"/>
+      <c r="C33" s="143" t="s">
         <v>193</v>
       </c>
-      <c r="D33" s="109" t="s">
+      <c r="D33" s="144" t="s">
         <v>194</v>
       </c>
-      <c r="E33" s="109" t="s">
+      <c r="E33" s="144" t="s">
         <v>178</v>
       </c>
-      <c r="F33" s="109" t="s">
+      <c r="F33" s="144" t="s">
         <v>195</v>
       </c>
-      <c r="G33" s="11" t="s">
+      <c r="G33" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="H33" s="109" t="s">
+      <c r="H33" s="144" t="s">
         <v>28</v>
       </c>
-      <c r="I33" s="109" t="s">
+      <c r="I33" s="144" t="s">
         <v>196</v>
       </c>
-      <c r="J33" s="11">
+      <c r="J33" s="17">
         <v>1</v>
       </c>
-      <c r="K33" s="13">
+      <c r="K33" s="19">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="L33" s="13">
+      <c r="L33" s="19">
         <f t="shared" si="7"/>
         <v>50</v>
       </c>
-      <c r="M33" s="13">
+      <c r="M33" s="19">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="N33" s="33" t="s">
+      <c r="N33" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="O33" s="37">
+      <c r="O33" s="57">
         <v>0.1</v>
       </c>
-      <c r="P33" s="35">
+      <c r="P33" s="55">
         <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
-      <c r="Q33" s="37">
-        <v>1.6E-2</v>
-      </c>
-      <c r="R33" s="35">
+      <c r="Q33" s="57">
+        <v>0.016</v>
+      </c>
+      <c r="R33" s="55">
         <f t="shared" si="10"/>
         <v>0.8</v>
       </c>
-      <c r="S33" s="74">
-        <v>6.6E-3</v>
-      </c>
-      <c r="T33" s="35">
+      <c r="S33" s="96">
+        <v>0.0066</v>
+      </c>
+      <c r="T33" s="55">
         <f t="shared" si="11"/>
         <v>0.66</v>
       </c>
-      <c r="U33" s="82"/>
-      <c r="V33" s="78"/>
-      <c r="W33" s="78"/>
+      <c r="U33" s="104"/>
+      <c r="V33" s="100"/>
+      <c r="W33" s="100"/>
     </row>
-    <row r="34" spans="1:23">
-      <c r="A34" s="8">
+    <row r="34" ht="15.75" spans="1:23">
+      <c r="A34" s="10">
         <v>31</v>
       </c>
-      <c r="B34" s="146"/>
-      <c r="C34" s="108" t="s">
+      <c r="B34" s="30"/>
+      <c r="C34" s="143" t="s">
         <v>197</v>
       </c>
-      <c r="D34" s="109" t="s">
+      <c r="D34" s="144" t="s">
         <v>198</v>
       </c>
-      <c r="E34" s="109" t="s">
+      <c r="E34" s="144" t="s">
         <v>178</v>
       </c>
-      <c r="F34" s="109" t="s">
+      <c r="F34" s="144" t="s">
         <v>199</v>
       </c>
-      <c r="G34" s="11" t="s">
+      <c r="G34" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="H34" s="109" t="s">
+      <c r="H34" s="144" t="s">
         <v>28</v>
       </c>
-      <c r="I34" s="109" t="s">
+      <c r="I34" s="144" t="s">
         <v>200</v>
       </c>
-      <c r="J34" s="11">
+      <c r="J34" s="17">
         <v>1</v>
       </c>
-      <c r="K34" s="13">
+      <c r="K34" s="19">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="L34" s="13">
+      <c r="L34" s="19">
         <f t="shared" si="7"/>
         <v>50</v>
       </c>
-      <c r="M34" s="13">
+      <c r="M34" s="19">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="N34" s="33" t="s">
+      <c r="N34" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="O34" s="37">
+      <c r="O34" s="57">
         <v>0.1</v>
       </c>
-      <c r="P34" s="35">
+      <c r="P34" s="55">
         <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
-      <c r="Q34" s="37">
-        <v>2.1999999999999999E-2</v>
-      </c>
-      <c r="R34" s="35">
+      <c r="Q34" s="57">
+        <v>0.022</v>
+      </c>
+      <c r="R34" s="55">
         <f t="shared" si="10"/>
-        <v>1.0999999999999999</v>
-      </c>
-      <c r="S34" s="74">
-        <v>8.9999999999999993E-3</v>
-      </c>
-      <c r="T34" s="35">
+        <v>1.1</v>
+      </c>
+      <c r="S34" s="96">
+        <v>0.009</v>
+      </c>
+      <c r="T34" s="55">
         <f t="shared" si="11"/>
-        <v>0.89999999999999991</v>
-      </c>
-      <c r="U34" s="82"/>
-      <c r="V34" s="78"/>
-      <c r="W34" s="78"/>
+        <v>0.9</v>
+      </c>
+      <c r="U34" s="104"/>
+      <c r="V34" s="100"/>
+      <c r="W34" s="100"/>
     </row>
-    <row r="35" spans="1:23">
-      <c r="A35" s="8">
+    <row r="35" ht="15.75" spans="1:23">
+      <c r="A35" s="10">
         <v>32</v>
       </c>
-      <c r="B35" s="146"/>
-      <c r="C35" s="108" t="s">
+      <c r="B35" s="30"/>
+      <c r="C35" s="143" t="s">
         <v>201</v>
       </c>
-      <c r="D35" s="109" t="s">
+      <c r="D35" s="144" t="s">
         <v>202</v>
       </c>
-      <c r="E35" s="109" t="s">
+      <c r="E35" s="144" t="s">
         <v>178</v>
       </c>
-      <c r="F35" s="109" t="s">
+      <c r="F35" s="144" t="s">
         <v>203</v>
       </c>
-      <c r="G35" s="11" t="s">
+      <c r="G35" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="H35" s="109" t="s">
+      <c r="H35" s="144" t="s">
         <v>28</v>
       </c>
-      <c r="I35" s="109" t="s">
+      <c r="I35" s="144" t="s">
         <v>204</v>
       </c>
-      <c r="J35" s="11">
+      <c r="J35" s="17">
         <v>1</v>
       </c>
-      <c r="K35" s="13">
+      <c r="K35" s="19">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="L35" s="13">
+      <c r="L35" s="19">
         <f t="shared" si="7"/>
         <v>50</v>
       </c>
-      <c r="M35" s="13">
+      <c r="M35" s="19">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="N35" s="33" t="s">
+      <c r="N35" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="O35" s="37">
+      <c r="O35" s="57">
         <v>0.1</v>
       </c>
-      <c r="P35" s="35">
+      <c r="P35" s="55">
         <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
-      <c r="Q35" s="37">
-        <v>2.1999999999999999E-2</v>
-      </c>
-      <c r="R35" s="35">
+      <c r="Q35" s="57">
+        <v>0.022</v>
+      </c>
+      <c r="R35" s="55">
         <f t="shared" si="10"/>
-        <v>1.0999999999999999</v>
-      </c>
-      <c r="S35" s="74">
-        <v>8.9999999999999993E-3</v>
-      </c>
-      <c r="T35" s="35">
+        <v>1.1</v>
+      </c>
+      <c r="S35" s="96">
+        <v>0.009</v>
+      </c>
+      <c r="T35" s="55">
         <f t="shared" si="11"/>
-        <v>0.89999999999999991</v>
-      </c>
-      <c r="U35" s="82"/>
-      <c r="V35" s="78"/>
-      <c r="W35" s="78"/>
+        <v>0.9</v>
+      </c>
+      <c r="U35" s="104"/>
+      <c r="V35" s="100"/>
+      <c r="W35" s="100"/>
     </row>
-    <row r="36" spans="1:23">
-      <c r="A36" s="8">
+    <row r="36" ht="15.75" spans="1:23">
+      <c r="A36" s="10">
         <v>33</v>
       </c>
-      <c r="B36" s="146"/>
-      <c r="C36" s="108" t="s">
+      <c r="B36" s="30"/>
+      <c r="C36" s="143" t="s">
         <v>205</v>
       </c>
-      <c r="D36" s="109" t="s">
+      <c r="D36" s="144" t="s">
         <v>206</v>
       </c>
-      <c r="E36" s="109" t="s">
+      <c r="E36" s="144" t="s">
         <v>178</v>
       </c>
-      <c r="F36" s="110" t="s">
+      <c r="F36" s="145" t="s">
         <v>207</v>
       </c>
-      <c r="G36" s="11" t="s">
+      <c r="G36" s="17" t="s">
         <v>208</v>
       </c>
-      <c r="H36" s="25" t="s">
+      <c r="H36" s="44" t="s">
         <v>209</v>
       </c>
-      <c r="I36" s="109" t="s">
+      <c r="I36" s="144" t="s">
         <v>210</v>
       </c>
-      <c r="J36" s="11">
+      <c r="J36" s="17">
         <v>5</v>
       </c>
-      <c r="K36" s="13">
+      <c r="K36" s="19">
         <f t="shared" si="6"/>
         <v>25</v>
       </c>
-      <c r="L36" s="13">
+      <c r="L36" s="19">
         <f t="shared" si="7"/>
         <v>250</v>
       </c>
-      <c r="M36" s="13">
+      <c r="M36" s="19">
         <f t="shared" si="8"/>
         <v>500</v>
       </c>
-      <c r="N36" s="33" t="s">
+      <c r="N36" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="O36" s="37">
+      <c r="O36" s="57">
         <v>0.223</v>
       </c>
-      <c r="P36" s="35">
+      <c r="P36" s="55">
         <f t="shared" si="9"/>
-        <v>5.5750000000000002</v>
-      </c>
-      <c r="Q36" s="37">
-        <v>8.6999999999999994E-2</v>
-      </c>
-      <c r="R36" s="35">
+        <v>5.575</v>
+      </c>
+      <c r="Q36" s="57">
+        <v>0.087</v>
+      </c>
+      <c r="R36" s="55">
         <f t="shared" si="10"/>
         <v>21.75</v>
       </c>
-      <c r="S36" s="74">
-        <v>8.6999999999999994E-2</v>
-      </c>
-      <c r="T36" s="35">
+      <c r="S36" s="96">
+        <v>0.087</v>
+      </c>
+      <c r="T36" s="55">
         <f t="shared" si="11"/>
         <v>43.5</v>
       </c>
-      <c r="U36" s="82"/>
-      <c r="V36" s="78"/>
-      <c r="W36" s="78"/>
+      <c r="U36" s="104"/>
+      <c r="V36" s="100"/>
+      <c r="W36" s="100"/>
     </row>
-    <row r="37" spans="1:23">
-      <c r="A37" s="8">
+    <row r="37" ht="15.75" spans="1:23">
+      <c r="A37" s="10">
         <v>34</v>
       </c>
-      <c r="B37" s="146"/>
-      <c r="C37" s="108" t="s">
+      <c r="B37" s="30"/>
+      <c r="C37" s="143" t="s">
         <v>211</v>
       </c>
-      <c r="D37" s="109" t="s">
+      <c r="D37" s="144" t="s">
         <v>212</v>
       </c>
-      <c r="E37" s="109" t="s">
+      <c r="E37" s="144" t="s">
         <v>178</v>
       </c>
-      <c r="F37" s="109" t="s">
+      <c r="F37" s="144" t="s">
         <v>213</v>
       </c>
-      <c r="G37" s="11" t="s">
+      <c r="G37" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="H37" s="109" t="s">
+      <c r="H37" s="144" t="s">
         <v>28</v>
       </c>
-      <c r="I37" s="109" t="s">
+      <c r="I37" s="144" t="s">
         <v>214</v>
       </c>
-      <c r="J37" s="11">
+      <c r="J37" s="17">
         <v>1</v>
       </c>
-      <c r="K37" s="13">
+      <c r="K37" s="19">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="L37" s="13">
+      <c r="L37" s="19">
         <f t="shared" si="7"/>
         <v>50</v>
       </c>
-      <c r="M37" s="13">
+      <c r="M37" s="19">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="N37" s="33" t="s">
+      <c r="N37" s="53" t="s">
         <v>79</v>
       </c>
-      <c r="O37" s="37">
-        <v>0.10100000000000001</v>
-      </c>
-      <c r="P37" s="35">
+      <c r="O37" s="57">
+        <v>0.101</v>
+      </c>
+      <c r="P37" s="55">
         <f t="shared" si="9"/>
         <v>0.505</v>
       </c>
-      <c r="Q37" s="37">
-        <v>1.6E-2</v>
-      </c>
-      <c r="R37" s="35">
+      <c r="Q37" s="57">
+        <v>0.016</v>
+      </c>
+      <c r="R37" s="55">
         <f t="shared" si="10"/>
         <v>0.8</v>
       </c>
-      <c r="S37" s="74">
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="T37" s="35">
+      <c r="S37" s="96">
+        <v>0.007</v>
+      </c>
+      <c r="T37" s="55">
         <f t="shared" si="11"/>
-        <v>0.70000000000000007</v>
-      </c>
-      <c r="U37" s="82"/>
-      <c r="V37" s="78"/>
-      <c r="W37" s="78"/>
+        <v>0.7</v>
+      </c>
+      <c r="U37" s="104"/>
+      <c r="V37" s="100"/>
+      <c r="W37" s="100"/>
     </row>
-    <row r="38" spans="1:23">
-      <c r="A38" s="8">
+    <row r="38" ht="15.75" spans="1:23">
+      <c r="A38" s="10">
         <v>35</v>
       </c>
-      <c r="B38" s="146"/>
-      <c r="C38" s="108" t="s">
+      <c r="B38" s="30"/>
+      <c r="C38" s="143" t="s">
         <v>215</v>
       </c>
-      <c r="D38" s="109" t="s">
+      <c r="D38" s="144" t="s">
         <v>216</v>
       </c>
-      <c r="E38" s="109" t="s">
+      <c r="E38" s="144" t="s">
         <v>178</v>
       </c>
-      <c r="F38" s="110" t="s">
+      <c r="F38" s="145" t="s">
         <v>217</v>
       </c>
-      <c r="G38" s="11" t="s">
+      <c r="G38" s="17" t="s">
         <v>208</v>
       </c>
-      <c r="H38" s="11" t="s">
+      <c r="H38" s="17" t="s">
         <v>218</v>
       </c>
-      <c r="I38" s="109" t="s">
+      <c r="I38" s="144" t="s">
         <v>219</v>
       </c>
-      <c r="J38" s="11">
+      <c r="J38" s="17">
         <v>1</v>
       </c>
-      <c r="K38" s="13">
+      <c r="K38" s="19">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="L38" s="13">
+      <c r="L38" s="19">
         <f t="shared" si="7"/>
         <v>50</v>
       </c>
-      <c r="M38" s="13">
+      <c r="M38" s="19">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="N38" s="33" t="s">
+      <c r="N38" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="O38" s="37">
+      <c r="O38" s="57">
         <v>0.1</v>
       </c>
-      <c r="P38" s="35">
+      <c r="P38" s="55">
         <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
-      <c r="Q38" s="37">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="R38" s="35">
+      <c r="Q38" s="57">
+        <v>0.015</v>
+      </c>
+      <c r="R38" s="55">
         <f t="shared" si="10"/>
         <v>0.75</v>
       </c>
-      <c r="S38" s="74">
-        <v>6.1000000000000004E-3</v>
-      </c>
-      <c r="T38" s="35">
+      <c r="S38" s="96">
+        <v>0.0061</v>
+      </c>
+      <c r="T38" s="55">
         <f t="shared" si="11"/>
         <v>0.61</v>
       </c>
-      <c r="U38" s="82"/>
-      <c r="V38" s="78"/>
-      <c r="W38" s="78"/>
+      <c r="U38" s="104"/>
+      <c r="V38" s="100"/>
+      <c r="W38" s="100"/>
     </row>
-    <row r="39" spans="1:23">
-      <c r="A39" s="8">
+    <row r="39" ht="15.75" spans="1:23">
+      <c r="A39" s="10">
         <v>36</v>
       </c>
-      <c r="B39" s="146"/>
-      <c r="C39" s="108" t="s">
+      <c r="B39" s="30"/>
+      <c r="C39" s="143" t="s">
         <v>220</v>
       </c>
-      <c r="D39" s="109" t="s">
+      <c r="D39" s="144" t="s">
         <v>221</v>
       </c>
-      <c r="E39" s="109" t="s">
+      <c r="E39" s="144" t="s">
         <v>178</v>
       </c>
-      <c r="F39" s="110" t="s">
+      <c r="F39" s="145" t="s">
         <v>222</v>
       </c>
-      <c r="G39" s="11" t="s">
+      <c r="G39" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="H39" s="11" t="s">
+      <c r="H39" s="17" t="s">
         <v>223</v>
       </c>
-      <c r="I39" s="109" t="s">
+      <c r="I39" s="144" t="s">
         <v>224</v>
       </c>
-      <c r="J39" s="11">
+      <c r="J39" s="17">
         <v>4</v>
       </c>
-      <c r="K39" s="13">
+      <c r="K39" s="19">
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-      <c r="L39" s="13">
+      <c r="L39" s="19">
         <f t="shared" si="7"/>
         <v>200</v>
       </c>
-      <c r="M39" s="13">
+      <c r="M39" s="19">
         <f t="shared" si="8"/>
         <v>400</v>
       </c>
-      <c r="N39" s="33" t="s">
+      <c r="N39" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="O39" s="37">
-        <v>1.2E-2</v>
-      </c>
-      <c r="P39" s="35">
+      <c r="O39" s="57">
+        <v>0.012</v>
+      </c>
+      <c r="P39" s="55">
         <f t="shared" si="9"/>
         <v>0.24</v>
       </c>
-      <c r="Q39" s="37">
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="R39" s="35">
+      <c r="Q39" s="57">
+        <v>0.0047</v>
+      </c>
+      <c r="R39" s="55">
         <f t="shared" si="10"/>
-        <v>0.94000000000000006</v>
-      </c>
-      <c r="S39" s="74">
-        <v>3.5999999999999999E-3</v>
-      </c>
-      <c r="T39" s="35">
+        <v>0.94</v>
+      </c>
+      <c r="S39" s="96">
+        <v>0.0036</v>
+      </c>
+      <c r="T39" s="55">
         <f t="shared" si="11"/>
         <v>1.44</v>
       </c>
-      <c r="U39" s="82"/>
-      <c r="V39" s="78"/>
-      <c r="W39" s="78"/>
+      <c r="U39" s="104"/>
+      <c r="V39" s="100"/>
+      <c r="W39" s="100"/>
     </row>
-    <row r="40" spans="1:23">
-      <c r="A40" s="8">
+    <row r="40" ht="15.75" spans="1:23">
+      <c r="A40" s="10">
         <v>37</v>
       </c>
-      <c r="B40" s="146"/>
-      <c r="C40" s="108" t="s">
+      <c r="B40" s="30"/>
+      <c r="C40" s="143" t="s">
         <v>225</v>
       </c>
-      <c r="D40" s="109" t="s">
+      <c r="D40" s="144" t="s">
         <v>226</v>
       </c>
-      <c r="E40" s="109" t="s">
+      <c r="E40" s="144" t="s">
         <v>178</v>
       </c>
-      <c r="F40" s="110" t="s">
+      <c r="F40" s="145" t="s">
         <v>227</v>
       </c>
-      <c r="G40" s="11" t="s">
+      <c r="G40" s="17" t="s">
         <v>228</v>
       </c>
-      <c r="H40" s="11" t="s">
+      <c r="H40" s="17" t="s">
         <v>229</v>
       </c>
-      <c r="I40" s="109" t="s">
+      <c r="I40" s="144" t="s">
         <v>230</v>
       </c>
-      <c r="J40" s="11">
+      <c r="J40" s="17">
         <v>3</v>
       </c>
-      <c r="K40" s="13">
+      <c r="K40" s="19">
         <f t="shared" si="6"/>
         <v>15</v>
       </c>
-      <c r="L40" s="13">
+      <c r="L40" s="19">
         <f t="shared" si="7"/>
         <v>150</v>
       </c>
-      <c r="M40" s="13">
+      <c r="M40" s="19">
         <f t="shared" si="8"/>
         <v>300</v>
       </c>
-      <c r="N40" s="33" t="s">
+      <c r="N40" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="O40" s="37">
-        <v>2.7E-2</v>
-      </c>
-      <c r="P40" s="35">
+      <c r="O40" s="57">
+        <v>0.027</v>
+      </c>
+      <c r="P40" s="55">
         <f t="shared" si="9"/>
-        <v>0.40499999999999997</v>
-      </c>
-      <c r="Q40" s="37">
-        <v>1.11E-2</v>
-      </c>
-      <c r="R40" s="35">
+        <v>0.405</v>
+      </c>
+      <c r="Q40" s="57">
+        <v>0.0111</v>
+      </c>
+      <c r="R40" s="55">
         <f t="shared" si="10"/>
         <v>1.665</v>
       </c>
-      <c r="S40" s="74">
-        <v>1.11E-2</v>
-      </c>
-      <c r="T40" s="35">
+      <c r="S40" s="96">
+        <v>0.0111</v>
+      </c>
+      <c r="T40" s="55">
         <f t="shared" si="11"/>
         <v>3.33</v>
       </c>
-      <c r="U40" s="82"/>
-      <c r="V40" s="78"/>
-      <c r="W40" s="78"/>
+      <c r="U40" s="104"/>
+      <c r="V40" s="100"/>
+      <c r="W40" s="100"/>
     </row>
-    <row r="41" spans="1:23">
-      <c r="A41" s="8">
+    <row r="41" ht="15.75" spans="1:23">
+      <c r="A41" s="10">
         <v>38</v>
       </c>
-      <c r="B41" s="146"/>
-      <c r="C41" s="108" t="s">
+      <c r="B41" s="30"/>
+      <c r="C41" s="143" t="s">
         <v>231</v>
       </c>
-      <c r="D41" s="109" t="s">
+      <c r="D41" s="144" t="s">
         <v>232</v>
       </c>
-      <c r="E41" s="109" t="s">
+      <c r="E41" s="144" t="s">
         <v>233</v>
       </c>
-      <c r="F41" s="110" t="s">
+      <c r="F41" s="145" t="s">
         <v>234</v>
       </c>
-      <c r="G41" s="11" t="s">
+      <c r="G41" s="17" t="s">
         <v>235</v>
       </c>
-      <c r="H41" s="11" t="s">
+      <c r="H41" s="17" t="s">
         <v>236</v>
       </c>
-      <c r="I41" s="109" t="s">
+      <c r="I41" s="144" t="s">
         <v>237</v>
       </c>
-      <c r="J41" s="11">
+      <c r="J41" s="17">
         <v>1</v>
       </c>
-      <c r="K41" s="13">
+      <c r="K41" s="19">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="L41" s="13">
+      <c r="L41" s="19">
         <f t="shared" si="7"/>
         <v>50</v>
       </c>
-      <c r="M41" s="13">
+      <c r="M41" s="19">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="N41" s="33" t="s">
+      <c r="N41" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="O41" s="37">
+      <c r="O41" s="57">
         <v>0.1</v>
       </c>
-      <c r="P41" s="35">
+      <c r="P41" s="55">
         <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
-      <c r="Q41" s="37">
-        <v>1.7000000000000001E-2</v>
-      </c>
-      <c r="R41" s="35">
+      <c r="Q41" s="57">
+        <v>0.017</v>
+      </c>
+      <c r="R41" s="55">
         <f t="shared" si="10"/>
-        <v>0.85000000000000009</v>
-      </c>
-      <c r="S41" s="74">
-        <v>6.7999999999999996E-3</v>
-      </c>
-      <c r="T41" s="35">
+        <v>0.85</v>
+      </c>
+      <c r="S41" s="96">
+        <v>0.0068</v>
+      </c>
+      <c r="T41" s="55">
         <f t="shared" si="11"/>
-        <v>0.67999999999999994</v>
-      </c>
-      <c r="U41" s="82"/>
-      <c r="V41" s="78"/>
-      <c r="W41" s="78"/>
+        <v>0.68</v>
+      </c>
+      <c r="U41" s="104"/>
+      <c r="V41" s="100"/>
+      <c r="W41" s="100"/>
     </row>
-    <row r="42" spans="1:23">
-      <c r="A42" s="8">
+    <row r="42" ht="15.75" spans="1:23">
+      <c r="A42" s="10">
         <v>39</v>
       </c>
-      <c r="B42" s="146"/>
-      <c r="C42" s="108" t="s">
+      <c r="B42" s="30"/>
+      <c r="C42" s="143" t="s">
         <v>238</v>
       </c>
-      <c r="D42" s="109" t="s">
+      <c r="D42" s="144" t="s">
         <v>239</v>
       </c>
-      <c r="E42" s="109" t="s">
+      <c r="E42" s="144" t="s">
         <v>178</v>
       </c>
-      <c r="F42" s="109" t="s">
+      <c r="F42" s="144" t="s">
         <v>240</v>
       </c>
-      <c r="G42" s="11" t="s">
+      <c r="G42" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="H42" s="109" t="s">
+      <c r="H42" s="144" t="s">
         <v>28</v>
       </c>
-      <c r="I42" s="109" t="s">
+      <c r="I42" s="144" t="s">
         <v>241</v>
       </c>
-      <c r="J42" s="11">
+      <c r="J42" s="17">
         <v>3</v>
       </c>
-      <c r="K42" s="13">
+      <c r="K42" s="19">
         <f t="shared" si="6"/>
         <v>15</v>
       </c>
-      <c r="L42" s="13">
+      <c r="L42" s="19">
         <f t="shared" si="7"/>
         <v>150</v>
       </c>
-      <c r="M42" s="13">
+      <c r="M42" s="19">
         <f t="shared" si="8"/>
         <v>300</v>
       </c>
-      <c r="N42" s="33" t="s">
+      <c r="N42" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="O42" s="37">
-        <v>1.6E-2</v>
-      </c>
-      <c r="P42" s="35">
+      <c r="O42" s="57">
+        <v>0.016</v>
+      </c>
+      <c r="P42" s="55">
         <f t="shared" si="9"/>
         <v>0.24</v>
       </c>
-      <c r="Q42" s="37">
-        <v>6.6E-3</v>
-      </c>
-      <c r="R42" s="35">
+      <c r="Q42" s="57">
+        <v>0.0066</v>
+      </c>
+      <c r="R42" s="55">
         <f t="shared" si="10"/>
         <v>0.99</v>
       </c>
-      <c r="S42" s="74">
-        <v>6.6E-3</v>
-      </c>
-      <c r="T42" s="35">
+      <c r="S42" s="96">
+        <v>0.0066</v>
+      </c>
+      <c r="T42" s="55">
         <f t="shared" si="11"/>
         <v>1.98</v>
       </c>
-      <c r="U42" s="82"/>
-      <c r="V42" s="78"/>
-      <c r="W42" s="78"/>
+      <c r="U42" s="104"/>
+      <c r="V42" s="100"/>
+      <c r="W42" s="100"/>
     </row>
-    <row r="43" spans="1:23">
-      <c r="A43" s="8">
+    <row r="43" ht="15.75" spans="1:23">
+      <c r="A43" s="10">
         <v>40</v>
       </c>
-      <c r="B43" s="146"/>
-      <c r="C43" s="108" t="s">
+      <c r="B43" s="30"/>
+      <c r="C43" s="143" t="s">
         <v>242</v>
       </c>
-      <c r="D43" s="109" t="s">
+      <c r="D43" s="144" t="s">
         <v>243</v>
       </c>
-      <c r="E43" s="109" t="s">
+      <c r="E43" s="144" t="s">
         <v>178</v>
       </c>
-      <c r="F43" s="110" t="s">
+      <c r="F43" s="145" t="s">
         <v>244</v>
       </c>
-      <c r="G43" s="11" t="s">
+      <c r="G43" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="H43" s="11" t="s">
+      <c r="H43" s="17" t="s">
         <v>245</v>
       </c>
-      <c r="I43" s="109" t="s">
+      <c r="I43" s="144" t="s">
         <v>246</v>
       </c>
-      <c r="J43" s="11">
+      <c r="J43" s="17">
         <v>2</v>
       </c>
-      <c r="K43" s="13">
+      <c r="K43" s="19">
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="L43" s="13">
+      <c r="L43" s="19">
         <f t="shared" si="7"/>
         <v>100</v>
       </c>
-      <c r="M43" s="13">
+      <c r="M43" s="19">
         <f t="shared" si="8"/>
         <v>200</v>
       </c>
-      <c r="N43" s="33" t="s">
+      <c r="N43" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="O43" s="37">
-        <v>1.2999999999999999E-2</v>
-      </c>
-      <c r="P43" s="35">
+      <c r="O43" s="57">
+        <v>0.013</v>
+      </c>
+      <c r="P43" s="55">
         <f t="shared" si="9"/>
         <v>0.13</v>
       </c>
-      <c r="Q43" s="37">
-        <v>5.4000000000000003E-3</v>
-      </c>
-      <c r="R43" s="35">
+      <c r="Q43" s="57">
+        <v>0.0054</v>
+      </c>
+      <c r="R43" s="55">
         <f t="shared" si="10"/>
         <v>0.54</v>
       </c>
-      <c r="S43" s="74">
-        <v>5.4000000000000003E-3</v>
-      </c>
-      <c r="T43" s="35">
+      <c r="S43" s="96">
+        <v>0.0054</v>
+      </c>
+      <c r="T43" s="55">
         <f t="shared" si="11"/>
         <v>1.08</v>
       </c>
-      <c r="U43" s="82"/>
-      <c r="V43" s="78"/>
-      <c r="W43" s="78"/>
+      <c r="U43" s="104"/>
+      <c r="V43" s="100"/>
+      <c r="W43" s="100"/>
     </row>
-    <row r="44" spans="1:23">
-      <c r="A44" s="8">
+    <row r="44" ht="15.75" spans="1:23">
+      <c r="A44" s="10">
         <v>41</v>
       </c>
-      <c r="B44" s="146"/>
-      <c r="C44" s="108" t="s">
+      <c r="B44" s="30"/>
+      <c r="C44" s="143" t="s">
         <v>247</v>
       </c>
-      <c r="D44" s="109" t="s">
+      <c r="D44" s="144" t="s">
         <v>248</v>
       </c>
-      <c r="E44" s="109" t="s">
+      <c r="E44" s="144" t="s">
         <v>249</v>
       </c>
-      <c r="F44" s="110" t="s">
+      <c r="F44" s="145" t="s">
         <v>250</v>
       </c>
-      <c r="G44" s="11" t="s">
+      <c r="G44" s="17" t="s">
         <v>251</v>
       </c>
-      <c r="H44" s="11" t="s">
+      <c r="H44" s="17" t="s">
         <v>252</v>
       </c>
-      <c r="I44" s="109" t="s">
+      <c r="I44" s="144" t="s">
         <v>253</v>
       </c>
-      <c r="J44" s="11">
+      <c r="J44" s="17">
         <v>1</v>
       </c>
-      <c r="K44" s="13">
+      <c r="K44" s="19">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="L44" s="13">
+      <c r="L44" s="19">
         <f t="shared" si="7"/>
         <v>50</v>
       </c>
-      <c r="M44" s="13">
+      <c r="M44" s="19">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="N44" s="33" t="s">
+      <c r="N44" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="O44" s="37">
+      <c r="O44" s="57">
         <v>0.3</v>
       </c>
-      <c r="P44" s="35">
+      <c r="P44" s="55">
         <f t="shared" si="9"/>
         <v>1.5</v>
       </c>
-      <c r="Q44" s="37">
-        <v>0.13339999999999999</v>
-      </c>
-      <c r="R44" s="35">
+      <c r="Q44" s="57">
+        <v>0.1334</v>
+      </c>
+      <c r="R44" s="55">
         <f t="shared" si="10"/>
         <v>6.67</v>
       </c>
-      <c r="S44" s="74">
-        <v>9.8900000000000002E-2</v>
-      </c>
-      <c r="T44" s="35">
+      <c r="S44" s="96">
+        <v>0.0989</v>
+      </c>
+      <c r="T44" s="55">
         <f t="shared" si="11"/>
         <v>9.89</v>
       </c>
-      <c r="U44" s="82"/>
-      <c r="V44" s="78"/>
-      <c r="W44" s="78"/>
+      <c r="U44" s="104"/>
+      <c r="V44" s="100"/>
+      <c r="W44" s="100"/>
     </row>
-    <row r="45" spans="1:23">
-      <c r="A45" s="8">
+    <row r="45" ht="15.75" spans="1:23">
+      <c r="A45" s="10">
         <v>42</v>
       </c>
-      <c r="B45" s="146"/>
-      <c r="C45" s="108" t="s">
+      <c r="B45" s="30"/>
+      <c r="C45" s="143" t="s">
         <v>254</v>
       </c>
-      <c r="D45" s="109" t="s">
+      <c r="D45" s="144" t="s">
         <v>255</v>
       </c>
-      <c r="E45" s="109" t="s">
+      <c r="E45" s="144" t="s">
         <v>178</v>
       </c>
-      <c r="F45" s="110" t="s">
+      <c r="F45" s="145" t="s">
         <v>256</v>
       </c>
-      <c r="G45" s="11" t="s">
+      <c r="G45" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="H45" s="11" t="s">
+      <c r="H45" s="17" t="s">
         <v>257</v>
       </c>
-      <c r="I45" s="109" t="s">
+      <c r="I45" s="144" t="s">
         <v>258</v>
       </c>
-      <c r="J45" s="11">
+      <c r="J45" s="17">
         <v>2</v>
       </c>
-      <c r="K45" s="13">
+      <c r="K45" s="19">
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="L45" s="13">
+      <c r="L45" s="19">
         <f t="shared" si="7"/>
         <v>100</v>
       </c>
-      <c r="M45" s="13">
+      <c r="M45" s="19">
         <f t="shared" si="8"/>
         <v>200</v>
       </c>
-      <c r="N45" s="33" t="s">
+      <c r="N45" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="O45" s="37">
-        <v>1.2E-2</v>
-      </c>
-      <c r="P45" s="35">
+      <c r="O45" s="57">
+        <v>0.012</v>
+      </c>
+      <c r="P45" s="55">
         <f t="shared" si="9"/>
         <v>0.12</v>
       </c>
-      <c r="Q45" s="37">
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="R45" s="35">
+      <c r="Q45" s="57">
+        <v>0.0047</v>
+      </c>
+      <c r="R45" s="55">
         <f t="shared" si="10"/>
-        <v>0.47000000000000003</v>
-      </c>
-      <c r="S45" s="74">
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="T45" s="35">
+        <v>0.47</v>
+      </c>
+      <c r="S45" s="96">
+        <v>0.0047</v>
+      </c>
+      <c r="T45" s="55">
         <f t="shared" si="11"/>
-        <v>0.94000000000000006</v>
-      </c>
-      <c r="U45" s="82"/>
-      <c r="V45" s="78"/>
-      <c r="W45" s="78"/>
+        <v>0.94</v>
+      </c>
+      <c r="U45" s="104"/>
+      <c r="V45" s="100"/>
+      <c r="W45" s="100"/>
     </row>
-    <row r="46" spans="1:23">
-      <c r="A46" s="8">
+    <row r="46" ht="15.75" spans="1:23">
+      <c r="A46" s="10">
         <v>43</v>
       </c>
-      <c r="B46" s="146"/>
-      <c r="C46" s="108" t="s">
+      <c r="B46" s="30"/>
+      <c r="C46" s="143" t="s">
         <v>259</v>
       </c>
-      <c r="D46" s="109" t="s">
+      <c r="D46" s="144" t="s">
         <v>260</v>
       </c>
-      <c r="E46" s="109" t="s">
+      <c r="E46" s="144" t="s">
         <v>178</v>
       </c>
-      <c r="F46" s="109" t="s">
+      <c r="F46" s="144" t="s">
         <v>261</v>
       </c>
-      <c r="G46" s="11" t="s">
+      <c r="G46" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="H46" s="109" t="s">
+      <c r="H46" s="144" t="s">
         <v>28</v>
       </c>
-      <c r="I46" s="109" t="s">
+      <c r="I46" s="144" t="s">
         <v>262</v>
       </c>
-      <c r="J46" s="11">
+      <c r="J46" s="17">
         <v>1</v>
       </c>
-      <c r="K46" s="13">
+      <c r="K46" s="19">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="L46" s="13">
+      <c r="L46" s="19">
         <f t="shared" si="7"/>
         <v>50</v>
       </c>
-      <c r="M46" s="13">
+      <c r="M46" s="19">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="N46" s="33" t="s">
+      <c r="N46" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="O46" s="37">
+      <c r="O46" s="57">
         <v>0.1</v>
       </c>
-      <c r="P46" s="35">
+      <c r="P46" s="55">
         <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
-      <c r="Q46" s="37">
-        <v>2.1999999999999999E-2</v>
-      </c>
-      <c r="R46" s="35">
+      <c r="Q46" s="57">
+        <v>0.022</v>
+      </c>
+      <c r="R46" s="55">
         <f t="shared" si="10"/>
-        <v>1.0999999999999999</v>
-      </c>
-      <c r="S46" s="74">
-        <v>8.9999999999999993E-3</v>
-      </c>
-      <c r="T46" s="35">
+        <v>1.1</v>
+      </c>
+      <c r="S46" s="96">
+        <v>0.009</v>
+      </c>
+      <c r="T46" s="55">
         <f t="shared" si="11"/>
-        <v>0.89999999999999991</v>
-      </c>
-      <c r="U46" s="82"/>
-      <c r="V46" s="78"/>
-      <c r="W46" s="78"/>
+        <v>0.9</v>
+      </c>
+      <c r="U46" s="104"/>
+      <c r="V46" s="100"/>
+      <c r="W46" s="100"/>
     </row>
-    <row r="47" spans="1:23">
-      <c r="A47" s="8">
+    <row r="47" ht="15.75" spans="1:23">
+      <c r="A47" s="10">
         <v>44</v>
       </c>
-      <c r="B47" s="146"/>
-      <c r="C47" s="108" t="s">
+      <c r="B47" s="30"/>
+      <c r="C47" s="143" t="s">
         <v>263</v>
       </c>
-      <c r="D47" s="109" t="s">
+      <c r="D47" s="144" t="s">
         <v>264</v>
       </c>
-      <c r="E47" s="109" t="s">
+      <c r="E47" s="144" t="s">
         <v>178</v>
       </c>
-      <c r="F47" s="109" t="s">
+      <c r="F47" s="144" t="s">
         <v>265</v>
       </c>
-      <c r="G47" s="11" t="s">
+      <c r="G47" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="H47" s="109" t="s">
+      <c r="H47" s="144" t="s">
         <v>28</v>
       </c>
-      <c r="I47" s="109" t="s">
+      <c r="I47" s="144" t="s">
         <v>266</v>
       </c>
-      <c r="J47" s="11">
+      <c r="J47" s="17">
         <v>1</v>
       </c>
-      <c r="K47" s="13">
+      <c r="K47" s="19">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="L47" s="13">
+      <c r="L47" s="19">
         <f t="shared" si="7"/>
         <v>50</v>
       </c>
-      <c r="M47" s="13">
+      <c r="M47" s="19">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="N47" s="33" t="s">
+      <c r="N47" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="O47" s="37">
+      <c r="O47" s="57">
         <v>0.1</v>
       </c>
-      <c r="P47" s="35">
+      <c r="P47" s="55">
         <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
-      <c r="Q47" s="37">
-        <v>1.6E-2</v>
-      </c>
-      <c r="R47" s="35">
+      <c r="Q47" s="57">
+        <v>0.016</v>
+      </c>
+      <c r="R47" s="55">
         <f t="shared" si="10"/>
         <v>0.8</v>
       </c>
-      <c r="S47" s="74">
-        <v>6.6E-3</v>
-      </c>
-      <c r="T47" s="35">
+      <c r="S47" s="96">
+        <v>0.0066</v>
+      </c>
+      <c r="T47" s="55">
         <f t="shared" si="11"/>
         <v>0.66</v>
       </c>
-      <c r="U47" s="82"/>
-      <c r="V47" s="78"/>
-      <c r="W47" s="78"/>
+      <c r="U47" s="104"/>
+      <c r="V47" s="100"/>
+      <c r="W47" s="100"/>
     </row>
-    <row r="48" spans="1:23">
-      <c r="A48" s="8">
+    <row r="48" ht="15.75" spans="1:23">
+      <c r="A48" s="10">
         <v>45</v>
       </c>
-      <c r="B48" s="146"/>
-      <c r="C48" s="108" t="s">
+      <c r="B48" s="30"/>
+      <c r="C48" s="143" t="s">
         <v>267</v>
       </c>
-      <c r="D48" s="109" t="s">
+      <c r="D48" s="144" t="s">
         <v>268</v>
       </c>
-      <c r="E48" s="109" t="s">
+      <c r="E48" s="144" t="s">
         <v>178</v>
       </c>
-      <c r="F48" s="109" t="s">
+      <c r="F48" s="144" t="s">
         <v>269</v>
       </c>
-      <c r="G48" s="11" t="s">
+      <c r="G48" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="H48" s="109" t="s">
+      <c r="H48" s="144" t="s">
         <v>28</v>
       </c>
-      <c r="I48" s="109" t="s">
+      <c r="I48" s="144" t="s">
         <v>270</v>
       </c>
-      <c r="J48" s="11">
+      <c r="J48" s="17">
         <v>1</v>
       </c>
-      <c r="K48" s="13">
+      <c r="K48" s="19">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="L48" s="13">
+      <c r="L48" s="19">
         <f t="shared" si="7"/>
         <v>50</v>
       </c>
-      <c r="M48" s="13">
+      <c r="M48" s="19">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="N48" s="33" t="s">
+      <c r="N48" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="O48" s="37">
+      <c r="O48" s="57">
         <v>0.1</v>
       </c>
-      <c r="P48" s="35">
+      <c r="P48" s="55">
         <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
-      <c r="Q48" s="37">
-        <v>1.6E-2</v>
-      </c>
-      <c r="R48" s="35">
+      <c r="Q48" s="57">
+        <v>0.016</v>
+      </c>
+      <c r="R48" s="55">
         <f t="shared" si="10"/>
         <v>0.8</v>
       </c>
-      <c r="S48" s="74">
-        <v>6.6E-3</v>
-      </c>
-      <c r="T48" s="35">
+      <c r="S48" s="96">
+        <v>0.0066</v>
+      </c>
+      <c r="T48" s="55">
         <f t="shared" si="11"/>
         <v>0.66</v>
       </c>
-      <c r="U48" s="82"/>
-      <c r="V48" s="78"/>
-      <c r="W48" s="78"/>
+      <c r="U48" s="104"/>
+      <c r="V48" s="100"/>
+      <c r="W48" s="100"/>
     </row>
-    <row r="49" spans="1:23">
-      <c r="A49" s="8">
+    <row r="49" ht="15.75" spans="1:23">
+      <c r="A49" s="10">
         <v>46</v>
       </c>
-      <c r="B49" s="146"/>
-      <c r="C49" s="108" t="s">
+      <c r="B49" s="30"/>
+      <c r="C49" s="143" t="s">
         <v>271</v>
       </c>
-      <c r="D49" s="109" t="s">
+      <c r="D49" s="144" t="s">
         <v>272</v>
       </c>
-      <c r="E49" s="109" t="s">
+      <c r="E49" s="144" t="s">
         <v>178</v>
       </c>
-      <c r="F49" s="109" t="s">
+      <c r="F49" s="144" t="s">
         <v>273</v>
       </c>
-      <c r="G49" s="11" t="s">
+      <c r="G49" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="H49" s="109" t="s">
+      <c r="H49" s="144" t="s">
         <v>28</v>
       </c>
-      <c r="I49" s="109" t="s">
+      <c r="I49" s="144" t="s">
         <v>274</v>
       </c>
-      <c r="J49" s="11">
+      <c r="J49" s="17">
         <v>1</v>
       </c>
-      <c r="K49" s="13">
+      <c r="K49" s="19">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="L49" s="13">
+      <c r="L49" s="19">
         <f t="shared" si="7"/>
         <v>50</v>
       </c>
-      <c r="M49" s="13">
+      <c r="M49" s="19">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="N49" s="33" t="s">
+      <c r="N49" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="O49" s="37">
+      <c r="O49" s="57">
         <v>0.1</v>
       </c>
-      <c r="P49" s="35">
+      <c r="P49" s="55">
         <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
-      <c r="Q49" s="37">
-        <v>2.1999999999999999E-2</v>
-      </c>
-      <c r="R49" s="35">
+      <c r="Q49" s="57">
+        <v>0.022</v>
+      </c>
+      <c r="R49" s="55">
         <f t="shared" si="10"/>
-        <v>1.0999999999999999</v>
-      </c>
-      <c r="S49" s="74">
-        <v>8.9999999999999993E-3</v>
-      </c>
-      <c r="T49" s="35">
+        <v>1.1</v>
+      </c>
+      <c r="S49" s="96">
+        <v>0.009</v>
+      </c>
+      <c r="T49" s="55">
         <f t="shared" si="11"/>
-        <v>0.89999999999999991</v>
-      </c>
-      <c r="U49" s="82"/>
-      <c r="V49" s="78"/>
-      <c r="W49" s="78"/>
+        <v>0.9</v>
+      </c>
+      <c r="U49" s="104"/>
+      <c r="V49" s="100"/>
+      <c r="W49" s="100"/>
     </row>
-    <row r="50" spans="1:23">
-      <c r="A50" s="8">
+    <row r="50" ht="15.75" spans="1:23">
+      <c r="A50" s="10">
         <v>47</v>
       </c>
-      <c r="B50" s="145"/>
-      <c r="C50" s="117" t="s">
+      <c r="B50" s="27"/>
+      <c r="C50" s="152" t="s">
         <v>275</v>
       </c>
-      <c r="D50" s="118" t="s">
+      <c r="D50" s="153" t="s">
         <v>276</v>
       </c>
-      <c r="E50" s="118" t="s">
+      <c r="E50" s="153" t="s">
         <v>178</v>
       </c>
-      <c r="F50" s="131" t="s">
+      <c r="F50" s="166" t="s">
         <v>277</v>
       </c>
-      <c r="G50" s="18" t="s">
+      <c r="G50" s="29" t="s">
         <v>180</v>
       </c>
-      <c r="H50" s="18" t="s">
+      <c r="H50" s="29" t="s">
         <v>278</v>
       </c>
-      <c r="I50" s="118" t="s">
+      <c r="I50" s="153" t="s">
         <v>279</v>
       </c>
-      <c r="J50" s="18">
+      <c r="J50" s="29">
         <v>1</v>
       </c>
-      <c r="K50" s="21">
+      <c r="K50" s="34">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="L50" s="21">
+      <c r="L50" s="34">
         <f t="shared" si="7"/>
         <v>50</v>
       </c>
-      <c r="M50" s="21">
+      <c r="M50" s="34">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="N50" s="51" t="s">
+      <c r="N50" s="71" t="s">
         <v>30</v>
       </c>
-      <c r="O50" s="52">
+      <c r="O50" s="72">
         <v>0.1</v>
       </c>
-      <c r="P50" s="53">
+      <c r="P50" s="73">
         <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
-      <c r="Q50" s="52">
-        <v>3.1E-2</v>
-      </c>
-      <c r="R50" s="53">
+      <c r="Q50" s="72">
+        <v>0.031</v>
+      </c>
+      <c r="R50" s="73">
         <f t="shared" si="10"/>
         <v>1.55</v>
       </c>
-      <c r="S50" s="91">
-        <v>1.2500000000000001E-2</v>
-      </c>
-      <c r="T50" s="53">
+      <c r="S50" s="113">
+        <v>0.0125</v>
+      </c>
+      <c r="T50" s="73">
         <f t="shared" si="11"/>
         <v>1.25</v>
       </c>
-      <c r="U50" s="86"/>
-      <c r="V50" s="78"/>
-      <c r="W50" s="78"/>
+      <c r="U50" s="108"/>
+      <c r="V50" s="100"/>
+      <c r="W50" s="100"/>
     </row>
-    <row r="51" spans="1:23">
-      <c r="A51" s="8">
+    <row r="51" ht="15.75" spans="1:23">
+      <c r="A51" s="10">
         <v>48</v>
       </c>
-      <c r="B51" s="144" t="s">
+      <c r="B51" s="23" t="s">
         <v>280</v>
       </c>
-      <c r="C51" s="105" t="s">
+      <c r="C51" s="140" t="s">
         <v>281</v>
       </c>
-      <c r="D51" s="106" t="s">
+      <c r="D51" s="141" t="s">
         <v>282</v>
       </c>
-      <c r="E51" s="106" t="s">
+      <c r="E51" s="141" t="s">
         <v>283</v>
       </c>
-      <c r="F51" s="106" t="s">
+      <c r="F51" s="141" t="s">
         <v>284</v>
       </c>
-      <c r="G51" s="9" t="s">
+      <c r="G51" s="13" t="s">
         <v>285</v>
       </c>
-      <c r="H51" s="106" t="s">
+      <c r="H51" s="141" t="s">
         <v>28</v>
       </c>
-      <c r="I51" s="106" t="s">
+      <c r="I51" s="141" t="s">
         <v>124</v>
       </c>
-      <c r="J51" s="9">
+      <c r="J51" s="13">
         <v>1</v>
       </c>
-      <c r="K51" s="10">
+      <c r="K51" s="14">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="L51" s="10">
+      <c r="L51" s="14">
         <f t="shared" si="7"/>
         <v>50</v>
       </c>
-      <c r="M51" s="10">
+      <c r="M51" s="14">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="N51" s="56" t="s">
+      <c r="N51" s="76" t="s">
         <v>30</v>
       </c>
-      <c r="O51" s="57">
+      <c r="O51" s="77">
         <v>1.2</v>
       </c>
-      <c r="P51" s="50">
+      <c r="P51" s="70">
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="Q51" s="57">
+      <c r="Q51" s="77">
         <v>1.2</v>
       </c>
-      <c r="R51" s="50">
+      <c r="R51" s="70">
         <f t="shared" si="10"/>
         <v>60</v>
       </c>
-      <c r="S51" s="71">
+      <c r="S51" s="93">
         <v>1</v>
       </c>
-      <c r="T51" s="50">
+      <c r="T51" s="70">
         <f t="shared" si="11"/>
         <v>100</v>
       </c>
-      <c r="U51" s="89" t="s">
+      <c r="U51" s="111" t="s">
         <v>138</v>
       </c>
-      <c r="V51" s="78"/>
-      <c r="W51" s="78"/>
+      <c r="V51" s="100"/>
+      <c r="W51" s="100"/>
     </row>
-    <row r="52" spans="1:23">
-      <c r="A52" s="8">
+    <row r="52" ht="15.75" spans="1:23">
+      <c r="A52" s="10">
         <v>49</v>
       </c>
-      <c r="B52" s="146"/>
-      <c r="C52" s="108" t="s">
+      <c r="B52" s="30"/>
+      <c r="C52" s="143" t="s">
         <v>286</v>
       </c>
-      <c r="D52" s="109" t="s">
+      <c r="D52" s="144" t="s">
         <v>287</v>
       </c>
-      <c r="E52" s="109" t="s">
+      <c r="E52" s="144" t="s">
         <v>288</v>
       </c>
-      <c r="F52" s="109" t="s">
+      <c r="F52" s="144" t="s">
         <v>289</v>
       </c>
-      <c r="G52" s="11" t="s">
+      <c r="G52" s="17" t="s">
         <v>290</v>
       </c>
-      <c r="H52" s="109" t="s">
+      <c r="H52" s="144" t="s">
         <v>28</v>
       </c>
-      <c r="I52" s="109" t="s">
+      <c r="I52" s="144" t="s">
         <v>124</v>
       </c>
-      <c r="J52" s="11">
+      <c r="J52" s="17">
         <v>1</v>
       </c>
-      <c r="K52" s="13">
+      <c r="K52" s="19">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="L52" s="13">
+      <c r="L52" s="19">
         <f t="shared" si="7"/>
         <v>50</v>
       </c>
-      <c r="M52" s="13">
+      <c r="M52" s="19">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="N52" s="33" t="s">
+      <c r="N52" s="53" t="s">
         <v>79</v>
       </c>
-      <c r="O52" s="37">
-        <v>0.65400000000000003</v>
-      </c>
-      <c r="P52" s="35">
+      <c r="O52" s="57">
+        <v>0.654</v>
+      </c>
+      <c r="P52" s="55">
         <f t="shared" si="9"/>
         <v>3.27</v>
       </c>
-      <c r="Q52" s="37">
-        <v>0.57599999999999996</v>
-      </c>
-      <c r="R52" s="35">
+      <c r="Q52" s="57">
+        <v>0.576</v>
+      </c>
+      <c r="R52" s="55">
         <f t="shared" si="10"/>
-        <v>28.799999999999997</v>
-      </c>
-      <c r="S52" s="74">
+        <v>28.8</v>
+      </c>
+      <c r="S52" s="96">
         <v>0.442</v>
       </c>
-      <c r="T52" s="35">
+      <c r="T52" s="55">
         <f t="shared" si="11"/>
         <v>44.2</v>
       </c>
-      <c r="U52" s="90" t="s">
+      <c r="U52" s="112" t="s">
         <v>138</v>
       </c>
-      <c r="V52" s="78"/>
-      <c r="W52" s="78"/>
+      <c r="V52" s="100"/>
+      <c r="W52" s="100"/>
     </row>
-    <row r="53" spans="1:23">
-      <c r="A53" s="8">
+    <row r="53" ht="15.75" spans="1:23">
+      <c r="A53" s="10">
         <v>50</v>
       </c>
-      <c r="B53" s="146"/>
-      <c r="C53" s="108" t="s">
+      <c r="B53" s="30"/>
+      <c r="C53" s="143" t="s">
         <v>291</v>
       </c>
-      <c r="D53" s="109" t="s">
+      <c r="D53" s="144" t="s">
         <v>292</v>
       </c>
-      <c r="E53" s="109" t="s">
+      <c r="E53" s="144" t="s">
         <v>135</v>
       </c>
-      <c r="F53" s="109" t="s">
+      <c r="F53" s="144" t="s">
         <v>293</v>
       </c>
-      <c r="G53" s="11" t="s">
+      <c r="G53" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="H53" s="109" t="s">
+      <c r="H53" s="144" t="s">
         <v>28</v>
       </c>
-      <c r="I53" s="109" t="s">
+      <c r="I53" s="144" t="s">
         <v>124</v>
       </c>
-      <c r="J53" s="11">
+      <c r="J53" s="17">
         <v>1</v>
       </c>
-      <c r="K53" s="13">
+      <c r="K53" s="19">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="L53" s="13">
+      <c r="L53" s="19">
         <f t="shared" si="7"/>
         <v>50</v>
       </c>
-      <c r="M53" s="13">
+      <c r="M53" s="19">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="N53" s="33" t="s">
+      <c r="N53" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="O53" s="37">
+      <c r="O53" s="57">
         <v>0.54</v>
       </c>
-      <c r="P53" s="35">
+      <c r="P53" s="55">
         <f t="shared" si="9"/>
         <v>2.7</v>
       </c>
-      <c r="Q53" s="37">
+      <c r="Q53" s="57">
         <v>0.4284</v>
       </c>
-      <c r="R53" s="35">
+      <c r="R53" s="55">
         <f t="shared" si="10"/>
         <v>21.42</v>
       </c>
-      <c r="S53" s="74">
-        <v>0.34279999999999999</v>
-      </c>
-      <c r="T53" s="35">
+      <c r="S53" s="96">
+        <v>0.3428</v>
+      </c>
+      <c r="T53" s="55">
         <f t="shared" si="11"/>
         <v>34.28</v>
       </c>
-      <c r="U53" s="90" t="s">
+      <c r="U53" s="112" t="s">
         <v>138</v>
       </c>
-      <c r="V53" s="78"/>
-      <c r="W53" s="78"/>
+      <c r="V53" s="100"/>
+      <c r="W53" s="100"/>
     </row>
-    <row r="54" spans="1:23">
-      <c r="A54" s="8">
+    <row r="54" ht="15.75" spans="1:23">
+      <c r="A54" s="10">
         <v>51</v>
       </c>
-      <c r="B54" s="146"/>
-      <c r="C54" s="108" t="s">
+      <c r="B54" s="30"/>
+      <c r="C54" s="143" t="s">
         <v>294</v>
       </c>
-      <c r="D54" s="109" t="s">
+      <c r="D54" s="144" t="s">
         <v>295</v>
       </c>
-      <c r="E54" s="109" t="s">
+      <c r="E54" s="144" t="s">
         <v>296</v>
       </c>
-      <c r="F54" s="109" t="s">
+      <c r="F54" s="144" t="s">
         <v>297</v>
       </c>
-      <c r="G54" s="11" t="s">
+      <c r="G54" s="17" t="s">
         <v>298</v>
       </c>
-      <c r="H54" s="109" t="s">
+      <c r="H54" s="144" t="s">
         <v>28</v>
       </c>
-      <c r="I54" s="109" t="s">
+      <c r="I54" s="144" t="s">
         <v>124</v>
       </c>
-      <c r="J54" s="11">
+      <c r="J54" s="17">
         <v>1</v>
       </c>
-      <c r="K54" s="13">
+      <c r="K54" s="19">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="L54" s="13">
+      <c r="L54" s="19">
         <f t="shared" si="7"/>
         <v>50</v>
       </c>
-      <c r="M54" s="13">
+      <c r="M54" s="19">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="N54" s="33" t="s">
+      <c r="N54" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="O54" s="37">
+      <c r="O54" s="57">
         <v>0.38</v>
       </c>
-      <c r="P54" s="35">
+      <c r="P54" s="55">
         <f t="shared" si="9"/>
         <v>1.9</v>
       </c>
-      <c r="Q54" s="37">
-        <v>0.28239999999999998</v>
-      </c>
-      <c r="R54" s="35">
+      <c r="Q54" s="57">
+        <v>0.2824</v>
+      </c>
+      <c r="R54" s="55">
         <f t="shared" si="10"/>
         <v>14.12</v>
       </c>
-      <c r="S54" s="74">
-        <v>0.21029999999999999</v>
-      </c>
-      <c r="T54" s="35">
+      <c r="S54" s="96">
+        <v>0.2103</v>
+      </c>
+      <c r="T54" s="55">
         <f t="shared" si="11"/>
-        <v>21.029999999999998</v>
-      </c>
-      <c r="U54" s="82"/>
-      <c r="V54" s="78"/>
-      <c r="W54" s="78"/>
+        <v>21.03</v>
+      </c>
+      <c r="U54" s="104"/>
+      <c r="V54" s="100"/>
+      <c r="W54" s="100"/>
     </row>
-    <row r="55" spans="1:23">
-      <c r="A55" s="8">
+    <row r="55" ht="15.75" spans="1:23">
+      <c r="A55" s="10">
         <v>52</v>
       </c>
-      <c r="B55" s="146"/>
-      <c r="C55" s="108" t="s">
+      <c r="B55" s="30"/>
+      <c r="C55" s="143" t="s">
         <v>299</v>
       </c>
-      <c r="D55" s="109" t="s">
+      <c r="D55" s="144" t="s">
         <v>300</v>
       </c>
-      <c r="E55" s="109" t="s">
+      <c r="E55" s="144" t="s">
         <v>301</v>
       </c>
-      <c r="F55" s="109" t="s">
+      <c r="F55" s="144" t="s">
         <v>302</v>
       </c>
-      <c r="G55" s="11" t="s">
+      <c r="G55" s="17" t="s">
         <v>303</v>
       </c>
-      <c r="H55" s="109" t="s">
+      <c r="H55" s="144" t="s">
         <v>28</v>
       </c>
-      <c r="I55" s="109" t="s">
+      <c r="I55" s="144" t="s">
         <v>124</v>
       </c>
-      <c r="J55" s="11">
+      <c r="J55" s="17">
         <v>1</v>
       </c>
-      <c r="K55" s="13">
+      <c r="K55" s="19">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="L55" s="13">
+      <c r="L55" s="19">
         <f t="shared" si="7"/>
         <v>50</v>
       </c>
-      <c r="M55" s="13">
+      <c r="M55" s="19">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="N55" s="33" t="s">
+      <c r="N55" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="O55" s="37">
-        <v>4.2300000000000004</v>
-      </c>
-      <c r="P55" s="35">
+      <c r="O55" s="57">
+        <v>4.23</v>
+      </c>
+      <c r="P55" s="55">
         <f t="shared" si="9"/>
-        <v>21.150000000000002</v>
-      </c>
-      <c r="Q55" s="37">
-        <v>3.8412000000000002</v>
-      </c>
-      <c r="R55" s="35">
+        <v>21.15</v>
+      </c>
+      <c r="Q55" s="57">
+        <v>3.8412</v>
+      </c>
+      <c r="R55" s="55">
         <f t="shared" si="10"/>
         <v>192.06</v>
       </c>
-      <c r="S55" s="74">
-        <v>3.8250000000000002</v>
-      </c>
-      <c r="T55" s="35">
+      <c r="S55" s="96">
+        <v>3.825</v>
+      </c>
+      <c r="T55" s="55">
         <f t="shared" si="11"/>
         <v>382.5</v>
       </c>
-      <c r="U55" s="90" t="s">
+      <c r="U55" s="112" t="s">
         <v>138</v>
       </c>
-      <c r="V55" s="78"/>
-      <c r="W55" s="78"/>
+      <c r="V55" s="100"/>
+      <c r="W55" s="100"/>
     </row>
-    <row r="56" spans="1:23">
-      <c r="A56" s="8">
+    <row r="56" ht="15.75" spans="1:23">
+      <c r="A56" s="10">
         <v>53</v>
       </c>
-      <c r="B56" s="146"/>
-      <c r="C56" s="108" t="s">
+      <c r="B56" s="30"/>
+      <c r="C56" s="143" t="s">
         <v>304</v>
       </c>
-      <c r="D56" s="109" t="s">
+      <c r="D56" s="144" t="s">
         <v>305</v>
       </c>
-      <c r="E56" s="109" t="s">
+      <c r="E56" s="144" t="s">
         <v>306</v>
       </c>
-      <c r="F56" s="109" t="s">
+      <c r="F56" s="144" t="s">
         <v>307</v>
       </c>
-      <c r="G56" s="11" t="s">
+      <c r="G56" s="17" t="s">
         <v>308</v>
       </c>
-      <c r="H56" s="109" t="s">
+      <c r="H56" s="144" t="s">
         <v>28</v>
       </c>
-      <c r="I56" s="109" t="s">
+      <c r="I56" s="144" t="s">
         <v>124</v>
       </c>
-      <c r="J56" s="11">
+      <c r="J56" s="17">
         <v>1</v>
       </c>
-      <c r="K56" s="13">
+      <c r="K56" s="19">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="L56" s="13">
+      <c r="L56" s="19">
         <f t="shared" si="7"/>
         <v>50</v>
       </c>
-      <c r="M56" s="13">
+      <c r="M56" s="19">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="N56" s="33" t="s">
+      <c r="N56" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="O56" s="37">
+      <c r="O56" s="57">
         <v>1.3006</v>
       </c>
-      <c r="P56" s="35">
+      <c r="P56" s="55">
         <f t="shared" si="9"/>
-        <v>6.5030000000000001</v>
-      </c>
-      <c r="Q56" s="37">
+        <v>6.503</v>
+      </c>
+      <c r="Q56" s="57">
         <v>1.0849</v>
       </c>
-      <c r="R56" s="35">
+      <c r="R56" s="55">
         <f t="shared" si="10"/>
-        <v>54.244999999999997</v>
-      </c>
-      <c r="S56" s="74">
-        <v>0.82869999999999999</v>
-      </c>
-      <c r="T56" s="35">
+        <v>54.245</v>
+      </c>
+      <c r="S56" s="96">
+        <v>0.8287</v>
+      </c>
+      <c r="T56" s="55">
         <f t="shared" si="11"/>
         <v>82.87</v>
       </c>
-      <c r="U56" s="82"/>
-      <c r="V56" s="78"/>
-      <c r="W56" s="78"/>
+      <c r="U56" s="104"/>
+      <c r="V56" s="100"/>
+      <c r="W56" s="100"/>
     </row>
-    <row r="57" spans="1:23">
-      <c r="A57" s="8">
+    <row r="57" ht="15.75" spans="1:23">
+      <c r="A57" s="10">
         <v>54</v>
       </c>
-      <c r="B57" s="146"/>
-      <c r="C57" s="108" t="s">
+      <c r="B57" s="30"/>
+      <c r="C57" s="143" t="s">
         <v>309</v>
       </c>
-      <c r="D57" s="109" t="s">
+      <c r="D57" s="144" t="s">
         <v>310</v>
       </c>
-      <c r="E57" s="109" t="s">
+      <c r="E57" s="144" t="s">
         <v>311</v>
       </c>
-      <c r="F57" s="109" t="s">
+      <c r="F57" s="144" t="s">
         <v>312</v>
       </c>
-      <c r="G57" s="11" t="s">
+      <c r="G57" s="17" t="s">
         <v>308</v>
       </c>
-      <c r="H57" s="109" t="s">
+      <c r="H57" s="144" t="s">
         <v>28</v>
       </c>
-      <c r="I57" s="109" t="s">
+      <c r="I57" s="144" t="s">
         <v>124</v>
       </c>
-      <c r="J57" s="11">
+      <c r="J57" s="17">
         <v>1</v>
       </c>
-      <c r="K57" s="13">
+      <c r="K57" s="19">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="L57" s="13">
+      <c r="L57" s="19">
         <f t="shared" si="7"/>
         <v>50</v>
       </c>
-      <c r="M57" s="13">
+      <c r="M57" s="19">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="N57" s="33" t="s">
+      <c r="N57" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="O57" s="37">
+      <c r="O57" s="57">
         <v>2.4</v>
       </c>
-      <c r="P57" s="35">
+      <c r="P57" s="55">
         <f t="shared" si="9"/>
         <v>12</v>
       </c>
-      <c r="Q57" s="37">
-        <v>2.0352000000000001</v>
-      </c>
-      <c r="R57" s="35">
+      <c r="Q57" s="57">
+        <v>2.0352</v>
+      </c>
+      <c r="R57" s="55">
         <f t="shared" si="10"/>
         <v>101.76</v>
       </c>
-      <c r="S57" s="74">
+      <c r="S57" s="96">
         <v>1.734</v>
       </c>
-      <c r="T57" s="35">
+      <c r="T57" s="55">
         <f t="shared" si="11"/>
         <v>173.4</v>
       </c>
-      <c r="U57" s="90" t="s">
+      <c r="U57" s="112" t="s">
         <v>138</v>
       </c>
-      <c r="V57" s="78"/>
-      <c r="W57" s="78"/>
+      <c r="V57" s="100"/>
+      <c r="W57" s="100"/>
     </row>
-    <row r="58" spans="1:23" ht="15.75" customHeight="1">
-      <c r="A58" s="8">
+    <row r="58" ht="15.75" customHeight="1" spans="1:23">
+      <c r="A58" s="10">
         <v>55</v>
       </c>
-      <c r="B58" s="146"/>
-      <c r="C58" s="108" t="s">
+      <c r="B58" s="30"/>
+      <c r="C58" s="143" t="s">
         <v>313</v>
       </c>
-      <c r="D58" s="109" t="s">
+      <c r="D58" s="144" t="s">
         <v>314</v>
       </c>
-      <c r="E58" s="109" t="s">
+      <c r="E58" s="144" t="s">
         <v>296</v>
       </c>
-      <c r="F58" s="109" t="s">
+      <c r="F58" s="144" t="s">
         <v>315</v>
       </c>
-      <c r="G58" s="11" t="s">
+      <c r="G58" s="17" t="s">
         <v>303</v>
       </c>
-      <c r="H58" s="109" t="s">
+      <c r="H58" s="144" t="s">
         <v>28</v>
       </c>
-      <c r="I58" s="109" t="s">
+      <c r="I58" s="144" t="s">
         <v>124</v>
       </c>
-      <c r="J58" s="11">
+      <c r="J58" s="17">
         <v>1</v>
       </c>
-      <c r="K58" s="13">
+      <c r="K58" s="19">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="L58" s="13">
+      <c r="L58" s="19">
         <f t="shared" si="7"/>
         <v>50</v>
       </c>
-      <c r="M58" s="13">
+      <c r="M58" s="19">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="N58" s="33" t="s">
+      <c r="N58" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="O58" s="37">
+      <c r="O58" s="57">
         <v>0.86</v>
       </c>
-      <c r="P58" s="35">
+      <c r="P58" s="55">
         <f t="shared" si="9"/>
         <v>4.3</v>
       </c>
-      <c r="Q58" s="37">
+      <c r="Q58" s="57">
         <v>0.86</v>
       </c>
-      <c r="R58" s="35">
+      <c r="R58" s="55">
         <f t="shared" si="10"/>
         <v>43</v>
       </c>
-      <c r="S58" s="74">
+      <c r="S58" s="96">
         <v>0.86</v>
       </c>
-      <c r="T58" s="35">
+      <c r="T58" s="55">
         <f t="shared" si="11"/>
         <v>86</v>
       </c>
-      <c r="U58" s="90" t="s">
+      <c r="U58" s="112" t="s">
         <v>138</v>
       </c>
-      <c r="V58" s="78"/>
-      <c r="W58" s="78"/>
+      <c r="V58" s="100"/>
+      <c r="W58" s="100"/>
     </row>
-    <row r="59" spans="1:23">
-      <c r="A59" s="8">
+    <row r="59" ht="15.75" spans="1:23">
+      <c r="A59" s="10">
         <v>56</v>
       </c>
-      <c r="B59" s="146"/>
-      <c r="C59" s="108" t="s">
+      <c r="B59" s="30"/>
+      <c r="C59" s="143" t="s">
         <v>316</v>
       </c>
-      <c r="D59" s="109" t="s">
+      <c r="D59" s="144" t="s">
         <v>317</v>
       </c>
-      <c r="E59" s="109" t="s">
+      <c r="E59" s="144" t="s">
         <v>296</v>
       </c>
-      <c r="F59" s="109" t="s">
+      <c r="F59" s="144" t="s">
         <v>318</v>
       </c>
-      <c r="G59" s="11" t="s">
+      <c r="G59" s="17" t="s">
         <v>308</v>
       </c>
-      <c r="H59" s="109" t="s">
+      <c r="H59" s="144" t="s">
         <v>28</v>
       </c>
-      <c r="I59" s="109" t="s">
+      <c r="I59" s="144" t="s">
         <v>124</v>
       </c>
-      <c r="J59" s="11">
+      <c r="J59" s="17">
         <v>1</v>
       </c>
-      <c r="K59" s="13">
+      <c r="K59" s="19">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="L59" s="13">
+      <c r="L59" s="19">
         <f t="shared" si="7"/>
         <v>50</v>
       </c>
-      <c r="M59" s="13">
+      <c r="M59" s="19">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="N59" s="33" t="s">
+      <c r="N59" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="O59" s="37">
+      <c r="O59" s="57">
         <v>4.01</v>
       </c>
-      <c r="P59" s="35">
+      <c r="P59" s="55">
         <f t="shared" si="9"/>
-        <v>20.049999999999997</v>
-      </c>
-      <c r="Q59" s="37">
-        <v>3.4079999999999999</v>
-      </c>
-      <c r="R59" s="35">
+        <v>20.05</v>
+      </c>
+      <c r="Q59" s="57">
+        <v>3.408</v>
+      </c>
+      <c r="R59" s="55">
         <f t="shared" si="10"/>
         <v>170.4</v>
       </c>
-      <c r="S59" s="74">
+      <c r="S59" s="96">
         <v>2.9537</v>
       </c>
-      <c r="T59" s="35">
+      <c r="T59" s="55">
         <f t="shared" si="11"/>
         <v>295.37</v>
       </c>
-      <c r="U59" s="82"/>
-      <c r="V59" s="78"/>
-      <c r="W59" s="78"/>
+      <c r="U59" s="104"/>
+      <c r="V59" s="100"/>
+      <c r="W59" s="100"/>
     </row>
-    <row r="60" spans="1:23">
-      <c r="A60" s="8">
+    <row r="60" ht="15.75" spans="1:23">
+      <c r="A60" s="10">
         <v>57</v>
       </c>
-      <c r="B60" s="145"/>
-      <c r="C60" s="117" t="s">
+      <c r="B60" s="27"/>
+      <c r="C60" s="152" t="s">
         <v>319</v>
       </c>
-      <c r="D60" s="118" t="s">
+      <c r="D60" s="153" t="s">
         <v>320</v>
       </c>
-      <c r="E60" s="118" t="s">
+      <c r="E60" s="153" t="s">
         <v>321</v>
       </c>
-      <c r="F60" s="131" t="s">
+      <c r="F60" s="166" t="s">
         <v>322</v>
       </c>
-      <c r="G60" s="18" t="s">
+      <c r="G60" s="29" t="s">
         <v>323</v>
       </c>
-      <c r="H60" s="18" t="s">
+      <c r="H60" s="29" t="s">
         <v>324</v>
       </c>
-      <c r="I60" s="118" t="s">
+      <c r="I60" s="153" t="s">
         <v>124</v>
       </c>
-      <c r="J60" s="18">
+      <c r="J60" s="29">
         <v>1</v>
       </c>
-      <c r="K60" s="21">
+      <c r="K60" s="34">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="L60" s="21">
+      <c r="L60" s="34">
         <f t="shared" si="7"/>
         <v>50</v>
       </c>
-      <c r="M60" s="21">
+      <c r="M60" s="34">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="N60" s="51" t="s">
+      <c r="N60" s="71" t="s">
         <v>30</v>
       </c>
-      <c r="O60" s="52">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="P60" s="53">
+      <c r="O60" s="72">
+        <v>1.15</v>
+      </c>
+      <c r="P60" s="73">
         <f t="shared" si="9"/>
         <v>5.75</v>
       </c>
-      <c r="Q60" s="52">
-        <v>0.97960000000000003</v>
-      </c>
-      <c r="R60" s="53">
+      <c r="Q60" s="72">
+        <v>0.9796</v>
+      </c>
+      <c r="R60" s="73">
         <f t="shared" si="10"/>
-        <v>48.980000000000004</v>
-      </c>
-      <c r="S60" s="91">
-        <v>0.80449999999999999</v>
-      </c>
-      <c r="T60" s="53">
+        <v>48.98</v>
+      </c>
+      <c r="S60" s="113">
+        <v>0.8045</v>
+      </c>
+      <c r="T60" s="73">
         <f t="shared" si="11"/>
         <v>80.45</v>
       </c>
-      <c r="U60" s="86"/>
-      <c r="V60" s="78"/>
-      <c r="W60" s="78"/>
+      <c r="U60" s="108"/>
+      <c r="V60" s="100"/>
+      <c r="W60" s="100"/>
     </row>
-    <row r="61" spans="1:23" ht="38.25">
-      <c r="A61" s="8">
+    <row r="61" ht="39" spans="1:21">
+      <c r="A61" s="10">
         <v>58</v>
       </c>
-      <c r="B61" s="144" t="s">
+      <c r="B61" s="23" t="s">
         <v>325</v>
       </c>
-      <c r="C61" s="132" t="s">
+      <c r="C61" s="167" t="s">
         <v>326</v>
       </c>
-      <c r="D61" s="106" t="s">
+      <c r="D61" s="141" t="s">
         <v>327</v>
       </c>
-      <c r="E61" s="106" t="s">
+      <c r="E61" s="141" t="s">
         <v>25</v>
       </c>
-      <c r="F61" s="130" t="s">
+      <c r="F61" s="165" t="s">
         <v>328</v>
       </c>
-      <c r="G61" s="9" t="s">
+      <c r="G61" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="H61" s="27" t="s">
+      <c r="H61" s="47" t="s">
         <v>329</v>
       </c>
-      <c r="I61" s="106" t="s">
+      <c r="I61" s="141" t="s">
         <v>124</v>
       </c>
-      <c r="J61" s="9">
+      <c r="J61" s="13">
         <v>1</v>
       </c>
-      <c r="K61" s="10">
+      <c r="K61" s="14">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="L61" s="10">
+      <c r="L61" s="14">
         <f t="shared" si="7"/>
         <v>50</v>
       </c>
-      <c r="M61" s="10">
+      <c r="M61" s="14">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="N61" s="69" t="s">
+      <c r="N61" s="90" t="s">
         <v>30</v>
       </c>
-      <c r="O61" s="57">
+      <c r="O61" s="77">
         <v>0.73</v>
       </c>
-      <c r="P61" s="50">
+      <c r="P61" s="70">
         <f t="shared" si="9"/>
         <v>3.65</v>
       </c>
-      <c r="Q61" s="57">
+      <c r="Q61" s="77">
         <v>0.73</v>
       </c>
-      <c r="R61" s="50">
+      <c r="R61" s="70">
         <f t="shared" si="10"/>
         <v>36.5</v>
       </c>
-      <c r="S61" s="71">
+      <c r="S61" s="93">
         <v>0.73</v>
       </c>
-      <c r="T61" s="50">
+      <c r="T61" s="70">
         <f t="shared" si="11"/>
         <v>73</v>
       </c>
-      <c r="U61" s="97" t="s">
+      <c r="U61" s="119" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="62" spans="1:23" ht="25.5">
-      <c r="A62" s="8">
+    <row r="62" ht="26.25" spans="1:21">
+      <c r="A62" s="10">
         <v>59</v>
       </c>
-      <c r="B62" s="146"/>
-      <c r="C62" s="113" t="s">
+      <c r="B62" s="30"/>
+      <c r="C62" s="148" t="s">
         <v>330</v>
       </c>
-      <c r="D62" s="109" t="s">
+      <c r="D62" s="144" t="s">
         <v>331</v>
       </c>
-      <c r="E62" s="109" t="s">
+      <c r="E62" s="144" t="s">
         <v>25</v>
       </c>
-      <c r="F62" s="110" t="s">
+      <c r="F62" s="145" t="s">
         <v>332</v>
       </c>
-      <c r="G62" s="11" t="s">
+      <c r="G62" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="H62" s="109" t="s">
+      <c r="H62" s="144" t="s">
         <v>333</v>
       </c>
-      <c r="I62" s="109" t="s">
+      <c r="I62" s="144" t="s">
         <v>124</v>
       </c>
-      <c r="J62" s="11">
+      <c r="J62" s="17">
         <v>1</v>
       </c>
-      <c r="K62" s="13">
+      <c r="K62" s="19">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="L62" s="13">
+      <c r="L62" s="19">
         <f t="shared" si="7"/>
         <v>50</v>
       </c>
-      <c r="M62" s="13">
+      <c r="M62" s="19">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="N62" s="36" t="s">
+      <c r="N62" s="56" t="s">
         <v>30</v>
       </c>
-      <c r="O62" s="37">
+      <c r="O62" s="57">
         <v>1.01</v>
       </c>
-      <c r="P62" s="35">
+      <c r="P62" s="55">
         <f t="shared" si="9"/>
         <v>5.05</v>
       </c>
-      <c r="Q62" s="37">
-        <v>0.79800000000000004</v>
-      </c>
-      <c r="R62" s="35">
+      <c r="Q62" s="57">
+        <v>0.798</v>
+      </c>
+      <c r="R62" s="55">
         <f t="shared" si="10"/>
-        <v>39.900000000000006</v>
-      </c>
-      <c r="S62" s="74">
-        <v>0.76339999999999997</v>
-      </c>
-      <c r="T62" s="35">
+        <v>39.9</v>
+      </c>
+      <c r="S62" s="96">
+        <v>0.7634</v>
+      </c>
+      <c r="T62" s="55">
         <f t="shared" si="11"/>
         <v>76.34</v>
       </c>
-      <c r="U62" s="75"/>
+      <c r="U62" s="97"/>
     </row>
-    <row r="63" spans="1:23" s="1" customFormat="1" ht="25.5">
-      <c r="A63" s="8">
+    <row r="63" s="1" customFormat="1" ht="26.25" spans="1:21">
+      <c r="A63" s="10">
         <v>60</v>
       </c>
-      <c r="B63" s="146"/>
-      <c r="C63" s="113" t="s">
+      <c r="B63" s="30"/>
+      <c r="C63" s="148" t="s">
         <v>334</v>
       </c>
-      <c r="D63" s="111" t="s">
+      <c r="D63" s="146" t="s">
         <v>335</v>
       </c>
-      <c r="E63" s="111" t="s">
+      <c r="E63" s="146" t="s">
         <v>25</v>
       </c>
-      <c r="F63" s="133" t="s">
+      <c r="F63" s="168" t="s">
         <v>336</v>
       </c>
-      <c r="G63" s="13" t="s">
+      <c r="G63" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="H63" s="11" t="s">
+      <c r="H63" s="17" t="s">
         <v>338</v>
       </c>
-      <c r="I63" s="111" t="s">
+      <c r="I63" s="146" t="s">
         <v>124</v>
       </c>
-      <c r="J63" s="13">
+      <c r="J63" s="19">
         <v>1</v>
       </c>
-      <c r="K63" s="13">
+      <c r="K63" s="19">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="L63" s="13">
+      <c r="L63" s="19">
         <f t="shared" si="7"/>
         <v>50</v>
       </c>
-      <c r="M63" s="13">
+      <c r="M63" s="19">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="N63" s="70" t="s">
+      <c r="N63" s="91" t="s">
         <v>30</v>
       </c>
-      <c r="O63" s="35">
+      <c r="O63" s="55">
         <v>0.35</v>
       </c>
-      <c r="P63" s="35">
+      <c r="P63" s="55">
         <f t="shared" si="9"/>
         <v>1.75</v>
       </c>
-      <c r="Q63" s="35">
-        <v>0.24099999999999999</v>
-      </c>
-      <c r="R63" s="35">
+      <c r="Q63" s="55">
+        <v>0.241</v>
+      </c>
+      <c r="R63" s="55">
         <f t="shared" si="10"/>
-        <v>12.049999999999999</v>
-      </c>
-      <c r="S63" s="74">
-        <v>0.23150000000000001</v>
-      </c>
-      <c r="T63" s="35">
+        <v>12.05</v>
+      </c>
+      <c r="S63" s="96">
+        <v>0.2315</v>
+      </c>
+      <c r="T63" s="55">
         <f t="shared" si="11"/>
-        <v>23.150000000000002</v>
-      </c>
-      <c r="U63" s="75" t="s">
+        <v>23.15</v>
+      </c>
+      <c r="U63" s="97" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="64" spans="1:23" ht="15.75" customHeight="1">
-      <c r="A64" s="8">
+    <row r="64" ht="15.75" customHeight="1" spans="1:21">
+      <c r="A64" s="10">
         <v>61</v>
       </c>
-      <c r="B64" s="146"/>
-      <c r="C64" s="108" t="s">
+      <c r="B64" s="30"/>
+      <c r="C64" s="143" t="s">
         <v>339</v>
       </c>
-      <c r="D64" s="109" t="s">
+      <c r="D64" s="144" t="s">
         <v>340</v>
       </c>
-      <c r="E64" s="109" t="s">
+      <c r="E64" s="144" t="s">
         <v>25</v>
       </c>
-      <c r="F64" s="109" t="s">
+      <c r="F64" s="144" t="s">
         <v>341</v>
       </c>
-      <c r="G64" s="11" t="s">
+      <c r="G64" s="17" t="s">
         <v>342</v>
       </c>
-      <c r="H64" s="109" t="s">
+      <c r="H64" s="144" t="s">
         <v>28</v>
       </c>
-      <c r="I64" s="109" t="s">
+      <c r="I64" s="144" t="s">
         <v>124</v>
       </c>
-      <c r="J64" s="11">
+      <c r="J64" s="17">
         <v>1</v>
       </c>
-      <c r="K64" s="13">
+      <c r="K64" s="19">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="L64" s="13">
+      <c r="L64" s="19">
         <f t="shared" si="7"/>
         <v>50</v>
       </c>
-      <c r="M64" s="13">
+      <c r="M64" s="19">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="N64" s="33" t="s">
+      <c r="N64" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="O64" s="37">
+      <c r="O64" s="57">
         <v>0.96</v>
       </c>
-      <c r="P64" s="35">
+      <c r="P64" s="55">
         <f t="shared" si="9"/>
         <v>4.8</v>
       </c>
-      <c r="Q64" s="37">
-        <v>0.81499999999999995</v>
-      </c>
-      <c r="R64" s="35">
+      <c r="Q64" s="57">
+        <v>0.815</v>
+      </c>
+      <c r="R64" s="55">
         <f t="shared" si="10"/>
         <v>40.75</v>
       </c>
-      <c r="S64" s="74">
-        <v>0.73180000000000001</v>
-      </c>
-      <c r="T64" s="35">
+      <c r="S64" s="96">
+        <v>0.7318</v>
+      </c>
+      <c r="T64" s="55">
         <f t="shared" si="11"/>
-        <v>73.180000000000007</v>
-      </c>
-      <c r="U64" s="82"/>
+        <v>73.18</v>
+      </c>
+      <c r="U64" s="104"/>
     </row>
-    <row r="65" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A65" s="8">
+    <row r="65" ht="15.75" customHeight="1" spans="1:21">
+      <c r="A65" s="10">
         <v>62</v>
       </c>
-      <c r="B65" s="146"/>
-      <c r="C65" s="108" t="s">
+      <c r="B65" s="30"/>
+      <c r="C65" s="143" t="s">
         <v>343</v>
       </c>
-      <c r="D65" s="109" t="s">
+      <c r="D65" s="144" t="s">
         <v>344</v>
       </c>
-      <c r="E65" s="109" t="s">
+      <c r="E65" s="144" t="s">
         <v>25</v>
       </c>
-      <c r="F65" s="110" t="s">
+      <c r="F65" s="145" t="s">
         <v>345</v>
       </c>
-      <c r="G65" s="11" t="s">
+      <c r="G65" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="H65" s="11" t="s">
+      <c r="H65" s="17" t="s">
         <v>346</v>
       </c>
-      <c r="I65" s="109" t="s">
+      <c r="I65" s="144" t="s">
         <v>124</v>
       </c>
-      <c r="J65" s="11">
+      <c r="J65" s="17">
         <v>1</v>
       </c>
-      <c r="K65" s="13">
+      <c r="K65" s="19">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="L65" s="13">
+      <c r="L65" s="19">
         <f t="shared" si="7"/>
         <v>50</v>
       </c>
-      <c r="M65" s="13">
+      <c r="M65" s="19">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="N65" s="33" t="s">
+      <c r="N65" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="O65" s="37">
+      <c r="O65" s="57">
         <v>0.15</v>
       </c>
-      <c r="P65" s="35">
+      <c r="P65" s="55">
         <f t="shared" si="9"/>
         <v>0.75</v>
       </c>
-      <c r="Q65" s="37">
-        <v>0.11799999999999999</v>
-      </c>
-      <c r="R65" s="35">
+      <c r="Q65" s="57">
+        <v>0.118</v>
+      </c>
+      <c r="R65" s="55">
         <f t="shared" si="10"/>
-        <v>5.8999999999999995</v>
-      </c>
-      <c r="S65" s="74">
-        <v>8.6800000000000002E-2</v>
-      </c>
-      <c r="T65" s="35">
+        <v>5.9</v>
+      </c>
+      <c r="S65" s="96">
+        <v>0.0868</v>
+      </c>
+      <c r="T65" s="55">
         <f t="shared" si="11"/>
         <v>8.68</v>
       </c>
-      <c r="U65" s="82"/>
+      <c r="U65" s="104"/>
     </row>
-    <row r="66" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A66" s="8">
+    <row r="66" ht="15.75" customHeight="1" spans="1:21">
+      <c r="A66" s="10">
         <v>63</v>
       </c>
-      <c r="B66" s="146"/>
-      <c r="C66" s="108" t="s">
+      <c r="B66" s="30"/>
+      <c r="C66" s="143" t="s">
         <v>347</v>
       </c>
-      <c r="D66" s="109" t="s">
+      <c r="D66" s="144" t="s">
         <v>348</v>
       </c>
-      <c r="E66" s="109" t="s">
+      <c r="E66" s="144" t="s">
         <v>25</v>
       </c>
-      <c r="F66" s="110" t="s">
+      <c r="F66" s="145" t="s">
         <v>349</v>
       </c>
-      <c r="G66" s="11" t="s">
+      <c r="G66" s="17" t="s">
         <v>350</v>
       </c>
-      <c r="H66" s="11" t="s">
+      <c r="H66" s="17" t="s">
         <v>351</v>
       </c>
-      <c r="I66" s="109" t="s">
+      <c r="I66" s="144" t="s">
         <v>124</v>
       </c>
-      <c r="J66" s="11">
+      <c r="J66" s="17">
         <v>1</v>
       </c>
-      <c r="K66" s="13">
+      <c r="K66" s="19">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="L66" s="13">
+      <c r="L66" s="19">
         <f t="shared" si="7"/>
         <v>50</v>
       </c>
-      <c r="M66" s="13">
+      <c r="M66" s="19">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="N66" s="33" t="s">
+      <c r="N66" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="O66" s="37">
+      <c r="O66" s="57">
         <v>0.45</v>
       </c>
-      <c r="P66" s="35">
+      <c r="P66" s="55">
         <f t="shared" si="9"/>
         <v>2.25</v>
       </c>
-      <c r="Q66" s="37">
+      <c r="Q66" s="57">
         <v>0.45</v>
       </c>
-      <c r="R66" s="35">
+      <c r="R66" s="55">
         <f t="shared" si="10"/>
         <v>22.5</v>
       </c>
-      <c r="S66" s="74">
+      <c r="S66" s="96">
         <v>0.4</v>
       </c>
-      <c r="T66" s="35">
+      <c r="T66" s="55">
         <f t="shared" si="11"/>
         <v>40</v>
       </c>
-      <c r="U66" s="75" t="s">
+      <c r="U66" s="97" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="67" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A67" s="8">
+    <row r="67" ht="15.75" customHeight="1" spans="1:21">
+      <c r="A67" s="10">
         <v>64</v>
       </c>
-      <c r="B67" s="146"/>
-      <c r="C67" s="108" t="s">
+      <c r="B67" s="30"/>
+      <c r="C67" s="143" t="s">
         <v>352</v>
       </c>
-      <c r="D67" s="109" t="s">
+      <c r="D67" s="144" t="s">
         <v>353</v>
       </c>
-      <c r="E67" s="109" t="s">
+      <c r="E67" s="144" t="s">
         <v>25</v>
       </c>
-      <c r="F67" s="110" t="s">
+      <c r="F67" s="145" t="s">
         <v>354</v>
       </c>
-      <c r="G67" s="11" t="s">
+      <c r="G67" s="17" t="s">
         <v>355</v>
       </c>
-      <c r="H67" s="11">
+      <c r="H67" s="17">
         <v>1715260000</v>
       </c>
-      <c r="I67" s="109" t="s">
+      <c r="I67" s="144" t="s">
         <v>124</v>
       </c>
-      <c r="J67" s="11">
+      <c r="J67" s="17">
         <v>1</v>
       </c>
-      <c r="K67" s="13">
+      <c r="K67" s="19">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="L67" s="13">
+      <c r="L67" s="19">
         <f t="shared" si="7"/>
         <v>50</v>
       </c>
-      <c r="M67" s="13">
+      <c r="M67" s="19">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="N67" s="33" t="s">
+      <c r="N67" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="O67" s="37">
+      <c r="O67" s="57">
         <v>2.13</v>
       </c>
-      <c r="P67" s="35">
+      <c r="P67" s="55">
         <f t="shared" si="9"/>
-        <v>10.649999999999999</v>
-      </c>
-      <c r="Q67" s="37">
-        <v>1.3431999999999999</v>
-      </c>
-      <c r="R67" s="35">
+        <v>10.65</v>
+      </c>
+      <c r="Q67" s="57">
+        <v>1.3432</v>
+      </c>
+      <c r="R67" s="55">
         <f t="shared" si="10"/>
         <v>67.16</v>
       </c>
-      <c r="S67" s="74">
+      <c r="S67" s="96">
         <v>1.3104</v>
       </c>
-      <c r="T67" s="35">
+      <c r="T67" s="55">
         <f t="shared" si="11"/>
         <v>131.04</v>
       </c>
-      <c r="U67" s="75" t="s">
+      <c r="U67" s="97" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="68" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A68" s="8">
+    <row r="68" ht="15.75" customHeight="1" spans="1:21">
+      <c r="A68" s="10">
         <v>65</v>
       </c>
-      <c r="B68" s="146"/>
-      <c r="C68" s="108" t="s">
+      <c r="B68" s="30"/>
+      <c r="C68" s="143" t="s">
         <v>352</v>
       </c>
-      <c r="D68" s="109" t="s">
+      <c r="D68" s="144" t="s">
         <v>356</v>
       </c>
-      <c r="E68" s="109" t="s">
+      <c r="E68" s="144" t="s">
         <v>25</v>
       </c>
-      <c r="F68" s="110" t="s">
+      <c r="F68" s="145" t="s">
         <v>357</v>
       </c>
-      <c r="G68" s="11" t="s">
+      <c r="G68" s="17" t="s">
         <v>355</v>
       </c>
-      <c r="H68" s="11">
+      <c r="H68" s="17">
         <v>1711725</v>
       </c>
-      <c r="I68" s="109" t="s">
+      <c r="I68" s="144" t="s">
         <v>124</v>
       </c>
-      <c r="J68" s="11">
+      <c r="J68" s="17">
         <v>2</v>
       </c>
-      <c r="K68" s="13">
+      <c r="K68" s="19">
         <f t="shared" ref="K68:K72" si="12">J68*5</f>
         <v>10</v>
       </c>
-      <c r="L68" s="13">
+      <c r="L68" s="19">
         <f t="shared" ref="L68:L72" si="13">J68*50</f>
         <v>100</v>
       </c>
-      <c r="M68" s="13">
+      <c r="M68" s="19">
         <f t="shared" ref="M68:M72" si="14">J68*100</f>
         <v>200</v>
       </c>
-      <c r="N68" s="33" t="s">
+      <c r="N68" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="O68" s="37">
-        <v>2.1120000000000001</v>
-      </c>
-      <c r="P68" s="35">
+      <c r="O68" s="57">
+        <v>2.112</v>
+      </c>
+      <c r="P68" s="55">
         <f t="shared" ref="P68" si="15">O68*K68</f>
         <v>21.12</v>
       </c>
-      <c r="Q68" s="37">
+      <c r="Q68" s="57">
         <v>1.92</v>
       </c>
-      <c r="R68" s="35">
+      <c r="R68" s="55">
         <f t="shared" ref="R68" si="16">Q68*L68</f>
         <v>192</v>
       </c>
-      <c r="S68" s="74">
+      <c r="S68" s="96">
         <v>1.92</v>
       </c>
-      <c r="T68" s="35">
+      <c r="T68" s="55">
         <f t="shared" ref="T68" si="17">S68*M68</f>
         <v>384</v>
       </c>
-      <c r="U68" s="75" t="s">
+      <c r="U68" s="97" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="69" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A69" s="8">
+    <row r="69" ht="15.75" customHeight="1" spans="1:21">
+      <c r="A69" s="10">
         <v>66</v>
       </c>
-      <c r="B69" s="146"/>
-      <c r="C69" s="134" t="s">
+      <c r="B69" s="30"/>
+      <c r="C69" s="169" t="s">
         <v>358</v>
       </c>
-      <c r="D69" s="110" t="s">
+      <c r="D69" s="145" t="s">
         <v>359</v>
       </c>
-      <c r="E69" s="110" t="s">
+      <c r="E69" s="145" t="s">
         <v>25</v>
       </c>
-      <c r="F69" s="110" t="s">
+      <c r="F69" s="145" t="s">
         <v>360</v>
       </c>
-      <c r="G69" s="12" t="s">
+      <c r="G69" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="H69" s="110" t="s">
+      <c r="H69" s="145" t="s">
         <v>28</v>
       </c>
-      <c r="I69" s="110" t="s">
+      <c r="I69" s="145" t="s">
         <v>124</v>
       </c>
-      <c r="J69" s="12">
+      <c r="J69" s="18">
         <v>1</v>
       </c>
-      <c r="K69" s="28">
+      <c r="K69" s="48">
         <f t="shared" si="12"/>
         <v>5</v>
       </c>
-      <c r="L69" s="28">
+      <c r="L69" s="48">
         <f t="shared" si="13"/>
         <v>50</v>
       </c>
-      <c r="M69" s="28">
+      <c r="M69" s="48">
         <f t="shared" si="14"/>
         <v>100</v>
       </c>
-      <c r="N69" s="110" t="s">
+      <c r="N69" s="145" t="s">
         <v>124</v>
       </c>
-      <c r="O69" s="110" t="s">
+      <c r="O69" s="145" t="s">
         <v>124</v>
       </c>
-      <c r="P69" s="110" t="s">
+      <c r="P69" s="145" t="s">
         <v>124</v>
       </c>
-      <c r="Q69" s="110" t="s">
+      <c r="Q69" s="145" t="s">
         <v>124</v>
       </c>
-      <c r="R69" s="110" t="s">
+      <c r="R69" s="145" t="s">
         <v>124</v>
       </c>
-      <c r="S69" s="110" t="s">
+      <c r="S69" s="145" t="s">
         <v>124</v>
       </c>
-      <c r="T69" s="110" t="s">
+      <c r="T69" s="145" t="s">
         <v>124</v>
       </c>
-      <c r="U69" s="75" t="s">
+      <c r="U69" s="97" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="70" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A70" s="8">
+    <row r="70" ht="15.75" customHeight="1" spans="1:21">
+      <c r="A70" s="10">
         <v>67</v>
       </c>
-      <c r="B70" s="146"/>
-      <c r="C70" s="134" t="s">
+      <c r="B70" s="30"/>
+      <c r="C70" s="169" t="s">
         <v>362</v>
       </c>
-      <c r="D70" s="110" t="s">
+      <c r="D70" s="145" t="s">
         <v>363</v>
       </c>
-      <c r="E70" s="110" t="s">
+      <c r="E70" s="145" t="s">
         <v>25</v>
       </c>
-      <c r="F70" s="110" t="s">
+      <c r="F70" s="145" t="s">
         <v>364</v>
       </c>
-      <c r="G70" s="12" t="s">
+      <c r="G70" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="H70" s="110" t="s">
+      <c r="H70" s="145" t="s">
         <v>28</v>
       </c>
-      <c r="I70" s="110" t="s">
+      <c r="I70" s="145" t="s">
         <v>124</v>
       </c>
-      <c r="J70" s="12">
+      <c r="J70" s="18">
         <v>6</v>
       </c>
-      <c r="K70" s="28">
+      <c r="K70" s="48">
         <f t="shared" si="12"/>
         <v>30</v>
       </c>
-      <c r="L70" s="28">
+      <c r="L70" s="48">
         <f t="shared" si="13"/>
         <v>300</v>
       </c>
-      <c r="M70" s="28">
+      <c r="M70" s="48">
         <f t="shared" si="14"/>
         <v>600</v>
       </c>
-      <c r="N70" s="110" t="s">
+      <c r="N70" s="145" t="s">
         <v>124</v>
       </c>
-      <c r="O70" s="110" t="s">
+      <c r="O70" s="145" t="s">
         <v>124</v>
       </c>
-      <c r="P70" s="110" t="s">
+      <c r="P70" s="145" t="s">
         <v>124</v>
       </c>
-      <c r="Q70" s="110" t="s">
+      <c r="Q70" s="145" t="s">
         <v>124</v>
       </c>
-      <c r="R70" s="110" t="s">
+      <c r="R70" s="145" t="s">
         <v>124</v>
       </c>
-      <c r="S70" s="110" t="s">
+      <c r="S70" s="145" t="s">
         <v>124</v>
       </c>
-      <c r="T70" s="110" t="s">
+      <c r="T70" s="145" t="s">
         <v>124</v>
       </c>
-      <c r="U70" s="75" t="s">
+      <c r="U70" s="97" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="71" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A71" s="8">
+    <row r="71" ht="15.75" customHeight="1" spans="1:21">
+      <c r="A71" s="10">
         <v>68</v>
       </c>
-      <c r="B71" s="146"/>
-      <c r="C71" s="134" t="s">
+      <c r="B71" s="30"/>
+      <c r="C71" s="169" t="s">
         <v>365</v>
       </c>
-      <c r="D71" s="110" t="s">
+      <c r="D71" s="145" t="s">
         <v>366</v>
       </c>
-      <c r="E71" s="110" t="s">
+      <c r="E71" s="145" t="s">
         <v>25</v>
       </c>
-      <c r="F71" s="110" t="s">
+      <c r="F71" s="145" t="s">
         <v>367</v>
       </c>
-      <c r="G71" s="12" t="s">
+      <c r="G71" s="18" t="s">
         <v>368</v>
       </c>
-      <c r="H71" s="98"/>
-      <c r="I71" s="110" t="s">
+      <c r="H71" s="121"/>
+      <c r="I71" s="145" t="s">
         <v>124</v>
       </c>
-      <c r="J71" s="12">
+      <c r="J71" s="18">
         <v>1</v>
       </c>
-      <c r="K71" s="28">
+      <c r="K71" s="48">
         <f t="shared" si="12"/>
         <v>5</v>
       </c>
-      <c r="L71" s="28">
+      <c r="L71" s="48">
         <f t="shared" si="13"/>
         <v>50</v>
       </c>
-      <c r="M71" s="28">
+      <c r="M71" s="48">
         <f t="shared" si="14"/>
         <v>100</v>
       </c>
-      <c r="N71" s="110" t="s">
+      <c r="N71" s="145" t="s">
         <v>124</v>
       </c>
-      <c r="O71" s="110" t="s">
+      <c r="O71" s="145" t="s">
         <v>124</v>
       </c>
-      <c r="P71" s="110" t="s">
+      <c r="P71" s="145" t="s">
         <v>124</v>
       </c>
-      <c r="Q71" s="110" t="s">
+      <c r="Q71" s="145" t="s">
         <v>124</v>
       </c>
-      <c r="R71" s="110" t="s">
+      <c r="R71" s="145" t="s">
         <v>124</v>
       </c>
-      <c r="S71" s="110" t="s">
+      <c r="S71" s="145" t="s">
         <v>124</v>
       </c>
-      <c r="T71" s="110" t="s">
+      <c r="T71" s="145" t="s">
         <v>124</v>
       </c>
-      <c r="U71" s="75" t="s">
+      <c r="U71" s="97" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="72" spans="1:21" ht="26.25" thickBot="1">
-      <c r="A72" s="8">
+    <row r="72" ht="26.25" spans="1:21">
+      <c r="A72" s="10">
         <v>69</v>
       </c>
-      <c r="B72" s="145"/>
-      <c r="C72" s="135" t="s">
+      <c r="B72" s="27"/>
+      <c r="C72" s="170" t="s">
         <v>369</v>
       </c>
-      <c r="D72" s="136" t="s">
+      <c r="D72" s="171" t="s">
         <v>370</v>
       </c>
-      <c r="E72" s="131" t="s">
+      <c r="E72" s="166" t="s">
         <v>25</v>
       </c>
-      <c r="F72" s="131" t="s">
+      <c r="F72" s="166" t="s">
         <v>371</v>
       </c>
-      <c r="G72" s="26" t="s">
+      <c r="G72" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="H72" s="131" t="s">
+      <c r="H72" s="166" t="s">
         <v>28</v>
       </c>
-      <c r="I72" s="131" t="s">
+      <c r="I72" s="166" t="s">
         <v>124</v>
       </c>
-      <c r="J72" s="26">
-        <v>10</v>
-      </c>
-      <c r="K72" s="99">
+      <c r="J72" s="45">
+        <v>11</v>
+      </c>
+      <c r="K72" s="123">
         <f t="shared" si="12"/>
-        <v>50</v>
-      </c>
-      <c r="L72" s="99">
+        <v>55</v>
+      </c>
+      <c r="L72" s="123">
         <f t="shared" si="13"/>
-        <v>500</v>
-      </c>
-      <c r="M72" s="99">
+        <v>550</v>
+      </c>
+      <c r="M72" s="123">
         <f t="shared" si="14"/>
-        <v>1000</v>
-      </c>
-      <c r="N72" s="131" t="s">
+        <v>1100</v>
+      </c>
+      <c r="N72" s="166" t="s">
         <v>124</v>
       </c>
-      <c r="O72" s="131" t="s">
+      <c r="O72" s="166" t="s">
         <v>124</v>
       </c>
-      <c r="P72" s="131" t="s">
+      <c r="P72" s="166" t="s">
         <v>124</v>
       </c>
-      <c r="Q72" s="131" t="s">
+      <c r="Q72" s="166" t="s">
         <v>124</v>
       </c>
-      <c r="R72" s="131" t="s">
+      <c r="R72" s="166" t="s">
         <v>124</v>
       </c>
-      <c r="S72" s="131" t="s">
+      <c r="S72" s="166" t="s">
         <v>124</v>
       </c>
-      <c r="T72" s="131" t="s">
+      <c r="T72" s="166" t="s">
         <v>124</v>
       </c>
-      <c r="U72" s="102" t="s">
+      <c r="U72" s="136" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="73" spans="1:21" ht="15.75" thickBot="1">
-      <c r="A73" s="147">
+    <row r="73" ht="15.75" spans="1:21">
+      <c r="A73" s="124">
         <v>70</v>
       </c>
-      <c r="B73" s="148" t="s">
+      <c r="B73" s="125" t="s">
+        <v>372</v>
+      </c>
+      <c r="C73" s="172" t="s">
+        <v>373</v>
+      </c>
+      <c r="D73" s="173" t="s">
+        <v>109</v>
+      </c>
+      <c r="E73" s="127" t="s">
+        <v>25</v>
+      </c>
+      <c r="F73" s="127" t="s">
         <v>374</v>
       </c>
-      <c r="C73" s="149" t="s">
+      <c r="G73" s="127" t="s">
         <v>375</v>
       </c>
-      <c r="D73" s="150" t="s">
+      <c r="H73" s="173" t="s">
         <v>109</v>
       </c>
-      <c r="E73" s="151" t="s">
-        <v>25</v>
-      </c>
-      <c r="F73" s="151" t="s">
-        <v>376</v>
-      </c>
-      <c r="G73" s="151" t="s">
-        <v>377</v>
-      </c>
-      <c r="H73" s="150" t="s">
+      <c r="I73" s="173" t="s">
         <v>109</v>
       </c>
-      <c r="I73" s="150" t="s">
-        <v>109</v>
-      </c>
-      <c r="J73" s="64">
+      <c r="J73" s="85">
         <v>1</v>
       </c>
-      <c r="K73" s="64">
+      <c r="K73" s="85">
         <f t="shared" ref="K73" si="18">J73*5</f>
         <v>5</v>
       </c>
-      <c r="L73" s="64">
+      <c r="L73" s="85">
         <f t="shared" ref="L73" si="19">J73*50</f>
         <v>50</v>
       </c>
-      <c r="M73" s="64">
+      <c r="M73" s="85">
         <f t="shared" ref="M73" si="20">J73*100</f>
         <v>100</v>
       </c>
-      <c r="N73" s="152" t="s">
-        <v>378</v>
-      </c>
-      <c r="O73" s="153">
+      <c r="N73" s="128" t="s">
+        <v>376</v>
+      </c>
+      <c r="O73" s="129">
         <v>14</v>
       </c>
-      <c r="P73" s="67">
+      <c r="P73" s="88">
         <f>O73*K73</f>
         <v>70</v>
       </c>
-      <c r="Q73" s="153">
+      <c r="Q73" s="129">
         <v>14</v>
       </c>
-      <c r="R73" s="67">
+      <c r="R73" s="88">
         <f>Q73*L73</f>
         <v>700</v>
       </c>
-      <c r="S73" s="153">
+      <c r="S73" s="129">
         <v>14</v>
       </c>
-      <c r="T73" s="67">
+      <c r="T73" s="88">
         <f>S73*M73</f>
         <v>1400</v>
       </c>
-      <c r="U73" s="156" t="s">
-        <v>381</v>
+      <c r="U73" s="137" t="s">
+        <v>377</v>
       </c>
     </row>
-    <row r="74" spans="1:21" ht="19.5" thickBot="1">
-      <c r="I74" s="140" t="s">
-        <v>372</v>
-      </c>
-      <c r="J74" s="140"/>
-      <c r="K74" s="140"/>
-      <c r="L74" s="140"/>
-      <c r="M74" s="140"/>
-      <c r="N74" s="140"/>
-      <c r="P74" s="100">
+    <row r="74" ht="19.5" spans="9:20">
+      <c r="I74" s="130" t="s">
+        <v>378</v>
+      </c>
+      <c r="J74" s="130"/>
+      <c r="K74" s="130"/>
+      <c r="L74" s="130"/>
+      <c r="M74" s="130"/>
+      <c r="N74" s="130"/>
+      <c r="P74" s="131">
         <f>SUM(P3:P73)</f>
-        <v>316.31150000000008</v>
-      </c>
-      <c r="Q74" s="103"/>
-      <c r="R74" s="100">
+        <v>316.3115</v>
+      </c>
+      <c r="Q74" s="138"/>
+      <c r="R74" s="131">
         <f>SUM(R3:R73)</f>
         <v>2626.779</v>
       </c>
-      <c r="S74" s="100"/>
-      <c r="T74" s="100">
+      <c r="S74" s="131"/>
+      <c r="T74" s="131">
         <f>SUM(T3:T73)</f>
-        <v>4844.5720000000001</v>
+        <v>4844.572</v>
       </c>
     </row>
-    <row r="75" spans="1:21" ht="19.5" thickBot="1">
-      <c r="I75" s="141" t="s">
-        <v>373</v>
-      </c>
-      <c r="J75" s="141"/>
-      <c r="K75" s="141"/>
-      <c r="L75" s="141"/>
-      <c r="M75" s="141"/>
-      <c r="N75" s="141"/>
-      <c r="P75" s="101">
+    <row r="75" ht="19.5" spans="9:20">
+      <c r="I75" s="132" t="s">
+        <v>379</v>
+      </c>
+      <c r="J75" s="132"/>
+      <c r="K75" s="132"/>
+      <c r="L75" s="132"/>
+      <c r="M75" s="132"/>
+      <c r="N75" s="132"/>
+      <c r="P75" s="133">
         <f>P74/5</f>
-        <v>63.262300000000018</v>
-      </c>
-      <c r="Q75" s="104"/>
-      <c r="R75" s="101">
+        <v>63.2623</v>
+      </c>
+      <c r="Q75" s="139"/>
+      <c r="R75" s="133">
         <f>R74/50</f>
-        <v>52.535580000000003</v>
-      </c>
-      <c r="S75" s="101"/>
-      <c r="T75" s="101">
+        <v>52.53558</v>
+      </c>
+      <c r="S75" s="133"/>
+      <c r="T75" s="133">
         <f>T74/100</f>
-        <v>48.445720000000001</v>
+        <v>48.44572</v>
       </c>
     </row>
-    <row r="76" spans="1:21" ht="18.75" customHeight="1" thickBot="1">
-      <c r="I76" s="141" t="s">
-        <v>379</v>
-      </c>
-      <c r="J76" s="141"/>
-      <c r="K76" s="141"/>
-      <c r="L76" s="141"/>
-      <c r="M76" s="141"/>
-      <c r="N76" s="141"/>
-      <c r="P76" s="154">
+    <row r="76" ht="18.75" customHeight="1" spans="9:20">
+      <c r="I76" s="132" t="s">
+        <v>380</v>
+      </c>
+      <c r="J76" s="132"/>
+      <c r="K76" s="132"/>
+      <c r="L76" s="132"/>
+      <c r="M76" s="132"/>
+      <c r="N76" s="132"/>
+      <c r="P76" s="134">
         <v>88</v>
       </c>
       <c r="Q76" s="5"/>
-      <c r="R76" s="154">
+      <c r="R76" s="134">
         <v>88</v>
       </c>
       <c r="S76" s="5"/>
-      <c r="T76" s="154">
+      <c r="T76" s="134">
         <v>88</v>
       </c>
     </row>
-    <row r="77" spans="1:21" ht="15.75" thickBot="1">
-      <c r="O77" s="155" t="s">
-        <v>380</v>
-      </c>
-      <c r="P77" s="35">
+    <row r="77" ht="15.75" spans="15:20">
+      <c r="O77" s="135" t="s">
+        <v>381</v>
+      </c>
+      <c r="P77" s="55">
         <f>SUM(P75:P76)</f>
-        <v>151.26230000000001</v>
-      </c>
-      <c r="R77" s="67">
+        <v>151.2623</v>
+      </c>
+      <c r="R77" s="88">
         <f>SUM(R75:R76)</f>
-        <v>140.53558000000001</v>
-      </c>
-      <c r="T77" s="67">
+        <v>140.53558</v>
+      </c>
+      <c r="T77" s="88">
         <f>SUM(T75:T76)</f>
-        <v>136.44571999999999</v>
+        <v>136.44572</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="I76:N76"/>
     <mergeCell ref="A1:U1"/>
     <mergeCell ref="I74:N74"/>
     <mergeCell ref="I75:N75"/>
+    <mergeCell ref="I76:N76"/>
     <mergeCell ref="B3:B17"/>
     <mergeCell ref="B18:B19"/>
     <mergeCell ref="B21:B25"/>
@@ -7815,6 +8458,70 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="J73">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P73">
+    <cfRule type="dataBar" priority="6">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{bf07b82c-6a88-402a-a52a-a26260fa55a7}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R73">
+    <cfRule type="dataBar" priority="5">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{8cdc9af2-977a-44a5-84d4-93b9898f73f8}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T73">
+    <cfRule type="dataBar" priority="4">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{6b27092c-c2a3-44d6-87c1-3602ec145664}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="P75:T75">
     <cfRule type="dataBar" priority="118">
       <dataBar>
@@ -7824,7 +8531,49 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0A14C4BB-6E11-4A2C-AFB4-BB3FC0D2DC4A}</x14:id>
+          <x14:id>{12dd464b-c95b-4f22-89e9-6e10202b4089}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P77">
+    <cfRule type="dataBar" priority="3">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{b0ed8c11-078f-4423-a2f2-f48fd90da626}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R77">
+    <cfRule type="dataBar" priority="2">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{70d1ba3d-bfa3-4497-96e7-b8b5e928beb4}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T77">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{fa97f012-0ee4-4434-8f90-0b46effade73}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -7884,7 +8633,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{71D3CD32-7046-4D62-B76E-152E3397A9EF}</x14:id>
+          <x14:id>{9147b24e-cc74-4210-888d-cbb02c93d650}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -7922,7 +8671,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8773B354-F065-4D6F-A876-C97ACD8986B2}</x14:id>
+          <x14:id>{f81b376d-fb26-48e0-9819-fa08e8945b86}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -8087,188 +8836,122 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J73">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P73">
-    <cfRule type="dataBar" priority="6">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{C320F112-81E2-41C6-9579-A4F14595733B}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R73">
-    <cfRule type="dataBar" priority="5">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0EBC8D64-A13D-47BF-81F8-0A11746F2C29}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T73">
-    <cfRule type="dataBar" priority="4">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{888F4A23-FBF8-4AE0-9BEE-62D1E14B3CC4}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P77">
-    <cfRule type="dataBar" priority="3">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0E2718F2-FFB7-4454-80F1-2C113A072728}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R77">
-    <cfRule type="dataBar" priority="2">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ADD52D28-0DDF-42C8-8259-DA2BDB0C31D6}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T77">
-    <cfRule type="dataBar" priority="1">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63C384"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1676CEA3-D4A4-4D1E-93CD-98366C3D20B2}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="N3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="N5" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="N6" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="N7" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="N8" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="N9" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="N10" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="N11" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="N12" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="N13" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="N14" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="N15" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="N16" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="N17" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="N19" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="N25" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="N27" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="N31" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="N32" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="N33" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="N34" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="N35" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="N36" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="N37" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="N38" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="N39" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="N42" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="N43" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="N46" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="N47" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="N48" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="N49" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="N54" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="N56" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="N59" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="N60" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="N64" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="N30" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="N40" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="N41" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="N44" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="N45" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="N50" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="N20" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="N21" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="N22" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="N23" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="N24" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="N29" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="N51" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="N53" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="N4" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="N26" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="N28" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="N52" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="N55" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="N57" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="N58" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="N61" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="N62" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="N63" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="N66" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="N67" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="N68" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="N65" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="N18" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="N73" r:id="rId67" xr:uid="{32C5E22F-0B62-4265-A0D5-52671D6968A4}"/>
+    <hyperlink ref="N3" r:id="rId1" display="Digikey"/>
+    <hyperlink ref="N5" r:id="rId2" display="Digikey"/>
+    <hyperlink ref="N6" r:id="rId3" display="Digikey"/>
+    <hyperlink ref="N7" r:id="rId4" display="Digikey"/>
+    <hyperlink ref="N8" r:id="rId5" display="Digikey"/>
+    <hyperlink ref="N9" r:id="rId6" display="Digikey"/>
+    <hyperlink ref="N10" r:id="rId7" display="Digikey"/>
+    <hyperlink ref="N11" r:id="rId8" display="Mouser"/>
+    <hyperlink ref="N12" r:id="rId9" display="Arrow"/>
+    <hyperlink ref="N13" r:id="rId10" display="Digikey"/>
+    <hyperlink ref="N14" r:id="rId11" display="Digikey"/>
+    <hyperlink ref="N15" r:id="rId12" display="Digikey"/>
+    <hyperlink ref="N16" r:id="rId13" display="Digikey"/>
+    <hyperlink ref="N17" r:id="rId14" display="Digikey"/>
+    <hyperlink ref="N19" r:id="rId15" display="Mouser"/>
+    <hyperlink ref="N25" r:id="rId16" display="Digikey"/>
+    <hyperlink ref="N27" r:id="rId17" display="Digikey"/>
+    <hyperlink ref="N31" r:id="rId18" display="Digikey"/>
+    <hyperlink ref="N32" r:id="rId19" display="Digikey"/>
+    <hyperlink ref="N33" r:id="rId20" display="Digikey"/>
+    <hyperlink ref="N34" r:id="rId21" display="Digikey"/>
+    <hyperlink ref="N35" r:id="rId22" display="Digikey"/>
+    <hyperlink ref="N36" r:id="rId23" display="Digikey"/>
+    <hyperlink ref="N37" r:id="rId24" display="Mouser"/>
+    <hyperlink ref="N38" r:id="rId25" display="Digikey"/>
+    <hyperlink ref="N39" r:id="rId26" display="Digikey"/>
+    <hyperlink ref="N42" r:id="rId27" display="Digikey"/>
+    <hyperlink ref="N43" r:id="rId28" display="Digikey"/>
+    <hyperlink ref="N46" r:id="rId29" display="Digikey"/>
+    <hyperlink ref="N47" r:id="rId30" display="Digikey"/>
+    <hyperlink ref="N48" r:id="rId31" display="Digikey"/>
+    <hyperlink ref="N49" r:id="rId32" display="Digikey"/>
+    <hyperlink ref="N54" r:id="rId33" display="Digikey"/>
+    <hyperlink ref="N56" r:id="rId34" display="Arrow"/>
+    <hyperlink ref="N59" r:id="rId35" display="Digikey"/>
+    <hyperlink ref="N60" r:id="rId36" display="Digikey"/>
+    <hyperlink ref="N64" r:id="rId37" display="Digikey"/>
+    <hyperlink ref="N30" r:id="rId38" display="Digikey"/>
+    <hyperlink ref="N40" r:id="rId39" display="Digikey"/>
+    <hyperlink ref="N41" r:id="rId40" display="Digikey"/>
+    <hyperlink ref="N44" r:id="rId41" display="Digikey"/>
+    <hyperlink ref="N45" r:id="rId42" display="Digikey"/>
+    <hyperlink ref="N50" r:id="rId43" display="Digikey"/>
+    <hyperlink ref="N20" r:id="rId44" display="Digikey"/>
+    <hyperlink ref="N21" r:id="rId45" display="Digikey"/>
+    <hyperlink ref="N22" r:id="rId46" display="Digikey"/>
+    <hyperlink ref="N23" r:id="rId47" display="Digikey"/>
+    <hyperlink ref="N24" r:id="rId48" display="Digikey"/>
+    <hyperlink ref="N29" r:id="rId49" display="Digikey"/>
+    <hyperlink ref="N51" r:id="rId50" display="Digikey"/>
+    <hyperlink ref="N53" r:id="rId51" display="Digikey"/>
+    <hyperlink ref="N4" r:id="rId52" display="Digikey"/>
+    <hyperlink ref="N26" r:id="rId53" display="Digikey"/>
+    <hyperlink ref="N28" r:id="rId54" display="Digikey"/>
+    <hyperlink ref="N52" r:id="rId55" display="Mouser"/>
+    <hyperlink ref="N55" r:id="rId56" display="Digikey"/>
+    <hyperlink ref="N57" r:id="rId57" display="Digikey"/>
+    <hyperlink ref="N58" r:id="rId58" display="Digikey"/>
+    <hyperlink ref="N61" r:id="rId59" display="Digikey"/>
+    <hyperlink ref="N62" r:id="rId60" display="Digikey"/>
+    <hyperlink ref="N63" r:id="rId61" display="Digikey"/>
+    <hyperlink ref="N66" r:id="rId62" display="Digikey"/>
+    <hyperlink ref="N67" r:id="rId63" display="Digikey"/>
+    <hyperlink ref="N68" r:id="rId64" display="Digikey"/>
+    <hyperlink ref="N65" r:id="rId65" display="Digikey"/>
+    <hyperlink ref="N18" r:id="rId66" display="Quest"/>
+    <hyperlink ref="N73" r:id="rId67" display="Custom Supplier"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0A14C4BB-6E11-4A2C-AFB4-BB3FC0D2DC4A}">
+          <x14:cfRule type="dataBar" id="{bf07b82c-6a88-402a-a52a-a26260fa55a7}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>P73</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{8cdc9af2-977a-44a5-84d4-93b9898f73f8}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF63C384"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>R73</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{6b27092c-c2a3-44d6-87c1-3602ec145664}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF63C384"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>T73</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{12dd464b-c95b-4f22-89e9-6e10202b4089}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -8281,7 +8964,46 @@
           <xm:sqref>P75:T75</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{71D3CD32-7046-4D62-B76E-152E3397A9EF}">
+          <x14:cfRule type="dataBar" id="{b0ed8c11-078f-4423-a2f2-f48fd90da626}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>P77</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{70d1ba3d-bfa3-4497-96e7-b8b5e928beb4}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF63C384"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>R77</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{fa97f012-0ee4-4434-8f90-0b46effade73}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF63C384"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>T77</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{9147b24e-cc74-4210-888d-cbb02c93d650}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -8294,7 +9016,7 @@
           <xm:sqref>P3:P68</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8773B354-F065-4D6F-A876-C97ACD8986B2}">
+          <x14:cfRule type="dataBar" id="{f81b376d-fb26-48e0-9819-fa08e8945b86}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -8306,84 +9028,6 @@
           </x14:cfRule>
           <xm:sqref>R3:T68</xm:sqref>
         </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{C320F112-81E2-41C6-9579-A4F14595733B}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:borderColor rgb="FF638EC6"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:negativeBorderColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>P73</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0EBC8D64-A13D-47BF-81F8-0A11746F2C29}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:borderColor rgb="FF63C384"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:negativeBorderColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>R73</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{888F4A23-FBF8-4AE0-9BEE-62D1E14B3CC4}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:borderColor rgb="FF63C384"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:negativeBorderColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>T73</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0E2718F2-FFB7-4454-80F1-2C113A072728}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:borderColor rgb="FF638EC6"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:negativeBorderColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>P77</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ADD52D28-0DDF-42C8-8259-DA2BDB0C31D6}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:borderColor rgb="FF63C384"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:negativeBorderColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>R77</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1676CEA3-D4A4-4D1E-93CD-98366C3D20B2}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:borderColor rgb="FF63C384"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:negativeBorderColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>T77</xm:sqref>
-        </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
   </extLst>
